--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -567,7 +567,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -590,25 +590,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.3694566654683316</v>
+        <v>0.4045542287774395</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1667245320087454</v>
+        <v>0.169242115947243</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1721071458950634</v>
+        <v>0.1653279534670555</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.2149150631391523</v>
+        <v>0.186470454735802</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.02550580886256415</v>
+        <v>0.03200280045672099</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-0.004592254134077156</v>
+        <v>0.003358850586688611</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.002207390185603675</v>
+        <v>0.004606124051295346</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="O2" s="3" t="n">
-        <v>0.1709282973064323</v>
+        <v>0.1709284096064327</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>3</v>
@@ -628,7 +628,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.3504196672628402</v>
+        <v>0.3504197189000531</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -661,25 +661,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5418102475555946</v>
+        <v>0.5951390841260489</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2431409198570362</v>
+        <v>0.2465053090414584</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.2065152422462757</v>
+        <v>0.2015065836070287</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.3236898273097844</v>
+        <v>0.2897558043187187</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.00241498055722289</v>
+        <v>0.02542034586776309</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.03035658094345428</v>
+        <v>0.037451917491238</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.001194791793952765</v>
+        <v>0.006640196224574346</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="O3" s="3" t="n">
-        <v>0.2119626877906462</v>
+        <v>0.211962557345279</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>2</v>
@@ -699,7 +699,7 @@
         <v>1</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.3666127431867172</v>
+        <v>0.3666127037075512</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
@@ -732,25 +732,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.06037184476057866</v>
+        <v>-0.07627833675248363</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.0809993967103747</v>
+        <v>-0.09151814207749209</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.02872477595945966</v>
+        <v>-0.04082007576541435</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.07872779495425297</v>
+        <v>-0.08084066098075393</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.08555841547757359</v>
+        <v>-0.08239942042864146</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.05382060558844559</v>
+        <v>-0.05285563743688049</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.006359704909692176</v>
+        <v>-0.004729643359325131</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -780,7 +780,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3534418555165442</v>
+        <v>0.3455255931845385</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1006229451462191</v>
+        <v>0.08440674119048963</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.1792409298033109</v>
+        <v>0.1587697894796574</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.07947802595397746</v>
+        <v>-0.1117385949011133</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.03596829360985931</v>
+        <v>0.03132757690232046</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.06666829709701871</v>
+        <v>-0.06417413446941878</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.009843613558783826</v>
+        <v>-0.001775966987907718</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -874,25 +874,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.06961137220877167</v>
+        <v>0.07317506502655013</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01140923343518918</v>
+        <v>0.01123326884296039</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03764809232944444</v>
+        <v>0.03676883453610258</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.01081576132650475</v>
+        <v>0.002841523906476962</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01884433063195645</v>
+        <v>-0.01718543754073143</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.02528685696838773</v>
+        <v>-0.02462995109663746</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.00309517668300241</v>
+        <v>0.0007755946225440624</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -945,25 +945,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.3868717257014338</v>
+        <v>0.398224368964057</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.3770878938932962</v>
+        <v>0.4077969862523569</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.3931780903400066</v>
+        <v>0.4483922587004499</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.007148259670798796</v>
+        <v>0.02212986606356004</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1665617533695485</v>
+        <v>0.1771888203706566</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-0.01154927468230826</v>
+        <v>-0.02802781650083963</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.008212560386473444</v>
+        <v>0.00422489437764062</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.3585298623490187</v>
+        <v>0.3585297434061203</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>1</v>
@@ -983,7 +983,7 @@
         <v>1</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.2829675895504425</v>
+        <v>0.2829675773923958</v>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
@@ -1016,25 +1016,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.01206583358687596</v>
+        <v>0.00694377928255796</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02040150602530266</v>
+        <v>-0.02163428343430396</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.006420049434663566</v>
+        <v>0.004025610947714808</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02447092673289952</v>
+        <v>-0.02455934635365076</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.03246431737514965</v>
+        <v>-0.03065750865253769</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.02665045820086021</v>
+        <v>-0.02555701179554382</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0</v>
+        <v>0.0007691568118450842</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -1087,25 +1087,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.04139441443237946</v>
+        <v>0.04176989932029018</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07761689042670139</v>
+        <v>0.07846259146605794</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.05588470000780399</v>
+        <v>0.05593203593403739</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.02787705503931392</v>
+        <v>0.03383729301655869</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01231960577261537</v>
+        <v>0.008073008073008037</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.02058197303051812</v>
+        <v>0.02133712660028442</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.002090592334494934</v>
+        <v>-0.00104347826086959</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -1156,25 +1156,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.03955766334074218</v>
+        <v>0.03831028151508176</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.01504327427369767</v>
+        <v>0.01530110205672175</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.0209956858941085</v>
+        <v>0.02062632886416327</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.001604606258478913</v>
+        <v>0.001371995875301568</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.002558283563271257</v>
+        <v>-0.001553580560208823</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>-0.005830006632396412</v>
+        <v>-0.00521760673504057</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0007397361607692776</v>
+        <v>0.0007392804337111869</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -590,25 +590,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4045542287774395</v>
+        <v>0.4006389131383741</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.169242115947243</v>
+        <v>0.1659829916338273</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1653279534670555</v>
+        <v>0.1653280617923467</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.186470454735802</v>
+        <v>0.183163086875705</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.03200280045672099</v>
+        <v>0.02912611886320082</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.003358850586688611</v>
+        <v>0.000562013275878126</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.004606124051295346</v>
+        <v>0.001805809997382779</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -628,7 +628,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.3504197189000531</v>
+        <v>0.3504197140881005</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -661,25 +661,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5951390841260489</v>
+        <v>0.5958261414910617</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2465053090414584</v>
+        <v>0.2470424125169357</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.2015065836070287</v>
+        <v>0.2015067066653458</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.2897558043187187</v>
+        <v>0.2903114117354655</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.02542034586776309</v>
+        <v>0.02586208154170944</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.037451917491238</v>
+        <v>0.03789883618541712</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.006640196224574346</v>
+        <v>0.007073841692301519</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -699,7 +699,7 @@
         <v>1</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.3666127037075512</v>
+        <v>0.36661269433525</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
@@ -732,25 +732,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.07627833675248363</v>
+        <v>-0.0782950294244148</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.09151814207749209</v>
+        <v>-0.09350164622282475</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.04082007576541435</v>
+        <v>-0.04081999037835338</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.08084066098075393</v>
+        <v>-0.08284755910088337</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.08239942042864146</v>
+        <v>-0.08440299746924063</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.05285563743688049</v>
+        <v>-0.05492363822850299</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.004729643359325131</v>
+        <v>-0.006902722740636635</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -803,25 +803,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3455255931845385</v>
+        <v>0.3396465535450257</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.08440674119048963</v>
+        <v>0.07966861487828414</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.1587697894796574</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1117385949011133</v>
+        <v>-0.115619698342978</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.03132757690232046</v>
+        <v>0.0268213707501348</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.06417413446941878</v>
+        <v>-0.06826306253366632</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.001775966987907718</v>
+        <v>-0.006137532972916415</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -874,25 +874,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07317506502655013</v>
+        <v>0.07040283241360634</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01123326884296039</v>
+        <v>0.008621038512826251</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03676883453610258</v>
+        <v>0.03676893785273116</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.002841523906476962</v>
+        <v>0.000250772708158209</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01718543754073143</v>
+        <v>-0.01972435400278072</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.02462995109663746</v>
+        <v>-0.02714963605892984</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.0007755946225440624</v>
+        <v>-0.001809720785935887</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.03697999132467844</v>
+        <v>0.03698009561642079</v>
       </c>
       <c r="P6" t="n">
         <v>6</v>
@@ -945,25 +945,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.398224368964057</v>
+        <v>0.3923418716189009</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.4077969862523569</v>
+        <v>0.4018743375806251</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4483922587004499</v>
+        <v>0.4483923845633841</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.02212986606356004</v>
+        <v>0.01782964332607584</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1771888203706566</v>
+        <v>0.1722362460454727</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-0.02802781650083963</v>
+        <v>-0.03211701986183924</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.00422489437764062</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.3585297434061203</v>
+        <v>0.3585298623490187</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>1</v>
@@ -983,7 +983,7 @@
         <v>1</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.2829675773923958</v>
+        <v>0.2829675915766495</v>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
@@ -1016,25 +1016,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.00694377928255796</v>
+        <v>0.005105761047725643</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02163428343430396</v>
+        <v>-0.02342013688946276</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>0.004025610947714808</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02455934635365076</v>
+        <v>-0.02633986056436066</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.03065750865253769</v>
+        <v>-0.03242689162262147</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.02555701179554382</v>
+        <v>-0.02733570492417137</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0007691568118450842</v>
+        <v>-0.001057590616286852</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -1087,25 +1087,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.04176989932029018</v>
+        <v>0.04430903208325754</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07846259146605794</v>
+        <v>0.08109115627812713</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.05593203593403739</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.03383729301655869</v>
+        <v>0.0363570914326854</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.008073008073008037</v>
+        <v>0.01053001053001057</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.02133712660028442</v>
+        <v>0.02382645803698424</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.00104347826086959</v>
+        <v>0.001391304347825972</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -1137,7 +1137,7 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>SGOV</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1152,29 +1152,29 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1-3 Year U.S. Treasury reserve</t>
+          <t>0-3 Month U.S. Treasury reserve</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.03831028151508176</v>
+        <v>0.05981879638558985</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.01530110205672175</v>
+        <v>0.03751730527109998</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.02062632886416327</v>
+        <v>0.03435396251839529</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.001371995875301568</v>
+        <v>0.018370063466838</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.001553580560208823</v>
+        <v>0.009031443340259626</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>-0.00521760673504057</v>
+        <v>0.003058278758852229</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0007392804337111869</v>
+        <v>9.932459276917882e-05</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -590,25 +590,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4006389131383741</v>
+        <v>0.3949672656502001</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1659829916338273</v>
+        <v>0.1612616727983498</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0.1653280617923467</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.183163086875705</v>
+        <v>0.1783722020964333</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.02912611886320082</v>
+        <v>0.02495896328380209</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.000562013275878126</v>
+        <v>-0.00348948002482885</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.001805809997382779</v>
+        <v>-0.002250719706883064</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="O2" s="3" t="n">
-        <v>0.1709284096064327</v>
+        <v>0.1709282973064323</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>3</v>
@@ -628,7 +628,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.3504197140881005</v>
+        <v>0.3504196853012613</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -661,25 +661,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5958261414910617</v>
+        <v>0.588568202139224</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2470424125169357</v>
+        <v>0.2413706055408109</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0.2015067066653458</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.2903114117354655</v>
+        <v>0.2844428083960777</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.02586208154170944</v>
+        <v>0.0211962484856496</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.03789883618541712</v>
+        <v>0.03317825747814851</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.007073841692301519</v>
+        <v>0.002493461439432076</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -699,7 +699,7 @@
         <v>1</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.36661269433525</v>
+        <v>0.3666127105820803</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
@@ -732,25 +732,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.0782950294244148</v>
+        <v>-0.07722736359396487</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.09350164622282475</v>
+        <v>-0.09245143218657159</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.04081999037835338</v>
+        <v>-0.04081990499127719</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.08284755910088337</v>
+        <v>-0.08178508362552073</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.08440299746924063</v>
+        <v>-0.08334224147109848</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.05492363822850299</v>
+        <v>-0.05382881427999697</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.006902722740636635</v>
+        <v>-0.005752268950530492</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="O4" s="4" t="n">
-        <v>-0.01073106390225198</v>
+        <v>-0.01073133838245888</v>
       </c>
       <c r="P4" t="n">
         <v>8</v>
@@ -803,25 +803,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3396465535450257</v>
+        <v>0.3407026684503274</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.07966861487828414</v>
+        <v>0.0805197752936504</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.1587697894796574</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.115619698342978</v>
+        <v>-0.1149224941318646</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.0268213707501348</v>
+        <v>0.02763086886130584</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.06826306253366632</v>
+        <v>-0.06752852455805303</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.006137532972916415</v>
+        <v>-0.005354018125310223</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -874,25 +874,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07040283241360634</v>
+        <v>0.07026398873321527</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.008621038512826251</v>
+        <v>0.00849052245634585</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03676893785273116</v>
+        <v>0.03676904116938062</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.000250772708158209</v>
+        <v>0.0001213389410887888</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01972435400278072</v>
+        <v>-0.01985129982588318</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.02714963605892984</v>
+        <v>-0.02727562030704456</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.001809720785935887</v>
+        <v>-0.001938986556359934</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -945,25 +945,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.3923418716189009</v>
+        <v>0.3889480032609609</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.4018743375806251</v>
+        <v>0.3984573543073542</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.4483923845633841</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.01782964332607584</v>
+        <v>0.01534874559291199</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1722362460454727</v>
+        <v>0.1693789916270974</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-0.03211701986183924</v>
+        <v>-0.03447617564703143</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0</v>
+        <v>-0.002437439064023383</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -983,7 +983,7 @@
         <v>1</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.2829675915766495</v>
+        <v>0.2829676041166584</v>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
@@ -1016,25 +1016,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.005105761047725643</v>
+        <v>0.006460164555269099</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02342013688946276</v>
+        <v>-0.02210417474454762</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.004025610947714808</v>
+        <v>0.004025682946822373</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02633986056436066</v>
+        <v>-0.02502790272489019</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.03242689162262147</v>
+        <v>-0.03112313574992809</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.02733570492417137</v>
+        <v>-0.02602508893465627</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.001057590616286852</v>
+        <v>0.0002884338044419898</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.008776631788367073</v>
+        <v>0.008776704452799766</v>
       </c>
       <c r="P8" t="n">
         <v>7</v>
@@ -1087,25 +1087,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.04430903208325754</v>
+        <v>0.04358356557955267</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.08109115627812713</v>
+        <v>0.08034013776039295</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.05593203593403739</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.0363570914326854</v>
+        <v>0.0356371490280778</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01053001053001057</v>
+        <v>0.009828009828009909</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.02382645803698424</v>
+        <v>0.02311522048364156</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.001391304347825972</v>
+        <v>0.0006956521739129862</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -1156,25 +1156,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05981879638558985</v>
+        <v>0.05971371096748745</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03751730527109998</v>
+        <v>0.03741434607688499</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03435396251839529</v>
+        <v>0.03435404383295459</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.018370063466838</v>
+        <v>0.01826884574787879</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009031443340259626</v>
+        <v>0.008931231656543304</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003058278758852229</v>
+        <v>0.002958660298353788</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>9.932459276917882e-05</v>
+        <v>0</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -590,16 +590,16 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.3949672656502001</v>
+        <v>0.3949675771872845</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1612616727983498</v>
+        <v>0.1612615648510574</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1653280617923467</v>
+        <v>0.1653279534670555</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1783722020964333</v>
+        <v>0.1783723132482604</v>
       </c>
       <c r="J2" s="3" t="n">
         <v>0.02495896328380209</v>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="O2" s="3" t="n">
-        <v>0.1709282973064323</v>
+        <v>0.1709284096064327</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>3</v>
@@ -628,7 +628,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.3504196853012613</v>
+        <v>0.350419700861626</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.588568202139224</v>
+        <v>0.5885680980357915</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0.2413706055408109</v>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="O3" s="3" t="n">
-        <v>0.211962557345279</v>
+        <v>0.2119626877906462</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>2</v>
@@ -699,7 +699,7 @@
         <v>1</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.3666127105820803</v>
+        <v>0.3666127363121962</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.07722736359396487</v>
+        <v>-0.0772271130217419</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>-0.09245143218657159</v>
@@ -741,7 +741,7 @@
         <v>-0.04081990499127719</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.08178508362552073</v>
+        <v>-0.08178516632652277</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>-0.08334224147109848</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="O4" s="4" t="n">
-        <v>-0.01073133838245888</v>
+        <v>-0.01073106390225198</v>
       </c>
       <c r="P4" t="n">
         <v>8</v>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07026398873321527</v>
+        <v>0.07026410192069132</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.00849052245634585</v>
+        <v>0.008490421957722205</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03676904116938062</v>
+        <v>0.03676893785273116</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>0.0001213389410887888</v>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.03698009561642079</v>
+        <v>0.03697988703295696</v>
       </c>
       <c r="P6" t="n">
         <v>6</v>
@@ -948,10 +948,10 @@
         <v>0.3889480032609609</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.3984573543073542</v>
+        <v>0.3984572327836926</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4483923845633841</v>
+        <v>0.4483922587004499</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0.01534874559291199</v>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.3585298623490187</v>
+        <v>0.3585297434061203</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>1</v>
@@ -983,7 +983,7 @@
         <v>1</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.2829676041166584</v>
+        <v>0.2829675628261778</v>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.006460164555269099</v>
+        <v>0.006460090273391561</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>-0.02210417474454762</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.008776704452799766</v>
+        <v>0.008776631788367073</v>
       </c>
       <c r="P8" t="n">
         <v>7</v>
@@ -1156,16 +1156,16 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05971371096748745</v>
+        <v>0.05971354076970092</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03741434607688499</v>
+        <v>0.03741426452174346</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03435404383295459</v>
+        <v>0.03435396251839529</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01826884574787879</v>
+        <v>0.0182687671751689</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>0.008931231656543304</v>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.3949675771872845</v>
+        <v>0.3949674214187249</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0.1612615648510574</v>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="O2" s="3" t="n">
-        <v>0.1709284096064327</v>
+        <v>0.1709282973064323</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>3</v>
@@ -628,7 +628,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.350419700861626</v>
+        <v>0.3504196804893185</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5885680980357915</v>
+        <v>0.588568202139224</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0.2413706055408109</v>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="O3" s="3" t="n">
-        <v>0.2119626877906462</v>
+        <v>0.211962557345279</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>2</v>
@@ -699,7 +699,7 @@
         <v>1</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.3666127363121962</v>
+        <v>0.3666127012097777</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
@@ -732,19 +732,19 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.0772271130217419</v>
+        <v>-0.07722719654583143</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.09245143218657159</v>
+        <v>-0.09245159376813938</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.04081990499127719</v>
+        <v>-0.04082007576541435</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>-0.08178516632652277</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.08334224147109848</v>
+        <v>-0.08334232389184626</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>-0.05382881427999697</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="O4" s="4" t="n">
-        <v>-0.01073106390225198</v>
+        <v>-0.01073115539567115</v>
       </c>
       <c r="P4" t="n">
         <v>8</v>
@@ -874,16 +874,16 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07026410192069132</v>
+        <v>0.07026387554576297</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.008490421957722205</v>
+        <v>0.008490321459118766</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03676893785273116</v>
+        <v>0.03676883453610258</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.0001213389410887888</v>
+        <v>0.0001212401035597388</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>-0.01985129982588318</v>
@@ -945,25 +945,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.3889480032609609</v>
+        <v>0.3914368720273382</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.3984572327836926</v>
+        <v>0.4009631420410862</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4483922587004499</v>
+        <v>0.4483923845633841</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.01534874559291199</v>
+        <v>0.01716813477290646</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1693789916270974</v>
+        <v>0.1714743115339061</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-0.03447617564703143</v>
+        <v>-0.03274612807122379</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.002437439064023383</v>
+        <v>-0.0006499837504062578</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.3585297434061203</v>
+        <v>0.3585299812919376</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>1</v>
@@ -983,7 +983,7 @@
         <v>1</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.2829675628261778</v>
+        <v>0.2829676183009037</v>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.006460090273391561</v>
+        <v>0.006460238837157739</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02210417474454762</v>
+        <v>-0.02210424486987206</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.004025682946822373</v>
+        <v>0.004025610947714808</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>-0.02502790272489019</v>
@@ -1156,16 +1156,16 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05971354076970092</v>
+        <v>0.05971345567082831</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03741426452174346</v>
+        <v>0.03741434607688499</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03435396251839529</v>
+        <v>0.03435404383295459</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.0182687671751689</v>
+        <v>0.01826892432060045</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>0.008931231656543304</v>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Survivor" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Survivor'!$A$1:$S$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Survivor'!$A$1:$T$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -461,11 +461,12 @@
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -541,25 +542,30 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Effective Portfolio Month</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>Official 12-1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Official Rank</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Official Selected</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Official Target Weight</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Official Status</t>
         </is>
@@ -590,25 +596,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.3949674214187249</v>
+        <v>0.3952420042366209</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1612615648510574</v>
+        <v>0.1614900157412154</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0.1653279534670555</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1783723132482604</v>
+        <v>0.1786041302755754</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.02495896328380209</v>
+        <v>0.02516059984409558</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-0.00348948002482885</v>
+        <v>-0.003293440026407635</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.002250719706883064</v>
+        <v>-0.002054436011515337</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -618,19 +624,24 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="O2" s="3" t="n">
-        <v>0.1709282973064323</v>
-      </c>
-      <c r="P2" s="2" t="n">
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0.1709285219064547</v>
+      </c>
+      <c r="Q2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q2" s="2" t="b">
+      <c r="R2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="R2" s="3" t="n">
-        <v>0.3504196804893185</v>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="S2" s="3" t="n">
+        <v>0.3504197296484753</v>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>SELECTED</t>
         </is>
@@ -661,7 +672,7 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.588568202139224</v>
+        <v>0.5885680980357915</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0.2413706055408109</v>
@@ -689,19 +700,24 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="O3" s="3" t="n">
-        <v>0.211962557345279</v>
-      </c>
-      <c r="P3" s="2" t="n">
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>0.2119626877906462</v>
+      </c>
+      <c r="Q3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" s="2" t="b">
+      <c r="R3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="R3" s="3" t="n">
-        <v>0.3666127012097777</v>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="3" t="n">
+        <v>0.3666127200653586</v>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>SELECTED</t>
         </is>
@@ -732,13 +748,13 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.07722719654583143</v>
+        <v>-0.07722728006990576</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.09245159376813938</v>
+        <v>-0.09245151297736265</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.04082007576541435</v>
+        <v>-0.04081999037835338</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>-0.08178516632652277</v>
@@ -760,19 +776,24 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="O4" s="4" t="n">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="n">
         <v>-0.01073115539567115</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>8</v>
       </c>
-      <c r="Q4" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="R4" t="b">
+        <v>0</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>NON_POSITIVE</t>
         </is>
@@ -831,19 +852,24 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="n">
         <v>0.168107649259597</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>4</v>
       </c>
-      <c r="Q5" t="b">
-        <v>0</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>POSITIVE_NOT_SELECTED</t>
         </is>
@@ -874,13 +900,13 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07026387554576297</v>
+        <v>0.07026410192069132</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.008490321459118766</v>
+        <v>0.008490220960535311</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03676883453610258</v>
+        <v>0.03676873121949464</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>0.0001212401035597388</v>
@@ -902,19 +928,24 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="O6" s="4" t="n">
-        <v>0.03697988703295696</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>0.03698009561642079</v>
+      </c>
+      <c r="Q6" t="n">
         <v>6</v>
       </c>
-      <c r="Q6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="R6" t="b">
+        <v>0</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>POSITIVE_NOT_SELECTED</t>
         </is>
@@ -948,13 +979,13 @@
         <v>0.3914368720273382</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.4009631420410862</v>
+        <v>0.4009630202996757</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4483923845633841</v>
+        <v>0.4483922587004499</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.01716813477290646</v>
+        <v>0.01716807059723213</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>0.1714743115339061</v>
@@ -973,19 +1004,24 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="O7" s="3" t="n">
-        <v>0.3585299812919376</v>
-      </c>
-      <c r="P7" s="2" t="n">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>0.3585297434061203</v>
+      </c>
+      <c r="Q7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" s="2" t="b">
+      <c r="R7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="R7" s="3" t="n">
-        <v>0.2829676183009037</v>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
+      <c r="S7" s="3" t="n">
+        <v>0.282967550286166</v>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>SELECTED</t>
         </is>
@@ -1016,7 +1052,7 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.006460238837157739</v>
+        <v>0.006460164555269099</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>-0.02210424486987206</v>
@@ -1044,19 +1080,24 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="O8" s="4" t="n">
-        <v>0.008776631788367073</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0.008776559123944594</v>
+      </c>
+      <c r="Q8" t="n">
         <v>7</v>
       </c>
-      <c r="Q8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="R8" t="b">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>POSITIVE_NOT_SELECTED</t>
         </is>
@@ -1115,19 +1156,24 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="O9" s="4" t="n">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="n">
         <v>0.06437978603290229</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>5</v>
       </c>
-      <c r="Q9" t="b">
-        <v>0</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="R9" t="b">
+        <v>0</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>POSITIVE_NOT_SELECTED</t>
         </is>
@@ -1165,7 +1211,7 @@
         <v>0.03435404383295459</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01826892432060045</v>
+        <v>0.01826884574787879</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>0.008931231656543304</v>
@@ -1182,22 +1228,27 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="O10" s="6" t="n"/>
-      <c r="P10" s="5" t="n"/>
-      <c r="Q10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="5" t="inlineStr">
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="n"/>
+      <c r="Q10" s="5" t="n"/>
+      <c r="R10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="5" t="inlineStr">
         <is>
           <t>RESERVE_UNUSED</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S10"/>
+  <autoFilter ref="A1:T10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -596,41 +596,41 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.3952420042366209</v>
+        <v>0.3859747274424008</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1614900157412154</v>
+        <v>0.1571616795791069</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1653279534670555</v>
+        <v>0.1529785657981089</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1786041302755754</v>
+        <v>0.1698209282852334</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.02516059984409558</v>
+        <v>0.0265364325837012</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-0.003293440026407635</v>
+        <v>0.003628093275179323</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.002054436011515337</v>
+        <v>2.622503704285961e-05</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.1709285219064547</v>
+        <v>0.1609548690014375</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>3</v>
@@ -639,7 +639,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3504197296484753</v>
+        <v>0.3464512197561446</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -672,41 +672,41 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5885680980357915</v>
+        <v>0.5923296669463916</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2413706055408109</v>
+        <v>0.2408578942643969</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.2015067066653458</v>
+        <v>0.1829783585344735</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.2844428083960777</v>
+        <v>0.27171934359007</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.0211962484856496</v>
+        <v>0.04162592862723091</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.03317825747814851</v>
+        <v>0.04892696076167202</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.002493461439432076</v>
+        <v>0.002325046974059441</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.2119626877906462</v>
+        <v>0.1982245316673374</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>2</v>
@@ -715,7 +715,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3666127200653586</v>
+        <v>0.3583095304551976</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -748,41 +748,41 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.07722728006990576</v>
+        <v>-0.09553009444706506</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.09245151297736265</v>
+        <v>-0.0990559644506378</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.04081999037835338</v>
+        <v>-0.04194975723566319</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.08178516632652277</v>
+        <v>-0.09021563762321838</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.08334232389184626</v>
+        <v>-0.09254646987060444</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.05382881427999697</v>
+        <v>-0.05960669353853687</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.005752268950530492</v>
+        <v>-0.01015685266135258</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.01073115539567115</v>
+        <v>-0.0380295852549698</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -824,41 +824,41 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3407026684503274</v>
+        <v>0.3251891441660304</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.0805197752936504</v>
+        <v>0.07418347539876757</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.1587697894796574</v>
+        <v>0.1161279432863531</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1149224941318646</v>
+        <v>-0.127860764697821</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.02763086886130584</v>
+        <v>0.009811440509877478</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.06752852455805303</v>
+        <v>-0.03758034026465029</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.005354018125310223</v>
+        <v>0.002625774603508102</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.168107649259597</v>
+        <v>0.1489577179508819</v>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
@@ -900,41 +900,41 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07026410192069132</v>
+        <v>0.06018186101123857</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.008490220960535311</v>
+        <v>0.0005005742894850229</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03676873121949464</v>
+        <v>0.03355877532059903</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.0001212401035597388</v>
+        <v>-0.01059310613078135</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01985129982588318</v>
+        <v>-0.02943920240551412</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.02727562030704456</v>
+        <v>-0.03198482932996205</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.001938986556359934</v>
+        <v>-0.008289081725165182</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03698009561642079</v>
+        <v>0.03715208976809348</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -976,41 +976,41 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.3914368720273382</v>
+        <v>0.3860972876631688</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.4009630202996757</v>
+        <v>0.4261478996986643</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4483922587004499</v>
+        <v>0.4824956855033913</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.01716807059723213</v>
+        <v>0.06422804311054819</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1714743115339061</v>
+        <v>0.1707661290883686</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-0.03274612807122379</v>
+        <v>-0.03800873510508307</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.0006499837504062578</v>
+        <v>0.007154471544715379</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.3585297434061203</v>
+        <v>0.4639559345596878</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>1</v>
@@ -1019,7 +1019,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.282967550286166</v>
+        <v>0.2952392497886577</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1052,41 +1052,41 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.006460164555269099</v>
+        <v>0.0007392789353775076</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02210424486987206</v>
+        <v>-0.023532879350044</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.004025610947714808</v>
+        <v>0.004202321939358766</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02502790272489019</v>
+        <v>-0.02671470566135237</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.03112313574992809</v>
+        <v>-0.0342279020173083</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.02602508893465627</v>
+        <v>-0.02761913678494521</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0002884338044419898</v>
+        <v>-0.0017301038062284</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.008776559123944594</v>
+        <v>0.004296339570848184</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
@@ -1128,41 +1128,41 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.04358356557955267</v>
+        <v>0.04574773171561031</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.08034013776039295</v>
+        <v>0.08490148781249474</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.05593203593403739</v>
+        <v>0.06046676961851971</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.0356371490280778</v>
+        <v>0.04075009015506659</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.009828009828009909</v>
+        <v>0.0183486238532109</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.02311522048364156</v>
+        <v>0.02304147465437789</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.0006956521739129862</v>
+        <v>0.003128258602711043</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.06437978603290229</v>
+        <v>0.05708350094550774</v>
       </c>
       <c r="Q9" t="n">
         <v>5</v>
@@ -1202,35 +1202,35 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05971345567082831</v>
+        <v>0.05687163914069981</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03741434607688499</v>
+        <v>0.03463224562554634</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03435404383295459</v>
+        <v>0.03463224562554634</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01826884574787879</v>
+        <v>0.01530544240350862</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.008931231656543304</v>
+        <v>0.005824795380049208</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.002958660298353788</v>
+        <v>0</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0</v>
+        <v>-0.002681764004767717</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="P10" s="6" t="n"/>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -596,25 +596,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.3859747274424008</v>
+        <v>0.388409774560702</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1571616795791069</v>
+        <v>0.1591949563400452</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1529785657981089</v>
+        <v>0.1529786725732387</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1698209282852334</v>
+        <v>0.1718763403928874</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.0265364325837012</v>
+        <v>0.02834008933275034</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.003628093275179323</v>
+        <v>0.005391499352657592</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>2.622503704285961e-05</v>
+        <v>0.001783302518914898</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.1609548690014375</v>
+        <v>0.1609549765152376</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>3</v>
@@ -639,7 +639,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512197561446</v>
+        <v>0.3464512421129409</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -672,25 +672,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5923296669463916</v>
+        <v>0.5934891978720511</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2408578942643969</v>
+        <v>0.2417615656057537</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0.1829783585344735</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.27171934359007</v>
+        <v>0.272645490194257</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.04162592862723091</v>
+        <v>0.04238450662755278</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.04892696076167202</v>
+        <v>0.04969085583619925</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.002325046974059441</v>
+        <v>0.003055003582194349</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -715,7 +715,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095304551976</v>
+        <v>0.3583095181980359</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -748,25 +748,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.09553009444706506</v>
+        <v>-0.08707161500820138</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.0990559644506378</v>
+        <v>-0.09063021490284862</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.04194975723566319</v>
+        <v>-0.04194950063178748</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.09021563762321838</v>
+        <v>-0.08170745810755031</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.09254646987060444</v>
+        <v>-0.08406017034666813</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.05960669353853687</v>
+        <v>-0.05081226334432654</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.01015685266135258</v>
+        <v>-0.0008999742864490567</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.0380295852549698</v>
+        <v>-0.03802932760111633</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -824,25 +824,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3251891441660304</v>
+        <v>0.3283820365100298</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.07418347539876757</v>
+        <v>0.07677159816580859</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.1161279432863531</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.127860764697821</v>
+        <v>-0.1257594445205792</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.009811440509877478</v>
+        <v>0.01224446618887676</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.03758034026465029</v>
+        <v>-0.03526149968494019</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.002625774603508102</v>
+        <v>0.005041487238735431</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -900,25 +900,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.06018186101123857</v>
+        <v>0.0647504512256829</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.0005005742894850229</v>
+        <v>0.004812413385318681</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03355877532059903</v>
+        <v>0.03355867228580878</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01059310613078135</v>
+        <v>-0.006328978208920866</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.02943920240551412</v>
+        <v>-0.02525629704824384</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.03198482932996205</v>
+        <v>-0.02781289506953211</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.008289081725165182</v>
+        <v>-0.004015023960626696</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715208976809348</v>
+        <v>0.03715198637508799</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -976,25 +976,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.3860972876631688</v>
+        <v>0.4031046163461525</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.4261478996986643</v>
+        <v>0.4436466469342308</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.4824956855033913</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.06422804311054819</v>
+        <v>0.07728605590945081</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1707661290883686</v>
+        <v>0.1851313576661402</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-0.03800873510508307</v>
+        <v>-0.02620516130269135</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.007154471544715379</v>
+        <v>0.01951219512195124</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1019,7 +1019,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392497886577</v>
+        <v>0.2952392396890233</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1052,25 +1052,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.0007392789353775076</v>
+        <v>0.005075459340537991</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.023532879350044</v>
+        <v>-0.01930194524254514</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.004202321939358766</v>
+        <v>0.004202466001761662</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02671470566135237</v>
+        <v>-0.02249769832019699</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.0342279020173083</v>
+        <v>-0.03004344751998289</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.02761913678494521</v>
+        <v>-0.02340604812283498</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.0017301038062284</v>
+        <v>0.002595155709342434</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.004296339570848184</v>
+        <v>0.004296483646738736</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
@@ -1128,25 +1128,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.04574773171561031</v>
+        <v>0.04937125122952435</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.08490148781249474</v>
+        <v>0.08866067522695253</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.06046676961851971</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.04075009015506659</v>
+        <v>0.04435629282365672</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.0183486238532109</v>
+        <v>0.02187720536344395</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.02304147465437789</v>
+        <v>0.02658631690889757</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.003128258602711043</v>
+        <v>0.006604101494612546</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05687163914069981</v>
+        <v>0.05687172401137119</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>0.03463224562554634</v>
@@ -1211,7 +1211,7 @@
         <v>0.03463224562554634</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01530544240350862</v>
+        <v>0.01530552072962088</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>0.005824795380049208</v>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -596,25 +596,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.388409774560702</v>
+        <v>0.3960430313346159</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1591949563400452</v>
+        <v>0.1648905357181594</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1529786725732387</v>
+        <v>0.1541614263711546</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1718763403928874</v>
+        <v>0.1805842102951865</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.02834008933275034</v>
+        <v>0.02794292748813687</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.005391499352657592</v>
+        <v>0.009296021424610057</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.001783302518914898</v>
+        <v>0.008337805468658033</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.1609549765152376</v>
+        <v>0.1609548690014375</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>3</v>
@@ -639,7 +639,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512421129409</v>
+        <v>0.3464512165360852</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -672,25 +672,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5934891978720511</v>
+        <v>0.602028361724636</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2417615656057537</v>
+        <v>0.2524714981337597</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1829783585344735</v>
+        <v>0.1799928314412171</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.272645490194257</v>
+        <v>0.2883020411419668</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.04238450662755278</v>
+        <v>0.04148140637929054</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.04969085583619925</v>
+        <v>0.06142297203960023</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.003055003582194349</v>
+        <v>0.01346306753096238</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -715,7 +715,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095181980359</v>
+        <v>0.3583095243242682</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -748,25 +748,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.08707161500820138</v>
+        <v>-0.08635807343377511</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.09063021490284862</v>
+        <v>-0.08439779001706282</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.04194950063178748</v>
+        <v>-0.04348371601185663</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.08170745810755031</v>
+        <v>-0.07868676752065296</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.08406017034666813</v>
+        <v>-0.07475166990175819</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.05081226334432654</v>
+        <v>-0.04277404858662448</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.0008999742864490567</v>
+        <v>0.005404709818556119</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.03802932760111633</v>
+        <v>-0.038029469654283</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -824,25 +824,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3283820365100298</v>
+        <v>0.3358486629342421</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.07677159816580859</v>
+        <v>0.07898210824930496</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.1161279432863531</v>
+        <v>0.1313091593405051</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1257594445205792</v>
+        <v>-0.1054004331524652</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.01224446618887676</v>
+        <v>0.00528615916049513</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.03526149968494019</v>
+        <v>-0.04625353791151499</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.005041487238735431</v>
+        <v>0.003631518444978443</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -900,25 +900,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.0647504512256829</v>
+        <v>0.07089969850490507</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.004812413385318681</v>
+        <v>0.01106851641622519</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03355867228580878</v>
+        <v>0.03176125469305457</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.006328978208920866</v>
+        <v>-0.0006660506786014819</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.02525629704824384</v>
+        <v>-0.01932309512443675</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.02781289506953211</v>
+        <v>-0.02005574272411048</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.004015023960626696</v>
+        <v>0.003641092327698381</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715198637508799</v>
+        <v>0.03715216747213934</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -976,25 +976,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.4031046163461525</v>
+        <v>0.3925968637614696</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.4436466469342308</v>
+        <v>0.4411140600946881</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4824956855033913</v>
+        <v>0.4900491624844652</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.07728605590945081</v>
+        <v>0.07031395850447453</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1851313576661402</v>
+        <v>0.1850562558050866</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-0.02620516130269135</v>
+        <v>-0.03284126700100565</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.01951219512195124</v>
+        <v>-0.001754385964912286</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.4639559345596878</v>
+        <v>0.4639560631420809</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>1</v>
@@ -1019,7 +1019,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392396890233</v>
+        <v>0.2952392591396466</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1052,25 +1052,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.005075459340537991</v>
+        <v>0.005988243075408572</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01930194524254514</v>
+        <v>-0.01954622112256033</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.004202466001761662</v>
+        <v>0.002883993594746892</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02249769832019699</v>
+        <v>-0.02497400363598912</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.03004344751998289</v>
+        <v>-0.02998830153914034</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.02340604812283498</v>
+        <v>-0.022365712146734</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.002595155709342434</v>
+        <v>0.001533889368229291</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -1128,25 +1128,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.04937125122952435</v>
+        <v>0.04537362713763704</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.08866067522695253</v>
+        <v>0.08604811984471983</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.06046676961851971</v>
+        <v>0.05934818338039349</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.04435629282365672</v>
+        <v>0.03661162957645359</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.02187720536344395</v>
+        <v>0.0197740112994349</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.02658631690889757</v>
+        <v>0.02520411785587484</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.006604101494612546</v>
+        <v>-0.002762430939226568</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05687172401137119</v>
+        <v>0.05997734225571572</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03463224562554634</v>
+        <v>0.03776565803703158</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03463224562554634</v>
+        <v>0.0345600408422948</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01530552072962088</v>
+        <v>0.01814704207359941</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.005824795380049208</v>
+        <v>0.009041763178202711</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0</v>
+        <v>0.003098531808870986</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>-0.002681764004767717</v>
+        <v>0.0001991833482721805</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -596,25 +596,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.3960430313346159</v>
+        <v>0.395118811559471</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1648905357181594</v>
+        <v>0.1641193454003647</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0.1541614263711546</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1805842102951865</v>
+        <v>0.1798026303231597</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.02794292748813687</v>
+        <v>0.0272624003410642</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.009296021424610057</v>
+        <v>0.008627839054125452</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.008337805468658033</v>
+        <v>0.007670257464102992</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -639,7 +639,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512165360852</v>
+        <v>0.3464512030450774</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -672,25 +672,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.602028361724636</v>
+        <v>0.5968304292193729</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2524714981337597</v>
+        <v>0.2484076090221559</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1799928314412171</v>
+        <v>0.1799927114918818</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.2883020411419668</v>
+        <v>0.2841220233493729</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.04148140637929054</v>
+        <v>0.03810222147521181</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.06142297203960023</v>
+        <v>0.05797908484008873</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.01346306753096238</v>
+        <v>0.0101747907766534</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.1982245316673374</v>
+        <v>0.1982246540542743</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>2</v>
@@ -715,7 +715,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095243242682</v>
+        <v>0.358309549312061</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -748,25 +748,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.08635807343377511</v>
+        <v>-0.09395884529469423</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.08439779001706282</v>
+        <v>-0.09201519407706626</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.04348371601185663</v>
+        <v>-0.04348380153258791</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.07868676752065296</v>
+        <v>-0.0863516852629066</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.07475166990175819</v>
+        <v>-0.082449160462294</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.04277404858662448</v>
+        <v>-0.05073765883132797</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.005404709818556119</v>
+        <v>-0.002959722043494928</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -824,25 +824,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3358486629342421</v>
+        <v>0.3219042320130752</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.07898210824930496</v>
+        <v>0.06771901244277179</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.1313091593405051</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1054004331524652</v>
+        <v>-0.1147388276938125</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.00528615916049513</v>
+        <v>-0.005207651846230399</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.04625353791151499</v>
+        <v>-0.05620934505188935</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.003631518444978443</v>
+        <v>-0.006845020378304922</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -900,25 +900,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07089969850490507</v>
+        <v>0.0671532403865378</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01106851641622519</v>
+        <v>0.007531580325343068</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03176125469305457</v>
+        <v>0.0317613578135878</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.0006660506786014819</v>
+        <v>-0.004162036248914869</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01932309512443675</v>
+        <v>-0.02275381246463382</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.02005574272411048</v>
+        <v>-0.02348389703176146</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.003641092327698381</v>
+        <v>0.0001300390117033867</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715216747213934</v>
+        <v>0.03715195976610053</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -976,25 +976,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.3925968637614696</v>
+        <v>0.4006066875504795</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.4411140600946881</v>
+        <v>0.4494029410921971</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.4900491624844652</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.07031395850447453</v>
+        <v>0.07647010205874216</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1850562558050866</v>
+        <v>0.191872364641799</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-0.03284126700100565</v>
+        <v>-0.02727844316525496</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.001754385964912286</v>
+        <v>0.003987240829345984</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1019,7 +1019,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392591396466</v>
+        <v>0.2952392476428616</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1052,25 +1052,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.005988243075408572</v>
+        <v>0.002521642448366057</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01954622112256033</v>
+        <v>-0.02292483087077402</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>0.002883993594746892</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02497400363598912</v>
+        <v>-0.02833390943374015</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02998830153914034</v>
+        <v>-0.033330928240068</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.022365712146734</v>
+        <v>-0.02573460602657685</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.001533889368229291</v>
+        <v>-0.001917361710286669</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -1128,25 +1128,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.04537362713763704</v>
+        <v>0.04573559861517773</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.08604811984471983</v>
+        <v>0.08642417528787938</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.05934818338039349</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.03661162957645359</v>
+        <v>0.03697056712132096</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.0197740112994349</v>
+        <v>0.02012711864406791</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.02520411785587484</v>
+        <v>0.02555910543130979</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.002762430939226568</v>
+        <v>-0.002417127071823177</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05997734225571572</v>
+        <v>0.06008280078950379</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03776565803703158</v>
+        <v>0.03786882663086688</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.0345600408422948</v>
+        <v>0.03455987772067659</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01814704207359941</v>
+        <v>0.01824849960638542</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009041763178202711</v>
+        <v>0.009142312679250919</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003098531808870986</v>
+        <v>0.003198412176470988</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0001991833482721805</v>
+        <v>0.0002987750224081598</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -8,9 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="Survivor" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Weekly History" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Survivor'!$A$1:$T$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Survivor'!$A$1:$AS$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Weekly Review'!$A$17:$H$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Weekly History'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%;[Red]-0.0%"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +36,14 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -69,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -79,6 +91,15 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:AS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -467,6 +488,31 @@
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="22" customWidth="1" min="30" max="30"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
+    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="34" max="34"/>
+    <col width="30" customWidth="1" min="35" max="35"/>
+    <col width="30" customWidth="1" min="36" max="36"/>
+    <col width="22" customWidth="1" min="37" max="37"/>
+    <col width="22" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="39" max="39"/>
+    <col width="22" customWidth="1" min="40" max="40"/>
+    <col width="22" customWidth="1" min="41" max="41"/>
+    <col width="22" customWidth="1" min="42" max="42"/>
+    <col width="22" customWidth="1" min="43" max="43"/>
+    <col width="70" customWidth="1" min="44" max="44"/>
+    <col width="70" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -570,6 +616,131 @@
           <t>Official Status</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Data As Of</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Current 21/252 Shadow Selected</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Current Shadow Target Weight</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Review Baseline Month</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Review Baseline Selected</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Review Baseline Target Weight</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly Review Date</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Previous Weekly Review Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly Shadow Selected</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Previous Weekly Shadow Selected</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly Shadow Target Weight</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly Change</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly Persistence</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly Observations</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly HIL Status</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio Weekly HIL Status</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly Candidate Still In Daily Shadow</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly 21/252 Score</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly Rank</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Previous Weekly Rank</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly Rank Movement</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly Score Change</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly 3-4 Gap</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Short Horizon Context</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>HIL Summary</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -596,25 +767,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.395118811559471</v>
+        <v>0.394738404744325</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1641193454003647</v>
+        <v>0.1638017964459786</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0.1541614263711546</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1798026303231597</v>
+        <v>0.1794808032758544</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.0272624003410642</v>
+        <v>0.02698218328050483</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.008627839054125452</v>
+        <v>0.008352705136867034</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.007670257464102992</v>
+        <v>0.007395384756345047</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -639,11 +810,104 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512030450774</v>
+        <v>0.3464512165360852</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
           <t>SELECTED</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>0.3463971227760583</v>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>0.3464512165360852</v>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>0.3463971227760583</v>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="n"/>
+      <c r="AL2" s="3" t="n">
+        <v>0.1541614263711546</v>
+      </c>
+      <c r="AM2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" s="3" t="n">
+        <v>-0.01423500709240733</v>
+      </c>
+      <c r="AQ2" s="3" t="n">
+        <v>0.02285226703064946</v>
+      </c>
+      <c r="AR2" s="2" t="inlineStr">
+        <is>
+          <t>CONTEXT ONLY; 1m +0.8%, 3m +2.7%, 6m +17.9%. No mechanical gate.</t>
+        </is>
+      </c>
+      <c r="AS2" s="2" t="inlineStr">
+        <is>
+          <t>No weekly membership exception; retain monthly authority.</t>
         </is>
       </c>
     </row>
@@ -706,7 +970,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.1982246540542743</v>
+        <v>0.1982245316673374</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>2</v>
@@ -715,11 +979,104 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.358309549312061</v>
+        <v>0.3583095243242682</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
           <t>SELECTED</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>0.3542858650441819</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>0.3583095243242682</v>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>0.3542858650441819</v>
+      </c>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="AH3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AK3" s="2" t="n"/>
+      <c r="AL3" s="3" t="n">
+        <v>0.1799927114918818</v>
+      </c>
+      <c r="AM3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" s="3" t="n">
+        <v>-0.01773986903845892</v>
+      </c>
+      <c r="AQ3" s="3" t="n">
+        <v>0.02285226703064946</v>
+      </c>
+      <c r="AR3" s="2" t="inlineStr">
+        <is>
+          <t>CONTEXT ONLY; 1m +5.8%, 3m +3.8%, 6m +28.4%. No mechanical gate.</t>
+        </is>
+      </c>
+      <c r="AS3" s="2" t="inlineStr">
+        <is>
+          <t>No weekly membership exception; retain monthly authority.</t>
         </is>
       </c>
     </row>
@@ -748,19 +1105,19 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.09395884529469423</v>
+        <v>-0.09395900696350357</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.09201519407706626</v>
+        <v>-0.0920150317138323</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.04348380153258791</v>
+        <v>-0.04348363049110981</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.0863516852629066</v>
+        <v>-0.08635160306540612</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.082449160462294</v>
+        <v>-0.08244924336347392</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>-0.05073765883132797</v>
@@ -796,6 +1153,98 @@
       <c r="T4" t="inlineStr">
         <is>
           <t>NON_POSITIVE</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="V4" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="Y4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AL4" s="4" t="n">
+        <v>-0.04348363049110981</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="4" t="n">
+        <v>-0.01880306629622497</v>
+      </c>
+      <c r="AQ4" s="4" t="n">
+        <v>0.02285226703064946</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>CONTEXT ONLY; 1m -5.1%, 3m -8.2%, 6m -8.6%. No mechanical gate.</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>No weekly membership exception; retain monthly authority.</t>
         </is>
       </c>
     </row>
@@ -874,6 +1323,98 @@
           <t>POSITIVE_NOT_SELECTED</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="V5" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="Y5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AL5" s="4" t="n">
+        <v>0.1313091593405051</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AP5" s="4" t="n">
+        <v>-0.09588412971926408</v>
+      </c>
+      <c r="AQ5" s="4" t="n">
+        <v>0.02285226703064946</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>CONTEXT ONLY; 1m -5.6%, 3m -0.5%, 6m -11.5%. No mechanical gate.</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>No weekly membership exception; retain monthly authority.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -900,7 +1441,7 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.0671532403865378</v>
+        <v>0.06715312741714952</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0.007531580325343068</v>
@@ -912,7 +1453,7 @@
         <v>-0.004162036248914869</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.02275381246463382</v>
+        <v>-0.02275371772858681</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>-0.02348389703176146</v>
@@ -934,7 +1475,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715195976610053</v>
+        <v>0.03715196348622696</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -948,6 +1489,98 @@
       <c r="T6" t="inlineStr">
         <is>
           <t>POSITIVE_NOT_SELECTED</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="V6" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="Y6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AL6" s="4" t="n">
+        <v>0.0317613578135878</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="4" t="n">
+        <v>-0.007071979722355071</v>
+      </c>
+      <c r="AQ6" s="4" t="n">
+        <v>0.02285226703064946</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>CONTEXT ONLY; 1m -2.3%, 3m -2.3%, 6m -0.4%. No mechanical gate.</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>No weekly membership exception; retain monthly authority.</t>
         </is>
       </c>
     </row>
@@ -976,25 +1609,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.4006066875504795</v>
+        <v>0.3977141325510336</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.4494029410921971</v>
+        <v>0.4464097340653188</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.4900491624844652</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.07647010205874216</v>
+        <v>0.07424705021970102</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.191872364641799</v>
+        <v>0.1894109920063194</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-0.02727844316525496</v>
+        <v>-0.02928724066149824</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.003987240829345984</v>
+        <v>0.00191387559808609</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1019,11 +1652,104 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392476428616</v>
+        <v>0.2952392591396466</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
           <t>SELECTED</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0.2993170121797599</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0.2952392591396466</v>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="3" t="n">
+        <v>0.2993170121797599</v>
+      </c>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="AG7" s="2" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="AH7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AK7" s="2" t="n"/>
+      <c r="AL7" s="3" t="n">
+        <v>0.4900491624844652</v>
+      </c>
+      <c r="AM7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="3" t="n">
+        <v>0.07693018597033974</v>
+      </c>
+      <c r="AQ7" s="3" t="n">
+        <v>0.02285226703064946</v>
+      </c>
+      <c r="AR7" s="2" t="inlineStr">
+        <is>
+          <t>CONTEXT ONLY; 1m -2.9%, 3m +18.9%, 6m +7.4%. No mechanical gate.</t>
+        </is>
+      </c>
+      <c r="AS7" s="2" t="inlineStr">
+        <is>
+          <t>No weekly membership exception; retain monthly authority.</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1787,7 @@
         <v>0.002883993594746892</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02833390943374015</v>
+        <v>-0.02833397862188713</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>-0.033330928240068</v>
@@ -1100,6 +1826,98 @@
       <c r="T8" t="inlineStr">
         <is>
           <t>POSITIVE_NOT_SELECTED</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="V8" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="Y8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AL8" s="4" t="n">
+        <v>0.002883993594746892</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="4" t="n">
+        <v>-0.00744549208068257</v>
+      </c>
+      <c r="AQ8" s="4" t="n">
+        <v>0.02285226703064946</v>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>CONTEXT ONLY; 1m -2.6%, 3m -3.3%, 6m -2.8%. No mechanical gate.</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>No weekly membership exception; retain monthly authority.</t>
         </is>
       </c>
     </row>
@@ -1178,6 +1996,98 @@
           <t>POSITIVE_NOT_SELECTED</t>
         </is>
       </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="V9" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="Y9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AL9" s="4" t="n">
+        <v>0.05934818338039349</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="4" t="n">
+        <v>0.006023869849343555</v>
+      </c>
+      <c r="AQ9" s="4" t="n">
+        <v>0.02285226703064946</v>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>CONTEXT ONLY; 1m +2.6%, 3m +2.0%, 6m +3.7%. No mechanical gate.</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>No weekly membership exception; retain monthly authority.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
@@ -1202,19 +2112,19 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.06008280078950379</v>
+        <v>0.06008271542783095</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03786882663086688</v>
+        <v>0.03786890845253477</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03455987772067659</v>
+        <v>0.03455995928147937</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0.01824849960638542</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009142312679250919</v>
+        <v>0.009142235324292258</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>0.003198412176470988</v>
@@ -1246,9 +2156,758 @@
           <t>RESERVE_UNUSED</t>
         </is>
       </c>
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="V10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="5" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="Y10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB10" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AC10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="5" t="inlineStr">
+        <is>
+          <t>RESERVE_CONTEXT</t>
+        </is>
+      </c>
+      <c r="AG10" s="5" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="AH10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AJ10" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AK10" s="5" t="n"/>
+      <c r="AL10" s="6" t="n"/>
+      <c r="AM10" s="5" t="n"/>
+      <c r="AN10" s="5" t="n"/>
+      <c r="AO10" s="5" t="n"/>
+      <c r="AP10" s="6" t="n"/>
+      <c r="AQ10" s="6" t="n">
+        <v>0.02285226703064946</v>
+      </c>
+      <c r="AR10" s="5" t="inlineStr">
+        <is>
+          <t>CONTEXT ONLY; 1m +0.3%, 3m +0.9%, 6m +1.8%. No mechanical gate.</t>
+        </is>
+      </c>
+      <c r="AS10" s="5" t="inlineStr">
+        <is>
+          <t>SGOV fills vacancies only; reserve-weight changes cannot trigger an exception.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T10"/>
+  <autoFilter ref="A1:AS10"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="67" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>SURVIVOR - WEEKLY EXCEPTION REVIEW (HIL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Data through</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Monthly model baseline</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>2026-10: QQQ 35.8%, SPY 34.6%, XLE 29.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Latest completed review</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02: QQQ 35.4%, SPY 34.6%, XLE 29.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Previous completed review</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-25: QQQ 38.3%, GLD 30.9%, XLE 30.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Current daily shadow</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>QQQ 35.4%, SPY 34.6%, XLE 29.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Persistent entries / exits</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Entries: None; exits: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>First observations (WATCH)</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Entries: None; exits: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Cleared changes</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Observation schedule</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Calendar Friday; use last verified common session in the completed week</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Portfolio authority</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Monthly model. This is a review flag; HIL decides any early action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Baseline scope</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Model target only. Actual holdings and previous HIL trades are not recorded here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>HIL Status</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Weeks</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>3m</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>6m</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>HIL Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>0.008352705136867034</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>0.02698218328050483</v>
+      </c>
+      <c r="G18" s="11" t="n">
+        <v>0.1794808032758544</v>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>No weekly membership exception; retain monthly authority.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>0.05797908484008873</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>0.03810222147521181</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>0.2841220233493729</v>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>No weekly membership exception; retain monthly authority.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>-0.05073765883132797</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>-0.08244924336347392</v>
+      </c>
+      <c r="G20" s="11" t="n">
+        <v>-0.08635160306540612</v>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>No weekly membership exception; retain monthly authority.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>-0.05620934505188935</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>-0.005207651846230399</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>-0.1147388276938125</v>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>No weekly membership exception; retain monthly authority.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>HYG</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>-0.02348389703176146</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>-0.02275371772858681</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>-0.004162036248914869</v>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>No weekly membership exception; retain monthly authority.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>-0.02928724066149824</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>0.1894109920063194</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>0.07424705021970102</v>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>No weekly membership exception; retain monthly authority.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>TIP</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>-0.02573460602657685</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>-0.033330928240068</v>
+      </c>
+      <c r="G24" s="11" t="n">
+        <v>-0.02833397862188713</v>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>No weekly membership exception; retain monthly authority.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>UUP</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>0.02555910543130979</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>0.02012711864406791</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>0.03697056712132096</v>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>No weekly membership exception; retain monthly authority.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>SGOV</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>RESERVE_CONTEXT</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>0.003198412176470988</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>0.009142235324292258</v>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>0.01824849960638542</v>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>SGOV fills vacancies only; reserve-weight changes cannot trigger an exception.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A17:H26"/>
+  <mergeCells count="13">
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B11:H11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="66" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Verified Session</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled Week End</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Baseline Month</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>In This Month</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>Shadow Risky Members</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>Shadow Targets</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>3-4 Score Gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>XLE, GLD, QQQ</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>QQQ 38.3%, GLD 30.9%, XLE 30.9%</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0.02933614706677878</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>XLE, QQQ, SPY</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>QQQ 35.4%, SPY 34.6%, XLE 29.9%</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0.02285226703064946</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -776,7 +776,7 @@
         <v>0.1541614263711546</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1794808032758544</v>
+        <v>0.1794806929508048</v>
       </c>
       <c r="J2" s="3" t="n">
         <v>0.02698218328050483</v>
@@ -810,7 +810,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512165360852</v>
+        <v>0.3464512062651334</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>1</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>0.3463971227760583</v>
+        <v>0.3463971259088848</v>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>1</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>0.3464512165360852</v>
+        <v>0.3464512062651334</v>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.3463971227760583</v>
+        <v>0.3463971259088848</v>
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.1982245316673374</v>
+        <v>0.1982246540542743</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>2</v>
@@ -979,7 +979,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095243242682</v>
+        <v>0.3583095554429965</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>1</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.3542858650441819</v>
+        <v>0.3542858700688071</v>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>1</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>0.3583095243242682</v>
+        <v>0.3583095554429965</v>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.3542858650441819</v>
+        <v>0.3542858700688071</v>
       </c>
       <c r="AF3" s="2" t="inlineStr">
         <is>
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.09395900696350357</v>
+        <v>-0.09395908779788664</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.0920150317138323</v>
+        <v>-0.09201495053219366</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.04348363049110981</v>
+        <v>-0.0434835449703479</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.08635160306540612</v>
+        <v>-0.086351520867891</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.08244924336347392</v>
+        <v>-0.08244932626463886</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>-0.05073765883132797</v>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="AL4" s="4" t="n">
-        <v>-0.04348363049110981</v>
+        <v>-0.0434835449703479</v>
       </c>
       <c r="AM4" t="n">
         <v>8</v>
@@ -1232,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="AP4" s="4" t="n">
-        <v>-0.01880306629622497</v>
+        <v>-0.01880289296518045</v>
       </c>
       <c r="AQ4" s="4" t="n">
         <v>0.02285226703064946</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.06715312741714952</v>
+        <v>0.0671532403865378</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0.007531580325343068</v>
@@ -1450,10 +1450,10 @@
         <v>0.0317613578135878</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.004162036248914869</v>
+        <v>-0.004162134623879599</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.02275371772858681</v>
+        <v>-0.02275381246463382</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>-0.02348389703176146</v>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715196348622696</v>
+        <v>0.03715185591311232</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1568,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="AP6" s="4" t="n">
-        <v>-0.007071979722355071</v>
+        <v>-0.007072079904586248</v>
       </c>
       <c r="AQ6" s="4" t="n">
         <v>0.02285226703064946</v>
@@ -1612,10 +1612,10 @@
         <v>0.3977141325510336</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.4464097340653188</v>
+        <v>0.4464096070240571</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4900491624844652</v>
+        <v>0.4900490316102593</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0.07424705021970102</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.4639560631420809</v>
+        <v>0.4639559345596878</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>1</v>
@@ -1652,7 +1652,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392591396466</v>
+        <v>0.2952392382918702</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>1</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.2993170121797599</v>
+        <v>0.2993170040223082</v>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>1</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.2952392591396466</v>
+        <v>0.2952392382918702</v>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.2993170121797599</v>
+        <v>0.2993170040223082</v>
       </c>
       <c r="AF7" s="2" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="AK7" s="2" t="n"/>
       <c r="AL7" s="3" t="n">
-        <v>0.4900491624844652</v>
+        <v>0.4900490316102593</v>
       </c>
       <c r="AM7" s="2" t="n">
         <v>1</v>
@@ -1737,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="AP7" s="3" t="n">
-        <v>0.07693018597033974</v>
+        <v>0.07693017783949019</v>
       </c>
       <c r="AQ7" s="3" t="n">
         <v>0.02285226703064946</v>
@@ -1787,7 +1787,7 @@
         <v>0.002883993594746892</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02833397862188713</v>
+        <v>-0.02833390943374015</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>-0.033330928240068</v>
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="AP8" s="4" t="n">
-        <v>-0.00744549208068257</v>
+        <v>-0.007445564518826053</v>
       </c>
       <c r="AQ8" s="4" t="n">
         <v>0.02285226703064946</v>
@@ -2115,13 +2115,13 @@
         <v>0.06008271542783095</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03786890845253477</v>
+        <v>0.03786882663086688</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03455995928147937</v>
+        <v>0.03455987772067659</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01824849960638542</v>
+        <v>0.01824857836371097</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>0.009142235324292258</v>
@@ -2484,7 +2484,7 @@
         <v>0.02698218328050483</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.1794808032758544</v>
+        <v>0.1794806929508048</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2549,10 +2549,10 @@
         <v>-0.05073765883132797</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.08244924336347392</v>
+        <v>-0.08244932626463886</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.08635160306540612</v>
+        <v>-0.086351520867891</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2617,10 +2617,10 @@
         <v>-0.02348389703176146</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.02275371772858681</v>
+        <v>-0.02275381246463382</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.004162036248914869</v>
+        <v>-0.004162134623879599</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>-0.033330928240068</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.02833397862188713</v>
+        <v>-0.02833390943374015</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>0.009142235324292258</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01824849960638542</v>
+        <v>0.01824857836371097</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.394738404744325</v>
+        <v>0.3947385590130958</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0.1638017964459786</v>
@@ -810,7 +810,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512062651334</v>
+        <v>0.3464512197561446</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>1</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>0.3463971259088848</v>
+        <v>0.3463971132196927</v>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>1</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>0.3464512062651334</v>
+        <v>0.3464512197561446</v>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.3463971259088848</v>
+        <v>0.3463971132196927</v>
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>-0.01423500709240733</v>
+        <v>-0.01423511612681194</v>
       </c>
       <c r="AQ2" s="3" t="n">
         <v>0.02285226703064946</v>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5968304292193729</v>
+        <v>0.5968303254068763</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2484076090221559</v>
+        <v>0.2484077359260441</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1799927114918818</v>
+        <v>0.1799928314412171</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>0.2841220233493729</v>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.1982246540542743</v>
+        <v>0.1982245316673374</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>2</v>
@@ -979,7 +979,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095554429965</v>
+        <v>0.3583095304551976</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>1</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.3542858700688071</v>
+        <v>0.3542858937225558</v>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>1</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>0.3583095554429965</v>
+        <v>0.3583095304551976</v>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.3542858700688071</v>
+        <v>0.3542858937225558</v>
       </c>
       <c r="AF3" s="2" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AK3" s="2" t="n"/>
       <c r="AL3" s="3" t="n">
-        <v>0.1799927114918818</v>
+        <v>0.1799928314412171</v>
       </c>
       <c r="AM3" s="2" t="n">
         <v>2</v>
@@ -1064,7 +1064,7 @@
         <v>1</v>
       </c>
       <c r="AP3" s="3" t="n">
-        <v>-0.01773986903845892</v>
+        <v>-0.01773974908912357</v>
       </c>
       <c r="AQ3" s="3" t="n">
         <v>0.02285226703064946</v>
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.09395908779788664</v>
+        <v>-0.09395916863225517</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.09201495053219366</v>
+        <v>-0.09201511289545661</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.0434835449703479</v>
+        <v>-0.04348371601185663</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.086351520867891</v>
+        <v>-0.08635160306540612</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.08244932626463886</v>
+        <v>-0.082449160462294</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>-0.05073765883132797</v>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="AL4" s="4" t="n">
-        <v>-0.0434835449703479</v>
+        <v>-0.04348371601185663</v>
       </c>
       <c r="AM4" t="n">
         <v>8</v>
@@ -1232,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="AP4" s="4" t="n">
-        <v>-0.01880289296518045</v>
+        <v>-0.01880332743758484</v>
       </c>
       <c r="AQ4" s="4" t="n">
         <v>0.02285226703064946</v>
@@ -1441,16 +1441,16 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.0671532403865378</v>
+        <v>0.06715335335595007</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.007531580325343068</v>
+        <v>0.007531479626482041</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0317613578135878</v>
+        <v>0.03176125469305457</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.004162134623879599</v>
+        <v>-0.004162036248914869</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>-0.02275381246463382</v>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="AL6" s="4" t="n">
-        <v>0.0317613578135878</v>
+        <v>0.03176125469305457</v>
       </c>
       <c r="AM6" t="n">
         <v>6</v>
@@ -1568,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="AP6" s="4" t="n">
-        <v>-0.007072079904586248</v>
+        <v>-0.007072078952478078</v>
       </c>
       <c r="AQ6" s="4" t="n">
         <v>0.02285226703064946</v>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.3977141325510336</v>
+        <v>0.397714251182226</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.4464096070240571</v>
@@ -1652,7 +1652,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392382918702</v>
+        <v>0.2952392497886577</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>1</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.2993170040223082</v>
+        <v>0.2993169930577514</v>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>1</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.2952392382918702</v>
+        <v>0.2952392497886577</v>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.2993170040223082</v>
+        <v>0.2993169930577514</v>
       </c>
       <c r="AF7" s="2" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="AP7" s="3" t="n">
-        <v>0.07693017783949019</v>
+        <v>0.07693005509613382</v>
       </c>
       <c r="AQ7" s="3" t="n">
         <v>0.02285226703064946</v>
@@ -1781,10 +1781,10 @@
         <v>0.002521642448366057</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02292483087077402</v>
+        <v>-0.02292497079196998</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.002883993594746892</v>
+        <v>0.0028838499776207</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>-0.02833390943374015</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.004296483646738736</v>
+        <v>0.004296411608788464</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="AL8" s="4" t="n">
-        <v>0.002883993594746892</v>
+        <v>0.0028838499776207</v>
       </c>
       <c r="AM8" t="n">
         <v>7</v>
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="AP8" s="4" t="n">
-        <v>-0.007445564518826053</v>
+        <v>-0.007445708135952245</v>
       </c>
       <c r="AQ8" s="4" t="n">
         <v>0.02285226703064946</v>
@@ -2115,13 +2115,13 @@
         <v>0.06008271542783095</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03786882663086688</v>
+        <v>0.03786890845253477</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03455987772067659</v>
+        <v>0.03455995928147937</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01824857836371097</v>
+        <v>0.01824849960638542</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>0.009142235324292258</v>
@@ -2549,10 +2549,10 @@
         <v>-0.05073765883132797</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.08244932626463886</v>
+        <v>-0.082449160462294</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.086351520867891</v>
+        <v>-0.08635160306540612</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>-0.02275381246463382</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.004162134623879599</v>
+        <v>-0.004162036248914869</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>0.009142235324292258</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01824857836371097</v>
+        <v>0.01824849960638542</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.02933614706677878</v>
+        <v>0.02933603803237417</v>
       </c>
     </row>
     <row r="3">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.3947385590130958</v>
+        <v>0.3947382504755879</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0.1638017964459786</v>
@@ -776,7 +776,7 @@
         <v>0.1541614263711546</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1794806929508048</v>
+        <v>0.1794808032758544</v>
       </c>
       <c r="J2" s="3" t="n">
         <v>0.02698218328050483</v>
@@ -810,7 +810,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512197561446</v>
+        <v>0.3464512062651334</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>1</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>0.3463971132196927</v>
+        <v>0.3463971385980751</v>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>1</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>0.3464512197561446</v>
+        <v>0.3464512062651334</v>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.3463971132196927</v>
+        <v>0.3463971385980751</v>
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5968303254068763</v>
+        <v>0.5968304292193729</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2484077359260441</v>
+        <v>0.2484074821182936</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1799928314412171</v>
+        <v>0.1799925915425706</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>0.2841220233493729</v>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.1982245316673374</v>
+        <v>0.1982246540542743</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>2</v>
@@ -979,7 +979,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095304551976</v>
+        <v>0.3583095554429965</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>1</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.3542858937225558</v>
+        <v>0.3542858464150614</v>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>1</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>0.3583095304551976</v>
+        <v>0.3583095554429965</v>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.3542858937225558</v>
+        <v>0.3542858464150614</v>
       </c>
       <c r="AF3" s="2" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AK3" s="2" t="n"/>
       <c r="AL3" s="3" t="n">
-        <v>0.1799928314412171</v>
+        <v>0.1799925915425706</v>
       </c>
       <c r="AM3" s="2" t="n">
         <v>2</v>
@@ -1064,7 +1064,7 @@
         <v>1</v>
       </c>
       <c r="AP3" s="3" t="n">
-        <v>-0.01773974908912357</v>
+        <v>-0.01773998898777007</v>
       </c>
       <c r="AQ3" s="3" t="n">
         <v>0.02285226703064946</v>
@@ -1117,7 +1117,7 @@
         <v>-0.08635160306540612</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.082449160462294</v>
+        <v>-0.08244924336347392</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>-0.05073765883132797</v>
@@ -1232,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="AP4" s="4" t="n">
-        <v>-0.01880332743758484</v>
+        <v>-0.01880323962727048</v>
       </c>
       <c r="AQ4" s="4" t="n">
         <v>0.02285226703064946</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.06715335335595007</v>
+        <v>0.06715301444778499</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0.007531479626482041</v>
@@ -1450,7 +1450,7 @@
         <v>0.03176125469305457</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.004162036248914869</v>
+        <v>-0.004162134623879599</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>-0.02275381246463382</v>
@@ -1568,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="AP6" s="4" t="n">
-        <v>-0.007072078952478078</v>
+        <v>-0.007071974879857335</v>
       </c>
       <c r="AQ6" s="4" t="n">
         <v>0.02285226703064946</v>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.397714251182226</v>
+        <v>0.3977143698134384</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.4464096070240571</v>
@@ -1652,7 +1652,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392497886577</v>
+        <v>0.2952392382918702</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>1</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.2993169930577514</v>
+        <v>0.2993170149868635</v>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>1</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.2952392497886577</v>
+        <v>0.2952392382918702</v>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.2993169930577514</v>
+        <v>0.2993170149868635</v>
       </c>
       <c r="AF7" s="2" t="inlineStr">
         <is>
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.002521642448366057</v>
+        <v>0.002521421492105214</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02292497079196998</v>
+        <v>-0.02292483087077402</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0028838499776207</v>
+        <v>0.002883993594746892</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>-0.02833390943374015</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.004296411608788464</v>
+        <v>0.004296555684699666</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="AL8" s="4" t="n">
-        <v>0.0028838499776207</v>
+        <v>0.002883993594746892</v>
       </c>
       <c r="AM8" t="n">
         <v>7</v>
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="AP8" s="4" t="n">
-        <v>-0.007445708135952245</v>
+        <v>-0.007445564518826053</v>
       </c>
       <c r="AQ8" s="4" t="n">
         <v>0.02285226703064946</v>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.06008271542783095</v>
+        <v>0.06008288615119062</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>0.03786890845253477</v>
@@ -2124,7 +2124,7 @@
         <v>0.01824849960638542</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009142235324292258</v>
+        <v>0.009142312679250919</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>0.003198412176470988</v>
@@ -2484,7 +2484,7 @@
         <v>0.02698218328050483</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.1794806929508048</v>
+        <v>0.1794808032758544</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>-0.05073765883132797</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.082449160462294</v>
+        <v>-0.08244924336347392</v>
       </c>
       <c r="G20" s="11" t="n">
         <v>-0.08635160306540612</v>
@@ -2620,7 +2620,7 @@
         <v>-0.02275381246463382</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.004162036248914869</v>
+        <v>-0.004162134623879599</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>0.003198412176470988</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009142235324292258</v>
+        <v>0.009142312679250919</v>
       </c>
       <c r="G26" s="11" t="n">
         <v>0.01824849960638542</v>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -767,25 +767,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.3947382504755879</v>
+        <v>0.3953136956198833</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1638017964459786</v>
+        <v>0.1703018458913388</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1541614263711546</v>
+        <v>0.1649019288480766</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1794808032758544</v>
+        <v>0.1818481282857911</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.02698218328050483</v>
+        <v>0.03884401066055787</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.008352705136867034</v>
+        <v>0.004635512148736698</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.007395384756345047</v>
+        <v>0.006743412504547575</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.1609548690014375</v>
+        <v>0.1609549765152376</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>3</v>
@@ -810,7 +810,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512062651334</v>
+        <v>0.3464512421129409</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -819,14 +819,14 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="V2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>0.3463971385980751</v>
+        <v>0.3474627273104928</v>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>1</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>0.3464512062651334</v>
+        <v>0.3464512421129409</v>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.3463971385980751</v>
+        <v>0.3463971132196927</v>
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
@@ -895,14 +895,14 @@
         <v>1</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>-0.01423511612681194</v>
+        <v>-0.01423489805802292</v>
       </c>
       <c r="AQ2" s="3" t="n">
         <v>0.02285226703064946</v>
       </c>
       <c r="AR2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +0.8%, 3m +2.7%, 6m +17.9%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +0.5%, 3m +3.9%, 6m +18.2%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AS2" s="2" t="inlineStr">
@@ -936,25 +936,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5968304292193729</v>
+        <v>0.5992608094372363</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2484074821182936</v>
+        <v>0.2542767731365188</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1799925915425706</v>
+        <v>0.1891295673283566</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.2841220233493729</v>
+        <v>0.2877142911189192</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.03810222147521181</v>
+        <v>0.06703687284820825</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.05797908484008873</v>
+        <v>0.05478562437441514</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.0101747907766534</v>
+        <v>0.008831612369593733</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.1982246540542743</v>
+        <v>0.1982245316673374</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>2</v>
@@ -979,7 +979,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095554429965</v>
+        <v>0.3583095181980359</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -988,14 +988,14 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="V3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.3542858464150614</v>
+        <v>0.354763034601805</v>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>1</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>0.3583095554429965</v>
+        <v>0.3583095181980359</v>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.3542858464150614</v>
+        <v>0.3542858937225558</v>
       </c>
       <c r="AF3" s="2" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AK3" s="2" t="n"/>
       <c r="AL3" s="3" t="n">
-        <v>0.1799925915425706</v>
+        <v>0.1799928314412171</v>
       </c>
       <c r="AM3" s="2" t="n">
         <v>2</v>
@@ -1064,14 +1064,14 @@
         <v>1</v>
       </c>
       <c r="AP3" s="3" t="n">
-        <v>-0.01773998898777007</v>
+        <v>-0.01773974908912357</v>
       </c>
       <c r="AQ3" s="3" t="n">
         <v>0.02285226703064946</v>
       </c>
       <c r="AR3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +5.8%, 3m +3.8%, 6m +28.4%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +5.5%, 3m +6.7%, 6m +28.8%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AS3" s="2" t="inlineStr">
@@ -1105,25 +1105,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.09395916863225517</v>
+        <v>-0.09769403099767038</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.09201511289545661</v>
+        <v>-0.09897476331544308</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.04348371601185663</v>
+        <v>-0.04486427025709272</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.08635160306540612</v>
+        <v>-0.08924560580034058</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.08244924336347392</v>
+        <v>-0.07711060626381039</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.05073765883132797</v>
+        <v>-0.05665215044663363</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.002959722043494928</v>
+        <v>-0.004775425916365594</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.038029469654283</v>
+        <v>-0.03802938342376228</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="V4" t="b">
@@ -1232,14 +1232,14 @@
         <v>0</v>
       </c>
       <c r="AP4" s="4" t="n">
-        <v>-0.01880323962727048</v>
+        <v>-0.01880332743758484</v>
       </c>
       <c r="AQ4" s="4" t="n">
         <v>0.02285226703064946</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -5.1%, 3m -8.2%, 6m -8.6%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -5.7%, 3m -7.7%, 6m -8.9%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1273,25 +1273,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3219042320130752</v>
+        <v>0.3171501943364796</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.06771901244277179</v>
+        <v>0.0697877617745708</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.1313091593405051</v>
+        <v>0.1562332647481608</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1147388276938125</v>
+        <v>-0.1124751549164035</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>-0.005207651846230399</v>
+        <v>0.005457098201276933</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.05620934505188935</v>
+        <v>-0.07476476037248314</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.006845020378304922</v>
+        <v>-0.001552059767453984</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="V5" t="b">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -5.6%, 3m -0.5%, 6m -11.5%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -7.5%, 3m +0.5%, 6m -11.2%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1441,25 +1441,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.06715301444778499</v>
+        <v>0.06595697734355821</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.007531479626482041</v>
+        <v>0.0088224749822301</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03176125469305457</v>
+        <v>0.03344858644739368</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.004162134623879599</v>
+        <v>-0.00500664267706441</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.02275381246463382</v>
+        <v>-0.02051537688645932</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.02348389703176146</v>
+        <v>-0.02382906299172449</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.0001300390117033867</v>
+        <v>0.0009101547263035137</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715185591311232</v>
+        <v>0.03715206361910939</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1493,31 +1493,31 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="V6" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="Y6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="V6" t="b">
-        <v>0</v>
-      </c>
-      <c r="W6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="Y6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
       <c r="AB6" t="inlineStr">
         <is>
           <t>2026-09-25</t>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="AL6" s="4" t="n">
-        <v>0.03176125469305457</v>
+        <v>0.031761151572542</v>
       </c>
       <c r="AM6" t="n">
         <v>6</v>
@@ -1568,14 +1568,14 @@
         <v>0</v>
       </c>
       <c r="AP6" s="4" t="n">
-        <v>-0.007071974879857335</v>
+        <v>-0.007072182072990651</v>
       </c>
       <c r="AQ6" s="4" t="n">
         <v>0.02285226703064946</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -2.3%, 3m -2.3%, 6m -0.4%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -2.4%, 3m -2.1%, 6m -0.5%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1609,25 +1609,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.3977143698134384</v>
+        <v>0.4096321017457492</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.4464096070240571</v>
+        <v>0.4757820091422109</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4900490316102593</v>
+        <v>0.49411389830913</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.07424705021970102</v>
+        <v>0.0772026705768063</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1894109920063194</v>
+        <v>0.1681396571831968</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-0.02928724066149824</v>
+        <v>-0.01226940542328459</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.00191387559808609</v>
+        <v>0.01002865329512903</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1652,7 +1652,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392382918702</v>
+        <v>0.2952392396890233</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1661,14 +1661,14 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="V7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.2993170149868635</v>
+        <v>0.2977742380877021</v>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>1</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.2952392382918702</v>
+        <v>0.2952392396890233</v>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.2993170149868635</v>
+        <v>0.2993169930577514</v>
       </c>
       <c r="AF7" s="2" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AR7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -2.9%, 3m +18.9%, 6m +7.4%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.2%, 3m +16.8%, 6m +7.7%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AS7" s="2" t="inlineStr">
@@ -1778,25 +1778,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.002521421492105214</v>
+        <v>0.002813217687533065</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02292483087077402</v>
+        <v>-0.02370597971287303</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.002883993594746892</v>
+        <v>0.004649549631877026</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02833390943374015</v>
+        <v>-0.02910914227374917</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.033330928240068</v>
+        <v>-0.03168188826679674</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.02573460602657685</v>
+        <v>-0.02822429906542057</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.001917361710286669</v>
+        <v>-0.001248679281529164</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.004296555684699666</v>
+        <v>0.004296483646738736</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
@@ -1830,31 +1830,31 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="V8" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="Y8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="V8" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="Y8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
       <c r="AB8" t="inlineStr">
         <is>
           <t>2026-09-25</t>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="AL8" s="4" t="n">
-        <v>0.002883993594746892</v>
+        <v>0.002884065403325309</v>
       </c>
       <c r="AM8" t="n">
         <v>7</v>
@@ -1905,14 +1905,14 @@
         <v>0</v>
       </c>
       <c r="AP8" s="4" t="n">
-        <v>-0.007445564518826053</v>
+        <v>-0.007445347833971105</v>
       </c>
       <c r="AQ8" s="4" t="n">
         <v>0.02285226703064946</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -2.6%, 3m -3.3%, 6m -2.8%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -2.8%, 3m -3.2%, 6m -2.9%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1946,25 +1946,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.04573559861517773</v>
+        <v>0.05378139560531237</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.08642417528787938</v>
+        <v>0.08860134145546716</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.05934818338039349</v>
+        <v>0.05180143408650029</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.03697056712132096</v>
+        <v>0.04168163851958329</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.02012711864406791</v>
+        <v>0.02077464788732386</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.02555910543130979</v>
+        <v>0.03498750446269172</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.002417127071823177</v>
+        <v>0.00346140533056416</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="V9" t="b">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +2.6%, 3m +2.0%, 6m +3.7%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +3.5%, 3m +2.1%, 6m +4.2%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -2112,25 +2112,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.06008288615119062</v>
+        <v>0.06008268949635265</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03786890845253477</v>
+        <v>0.03786884310904792</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03455995928147937</v>
+        <v>0.03455998713970621</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01824849960638542</v>
+        <v>0.01824846062488472</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009142312679250919</v>
+        <v>0.00904180292197676</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003198412176470988</v>
+        <v>0.003198322002081033</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0002987750224081598</v>
+        <v>9.956192751903181e-05</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="V10" s="5" t="b">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>QQQ 35.4%, SPY 34.6%, XLE 29.9%</t>
+          <t>QQQ 35.5%, SPY 34.7%, XLE 29.8%</t>
         </is>
       </c>
     </row>
@@ -2478,13 +2478,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.008352705136867034</v>
+        <v>0.004635512148736698</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.02698218328050483</v>
+        <v>0.03884401066055787</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.1794808032758544</v>
+        <v>0.1818481282857911</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2512,13 +2512,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.05797908484008873</v>
+        <v>0.05478562437441514</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.03810222147521181</v>
+        <v>0.06703687284820825</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.2841220233493729</v>
+        <v>0.2877142911189192</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2546,13 +2546,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.05073765883132797</v>
+        <v>-0.05665215044663363</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.08244924336347392</v>
+        <v>-0.07711060626381039</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.08635160306540612</v>
+        <v>-0.08924560580034058</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.05620934505188935</v>
+        <v>-0.07476476037248314</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-0.005207651846230399</v>
+        <v>0.005457098201276933</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1147388276938125</v>
+        <v>-0.1124751549164035</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2614,13 +2614,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.02348389703176146</v>
+        <v>-0.02382906299172449</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.02275381246463382</v>
+        <v>-0.02051537688645932</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.004162134623879599</v>
+        <v>-0.00500664267706441</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2648,13 +2648,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>-0.02928724066149824</v>
+        <v>-0.01226940542328459</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1894109920063194</v>
+        <v>0.1681396571831968</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.07424705021970102</v>
+        <v>0.0772026705768063</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2682,13 +2682,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.02573460602657685</v>
+        <v>-0.02822429906542057</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.033330928240068</v>
+        <v>-0.03168188826679674</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.02833390943374015</v>
+        <v>-0.02910914227374917</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -2716,13 +2716,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.02555910543130979</v>
+        <v>0.03498750446269172</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.02012711864406791</v>
+        <v>0.02077464788732386</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.03697056712132096</v>
+        <v>0.04168163851958329</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -2750,13 +2750,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003198412176470988</v>
+        <v>0.003198322002081033</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009142312679250919</v>
+        <v>0.00904180292197676</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01824849960638542</v>
+        <v>0.01824846062488472</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.02933603803237417</v>
+        <v>0.02933625610116319</v>
       </c>
     </row>
     <row r="3">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -776,7 +776,7 @@
         <v>0.1649019288480766</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1818481282857911</v>
+        <v>0.1818480182593816</v>
       </c>
       <c r="J2" s="3" t="n">
         <v>0.03884401066055787</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.1609549765152376</v>
+        <v>0.1609548690014375</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>3</v>
@@ -810,7 +810,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512421129409</v>
+        <v>0.3464512062651334</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>1</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>0.3474627273104928</v>
+        <v>0.3474627399143715</v>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>1</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>0.3464512421129409</v>
+        <v>0.3464512062651334</v>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>-0.01423489805802292</v>
+        <v>-0.01423500709240733</v>
       </c>
       <c r="AQ2" s="3" t="n">
         <v>0.02285226703064946</v>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5992608094372363</v>
+        <v>0.5992607062200634</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2542767731365188</v>
+        <v>0.2542766461580404</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1891295673283566</v>
+        <v>0.1891294469451474</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>0.2877142911189192</v>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.1982245316673374</v>
+        <v>0.1982246540542743</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>2</v>
@@ -979,7 +979,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095181980359</v>
+        <v>0.3583095554429965</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>1</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.354763034601805</v>
+        <v>0.3547630111964502</v>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>1</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>0.3583095181980359</v>
+        <v>0.3583095554429965</v>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>1</v>
       </c>
       <c r="AP3" s="3" t="n">
-        <v>-0.01773974908912357</v>
+        <v>-0.01773987230214424</v>
       </c>
       <c r="AQ3" s="3" t="n">
         <v>0.02285226703064946</v>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.09769403099767038</v>
+        <v>-0.09769386988967155</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>-0.09897476331544308</v>
@@ -1114,7 +1114,7 @@
         <v>-0.04486427025709272</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.08924560580034058</v>
+        <v>-0.0892455237308093</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>-0.07711060626381039</v>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.03802938342376228</v>
+        <v>-0.03802955588478829</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -1232,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="AP4" s="4" t="n">
-        <v>-0.01880332743758484</v>
+        <v>-0.01880323962727048</v>
       </c>
       <c r="AQ4" s="4" t="n">
         <v>0.02285226703064946</v>
@@ -1441,16 +1441,16 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.06595697734355821</v>
+        <v>0.06595720257116189</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.0088224749822301</v>
+        <v>0.008822374116968401</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03344858644739368</v>
+        <v>0.03344848311993531</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.00500664267706441</v>
+        <v>-0.005006544558182835</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>-0.02051537688645932</v>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="AL6" s="4" t="n">
-        <v>0.031761151572542</v>
+        <v>0.03176125469305457</v>
       </c>
       <c r="AM6" t="n">
         <v>6</v>
@@ -1568,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="AP6" s="4" t="n">
-        <v>-0.007072182072990651</v>
+        <v>-0.007072183025119472</v>
       </c>
       <c r="AQ6" s="4" t="n">
         <v>0.02285226703064946</v>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.4096321017457492</v>
+        <v>0.4096319822682493</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.4757820091422109</v>
@@ -1652,7 +1652,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392396890233</v>
+        <v>0.2952392382918702</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>1</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.2977742380877021</v>
+        <v>0.2977742488891784</v>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>1</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.2952392396890233</v>
+        <v>0.2952392382918702</v>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>0.004649549631877026</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02910914227374917</v>
+        <v>-0.02910921143789935</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>-0.03168188826679674</v>
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="AP8" s="4" t="n">
-        <v>-0.007445347833971105</v>
+        <v>-0.007445420272104153</v>
       </c>
       <c r="AQ8" s="4" t="n">
         <v>0.02285226703064946</v>
@@ -2121,10 +2121,10 @@
         <v>0.03455998713970621</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01824846062488472</v>
+        <v>0.0182485393743621</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.00904180292197676</v>
+        <v>0.009041880253842338</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>0.003198322002081033</v>
@@ -2484,7 +2484,7 @@
         <v>0.03884401066055787</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.1818481282857911</v>
+        <v>0.1818480182593816</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>-0.07711060626381039</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.08924560580034058</v>
+        <v>-0.0892455237308093</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>-0.02051537688645932</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.00500664267706441</v>
+        <v>-0.005006544558182835</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>-0.03168188826679674</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.02910914227374917</v>
+        <v>-0.02910921143789935</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -2753,10 +2753,10 @@
         <v>0.003198322002081033</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.00904180292197676</v>
+        <v>0.009041880253842338</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01824846062488472</v>
+        <v>0.0182485393743621</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.02933625610116319</v>
+        <v>0.02933627027979946</v>
       </c>
     </row>
     <row r="3">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -767,25 +767,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.3953136956198833</v>
+        <v>0.4757091163598373</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1703018458913388</v>
+        <v>0.1767536980010154</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1649019288480766</v>
+        <v>0.1604294091184051</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1818480182593816</v>
+        <v>0.1878231419881153</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.03884401066055787</v>
+        <v>0.04779261808456403</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.004635512148736698</v>
+        <v>0.01406745533535902</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.006743412504547575</v>
+        <v>0.005497980202108899</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -810,7 +810,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512062651334</v>
+        <v>0.3464512030450774</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -819,14 +819,14 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="V2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>0.3474627399143715</v>
+        <v>0.3463251219374191</v>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>1</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>0.3464512062651334</v>
+        <v>0.3464512030450774</v>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.3463971132196927</v>
+        <v>0.3463971100868694</v>
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
@@ -895,14 +895,14 @@
         <v>1</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>-0.01423500709240733</v>
+        <v>-0.01423489805802292</v>
       </c>
       <c r="AQ2" s="3" t="n">
         <v>0.02285226703064946</v>
       </c>
       <c r="AR2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +0.5%, 3m +3.9%, 6m +18.2%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +1.4%, 3m +4.8%, 6m +18.8%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AS2" s="2" t="inlineStr">
@@ -936,25 +936,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5992607062200634</v>
+        <v>0.6974488481593779</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2542766461580404</v>
+        <v>0.2653424833531151</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1891294469451474</v>
+        <v>0.1963031263825441</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.2877142911189192</v>
+        <v>0.2934084165831239</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.06703687284820825</v>
+        <v>0.06889063841010645</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.05478562437441514</v>
+        <v>0.05771058810097451</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.008831612369593733</v>
+        <v>0.004575509124570054</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -979,7 +979,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095554429965</v>
+        <v>0.358309549312061</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -988,14 +988,14 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="V3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.3547630111964502</v>
+        <v>0.3575505523661724</v>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>1</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>0.3583095554429965</v>
+        <v>0.358309549312061</v>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.3542858937225558</v>
+        <v>0.3542858886979251</v>
       </c>
       <c r="AF3" s="2" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
         <v>1</v>
       </c>
       <c r="AP3" s="3" t="n">
-        <v>-0.01773987230214424</v>
+        <v>-0.01773974908912357</v>
       </c>
       <c r="AQ3" s="3" t="n">
         <v>0.02285226703064946</v>
       </c>
       <c r="AR3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +5.5%, 3m +6.7%, 6m +28.8%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +5.8%, 3m +6.9%, 6m +29.3%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AS3" s="2" t="inlineStr">
@@ -1105,25 +1105,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.09769386988967155</v>
+        <v>-0.0998398349157541</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.09897476331544308</v>
+        <v>-0.09527082059741276</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.04486427025709272</v>
+        <v>-0.04141523517561818</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.0892455237308093</v>
+        <v>-0.08713220072417915</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.07711060626381039</v>
+        <v>-0.07299282634314253</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.05665215044663363</v>
+        <v>-0.05618239241645073</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.004775425916365594</v>
+        <v>0.00220464271819476</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.03802955588478829</v>
+        <v>-0.03802938342376228</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="V4" t="b">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -5.7%, 3m -7.7%, 6m -8.9%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -5.6%, 3m -7.3%, 6m -8.7%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1273,25 +1273,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3171501943364796</v>
+        <v>0.3346484184065357</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.0697877617745708</v>
+        <v>0.06886813555530691</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.1562332647481608</v>
+        <v>0.1373727770942847</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1124751549164035</v>
+        <v>-0.1147263842893865</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.005457098201276933</v>
+        <v>0.02088396314594743</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.07476476037248314</v>
+        <v>-0.06023059714334877</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.001552059767453984</v>
+        <v>0.007166381240943043</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="V5" t="b">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -7.5%, 3m +0.5%, 6m -11.2%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -6.0%, 3m +2.1%, 6m -11.5%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1441,25 +1441,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.06595720257116189</v>
+        <v>0.08343844158707925</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.008822374116968401</v>
+        <v>0.01375027838253562</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03344848311993531</v>
+        <v>0.03394605049000199</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.005006544558182835</v>
+        <v>-0.001508729897291117</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.02051537688645932</v>
+        <v>-0.01559115258730304</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.02382906299172449</v>
+        <v>-0.01953271362456033</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.0009101547263035137</v>
+        <v>0.003767212262925312</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715206361910939</v>
+        <v>0.0371520673392467</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="V6" t="b">
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="AL6" s="4" t="n">
-        <v>0.03176125469305457</v>
+        <v>0.031761151572542</v>
       </c>
       <c r="AM6" t="n">
         <v>6</v>
@@ -1568,14 +1568,14 @@
         <v>0</v>
       </c>
       <c r="AP6" s="4" t="n">
-        <v>-0.007072183025119472</v>
+        <v>-0.007072081890769244</v>
       </c>
       <c r="AQ6" s="4" t="n">
         <v>0.02285226703064946</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -2.4%, 3m -2.1%, 6m -0.5%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -2.0%, 3m -1.6%, 6m -0.2%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1609,25 +1609,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.4096319822682493</v>
+        <v>0.5371246910009411</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.4757820091422109</v>
+        <v>0.4747555024921795</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.49411389830913</v>
+        <v>0.4731702896601759</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.0772026705768063</v>
+        <v>0.07366047867035697</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1681396571831968</v>
+        <v>0.1533980925338752</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-0.01226940542328459</v>
+        <v>0.001076055390968556</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.01002865329512903</v>
+        <v>0.004728132387706863</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.4639559345596878</v>
+        <v>0.4639560631420809</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>1</v>
@@ -1652,7 +1652,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392382918702</v>
+        <v>0.2952392476428616</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1661,14 +1661,14 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="V7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.2977742488891784</v>
+        <v>0.2961243256964085</v>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>1</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.2952392382918702</v>
+        <v>0.2952392476428616</v>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.2993169930577514</v>
+        <v>0.2993170012152055</v>
       </c>
       <c r="AF7" s="2" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="AK7" s="2" t="n"/>
       <c r="AL7" s="3" t="n">
-        <v>0.4900490316102593</v>
+        <v>0.4900491624844652</v>
       </c>
       <c r="AM7" s="2" t="n">
         <v>1</v>
@@ -1737,14 +1737,14 @@
         <v>0</v>
       </c>
       <c r="AP7" s="3" t="n">
-        <v>0.07693005509613382</v>
+        <v>0.07693018597033974</v>
       </c>
       <c r="AQ7" s="3" t="n">
         <v>0.02285226703064946</v>
       </c>
       <c r="AR7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.2%, 3m +16.8%, 6m +7.7%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +0.1%, 3m +15.3%, 6m +7.4%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AS7" s="2" t="inlineStr">
@@ -1778,25 +1778,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.002813217687533065</v>
+        <v>-0.001505293291364285</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02370597971287303</v>
+        <v>-0.02077119203782429</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.004649549631877026</v>
+        <v>0.005453115643251349</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02910921143789935</v>
+        <v>-0.02838211140453972</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.03168188826679674</v>
+        <v>-0.02874186113479105</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.02822429906542057</v>
+        <v>-0.02608207908759463</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.001248679281529164</v>
+        <v>0.00192344681669554</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="V8" t="b">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="AL8" s="4" t="n">
-        <v>0.002884065403325309</v>
+        <v>0.002883993594746892</v>
       </c>
       <c r="AM8" t="n">
         <v>7</v>
@@ -1905,14 +1905,14 @@
         <v>0</v>
       </c>
       <c r="AP8" s="4" t="n">
-        <v>-0.007445420272104153</v>
+        <v>-0.00744549208068257</v>
       </c>
       <c r="AQ8" s="4" t="n">
         <v>0.02285226703064946</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -2.8%, 3m -3.2%, 6m -2.9%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -2.6%, 3m -2.9%, 6m -2.8%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1946,25 +1946,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.05378139560531237</v>
+        <v>0.06930259084147483</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.08860134145546716</v>
+        <v>0.08719558611885803</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.05180143408650029</v>
+        <v>0.05634782208365174</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.04168163851958329</v>
+        <v>0.04144144144144146</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.02077464788732386</v>
+        <v>0.01904090267983061</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.03498750446269172</v>
+        <v>0.02920227920227925</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.00346140533056416</v>
+        <v>-0.003104518799586065</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="V9" t="b">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +3.5%, 3m +2.1%, 6m +4.2%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +2.9%, 3m +1.9%, 6m +4.1%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -2112,25 +2112,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.06008268949635265</v>
+        <v>0.05997695940184089</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03786884310904792</v>
+        <v>0.03755864897730188</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03455998713970621</v>
+        <v>0.03455969281444959</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.0182485393743621</v>
+        <v>0.01824842305460916</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009041880253842338</v>
+        <v>0.009041822437674263</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003198322002081033</v>
+        <v>0.002898775376309004</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>9.956192751903181e-05</v>
+        <v>9.955201592815044e-05</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="V10" s="5" t="b">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>QQQ 35.5%, SPY 34.7%, XLE 29.8%</t>
+          <t>QQQ 35.8%, SPY 34.6%, XLE 29.6%</t>
         </is>
       </c>
     </row>
@@ -2478,13 +2478,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.004635512148736698</v>
+        <v>0.01406745533535902</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.03884401066055787</v>
+        <v>0.04779261808456403</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.1818480182593816</v>
+        <v>0.1878231419881153</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2512,13 +2512,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.05478562437441514</v>
+        <v>0.05771058810097451</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.06703687284820825</v>
+        <v>0.06889063841010645</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.2877142911189192</v>
+        <v>0.2934084165831239</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2546,13 +2546,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.05665215044663363</v>
+        <v>-0.05618239241645073</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.07711060626381039</v>
+        <v>-0.07299282634314253</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.0892455237308093</v>
+        <v>-0.08713220072417915</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.07476476037248314</v>
+        <v>-0.06023059714334877</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.005457098201276933</v>
+        <v>0.02088396314594743</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1124751549164035</v>
+        <v>-0.1147263842893865</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2614,13 +2614,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.02382906299172449</v>
+        <v>-0.01953271362456033</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.02051537688645932</v>
+        <v>-0.01559115258730304</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.005006544558182835</v>
+        <v>-0.001508729897291117</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2648,13 +2648,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>-0.01226940542328459</v>
+        <v>0.001076055390968556</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1681396571831968</v>
+        <v>0.1533980925338752</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.0772026705768063</v>
+        <v>0.07366047867035697</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2682,13 +2682,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.02822429906542057</v>
+        <v>-0.02608207908759463</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.03168188826679674</v>
+        <v>-0.02874186113479105</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.02910921143789935</v>
+        <v>-0.02838211140453972</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -2716,13 +2716,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.03498750446269172</v>
+        <v>0.02920227920227925</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.02077464788732386</v>
+        <v>0.01904090267983061</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.04168163851958329</v>
+        <v>0.04144144144144146</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -2750,13 +2750,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003198322002081033</v>
+        <v>0.002898775376309004</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009041880253842338</v>
+        <v>0.009041822437674263</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.0182485393743621</v>
+        <v>0.01824842305460916</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.02933627027979946</v>
+        <v>0.02933625610116319</v>
       </c>
     </row>
     <row r="3">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4757091163598373</v>
+        <v>0.4757089457539982</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0.1767536980010154</v>
@@ -810,7 +810,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512030450774</v>
+        <v>0.3464512062651334</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>1</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>0.3463251219374191</v>
+        <v>0.346325118766038</v>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>1</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>0.3464512030450774</v>
+        <v>0.3464512062651334</v>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.3463971100868694</v>
+        <v>0.3463971132196927</v>
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>-0.01423489805802292</v>
+        <v>-0.01423511612681194</v>
       </c>
       <c r="AQ2" s="3" t="n">
         <v>0.02285226703064946</v>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.6974488481593779</v>
+        <v>0.6974487324085343</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0.2653424833531151</v>
@@ -979,7 +979,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.358309549312061</v>
+        <v>0.3583095554429965</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>1</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.3575505523661724</v>
+        <v>0.3575505464545898</v>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>1</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>0.358309549312061</v>
+        <v>0.3583095554429965</v>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.3542858886979251</v>
+        <v>0.3542858937225558</v>
       </c>
       <c r="AF3" s="2" t="inlineStr">
         <is>
@@ -1105,16 +1105,16 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.0998398349157541</v>
+        <v>-0.09983959493085304</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.09527082059741276</v>
+        <v>-0.09527073978832434</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.04141523517561818</v>
+        <v>-0.0414151495562276</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.08713220072417915</v>
+        <v>-0.08713228299364917</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>-0.07299282634314253</v>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.03802938342376228</v>
+        <v>-0.03802955588478829</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -1441,19 +1441,19 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.08343844158707925</v>
+        <v>0.08343867338936617</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01375027838253562</v>
+        <v>0.01375017691172942</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03394605049000199</v>
+        <v>0.03394594699771059</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>-0.001508729897291117</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01559115258730304</v>
+        <v>-0.0155912482692746</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>-0.01953271362456033</v>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.0371520673392467</v>
+        <v>0.03715185963322809</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="AL6" s="4" t="n">
-        <v>0.031761151572542</v>
+        <v>0.0317613578135878</v>
       </c>
       <c r="AM6" t="n">
         <v>6</v>
@@ -1568,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="AP6" s="4" t="n">
-        <v>-0.007072081890769244</v>
+        <v>-0.007071979722355071</v>
       </c>
       <c r="AQ6" s="4" t="n">
         <v>0.02285226703064946</v>
@@ -1612,10 +1612,10 @@
         <v>0.5371246910009411</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.4747555024921795</v>
+        <v>0.4747556326495612</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4731702896601759</v>
+        <v>0.4731704196776516</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0.07366047867035697</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.4639560631420809</v>
+        <v>0.4639559345596878</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>1</v>
@@ -1652,7 +1652,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392476428616</v>
+        <v>0.2952392382918702</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>1</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.2961243256964085</v>
+        <v>0.2961243347793723</v>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>1</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.2952392476428616</v>
+        <v>0.2952392382918702</v>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.2993170012152055</v>
+        <v>0.2993169930577514</v>
       </c>
       <c r="AF7" s="2" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="AK7" s="2" t="n"/>
       <c r="AL7" s="3" t="n">
-        <v>0.4900491624844652</v>
+        <v>0.4900490316102593</v>
       </c>
       <c r="AM7" s="2" t="n">
         <v>1</v>
@@ -1737,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="AP7" s="3" t="n">
-        <v>0.07693018597033974</v>
+        <v>0.07693005509613382</v>
       </c>
       <c r="AQ7" s="3" t="n">
         <v>0.02285226703064946</v>
@@ -1781,13 +1781,13 @@
         <v>-0.001505293291364285</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02077119203782429</v>
+        <v>-0.02077112181567742</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.005453115643251349</v>
+        <v>0.005453187745987575</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02838211140453972</v>
+        <v>-0.02838204226973218</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>-0.02874186113479105</v>
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="AP8" s="4" t="n">
-        <v>-0.00744549208068257</v>
+        <v>-0.007445636956979973</v>
       </c>
       <c r="AQ8" s="4" t="n">
         <v>0.02285226703064946</v>
@@ -2115,13 +2115,13 @@
         <v>0.05997695940184089</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03755864897730188</v>
+        <v>0.03755881249030013</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03455969281444959</v>
+        <v>0.03455985585483035</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01824842305460916</v>
+        <v>0.01824850179624615</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>0.009041822437674263</v>
@@ -2552,7 +2552,7 @@
         <v>-0.07299282634314253</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.08713220072417915</v>
+        <v>-0.08713228299364917</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>-0.01953271362456033</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01559115258730304</v>
+        <v>-0.0155912482692746</v>
       </c>
       <c r="G22" s="11" t="n">
         <v>-0.001508729897291117</v>
@@ -2688,7 +2688,7 @@
         <v>-0.02874186113479105</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.02838211140453972</v>
+        <v>-0.02838204226973218</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>0.009041822437674263</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01824842305460916</v>
+        <v>0.01824850179624615</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.02933625610116319</v>
+        <v>0.02933603803237417</v>
       </c>
     </row>
     <row r="3">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Weekly History" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Survivor'!$A$1:$AS$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Survivor'!$A$1:$AY$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Weekly Review'!$A$17:$H$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Weekly History'!$A$1:$G$3</definedName>
   </definedNames>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS10"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -513,6 +513,12 @@
     <col width="22" customWidth="1" min="43" max="43"/>
     <col width="70" customWidth="1" min="44" max="44"/>
     <col width="70" customWidth="1" min="45" max="45"/>
+    <col width="22" customWidth="1" min="46" max="46"/>
+    <col width="22" customWidth="1" min="47" max="47"/>
+    <col width="22" customWidth="1" min="48" max="48"/>
+    <col width="26" customWidth="1" min="49" max="49"/>
+    <col width="22" customWidth="1" min="50" max="50"/>
+    <col width="42" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -741,6 +747,36 @@
           <t>HIL Summary</t>
         </is>
       </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>Live Last</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Live Previous Close</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Live Day %</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Live Quote Time</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Live Quote Delayed</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Live Quote Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -767,7 +803,7 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4757089457539982</v>
+        <v>0.4757091163598373</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0.1767536980010154</v>
@@ -801,7 +837,7 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.1609548690014375</v>
+        <v>0.1609549765152376</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>3</v>
@@ -810,7 +846,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512062651334</v>
+        <v>0.3464512254018678</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -826,7 +862,7 @@
         <v>1</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>0.346325118766038</v>
+        <v>0.3463251219374191</v>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
@@ -837,7 +873,7 @@
         <v>1</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>0.3464512062651334</v>
+        <v>0.3464512254018678</v>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
@@ -856,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.3463971132196927</v>
+        <v>0.3463971100868694</v>
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
@@ -895,7 +931,7 @@
         <v>1</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>-0.01423511612681194</v>
+        <v>-0.01423500709240733</v>
       </c>
       <c r="AQ2" s="3" t="n">
         <v>0.02285226703064946</v>
@@ -908,6 +944,26 @@
       <c r="AS2" s="2" t="inlineStr">
         <is>
           <t>No weekly membership exception; retain monthly authority.</t>
+        </is>
+      </c>
+      <c r="AT2" s="2" t="n">
+        <v>776.64</v>
+      </c>
+      <c r="AU2" s="2" t="n">
+        <v>779.09003</v>
+      </c>
+      <c r="AV2" s="3" t="n">
+        <v>-0.003144732836588782</v>
+      </c>
+      <c r="AW2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:30:03Z</t>
+        </is>
+      </c>
+      <c r="AX2" s="2" t="n"/>
+      <c r="AY2" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -979,7 +1035,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095554429965</v>
+        <v>0.358309537054902</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -995,7 +1051,7 @@
         <v>1</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.3575505464545898</v>
+        <v>0.3575505523661724</v>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
@@ -1006,7 +1062,7 @@
         <v>1</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>0.3583095554429965</v>
+        <v>0.358309537054902</v>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
@@ -1025,7 +1081,7 @@
         <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.3542858937225558</v>
+        <v>0.3542858886979251</v>
       </c>
       <c r="AF3" s="2" t="inlineStr">
         <is>
@@ -1079,6 +1135,26 @@
           <t>No weekly membership exception; retain monthly authority.</t>
         </is>
       </c>
+      <c r="AT3" s="2" t="n">
+        <v>756.11</v>
+      </c>
+      <c r="AU3" s="2" t="n">
+        <v>759.65997</v>
+      </c>
+      <c r="AV3" s="3" t="n">
+        <v>-0.004673103941491119</v>
+      </c>
+      <c r="AW3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:30:04Z</t>
+        </is>
+      </c>
+      <c r="AX3" s="2" t="n"/>
+      <c r="AY3" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1105,13 +1181,13 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.09983959493085304</v>
+        <v>-0.09983975492080122</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.09527073978832434</v>
+        <v>-0.09527082059741276</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.0414151495562276</v>
+        <v>-0.04141523517561818</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>-0.08713228299364917</v>
@@ -1139,7 +1215,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.03802955588478829</v>
+        <v>-0.038029469654283</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -1232,7 +1308,7 @@
         <v>0</v>
       </c>
       <c r="AP4" s="4" t="n">
-        <v>-0.01880323962727048</v>
+        <v>-0.01880297619642213</v>
       </c>
       <c r="AQ4" s="4" t="n">
         <v>0.02285226703064946</v>
@@ -1245,6 +1321,25 @@
       <c r="AS4" t="inlineStr">
         <is>
           <t>No weekly membership exception; retain monthly authority.</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>76.875</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>77.28</v>
+      </c>
+      <c r="AV4" s="4" t="n">
+        <v>-0.005240683229813636</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:30:03Z</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1415,6 +1510,25 @@
           <t>No weekly membership exception; retain monthly authority.</t>
         </is>
       </c>
+      <c r="AT5" t="n">
+        <v>377.14</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>382.26999</v>
+      </c>
+      <c r="AV5" s="4" t="n">
+        <v>-0.01341980834017342</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:30:01Z</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1444,16 +1558,16 @@
         <v>0.08343867338936617</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01375017691172942</v>
+        <v>0.01375007544094364</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03394594699771059</v>
+        <v>0.03394584350543983</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.001508729897291117</v>
+        <v>-0.001508828336396206</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.0155912482692746</v>
+        <v>-0.01559115258730304</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>-0.01953271362456033</v>
@@ -1475,7 +1589,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715185963322809</v>
+        <v>0.03715206361910939</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1568,7 +1682,7 @@
         <v>0</v>
       </c>
       <c r="AP6" s="4" t="n">
-        <v>-0.007071979722355071</v>
+        <v>-0.007071975831944854</v>
       </c>
       <c r="AQ6" s="4" t="n">
         <v>0.02285226703064946</v>
@@ -1581,6 +1695,25 @@
       <c r="AS6" t="inlineStr">
         <is>
           <t>No weekly membership exception; retain monthly authority.</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>77.14</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>77.27</v>
+      </c>
+      <c r="AV6" s="4" t="n">
+        <v>-0.001682412320434756</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:30:02Z</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1609,13 +1742,13 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.5371246910009411</v>
+        <v>0.5371248323842484</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.4747556326495612</v>
+        <v>0.4747555024921795</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4731704196776516</v>
+        <v>0.4731702896601759</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0.07366047867035697</v>
@@ -1643,7 +1776,7 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.4639559345596878</v>
+        <v>0.4639560631420809</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>1</v>
@@ -1652,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392382918702</v>
+        <v>0.2952392375432301</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1668,7 +1801,7 @@
         <v>1</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.2961243347793723</v>
+        <v>0.2961243256964085</v>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
@@ -1679,7 +1812,7 @@
         <v>1</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.2952392382918702</v>
+        <v>0.2952392375432301</v>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
@@ -1698,7 +1831,7 @@
         <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.2993169930577514</v>
+        <v>0.2993170012152055</v>
       </c>
       <c r="AF7" s="2" t="inlineStr">
         <is>
@@ -1725,7 +1858,7 @@
       </c>
       <c r="AK7" s="2" t="n"/>
       <c r="AL7" s="3" t="n">
-        <v>0.4900490316102593</v>
+        <v>0.4900491624844652</v>
       </c>
       <c r="AM7" s="2" t="n">
         <v>1</v>
@@ -1737,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="AP7" s="3" t="n">
-        <v>0.07693005509613382</v>
+        <v>0.07693018597033974</v>
       </c>
       <c r="AQ7" s="3" t="n">
         <v>0.02285226703064946</v>
@@ -1750,6 +1883,26 @@
       <c r="AS7" s="2" t="inlineStr">
         <is>
           <t>No weekly membership exception; retain monthly authority.</t>
+        </is>
+      </c>
+      <c r="AT7" s="2" t="n">
+        <v>63.155</v>
+      </c>
+      <c r="AU7" s="2" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="AV7" s="3" t="n">
+        <v>-0.009333333333333305</v>
+      </c>
+      <c r="AW7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:30:02Z</t>
+        </is>
+      </c>
+      <c r="AX7" s="2" t="n"/>
+      <c r="AY7" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1781,13 +1934,13 @@
         <v>-0.001505293291364285</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02077112181567742</v>
+        <v>-0.02077126225996107</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.005453187745987575</v>
+        <v>0.00545304354052556</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02838204226973218</v>
+        <v>-0.02838211140453972</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>-0.02874186113479105</v>
@@ -1905,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="AP8" s="4" t="n">
-        <v>-0.007445636956979973</v>
+        <v>-0.007445419642549522</v>
       </c>
       <c r="AQ8" s="4" t="n">
         <v>0.02285226703064946</v>
@@ -1918,6 +2071,25 @@
       <c r="AS8" t="inlineStr">
         <is>
           <t>No weekly membership exception; retain monthly authority.</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>104.18</v>
+      </c>
+      <c r="AV8" s="4" t="n">
+        <v>-0.001247840276444756</v>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:29:14Z</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2088,6 +2260,25 @@
           <t>No weekly membership exception; retain monthly authority.</t>
         </is>
       </c>
+      <c r="AT9" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="AV9" s="4" t="n">
+        <v>0.004844290657439521</v>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:22:39Z</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
@@ -2115,10 +2306,10 @@
         <v>0.05997695940184089</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03755881249030013</v>
+        <v>0.03755864897730188</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03455985585483035</v>
+        <v>0.03455969281444959</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0.01824850179624615</v>
@@ -2239,9 +2430,29 @@
           <t>SGOV fills vacancies only; reserve-weight changes cannot trigger an exception.</t>
         </is>
       </c>
+      <c r="AT10" s="5" t="n">
+        <v>100.4656</v>
+      </c>
+      <c r="AU10" s="5" t="n">
+        <v>100.46</v>
+      </c>
+      <c r="AV10" s="6" t="n">
+        <v>5.574357953408438e-05</v>
+      </c>
+      <c r="AW10" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:30:04Z</t>
+        </is>
+      </c>
+      <c r="AX10" s="5" t="n"/>
+      <c r="AY10" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS10"/>
+  <autoFilter ref="A1:AY10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2617,10 +2828,10 @@
         <v>-0.01953271362456033</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.0155912482692746</v>
+        <v>-0.01559115258730304</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.001508729897291117</v>
+        <v>-0.001508828336396206</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2688,7 +2899,7 @@
         <v>-0.02874186113479105</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.02838204226973218</v>
+        <v>-0.02838211140453972</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -2870,7 +3081,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.02933603803237417</v>
+        <v>0.02933614706677878</v>
       </c>
     </row>
     <row r="3">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -947,17 +947,17 @@
         </is>
       </c>
       <c r="AT2" s="2" t="n">
-        <v>776.64</v>
+        <v>776.6799999999999</v>
       </c>
       <c r="AU2" s="2" t="n">
         <v>779.09003</v>
       </c>
       <c r="AV2" s="3" t="n">
-        <v>-0.003144732836588782</v>
+        <v>-0.003093390888341929</v>
       </c>
       <c r="AW2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T16:30:03Z</t>
+          <t>2026-10-07T16:31:59Z</t>
         </is>
       </c>
       <c r="AX2" s="2" t="n"/>
@@ -1136,17 +1136,17 @@
         </is>
       </c>
       <c r="AT3" s="2" t="n">
-        <v>756.11</v>
+        <v>756.295</v>
       </c>
       <c r="AU3" s="2" t="n">
         <v>759.65997</v>
       </c>
       <c r="AV3" s="3" t="n">
-        <v>-0.004673103941491119</v>
+        <v>-0.004429573931610586</v>
       </c>
       <c r="AW3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T16:30:04Z</t>
+          <t>2026-10-07T16:32:00Z</t>
         </is>
       </c>
       <c r="AX3" s="2" t="n"/>
@@ -1324,17 +1324,17 @@
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>76.875</v>
+        <v>76.88500000000001</v>
       </c>
       <c r="AU4" t="n">
         <v>77.28</v>
       </c>
       <c r="AV4" s="4" t="n">
-        <v>-0.005240683229813636</v>
+        <v>-0.005111283643892239</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2026-10-07T16:30:03Z</t>
+          <t>2026-10-07T16:31:58Z</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1511,17 +1511,17 @@
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>377.14</v>
+        <v>377.04</v>
       </c>
       <c r="AU5" t="n">
         <v>382.26999</v>
       </c>
       <c r="AV5" s="4" t="n">
-        <v>-0.01341980834017342</v>
+        <v>-0.01368140355459235</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2026-10-07T16:30:01Z</t>
+          <t>2026-10-07T16:32:01Z</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1698,17 +1698,17 @@
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>77.14</v>
+        <v>77.145</v>
       </c>
       <c r="AU6" t="n">
         <v>77.27</v>
       </c>
       <c r="AV6" s="4" t="n">
-        <v>-0.001682412320434756</v>
+        <v>-0.001617704154264321</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2026-10-07T16:30:02Z</t>
+          <t>2026-10-07T16:32:00Z</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1886,17 +1886,17 @@
         </is>
       </c>
       <c r="AT7" s="2" t="n">
-        <v>63.155</v>
+        <v>63.15</v>
       </c>
       <c r="AU7" s="2" t="n">
         <v>63.75</v>
       </c>
       <c r="AV7" s="3" t="n">
-        <v>-0.009333333333333305</v>
+        <v>-0.009411764705882342</v>
       </c>
       <c r="AW7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T16:30:02Z</t>
+          <t>2026-10-07T16:32:02Z</t>
         </is>
       </c>
       <c r="AX7" s="2" t="n"/>
@@ -2074,17 +2074,17 @@
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>104.05</v>
+        <v>104.045</v>
       </c>
       <c r="AU8" t="n">
         <v>104.18</v>
       </c>
       <c r="AV8" s="4" t="n">
-        <v>-0.001247840276444756</v>
+        <v>-0.001295834133230978</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2026-10-07T16:29:14Z</t>
+          <t>2026-10-07T16:31:12Z</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -2261,17 +2261,17 @@
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>29.04</v>
+        <v>29.035</v>
       </c>
       <c r="AU9" t="n">
         <v>28.9</v>
       </c>
       <c r="AV9" s="4" t="n">
-        <v>0.004844290657439521</v>
+        <v>0.004671280276816736</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2026-10-07T16:22:39Z</t>
+          <t>2026-10-07T16:32:02Z</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -2431,17 +2431,17 @@
         </is>
       </c>
       <c r="AT10" s="5" t="n">
-        <v>100.4656</v>
+        <v>100.4601</v>
       </c>
       <c r="AU10" s="5" t="n">
         <v>100.46</v>
       </c>
       <c r="AV10" s="6" t="n">
-        <v>5.574357953408438e-05</v>
+        <v>9.954210631324401e-07</v>
       </c>
       <c r="AW10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-07T16:30:04Z</t>
+          <t>2026-10-07T16:32:02Z</t>
         </is>
       </c>
       <c r="AX10" s="5" t="n"/>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Weekly History" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Survivor'!$A$1:$AY$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Survivor'!$A$1:$BA$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Weekly Review'!$A$17:$H$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Weekly History'!$A$1:$G$3</definedName>
   </definedNames>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:BA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -502,23 +502,25 @@
     <col width="22" customWidth="1" min="32" max="32"/>
     <col width="22" customWidth="1" min="33" max="33"/>
     <col width="22" customWidth="1" min="34" max="34"/>
-    <col width="30" customWidth="1" min="35" max="35"/>
-    <col width="30" customWidth="1" min="36" max="36"/>
-    <col width="22" customWidth="1" min="37" max="37"/>
-    <col width="22" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="35" max="35"/>
+    <col width="22" customWidth="1" min="36" max="36"/>
+    <col width="30" customWidth="1" min="37" max="37"/>
+    <col width="30" customWidth="1" min="38" max="38"/>
     <col width="22" customWidth="1" min="39" max="39"/>
     <col width="22" customWidth="1" min="40" max="40"/>
     <col width="22" customWidth="1" min="41" max="41"/>
     <col width="22" customWidth="1" min="42" max="42"/>
     <col width="22" customWidth="1" min="43" max="43"/>
-    <col width="70" customWidth="1" min="44" max="44"/>
-    <col width="70" customWidth="1" min="45" max="45"/>
-    <col width="22" customWidth="1" min="46" max="46"/>
-    <col width="22" customWidth="1" min="47" max="47"/>
+    <col width="22" customWidth="1" min="44" max="44"/>
+    <col width="22" customWidth="1" min="45" max="45"/>
+    <col width="70" customWidth="1" min="46" max="46"/>
+    <col width="70" customWidth="1" min="47" max="47"/>
     <col width="22" customWidth="1" min="48" max="48"/>
-    <col width="26" customWidth="1" min="49" max="49"/>
+    <col width="22" customWidth="1" min="49" max="49"/>
     <col width="22" customWidth="1" min="50" max="50"/>
-    <col width="42" customWidth="1" min="51" max="51"/>
+    <col width="26" customWidth="1" min="51" max="51"/>
+    <col width="22" customWidth="1" min="52" max="52"/>
+    <col width="42" customWidth="1" min="53" max="53"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -629,150 +631,160 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>Current As Of</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Current Data Mode</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>Current 21/252 Shadow Selected</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Current Shadow Target Weight</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Review Baseline Month</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Review Baseline Selected</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Review Baseline Target Weight</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Weekly Review Date</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Previous Weekly Review Date</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Weekly Shadow Selected</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Previous Weekly Shadow Selected</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Weekly Shadow Target Weight</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Weekly Change</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Weekly Persistence</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Weekly Observations</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Weekly HIL Status</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Portfolio Weekly HIL Status</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Weekly Candidate Still In Daily Shadow</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Weekly 21/252 Score</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Weekly Rank</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Previous Weekly Rank</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Weekly Rank Movement</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Weekly Score Change</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Weekly 3-4 Gap</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Short Horizon Context</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>HIL Summary</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Live Last</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Live Previous Close</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Live Day %</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>Live Quote Time</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>Live Quote Delayed</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>Live Quote Status</t>
         </is>
@@ -803,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4757091163598373</v>
+        <v>0.5623835844156047</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1767536980010154</v>
+        <v>0.168740782490445</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1604294091184051</v>
+        <v>0.1499319981813472</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1878231419881153</v>
+        <v>0.1545597209525387</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.04779261808456403</v>
+        <v>0.03562321888964037</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.01406745533535902</v>
+        <v>0.01635643180539748</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.005497980202108899</v>
+        <v>-0.003247378351666774</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -858,110 +870,120 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="V2" s="2" t="b">
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:37:33Z</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>LIVE_PRICE_OVERLAY</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="W2" s="3" t="n">
+      <c r="Y2" s="3" t="n">
         <v>0.3463251219374191</v>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="b">
+      <c r="AA2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Z2" s="3" t="n">
+      <c r="AB2" s="3" t="n">
         <v>0.3464512254018678</v>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AD2" s="2" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="b">
+      <c r="AE2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AD2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="3" t="n">
+      <c r="AF2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="3" t="n">
         <v>0.3463971100868694</v>
       </c>
-      <c r="AF2" s="2" t="inlineStr">
+      <c r="AH2" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
-      <c r="AG2" s="2" t="inlineStr">
+      <c r="AI2" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="2" t="inlineStr">
+      <c r="AJ2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr">
+      <c r="AL2" s="2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AK2" s="2" t="n"/>
-      <c r="AL2" s="3" t="n">
+      <c r="AM2" s="2" t="n"/>
+      <c r="AN2" s="3" t="n">
         <v>0.1541614263711546</v>
       </c>
-      <c r="AM2" s="2" t="n">
+      <c r="AO2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AN2" s="2" t="n">
+      <c r="AP2" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AO2" s="2" t="n">
+      <c r="AQ2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP2" s="3" t="n">
+      <c r="AR2" s="3" t="n">
         <v>-0.01423500709240733</v>
       </c>
-      <c r="AQ2" s="3" t="n">
+      <c r="AS2" s="3" t="n">
         <v>0.02285226703064946</v>
       </c>
-      <c r="AR2" s="2" t="inlineStr">
+      <c r="AT2" s="2" t="inlineStr">
         <is>
           <t>CONTEXT ONLY; 1m +1.4%, 3m +4.8%, 6m +18.8%. No mechanical gate.</t>
         </is>
       </c>
-      <c r="AS2" s="2" t="inlineStr">
+      <c r="AU2" s="2" t="inlineStr">
         <is>
           <t>No weekly membership exception; retain monthly authority.</t>
         </is>
       </c>
-      <c r="AT2" s="2" t="n">
-        <v>776.6799999999999</v>
-      </c>
-      <c r="AU2" s="2" t="n">
+      <c r="AV2" s="2" t="n">
+        <v>776.5599999999999</v>
+      </c>
+      <c r="AW2" s="2" t="n">
         <v>779.09003</v>
       </c>
-      <c r="AV2" s="3" t="n">
-        <v>-0.003093390888341929</v>
-      </c>
-      <c r="AW2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07T16:31:59Z</t>
-        </is>
-      </c>
-      <c r="AX2" s="2" t="n"/>
+      <c r="AX2" s="3" t="n">
+        <v>-0.00324741673308282</v>
+      </c>
       <c r="AY2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:37:33Z</t>
+        </is>
+      </c>
+      <c r="AZ2" s="2" t="n"/>
+      <c r="BA2" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -992,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.6974487324085343</v>
+        <v>0.8013756900803528</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2653424833531151</v>
+        <v>0.2500249225395283</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1963031263825441</v>
+        <v>0.1863947744178189</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.2934084165831239</v>
+        <v>0.2501769447591538</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.06889063841010645</v>
+        <v>0.04646603174307273</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.05771058810097451</v>
+        <v>0.0536331999211086</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.004575509124570054</v>
+        <v>-0.00468617539425531</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1047,110 +1069,120 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="V3" s="2" t="b">
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:37:33Z</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>LIVE_PRICE_OVERLAY</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="W3" s="3" t="n">
+      <c r="Y3" s="3" t="n">
         <v>0.3575505523661724</v>
       </c>
-      <c r="X3" s="2" t="inlineStr">
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="Y3" s="2" t="b">
+      <c r="AA3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Z3" s="3" t="n">
+      <c r="AB3" s="3" t="n">
         <v>0.358309537054902</v>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
+      <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
+      <c r="AD3" s="2" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="AC3" s="2" t="b">
+      <c r="AE3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AD3" s="2" t="b">
+      <c r="AF3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AE3" s="3" t="n">
+      <c r="AG3" s="3" t="n">
         <v>0.3542858886979251</v>
       </c>
-      <c r="AF3" s="2" t="inlineStr">
+      <c r="AH3" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
-      <c r="AG3" s="2" t="inlineStr">
+      <c r="AI3" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
-      <c r="AH3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="2" t="inlineStr">
+      <c r="AJ3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="inlineStr">
+      <c r="AL3" s="2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AK3" s="2" t="n"/>
-      <c r="AL3" s="3" t="n">
+      <c r="AM3" s="2" t="n"/>
+      <c r="AN3" s="3" t="n">
         <v>0.1799928314412171</v>
       </c>
-      <c r="AM3" s="2" t="n">
+      <c r="AO3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AN3" s="2" t="n">
+      <c r="AP3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AO3" s="2" t="n">
+      <c r="AQ3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP3" s="3" t="n">
+      <c r="AR3" s="3" t="n">
         <v>-0.01773974908912357</v>
       </c>
-      <c r="AQ3" s="3" t="n">
+      <c r="AS3" s="3" t="n">
         <v>0.02285226703064946</v>
       </c>
-      <c r="AR3" s="2" t="inlineStr">
+      <c r="AT3" s="2" t="inlineStr">
         <is>
           <t>CONTEXT ONLY; 1m +5.8%, 3m +6.9%, 6m +29.3%. No mechanical gate.</t>
         </is>
       </c>
-      <c r="AS3" s="2" t="inlineStr">
+      <c r="AU3" s="2" t="inlineStr">
         <is>
           <t>No weekly membership exception; retain monthly authority.</t>
         </is>
       </c>
-      <c r="AT3" s="2" t="n">
-        <v>756.295</v>
-      </c>
-      <c r="AU3" s="2" t="n">
+      <c r="AV3" s="2" t="n">
+        <v>756.1001</v>
+      </c>
+      <c r="AW3" s="2" t="n">
         <v>759.65997</v>
       </c>
-      <c r="AV3" s="3" t="n">
-        <v>-0.004429573931610586</v>
-      </c>
-      <c r="AW3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07T16:32:00Z</t>
-        </is>
-      </c>
-      <c r="AX3" s="2" t="n"/>
+      <c r="AX3" s="3" t="n">
+        <v>-0.004686136087965864</v>
+      </c>
       <c r="AY3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:37:33Z</t>
+        </is>
+      </c>
+      <c r="AZ3" s="2" t="n"/>
+      <c r="BA3" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1181,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.09983975492080122</v>
+        <v>-0.1144893367415423</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.09527082059741276</v>
+        <v>-0.09310081535507364</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.04141523517561818</v>
+        <v>-0.03385716664404825</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.08713228299364917</v>
+        <v>-0.09513597482153802</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.07299282634314253</v>
+        <v>-0.07956917293774246</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.05618239241645073</v>
+        <v>-0.0613197621155448</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.00220464271819476</v>
+        <v>-0.005564182194617073</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1236,108 +1268,118 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="V4" t="b">
-        <v>0</v>
-      </c>
-      <c r="W4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:37:22Z</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>LIVE_PRICE_OVERLAY</t>
+        </is>
+      </c>
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="Y4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="AC4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AL4" s="4" t="n">
+      <c r="AN4" s="4" t="n">
         <v>-0.04348371601185663</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AO4" t="n">
         <v>8</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AP4" t="n">
         <v>8</v>
       </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" s="4" t="n">
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="4" t="n">
         <v>-0.01880297619642213</v>
       </c>
-      <c r="AQ4" s="4" t="n">
+      <c r="AS4" s="4" t="n">
         <v>0.02285226703064946</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AT4" t="inlineStr">
         <is>
           <t>CONTEXT ONLY; 1m -5.6%, 3m -7.3%, 6m -8.7%. No mechanical gate.</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AU4" t="inlineStr">
         <is>
           <t>No weekly membership exception; retain monthly authority.</t>
         </is>
       </c>
-      <c r="AT4" t="n">
-        <v>76.88500000000001</v>
-      </c>
-      <c r="AU4" t="n">
+      <c r="AV4" t="n">
+        <v>76.84999999999999</v>
+      </c>
+      <c r="AW4" t="n">
         <v>77.28</v>
       </c>
-      <c r="AV4" s="4" t="n">
-        <v>-0.005111283643892239</v>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>2026-10-07T16:31:58Z</t>
-        </is>
+      <c r="AX4" s="4" t="n">
+        <v>-0.005564182194617073</v>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:37:22Z</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1368,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3346484184065357</v>
+        <v>0.3474009724009721</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.06886813555530691</v>
+        <v>0.03434601240463242</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.1373727770942847</v>
+        <v>0.09698666227564634</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1147263842893865</v>
+        <v>-0.1326375624237682</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.02088396314594743</v>
+        <v>-0.003397852874292728</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.06023059714334877</v>
+        <v>-0.05710247173021121</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.007166381240943043</v>
+        <v>-0.01406074240719912</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1423,108 +1465,118 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="V5" t="b">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:37:31Z</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>LIVE_PRICE_OVERLAY</t>
+        </is>
+      </c>
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="Y5" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="AC5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="b">
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="b">
         <v>1</v>
       </c>
-      <c r="AE5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AG5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AL5" s="4" t="n">
+      <c r="AN5" s="4" t="n">
         <v>0.1313091593405051</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AO5" t="n">
         <v>4</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AP5" t="n">
         <v>2</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AQ5" t="n">
         <v>-2</v>
       </c>
-      <c r="AP5" s="4" t="n">
+      <c r="AR5" s="4" t="n">
         <v>-0.09588412971926408</v>
       </c>
-      <c r="AQ5" s="4" t="n">
+      <c r="AS5" s="4" t="n">
         <v>0.02285226703064946</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>CONTEXT ONLY; 1m -6.0%, 3m +2.1%, 6m -11.5%. No mechanical gate.</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AU5" t="inlineStr">
         <is>
           <t>No weekly membership exception; retain monthly authority.</t>
         </is>
       </c>
-      <c r="AT5" t="n">
-        <v>377.04</v>
-      </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="n">
+        <v>376.895</v>
+      </c>
+      <c r="AW5" t="n">
         <v>382.26999</v>
       </c>
-      <c r="AV5" s="4" t="n">
-        <v>-0.01368140355459235</v>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>2026-10-07T16:32:01Z</t>
-        </is>
+      <c r="AX5" s="4" t="n">
+        <v>-0.01406071661550001</v>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:37:31Z</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1555,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.08343867338936617</v>
+        <v>0.09697206999955554</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01375007544094364</v>
+        <v>0.01153200597854287</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03394584350543983</v>
+        <v>0.03316798008436184</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.001508828336396206</v>
+        <v>-0.009287925052411272</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01559115258730304</v>
+        <v>-0.01861097197903094</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01953271362456033</v>
+        <v>-0.02094139048332899</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.003767212262925312</v>
+        <v>-0.001941244985117052</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1610,108 +1662,118 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="V6" t="b">
-        <v>0</v>
-      </c>
-      <c r="W6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:37:35Z</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>LIVE_PRICE_OVERLAY</t>
+        </is>
+      </c>
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="Y6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="AC6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AL6" s="4" t="n">
+      <c r="AN6" s="4" t="n">
         <v>0.0317613578135878</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AO6" t="n">
         <v>6</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AP6" t="n">
         <v>6</v>
       </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" s="4" t="n">
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="4" t="n">
         <v>-0.007071975831944854</v>
       </c>
-      <c r="AQ6" s="4" t="n">
+      <c r="AS6" s="4" t="n">
         <v>0.02285226703064946</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AT6" t="inlineStr">
         <is>
           <t>CONTEXT ONLY; 1m -2.0%, 3m -1.6%, 6m -0.2%. No mechanical gate.</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AU6" t="inlineStr">
         <is>
           <t>No weekly membership exception; retain monthly authority.</t>
         </is>
       </c>
-      <c r="AT6" t="n">
-        <v>77.145</v>
-      </c>
-      <c r="AU6" t="n">
+      <c r="AV6" t="n">
+        <v>77.12</v>
+      </c>
+      <c r="AW6" t="n">
         <v>77.27</v>
       </c>
-      <c r="AV6" s="4" t="n">
-        <v>-0.001617704154264321</v>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>2026-10-07T16:32:00Z</t>
-        </is>
+      <c r="AX6" s="4" t="n">
+        <v>-0.001941244985117052</v>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:37:35Z</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1742,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.5371248323842484</v>
+        <v>0.6757390447973726</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.4747555024921795</v>
+        <v>0.4526463984091413</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4731702896601759</v>
+        <v>0.4821638378972259</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.07366047867035697</v>
+        <v>0.101428129785923</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1533980925338752</v>
+        <v>0.1579733040093481</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.001076055390968556</v>
+        <v>-0.01991509894746957</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.004728132387706863</v>
+        <v>-0.01011764705882356</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1797,110 +1859,120 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="V7" s="2" t="b">
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:37:30Z</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>LIVE_PRICE_OVERLAY</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="Y7" s="3" t="n">
         <v>0.2961243256964085</v>
       </c>
-      <c r="X7" s="2" t="inlineStr">
+      <c r="Z7" s="2" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="Y7" s="2" t="b">
+      <c r="AA7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Z7" s="3" t="n">
+      <c r="AB7" s="3" t="n">
         <v>0.2952392375432301</v>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
+      <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
+      <c r="AD7" s="2" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="AC7" s="2" t="b">
+      <c r="AE7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AD7" s="2" t="b">
+      <c r="AF7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AE7" s="3" t="n">
+      <c r="AG7" s="3" t="n">
         <v>0.2993170012152055</v>
       </c>
-      <c r="AF7" s="2" t="inlineStr">
+      <c r="AH7" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
-      <c r="AG7" s="2" t="inlineStr">
+      <c r="AI7" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
-      <c r="AH7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="2" t="inlineStr">
+      <c r="AJ7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AJ7" s="2" t="inlineStr">
+      <c r="AL7" s="2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AK7" s="2" t="n"/>
-      <c r="AL7" s="3" t="n">
+      <c r="AM7" s="2" t="n"/>
+      <c r="AN7" s="3" t="n">
         <v>0.4900491624844652</v>
       </c>
-      <c r="AM7" s="2" t="n">
+      <c r="AO7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AN7" s="2" t="n">
+      <c r="AP7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AO7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" s="3" t="n">
+      <c r="AQ7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="3" t="n">
         <v>0.07693018597033974</v>
       </c>
-      <c r="AQ7" s="3" t="n">
+      <c r="AS7" s="3" t="n">
         <v>0.02285226703064946</v>
       </c>
-      <c r="AR7" s="2" t="inlineStr">
+      <c r="AT7" s="2" t="inlineStr">
         <is>
           <t>CONTEXT ONLY; 1m +0.1%, 3m +15.3%, 6m +7.4%. No mechanical gate.</t>
         </is>
       </c>
-      <c r="AS7" s="2" t="inlineStr">
+      <c r="AU7" s="2" t="inlineStr">
         <is>
           <t>No weekly membership exception; retain monthly authority.</t>
         </is>
       </c>
-      <c r="AT7" s="2" t="n">
-        <v>63.15</v>
-      </c>
-      <c r="AU7" s="2" t="n">
+      <c r="AV7" s="2" t="n">
+        <v>63.105</v>
+      </c>
+      <c r="AW7" s="2" t="n">
         <v>63.75</v>
       </c>
-      <c r="AV7" s="3" t="n">
-        <v>-0.009411764705882342</v>
-      </c>
-      <c r="AW7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07T16:32:02Z</t>
-        </is>
-      </c>
-      <c r="AX7" s="2" t="n"/>
+      <c r="AX7" s="3" t="n">
+        <v>-0.01011764705882356</v>
+      </c>
       <c r="AY7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:37:30Z</t>
+        </is>
+      </c>
+      <c r="AZ7" s="2" t="n"/>
+      <c r="BA7" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1931,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.001505293291364285</v>
+        <v>0.0003445772896872867</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02077126225996107</v>
+        <v>-0.0205523149329051</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.00545304354052556</v>
+        <v>0.007929581220211368</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02838211140453972</v>
+        <v>-0.03000262083769045</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02874186113479105</v>
+        <v>-0.03081485057728461</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.02608207908759463</v>
+        <v>-0.02825782344698735</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.00192344681669554</v>
+        <v>-0.001487809560376308</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -1986,108 +2058,118 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="V8" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:37:23Z</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>LIVE_PRICE_OVERLAY</t>
+        </is>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="Y8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="AC8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AL8" s="4" t="n">
+      <c r="AN8" s="4" t="n">
         <v>0.002883993594746892</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AO8" t="n">
         <v>7</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AP8" t="n">
         <v>7</v>
       </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" s="4" t="n">
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="4" t="n">
         <v>-0.007445419642549522</v>
       </c>
-      <c r="AQ8" s="4" t="n">
+      <c r="AS8" s="4" t="n">
         <v>0.02285226703064946</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AT8" t="inlineStr">
         <is>
           <t>CONTEXT ONLY; 1m -2.6%, 3m -2.9%, 6m -2.8%. No mechanical gate.</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AU8" t="inlineStr">
         <is>
           <t>No weekly membership exception; retain monthly authority.</t>
         </is>
       </c>
-      <c r="AT8" t="n">
-        <v>104.045</v>
-      </c>
-      <c r="AU8" t="n">
+      <c r="AV8" t="n">
+        <v>104.025</v>
+      </c>
+      <c r="AW8" t="n">
         <v>104.18</v>
       </c>
-      <c r="AV8" s="4" t="n">
-        <v>-0.001295834133230978</v>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>2026-10-07T16:31:12Z</t>
-        </is>
+      <c r="AX8" s="4" t="n">
+        <v>-0.001487809560376308</v>
       </c>
       <c r="AY8" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:37:23Z</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2118,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.06930259084147483</v>
+        <v>0.06269595894542745</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.08719558611885803</v>
+        <v>0.08732035636934321</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.05634782208365174</v>
+        <v>0.04800608728574107</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.04144144144144146</v>
+        <v>0.0548492553577915</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01904090267983061</v>
+        <v>0.02397743300423127</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.02920227920227925</v>
+        <v>0.037513397642015</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.003104518799586065</v>
+        <v>0.004844290657439521</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2173,108 +2255,118 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="V9" t="b">
-        <v>0</v>
-      </c>
-      <c r="W9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:35:12Z</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>LIVE_PRICE_OVERLAY</t>
+        </is>
+      </c>
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="Y9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="AC9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AL9" s="4" t="n">
+      <c r="AN9" s="4" t="n">
         <v>0.05934818338039349</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AO9" t="n">
         <v>5</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AP9" t="n">
         <v>5</v>
       </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" s="4" t="n">
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="4" t="n">
         <v>0.006023869849343555</v>
       </c>
-      <c r="AQ9" s="4" t="n">
+      <c r="AS9" s="4" t="n">
         <v>0.02285226703064946</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AT9" t="inlineStr">
         <is>
           <t>CONTEXT ONLY; 1m +2.9%, 3m +1.9%, 6m +4.1%. No mechanical gate.</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AU9" t="inlineStr">
         <is>
           <t>No weekly membership exception; retain monthly authority.</t>
         </is>
       </c>
-      <c r="AT9" t="n">
-        <v>29.035</v>
-      </c>
-      <c r="AU9" t="n">
+      <c r="AV9" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="AW9" t="n">
         <v>28.9</v>
       </c>
-      <c r="AV9" s="4" t="n">
-        <v>0.004671280276816736</v>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>2026-10-07T16:32:02Z</t>
-        </is>
+      <c r="AX9" s="4" t="n">
+        <v>0.004844290657439521</v>
       </c>
       <c r="AY9" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:35:12Z</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2303,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05997695940184089</v>
+        <v>0.05966021488712636</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>0.03755864897730188</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03455969281444959</v>
+        <v>0.03466265846584426</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0.01824850179624615</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009041822437674263</v>
+        <v>0.008941409796411781</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.002898775376309004</v>
+        <v>0.002798970744485763</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>9.955201592815044e-05</v>
+        <v>0</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2352,107 +2444,117 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="V10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="W10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" s="5" t="inlineStr">
+      <c r="V10" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:37:37Z</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="inlineStr">
+        <is>
+          <t>LIVE_PRICE_OVERLAY</t>
+        </is>
+      </c>
+      <c r="X10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="5" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="Y10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="5" t="inlineStr">
+      <c r="AA10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="AB10" s="5" t="inlineStr">
+      <c r="AD10" s="5" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="AC10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="5" t="inlineStr">
+      <c r="AE10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="5" t="inlineStr">
         <is>
           <t>RESERVE_CONTEXT</t>
         </is>
       </c>
-      <c r="AG10" s="5" t="inlineStr">
+      <c r="AI10" s="5" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
-      <c r="AH10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="5" t="inlineStr">
+      <c r="AJ10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AJ10" s="5" t="inlineStr">
+      <c r="AL10" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AK10" s="5" t="n"/>
-      <c r="AL10" s="6" t="n"/>
       <c r="AM10" s="5" t="n"/>
-      <c r="AN10" s="5" t="n"/>
+      <c r="AN10" s="6" t="n"/>
       <c r="AO10" s="5" t="n"/>
-      <c r="AP10" s="6" t="n"/>
-      <c r="AQ10" s="6" t="n">
+      <c r="AP10" s="5" t="n"/>
+      <c r="AQ10" s="5" t="n"/>
+      <c r="AR10" s="6" t="n"/>
+      <c r="AS10" s="6" t="n">
         <v>0.02285226703064946</v>
       </c>
-      <c r="AR10" s="5" t="inlineStr">
+      <c r="AT10" s="5" t="inlineStr">
         <is>
           <t>CONTEXT ONLY; 1m +0.3%, 3m +0.9%, 6m +1.8%. No mechanical gate.</t>
         </is>
       </c>
-      <c r="AS10" s="5" t="inlineStr">
+      <c r="AU10" s="5" t="inlineStr">
         <is>
           <t>SGOV fills vacancies only; reserve-weight changes cannot trigger an exception.</t>
         </is>
       </c>
-      <c r="AT10" s="5" t="n">
-        <v>100.4601</v>
-      </c>
-      <c r="AU10" s="5" t="n">
+      <c r="AV10" s="5" t="n">
         <v>100.46</v>
       </c>
-      <c r="AV10" s="6" t="n">
-        <v>9.954210631324401e-07</v>
-      </c>
-      <c r="AW10" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-07T16:32:02Z</t>
-        </is>
-      </c>
-      <c r="AX10" s="5" t="n"/>
+      <c r="AW10" s="5" t="n">
+        <v>100.46</v>
+      </c>
+      <c r="AX10" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
+          <t>2026-10-07T16:37:37Z</t>
+        </is>
+      </c>
+      <c r="AZ10" s="5" t="n"/>
+      <c r="BA10" s="5" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AY10"/>
+  <autoFilter ref="A1:BA10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2689,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.01406745533535902</v>
+        <v>0.01635643180539748</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.04779261808456403</v>
+        <v>0.03562321888964037</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.1878231419881153</v>
+        <v>0.1545597209525387</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2723,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.05771058810097451</v>
+        <v>0.0536331999211086</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.06889063841010645</v>
+        <v>0.04646603174307273</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.2934084165831239</v>
+        <v>0.2501769447591538</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2757,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.05618239241645073</v>
+        <v>-0.0613197621155448</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.07299282634314253</v>
+        <v>-0.07956917293774246</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.08713228299364917</v>
+        <v>-0.09513597482153802</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2791,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.06023059714334877</v>
+        <v>-0.05710247173021121</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02088396314594743</v>
+        <v>-0.003397852874292728</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1147263842893865</v>
+        <v>-0.1326375624237682</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.01953271362456033</v>
+        <v>-0.02094139048332899</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01559115258730304</v>
+        <v>-0.01861097197903094</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.001508828336396206</v>
+        <v>-0.009287925052411272</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.001076055390968556</v>
+        <v>-0.01991509894746957</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1533980925338752</v>
+        <v>0.1579733040093481</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.07366047867035697</v>
+        <v>0.101428129785923</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.02608207908759463</v>
+        <v>-0.02825782344698735</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.02874186113479105</v>
+        <v>-0.03081485057728461</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.02838211140453972</v>
+        <v>-0.03000262083769045</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -2927,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.02920227920227925</v>
+        <v>0.037513397642015</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.01904090267983061</v>
+        <v>0.02397743300423127</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.04144144144144146</v>
+        <v>0.0548492553577915</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -2961,10 +3063,10 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.002898775376309004</v>
+        <v>0.002798970744485763</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009041822437674263</v>
+        <v>0.008941409796411781</v>
       </c>
       <c r="G26" s="11" t="n">
         <v>0.01824850179624615</v>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.5623835844156047</v>
+        <v>0.563711457555754</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.168740782490445</v>
+        <v>0.1697342052247972</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1499319981813472</v>
+        <v>0.1499321038133348</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1545597209525387</v>
+        <v>0.1555409837214539</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.03562321888964037</v>
+        <v>0.03650339727182228</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.01635643180539748</v>
+        <v>0.0172202353041504</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.003247378351666774</v>
+        <v>-0.002400236172971026</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -858,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512254018678</v>
+        <v>0.3464512286219292</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -867,24 +867,24 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T16:37:33Z</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.3463251219374191</v>
+        <v>0.3450457975031206</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>0.3464512254018678</v>
+        <v>0.3464512286219292</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>0.3463971100868694</v>
+        <v>0.3463971598605515</v>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
       </c>
       <c r="AM2" s="2" t="n"/>
       <c r="AN2" s="3" t="n">
-        <v>0.1541614263711546</v>
+        <v>0.1541615328928427</v>
       </c>
       <c r="AO2" s="2" t="n">
         <v>3</v>
@@ -953,14 +953,14 @@
         <v>1</v>
       </c>
       <c r="AR2" s="3" t="n">
-        <v>-0.01423500709240733</v>
+        <v>-0.01423490057071919</v>
       </c>
       <c r="AS2" s="3" t="n">
-        <v>0.02285226703064946</v>
+        <v>0.0228523735523376</v>
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +1.4%, 3m +4.8%, 6m +18.8%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +1.7%, 3m +3.7%, 6m +15.6%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>776.5599999999999</v>
+        <v>777.23</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>779.09003</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.00324741673308282</v>
+        <v>-0.002387439099945765</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T16:37:33Z</t>
+          <t>2026-10-07T20:15:09Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8013756900803528</v>
+        <v>0.8057352161635702</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2500249225395283</v>
+        <v>0.253050084159951</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1863947744178189</v>
+        <v>0.1863946547028097</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.2501769447591538</v>
+        <v>0.2532026007420252</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.04646603174307273</v>
+        <v>0.04899867020124327</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.0536331999211086</v>
+        <v>0.05618318423209545</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.00468617539425531</v>
+        <v>-0.002277334597056591</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1057,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.358309537054902</v>
+        <v>0.3583095431858343</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T16:37:33Z</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.3575505523661724</v>
+        <v>0.3563369230031548</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0.358309537054902</v>
+        <v>0.3583095431858343</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>0.3542858886979251</v>
+        <v>0.3542858348897226</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="AM3" s="2" t="n"/>
       <c r="AN3" s="3" t="n">
-        <v>0.1799928314412171</v>
+        <v>0.1799925915425706</v>
       </c>
       <c r="AO3" s="2" t="n">
         <v>2</v>
@@ -1152,14 +1152,14 @@
         <v>1</v>
       </c>
       <c r="AR3" s="3" t="n">
-        <v>-0.01773974908912357</v>
+        <v>-0.01773998898777007</v>
       </c>
       <c r="AS3" s="3" t="n">
-        <v>0.02285226703064946</v>
+        <v>0.0228523735523376</v>
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +5.8%, 3m +6.9%, 6m +29.3%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +5.6%, 3m +4.9%, 6m +25.3%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>756.1001</v>
+        <v>757.79</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>759.65997</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.004686136087965864</v>
+        <v>-0.002461588176088991</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T16:37:33Z</t>
+          <t>2026-10-07T20:15:00Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.1144893367415423</v>
+        <v>-0.1104564319641776</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.09310081535507364</v>
+        <v>-0.08897058228897681</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.03385716664404825</v>
+        <v>-0.03385725362947933</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.09513597482153802</v>
+        <v>-0.09101476520163687</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.07956917293774246</v>
+        <v>-0.0753773148184701</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.0613197621155448</v>
+        <v>-0.05704470572960374</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.005564182194617073</v>
+        <v>-0.001035196687370621</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.038029469654283</v>
+        <v>-0.03802929719322601</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-07T16:37:22Z</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="AN4" s="4" t="n">
-        <v>-0.04348371601185663</v>
+        <v>-0.0434835449703479</v>
       </c>
       <c r="AO4" t="n">
         <v>8</v>
@@ -1350,14 +1350,14 @@
         <v>0</v>
       </c>
       <c r="AR4" s="4" t="n">
-        <v>-0.01880297619642213</v>
+        <v>-0.01880289296518045</v>
       </c>
       <c r="AS4" s="4" t="n">
-        <v>0.02285226703064946</v>
+        <v>0.0228523735523376</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -5.6%, 3m -7.3%, 6m -8.7%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -5.7%, 3m -7.5%, 6m -9.1%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>76.84999999999999</v>
+        <v>77.12</v>
       </c>
       <c r="AW4" t="n">
         <v>77.28</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>-0.005564182194617073</v>
+        <v>-0.002070393374741131</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-07T16:37:22Z</t>
+          <t>2026-10-07T20:15:07Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3474009724009721</v>
+        <v>0.3437723437723437</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.03434601240463242</v>
+        <v>0.03156045886162806</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.09698666227564634</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1326375624237682</v>
+        <v>-0.1349734195567625</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>-0.003397852874292728</v>
+        <v>-0.006081760008461612</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.05710247173021121</v>
+        <v>-0.0596417492244572</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.01406074240719912</v>
+        <v>-0.01671593376409342</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-07T16:37:31Z</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1550,11 +1550,11 @@
         <v>-0.09588412971926408</v>
       </c>
       <c r="AS5" s="4" t="n">
-        <v>0.02285226703064946</v>
+        <v>0.0228523735523376</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -6.0%, 3m +2.1%, 6m -11.5%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -6.0%, 3m -0.6%, 6m -13.5%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>376.895</v>
+        <v>376.4</v>
       </c>
       <c r="AW5" t="n">
         <v>382.26999</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.01406071661550001</v>
+        <v>-0.01535561292687404</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-07T16:37:31Z</t>
+          <t>2026-10-07T20:13:52Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.09697206999955554</v>
+        <v>0.09782528509667565</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01153200597854287</v>
+        <v>0.01231918887864358</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03316798008436184</v>
+        <v>0.03316818686206124</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.009287925052411272</v>
+        <v>-0.008517142836425129</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01861097197903094</v>
+        <v>-0.01784744317092335</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.02094139048332899</v>
+        <v>-0.02017967476015725</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.001941244985117052</v>
+        <v>-0.001164746991070165</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715206361910939</v>
+        <v>0.03715216747213934</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1659,17 +1659,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-07T16:37:35Z</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="AN6" s="4" t="n">
-        <v>0.0317613578135878</v>
+        <v>0.03176146093414167</v>
       </c>
       <c r="AO6" t="n">
         <v>6</v>
@@ -1744,14 +1744,14 @@
         <v>0</v>
       </c>
       <c r="AR6" s="4" t="n">
-        <v>-0.007071975831944854</v>
+        <v>-0.007071872711390981</v>
       </c>
       <c r="AS6" s="4" t="n">
-        <v>0.02285226703064946</v>
+        <v>0.0228523735523376</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -2.0%, 3m -1.6%, 6m -0.2%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -2.0%, 3m -1.8%, 6m -0.9%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.12</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="AW6" t="n">
         <v>77.27</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.001941244985117052</v>
+        <v>-0.001164746991070165</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-07T16:37:35Z</t>
+          <t>2026-10-07T20:11:57Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.6757390447973726</v>
+        <v>0.6830416077847632</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.4526463984091413</v>
+        <v>0.4589768927479603</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4821638378972259</v>
+        <v>0.4821639680642813</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.101428129785923</v>
+        <v>0.1062279512848714</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1579733040093481</v>
+        <v>0.1630195389923539</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-0.01991509894746957</v>
+        <v>-0.01564406895318304</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.01011764705882356</v>
+        <v>-0.005803921568627413</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.4639560631420809</v>
+        <v>0.4639559345596878</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>1</v>
@@ -1847,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392375432301</v>
+        <v>0.2952392281922366</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1856,24 +1856,24 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T16:37:30Z</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2961243256964085</v>
+        <v>0.2986172794937245</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>1</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.2952392375432301</v>
+        <v>0.2952392281922366</v>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2993170012152055</v>
+        <v>0.2993170052497259</v>
       </c>
       <c r="AH7" s="2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AM7" s="2" t="n"/>
       <c r="AN7" s="3" t="n">
-        <v>0.4900491624844652</v>
+        <v>0.4900490316102593</v>
       </c>
       <c r="AO7" s="2" t="n">
         <v>1</v>
@@ -1942,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="AR7" s="3" t="n">
-        <v>0.07693018597033974</v>
+        <v>0.07693005509613382</v>
       </c>
       <c r="AS7" s="3" t="n">
-        <v>0.02285226703064946</v>
+        <v>0.0228523735523376</v>
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +0.1%, 3m +15.3%, 6m +7.4%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.6%, 3m +16.3%, 6m +10.6%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>63.105</v>
+        <v>63.4</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>63.75</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>-0.01011764705882356</v>
+        <v>-0.005490196078431375</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T16:37:30Z</t>
+          <t>2026-10-07T20:15:12Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.0003445772896872867</v>
+        <v>0.002412026784376797</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.0205523149329051</v>
+        <v>-0.01852805232152099</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.007929581220211368</v>
+        <v>0.007929508816012953</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.03000262083769045</v>
+        <v>-0.0279978197175762</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.03081485057728461</v>
+        <v>-0.02881172818241917</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.02825782344698735</v>
+        <v>-0.02624941616067256</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.001487809560376308</v>
+        <v>0.000575926281435768</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.004296483646738736</v>
+        <v>0.004296411608788464</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
@@ -2055,17 +2055,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-07T16:37:23Z</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2140,10 +2140,10 @@
         <v>0</v>
       </c>
       <c r="AR8" s="4" t="n">
-        <v>-0.007445419642549522</v>
+        <v>-0.00744549208068257</v>
       </c>
       <c r="AS8" s="4" t="n">
-        <v>0.02285226703064946</v>
+        <v>0.0228523735523376</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>104.025</v>
+        <v>104.24</v>
       </c>
       <c r="AW8" t="n">
         <v>104.18</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>-0.001487809560376308</v>
+        <v>0.000575926281435768</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-07T16:37:23Z</t>
+          <t>2026-10-07T20:10:00Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2252,17 +2252,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-07T16:35:12Z</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2340,11 +2340,11 @@
         <v>0.006023869849343555</v>
       </c>
       <c r="AS9" s="4" t="n">
-        <v>0.02285226703064946</v>
+        <v>0.0228523735523376</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +2.9%, 3m +1.9%, 6m +4.1%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +3.8%, 3m +2.4%, 6m +5.5%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-07T16:35:12Z</t>
+          <t>2026-10-07T20:10:00Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05966021488712636</v>
+        <v>0.05976578098203778</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03755864897730188</v>
+        <v>0.03766201151527326</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03466265846584426</v>
+        <v>0.03466273999414149</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01824850179624615</v>
+        <v>0.01834978164738787</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.008941409796411781</v>
+        <v>0.009041841949487317</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.002798970744485763</v>
+        <v>0.002898791466240169</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0</v>
+        <v>9.954210631102356e-05</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-07T16:37:37Z</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2520,7 +2520,7 @@
       <c r="AQ10" s="5" t="n"/>
       <c r="AR10" s="6" t="n"/>
       <c r="AS10" s="6" t="n">
-        <v>0.02285226703064946</v>
+        <v>0.0228523735523376</v>
       </c>
       <c r="AT10" s="5" t="inlineStr">
         <is>
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.46</v>
+        <v>100.4695</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.46</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>0</v>
+        <v>9.456500099536136e-05</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-07T16:37:37Z</t>
+          <t>2026-10-07T20:14:46Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>QQQ 35.8%, SPY 34.6%, XLE 29.6%</t>
+          <t>QQQ 35.6%, SPY 34.5%, XLE 29.9%</t>
         </is>
       </c>
     </row>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.01635643180539748</v>
+        <v>0.0172202353041504</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.03562321888964037</v>
+        <v>0.03650339727182228</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.1545597209525387</v>
+        <v>0.1555409837214539</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.0536331999211086</v>
+        <v>0.05618318423209545</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.04646603174307273</v>
+        <v>0.04899867020124327</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.2501769447591538</v>
+        <v>0.2532026007420252</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.0613197621155448</v>
+        <v>-0.05704470572960374</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.07956917293774246</v>
+        <v>-0.0753773148184701</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.09513597482153802</v>
+        <v>-0.09101476520163687</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.05710247173021121</v>
+        <v>-0.0596417492244572</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-0.003397852874292728</v>
+        <v>-0.006081760008461612</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1326375624237682</v>
+        <v>-0.1349734195567625</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.02094139048332899</v>
+        <v>-0.02017967476015725</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01861097197903094</v>
+        <v>-0.01784744317092335</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.009287925052411272</v>
+        <v>-0.008517142836425129</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>-0.01991509894746957</v>
+        <v>-0.01564406895318304</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1579733040093481</v>
+        <v>0.1630195389923539</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.101428129785923</v>
+        <v>0.1062279512848714</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.02825782344698735</v>
+        <v>-0.02624941616067256</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.03081485057728461</v>
+        <v>-0.02881172818241917</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.03000262083769045</v>
+        <v>-0.0279978197175762</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.002798970744485763</v>
+        <v>0.002898791466240169</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.008941409796411781</v>
+        <v>0.009041841949487317</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01824850179624615</v>
+        <v>0.01834978164738787</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.02285226703064946</v>
+        <v>0.0228523735523376</v>
       </c>
     </row>
   </sheetData>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>777.23</v>
+        <v>777.78</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>779.09003</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.002387439099945765</v>
+        <v>-0.001681487311549823</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T20:15:09Z</t>
+          <t>2026-10-07T23:38:56Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8057352161635702</v>
+        <v>0.8052587248738303</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.253050084159951</v>
+        <v>0.2527194335499581</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0.1863946547028097</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.2532026007420252</v>
+        <v>0.2528719098864733</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.04899867020124327</v>
+        <v>0.04872186398689604</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.05618318423209545</v>
+        <v>0.05590448219253208</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.002277334597056591</v>
+        <v>-0.002540610273016775</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>757.79</v>
+        <v>759.1</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>759.65997</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.002461588176088991</v>
+        <v>-0.0007371324304478177</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T20:15:00Z</t>
+          <t>2026-10-07T23:40:42Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.1104564319641776</v>
+        <v>-0.1110325612180868</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.08897058228897681</v>
+        <v>-0.08956062724863423</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>-0.03385725362947933</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.09101476520163687</v>
+        <v>-0.09160348620863068</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.0753773148184701</v>
+        <v>-0.07597616370783633</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.05704470572960374</v>
+        <v>-0.05765542807045243</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.001035196687370621</v>
+        <v>-0.001682194616977162</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -5.7%, 3m -7.5%, 6m -9.1%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -5.8%, 3m -7.6%, 6m -9.2%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>77.12</v>
+        <v>77.10550000000001</v>
       </c>
       <c r="AW4" t="n">
         <v>77.28</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>-0.002070393374741131</v>
+        <v>-0.002258022774327073</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-07T20:15:07Z</t>
+          <t>2026-10-07T23:40:48Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>376.4</v>
+        <v>376.8</v>
       </c>
       <c r="AW5" t="n">
         <v>382.26999</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.01535561292687404</v>
+        <v>-0.01430923206919799</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-07T20:13:52Z</t>
+          <t>2026-10-07T23:40:12Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.18000000000001</v>
+        <v>77.13</v>
       </c>
       <c r="AW6" t="n">
         <v>77.27</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.001164746991070165</v>
+        <v>-0.00181182865277596</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-07T20:11:57Z</t>
+          <t>2026-10-07T23:33:13Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.6830416077847632</v>
+        <v>0.6825105122947712</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.4589768927479603</v>
+        <v>0.4585165024378473</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.4821639680642813</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.1062279512848714</v>
+        <v>0.105878873357675</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1630195389923539</v>
+        <v>0.1626525400844989</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-0.01564406895318304</v>
+        <v>-0.01595468931640398</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.005803921568627413</v>
+        <v>-0.006117647058823561</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>63.4</v>
+        <v>63.4337</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>63.75</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>-0.005490196078431375</v>
+        <v>-0.004961568627451007</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T20:15:12Z</t>
+          <t>2026-10-07T23:40:56Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-07T20:10:00Z</t>
+          <t>2026-10-07T22:30:00Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-07T20:10:00Z</t>
+          <t>2026-10-07T22:30:00Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.4695</v>
+        <v>100.47</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.46</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>9.456500099536136e-05</v>
+        <v>9.954210631102356e-05</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-07T20:14:46Z</t>
+          <t>2026-10-07T23:40:50Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.05618318423209545</v>
+        <v>0.05590448219253208</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.04899867020124327</v>
+        <v>0.04872186398689604</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.2532026007420252</v>
+        <v>0.2528719098864733</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.05704470572960374</v>
+        <v>-0.05765542807045243</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.0753773148184701</v>
+        <v>-0.07597616370783633</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.09101476520163687</v>
+        <v>-0.09160348620863068</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>-0.01564406895318304</v>
+        <v>-0.01595468931640398</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1630195389923539</v>
+        <v>0.1626525400844989</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.1062279512848714</v>
+        <v>0.105878873357675</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.563711457555754</v>
+        <v>0.5626318222400375</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1697342052247972</v>
+        <v>0.171186684981363</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1499321038133348</v>
+        <v>0.148846840963506</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1555409837214539</v>
+        <v>0.146074627734269</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.03650339727182228</v>
+        <v>0.02950557414620114</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.0172202353041504</v>
+        <v>0.01944545018648536</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.002400236172971026</v>
+        <v>-0.002470343017421106</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,12 +872,12 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08T14:00:07Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>777.78</v>
+        <v>775.3</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>779.09003</v>
+        <v>777.21997</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.001681487311549823</v>
+        <v>-0.002470304513663035</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T23:38:56Z</t>
+          <t>2026-10-08T14:00:07Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8052587248738303</v>
+        <v>0.7898610728082989</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2527194335499581</v>
+        <v>0.251622586884799</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1863946547028097</v>
+        <v>0.1892714699137903</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.2528719098864733</v>
+        <v>0.2368167397004304</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.04872186398689604</v>
+        <v>0.0390824421007927</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.05590448219253208</v>
+        <v>0.05242799356443695</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.002540610273016775</v>
+        <v>-0.006136750557586446</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08T14:00:08Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>759.1</v>
+        <v>753.08</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>759.65997</v>
+        <v>757.72998</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.0007371324304478177</v>
+        <v>-0.006136724324936838</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T23:40:42Z</t>
+          <t>2026-10-08T14:00:08Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.1110325612180868</v>
+        <v>-0.08156494845119766</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.08956062724863423</v>
+        <v>-0.09296365740053103</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.03385725362947933</v>
+        <v>-0.04487475970667498</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.09160348620863068</v>
+        <v>-0.08748426795560627</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.07597616370783633</v>
+        <v>-0.07391609224161433</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.05765542807045243</v>
+        <v>-0.05034826393980296</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.001682194616977162</v>
+        <v>0.001992222942320154</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08T14:00:07Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>77.10550000000001</v>
+        <v>77.30370000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>77.28</v>
+        <v>77.145</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>-0.002258022774327073</v>
+        <v>0.00205716507874798</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-07T23:40:48Z</t>
+          <t>2026-10-08T14:00:07Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3437723437723437</v>
+        <v>0.3823389719045707</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.03156045886162806</v>
+        <v>0.03303664063779843</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.09698666227564634</v>
+        <v>0.1012668596079289</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1349734195567625</v>
+        <v>-0.1359868466123176</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>-0.006081760008461612</v>
+        <v>0.003580806875149278</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.0596417492244572</v>
+        <v>-0.0619561175158051</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.01671593376409342</v>
+        <v>0.006597850377780157</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08T14:00:08Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>376.8</v>
+        <v>378.36</v>
       </c>
       <c r="AW5" t="n">
-        <v>382.26999</v>
+        <v>375.88</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.01430923206919799</v>
+        <v>0.006597850377780157</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-07T23:40:12Z</t>
+          <t>2026-10-08T14:00:08Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.09782528509667565</v>
+        <v>0.1063424649545346</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01231918887864358</v>
+        <v>0.01252791424346755</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03316818686206124</v>
+        <v>0.03248908937217054</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.008517142836425129</v>
+        <v>-0.01052683538148103</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01784744317092335</v>
+        <v>-0.01824573887567393</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.02017967476015725</v>
+        <v>-0.01933306156372161</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.001164746991070165</v>
+        <v>-0.0009069707178026576</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08T14:00:08Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.13</v>
+        <v>77.11</v>
       </c>
       <c r="AW6" t="n">
-        <v>77.27</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.00181182865277596</v>
+        <v>-0.0009069707178026576</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-07T23:33:13Z</t>
+          <t>2026-10-08T14:00:08Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.6825105122947712</v>
+        <v>0.7309412860449502</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.4585165024378473</v>
+        <v>0.488641679296846</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4821639680642813</v>
+        <v>0.4921832066089715</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.105878873357675</v>
+        <v>0.1446865070313428</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1626525400844989</v>
+        <v>0.1829156588069594</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-0.01595468931640398</v>
+        <v>-0.002373386388775822</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.006117647058823561</v>
+        <v>0.02225378787878785</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08T14:00:07Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>63.4337</v>
+        <v>64.77</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>63.75</v>
+        <v>63.36</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>-0.004961568627451007</v>
+        <v>0.02225378787878785</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T23:40:56Z</t>
+          <t>2026-10-08T14:00:07Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.002412026784376797</v>
+        <v>0.01519706690115163</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01852805232152099</v>
+        <v>-0.02070149046344816</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.007929508816012953</v>
+        <v>0.002771628173573681</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.0279978197175762</v>
+        <v>-0.02787656745958678</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02881172818241917</v>
+        <v>-0.02834255409730391</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.02624941616067256</v>
+        <v>-0.02340823970037453</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.000575926281435768</v>
+        <v>0.0005755947812740025</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08T13:59:57Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="AW8" t="n">
         <v>104.24</v>
       </c>
-      <c r="AW8" t="n">
-        <v>104.18</v>
-      </c>
       <c r="AX8" s="4" t="n">
-        <v>0.000575926281435768</v>
+        <v>0.0005755947812740025</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-07T22:30:00Z</t>
+          <t>2026-10-08T13:59:57Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.06269595894542745</v>
+        <v>0.0578745959563951</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.08732035636934321</v>
+        <v>0.08072283027153682</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.04800608728574107</v>
+        <v>0.04159776759317979</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.0548492553577915</v>
+        <v>0.05644104803493444</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.02397743300423127</v>
+        <v>0.0225783726664317</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.037513397642015</v>
+        <v>0.03756254467476761</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.004844290657439521</v>
+        <v>-0.0003099173553718915</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08T13:58:29Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
+        <v>29.031</v>
+      </c>
+      <c r="AW9" t="n">
         <v>29.04</v>
       </c>
-      <c r="AW9" t="n">
-        <v>28.9</v>
-      </c>
       <c r="AX9" s="4" t="n">
-        <v>0.004844290657439521</v>
+        <v>-0.0003099173553718915</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-07T22:30:00Z</t>
+          <t>2026-10-08T13:58:29Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05976578098203778</v>
+        <v>0.05971305620673384</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03766201151527326</v>
+        <v>0.03750702592129085</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03466273999414149</v>
+        <v>0.03455966641835051</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01834978164738787</v>
+        <v>0.01829913707643227</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009041841949487317</v>
+        <v>0.008891263408960626</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.002898791466240169</v>
+        <v>0.002848902386794361</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>9.954210631102356e-05</v>
+        <v>4.976609933304843e-05</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08T14:00:11Z</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
+        <v>100.475</v>
+      </c>
+      <c r="AW10" s="5" t="n">
         <v>100.47</v>
       </c>
-      <c r="AW10" s="5" t="n">
-        <v>100.46</v>
-      </c>
       <c r="AX10" s="6" t="n">
-        <v>9.954210631102356e-05</v>
+        <v>4.976609933304843e-05</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-07T23:40:50Z</t>
+          <t>2026-10-08T14:00:11Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.0172202353041504</v>
+        <v>0.01944545018648536</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.03650339727182228</v>
+        <v>0.02950557414620114</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.1555409837214539</v>
+        <v>0.146074627734269</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.05590448219253208</v>
+        <v>0.05242799356443695</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.04872186398689604</v>
+        <v>0.0390824421007927</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.2528719098864733</v>
+        <v>0.2368167397004304</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.05765542807045243</v>
+        <v>-0.05034826393980296</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.07597616370783633</v>
+        <v>-0.07391609224161433</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.09160348620863068</v>
+        <v>-0.08748426795560627</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.0596417492244572</v>
+        <v>-0.0619561175158051</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-0.006081760008461612</v>
+        <v>0.003580806875149278</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1349734195567625</v>
+        <v>-0.1359868466123176</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.02017967476015725</v>
+        <v>-0.01933306156372161</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01784744317092335</v>
+        <v>-0.01824573887567393</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.008517142836425129</v>
+        <v>-0.01052683538148103</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>-0.01595468931640398</v>
+        <v>-0.002373386388775822</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1626525400844989</v>
+        <v>0.1829156588069594</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.105878873357675</v>
+        <v>0.1446865070313428</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.02624941616067256</v>
+        <v>-0.02340823970037453</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.02881172818241917</v>
+        <v>-0.02834255409730391</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.0279978197175762</v>
+        <v>-0.02787656745958678</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.037513397642015</v>
+        <v>0.03756254467476761</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.02397743300423127</v>
+        <v>0.0225783726664317</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.0548492553577915</v>
+        <v>0.05644104803493444</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.002898791466240169</v>
+        <v>0.002848902386794361</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009041841949487317</v>
+        <v>0.008891263408960626</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01834978164738787</v>
+        <v>0.01829913707643227</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.5626318222400375</v>
+        <v>0.5604148474021566</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.171186684981363</v>
+        <v>0.1695249987263916</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0.148846840963506</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.146074627734269</v>
+        <v>0.1444484673503572</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.02950557414620114</v>
+        <v>0.02804490584804453</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.01944545018648536</v>
+        <v>0.01799905524877743</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.002470343017421106</v>
+        <v>-0.003885643704485187</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.1609549765152376</v>
+        <v>0.1609548690014375</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>3</v>
@@ -858,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512286219292</v>
+        <v>0.3464512062651334</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -867,24 +867,24 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T14:00:07Z</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.3450457975031206</v>
+        <v>0.3443143087082896</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>0.3464512286219292</v>
+        <v>0.3464512062651334</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>0.3463971598605515</v>
+        <v>0.3463971344821685</v>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +1.7%, 3m +3.7%, 6m +15.6%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +1.8%, 3m +2.8%, 6m +14.4%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>775.3</v>
+        <v>774.38</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>777.21997</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.002470304513663035</v>
+        <v>-0.003654010588533874</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T14:00:07Z</t>
+          <t>2026-10-08T20:15:07Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.7898610728082989</v>
+        <v>0.7767889782730402</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.251622586884799</v>
+        <v>0.2424814343582089</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1892714699137903</v>
+        <v>0.1892713492732458</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.2368167397004304</v>
+        <v>0.2277837222880845</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.0390824421007927</v>
+        <v>0.03149366875459525</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.05242799356443695</v>
+        <v>0.04474175310578121</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.006136750557586446</v>
+        <v>-0.01339527272247365</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1057,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095431858343</v>
+        <v>0.3583095554429965</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T14:00:08Z</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.3563369230031548</v>
+        <v>0.3565968482763557</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0.3583095431858343</v>
+        <v>0.3583095554429965</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>0.3542858348897226</v>
+        <v>0.3542858821972162</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="AM3" s="2" t="n"/>
       <c r="AN3" s="3" t="n">
-        <v>0.1799925915425706</v>
+        <v>0.1799928314412171</v>
       </c>
       <c r="AO3" s="2" t="n">
         <v>2</v>
@@ -1152,14 +1152,14 @@
         <v>1</v>
       </c>
       <c r="AR3" s="3" t="n">
-        <v>-0.01773998898777007</v>
+        <v>-0.01773974908912357</v>
       </c>
       <c r="AS3" s="3" t="n">
         <v>0.0228523735523376</v>
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +5.6%, 3m +4.9%, 6m +25.3%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +4.5%, 3m +3.1%, 6m +22.8%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>753.08</v>
+        <v>748.03</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>757.72998</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.006136724324936838</v>
+        <v>-0.01280136757951689</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T14:00:08Z</t>
+          <t>2026-10-08T20:15:01Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.08156494845119766</v>
+        <v>-0.07483698065319155</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.09296365740053103</v>
+        <v>-0.08631927023117669</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.04487475970667498</v>
+        <v>-0.04487501621173673</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.08748426795560627</v>
+        <v>-0.08079949531138952</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.07391609224161433</v>
+        <v>-0.06713192386463396</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.05034826393980296</v>
+        <v>-0.04339144585566357</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.001992222942320154</v>
+        <v>0.009332469215813433</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.03802929719322601</v>
+        <v>-0.03802964211527826</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-08T14:00:07Z</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="AN4" s="4" t="n">
-        <v>-0.0434835449703479</v>
+        <v>-0.04348380153258791</v>
       </c>
       <c r="AO4" t="n">
         <v>8</v>
@@ -1350,14 +1350,14 @@
         <v>0</v>
       </c>
       <c r="AR4" s="4" t="n">
-        <v>-0.01880289296518045</v>
+        <v>-0.01880332514800176</v>
       </c>
       <c r="AS4" s="4" t="n">
         <v>0.0228523735523376</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -5.8%, 3m -7.6%, 6m -9.2%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -4.3%, 3m -6.7%, 6m -8.1%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>77.30370000000001</v>
+        <v>77.87</v>
       </c>
       <c r="AW4" t="n">
         <v>77.145</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>0.00205716507874798</v>
+        <v>0.009397887095728974</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-08T14:00:07Z</t>
+          <t>2026-10-08T20:15:05Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3823389719045707</v>
+        <v>0.3832888823937746</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.03303664063779843</v>
+        <v>0.03374651886637903</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.1012668596079289</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1359868466123176</v>
+        <v>-0.1353931173072093</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.003580806875149278</v>
+        <v>0.004270443754807562</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.0619561175158051</v>
+        <v>-0.06131151605305574</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.006597850377780157</v>
+        <v>0.0072895604980312</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-08T14:00:08Z</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -6.0%, 3m -0.6%, 6m -13.5%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -6.1%, 3m +0.4%, 6m -13.5%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>378.36</v>
+        <v>378.8</v>
       </c>
       <c r="AW5" t="n">
         <v>375.88</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>0.006597850377780157</v>
+        <v>0.007768436735128281</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-08T14:00:08Z</t>
+          <t>2026-10-08T20:14:37Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1063424649545346</v>
+        <v>0.1067730137278899</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01252791424346755</v>
+        <v>0.01292194435920169</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03248908937217054</v>
+        <v>0.03248919280821605</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01052683538148103</v>
+        <v>-0.01014187629785301</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01824573887567393</v>
+        <v>-0.01786378286693668</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01933306156372161</v>
+        <v>-0.01895152858287497</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.0009069707178026576</v>
+        <v>-0.0005182689816015662</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715216747213934</v>
+        <v>0.03715185591311232</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1659,17 +1659,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-08T14:00:08Z</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="AN6" s="4" t="n">
-        <v>0.03176146093414167</v>
+        <v>0.03176125469305457</v>
       </c>
       <c r="AO6" t="n">
         <v>6</v>
@@ -1744,14 +1744,14 @@
         <v>0</v>
       </c>
       <c r="AR6" s="4" t="n">
-        <v>-0.007071872711390981</v>
+        <v>-0.007072183025119472</v>
       </c>
       <c r="AS6" s="4" t="n">
         <v>0.0228523735523376</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -2.0%, 3m -1.8%, 6m -0.9%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.9%, 3m -1.8%, 6m -1.0%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.11</v>
+        <v>77.08</v>
       </c>
       <c r="AW6" t="n">
         <v>77.18000000000001</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.0009069707178026576</v>
+        <v>-0.001295672454003749</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-08T14:00:08Z</t>
+          <t>2026-10-08T20:11:44Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7309412860449502</v>
+        <v>0.7435017678180107</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.488641679296846</v>
+        <v>0.4994439270854751</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.4921832066089715</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.1446865070313428</v>
+        <v>0.15299286272541</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1829156588069594</v>
+        <v>0.1914994222721327</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-0.002373386388775822</v>
+        <v>0.00486583714676958</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.02225378787878785</v>
+        <v>0.02967171717171713</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1847,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392281922366</v>
+        <v>0.2952392382918702</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1856,24 +1856,24 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T14:00:07Z</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2986172794937245</v>
+        <v>0.2990888430153547</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>1</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.2952392281922366</v>
+        <v>0.2952392382918702</v>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2993170052497259</v>
+        <v>0.2993169833206153</v>
       </c>
       <c r="AH7" s="2" t="inlineStr">
         <is>
@@ -1942,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="AR7" s="3" t="n">
-        <v>0.07693005509613382</v>
+        <v>0.07692993235275614</v>
       </c>
       <c r="AS7" s="3" t="n">
         <v>0.0228523735523376</v>
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.6%, 3m +16.3%, 6m +10.6%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +0.5%, 3m +19.1%, 6m +15.3%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>64.77</v>
+        <v>65.11</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>63.36</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.02225378787878785</v>
+        <v>0.02761994949494939</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T14:00:07Z</t>
+          <t>2026-10-08T20:13:57Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.01519706690115163</v>
+        <v>0.01733857326723887</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02070149046344816</v>
+        <v>-0.01863585602339024</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>0.002771628173573681</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02787656745958678</v>
+        <v>-0.02582606741012483</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02834255409730391</v>
+        <v>-0.02629303695350149</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.02340823970037453</v>
+        <v>-0.02134831460674158</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0005755947812740025</v>
+        <v>0.002686108979278679</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -2055,17 +2055,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-08T13:59:57Z</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2140,14 +2140,14 @@
         <v>0</v>
       </c>
       <c r="AR8" s="4" t="n">
-        <v>-0.00744549208068257</v>
+        <v>-0.007445564518826053</v>
       </c>
       <c r="AS8" s="4" t="n">
         <v>0.0228523735523376</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -2.6%, 3m -2.9%, 6m -2.8%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -2.1%, 3m -2.6%, 6m -2.6%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>104.3</v>
+        <v>104.51</v>
       </c>
       <c r="AW8" t="n">
         <v>104.24</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>0.0005755947812740025</v>
+        <v>0.002590176515733011</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-08T13:59:57Z</t>
+          <t>2026-10-08T20:10:59Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.0578745959563951</v>
+        <v>0.05601618238491035</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.08072283027153682</v>
+        <v>0.07882427822910487</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.04159776759317979</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05644104803493444</v>
+        <v>0.05458515283842802</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.0225783726664317</v>
+        <v>0.02078196548080302</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.03756254467476761</v>
+        <v>0.03573981415296634</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.0003099173553718915</v>
+        <v>-0.002066115702479276</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2252,17 +2252,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-08T13:58:29Z</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +3.8%, 3m +2.4%, 6m +5.5%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +3.6%, 3m +2.1%, 6m +5.5%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>29.031</v>
+        <v>28.98</v>
       </c>
       <c r="AW9" t="n">
         <v>29.04</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>-0.0003099173553718915</v>
+        <v>-0.002066115702479276</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-08T13:58:29Z</t>
+          <t>2026-10-08T20:10:00Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05971305620673384</v>
+        <v>0.05966023577775803</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03750702592129085</v>
+        <v>0.03745531408093994</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03455966641835051</v>
+        <v>0.03455958491441069</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01829913707643227</v>
+        <v>0.01824846282228565</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.008891263408960626</v>
+        <v>0.008841057324690427</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.002848902386794361</v>
+        <v>0.002798996992298797</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>4.976609933304843e-05</v>
+        <v>0</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-08T14:00:11Z</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.475</v>
+        <v>100.48</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.47</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>4.976609933304843e-05</v>
+        <v>9.953219866631891e-05</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-08T14:00:11Z</t>
+          <t>2026-10-08T20:13:37Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>QQQ 35.6%, SPY 34.5%, XLE 29.9%</t>
+          <t>QQQ 35.7%, SPY 34.4%, XLE 29.9%</t>
         </is>
       </c>
     </row>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.01944545018648536</v>
+        <v>0.01799905524877743</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.02950557414620114</v>
+        <v>0.02804490584804453</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.146074627734269</v>
+        <v>0.1444484673503572</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.05242799356443695</v>
+        <v>0.04474175310578121</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.0390824421007927</v>
+        <v>0.03149366875459525</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.2368167397004304</v>
+        <v>0.2277837222880845</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.05034826393980296</v>
+        <v>-0.04339144585566357</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.07391609224161433</v>
+        <v>-0.06713192386463396</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.08748426795560627</v>
+        <v>-0.08079949531138952</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.0619561175158051</v>
+        <v>-0.06131151605305574</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.003580806875149278</v>
+        <v>0.004270443754807562</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1359868466123176</v>
+        <v>-0.1353931173072093</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.01933306156372161</v>
+        <v>-0.01895152858287497</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01824573887567393</v>
+        <v>-0.01786378286693668</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01052683538148103</v>
+        <v>-0.01014187629785301</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>-0.002373386388775822</v>
+        <v>0.00486583714676958</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1829156588069594</v>
+        <v>0.1914994222721327</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.1446865070313428</v>
+        <v>0.15299286272541</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.02340823970037453</v>
+        <v>-0.02134831460674158</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.02834255409730391</v>
+        <v>-0.02629303695350149</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.02787656745958678</v>
+        <v>-0.02582606741012483</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.03756254467476761</v>
+        <v>0.03573981415296634</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.0225783726664317</v>
+        <v>0.02078196548080302</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05644104803493444</v>
+        <v>0.05458515283842802</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.002848902386794361</v>
+        <v>0.002798996992298797</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.008891263408960626</v>
+        <v>0.008841057324690427</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01829913707643227</v>
+        <v>0.01824846282228565</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.5604148474021566</v>
+        <v>0.5889912796651864</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1695249987263916</v>
+        <v>0.1653404770754798</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.148846840963506</v>
+        <v>0.1351911650765494</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1444484673503572</v>
+        <v>0.1479134002601734</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.02804490584804453</v>
+        <v>0.03842521604351568</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.01799905524877743</v>
+        <v>0.02655879725499566</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.003885643704485187</v>
+        <v>0.002713423694649331</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,12 +872,12 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09T14:00:07Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>774.38</v>
+        <v>776.03</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>777.21997</v>
+        <v>773.92999</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.003654010588533874</v>
+        <v>0.002713436650775058</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T20:15:07Z</t>
+          <t>2026-10-09T14:00:07Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.7767889782730402</v>
+        <v>0.8140202660761879</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2424814343582089</v>
+        <v>0.2315542828101813</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1892713492732458</v>
+        <v>0.1632844869027379</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.2277837222880845</v>
+        <v>0.2291643770971514</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.03149366875459525</v>
+        <v>0.05415042871985998</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.04474175310578121</v>
+        <v>0.05868710248961784</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.01339527272247365</v>
+        <v>0.002568287006072811</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09T14:00:07Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>748.03</v>
+        <v>749.5</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>757.72998</v>
+        <v>747.58002</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.01280136757951689</v>
+        <v>0.002568260184374616</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T20:15:01Z</t>
+          <t>2026-10-09T14:00:07Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.07483698065319155</v>
+        <v>-0.05988101685730907</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.08631927023117669</v>
+        <v>-0.08979096751387028</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.04487501621173673</v>
+        <v>-0.0567173894600016</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.08079949531138952</v>
+        <v>-0.08134837965646224</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.06713192386463396</v>
+        <v>-0.06440917889248798</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.04339144585566357</v>
+        <v>-0.0350622153788408</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.009332469215813433</v>
+        <v>-0.003017850263259292</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09T14:00:04Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
+        <v>77.63500000000001</v>
+      </c>
+      <c r="AW4" t="n">
         <v>77.87</v>
       </c>
-      <c r="AW4" t="n">
-        <v>77.145</v>
-      </c>
       <c r="AX4" s="4" t="n">
-        <v>0.009397887095728974</v>
+        <v>-0.003017850263259292</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-08T20:15:05Z</t>
+          <t>2026-10-09T14:00:04Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3832888823937746</v>
+        <v>0.3959665697674419</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.03374651886637903</v>
+        <v>0.03188289014235823</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.1012668596079289</v>
+        <v>0.06462530217566487</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1353931173072093</v>
+        <v>-0.1211538901470958</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.004270443754807562</v>
+        <v>0.04641407675755183</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.06131151605305574</v>
+        <v>-0.03075486931072757</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.0072895604980312</v>
+        <v>0.0146584966457135</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09T14:00:07Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>378.8</v>
+        <v>384.17</v>
       </c>
       <c r="AW5" t="n">
-        <v>375.88</v>
+        <v>378.62</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>0.007768436735128281</v>
+        <v>0.0146584966457135</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-08T20:14:37Z</t>
+          <t>2026-10-09T14:00:07Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1067730137278899</v>
+        <v>0.1116706343550791</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01292194435920169</v>
+        <v>0.01423156802463255</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03248919280821605</v>
+        <v>0.02931197566237409</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01014187629785301</v>
+        <v>-0.006373850622725774</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01786378286693668</v>
+        <v>-0.01570869936574026</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01895152858287497</v>
+        <v>-0.0146509590817081</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.0005182689816015662</v>
+        <v>-0.0001944516463572299</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09T14:00:07Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.08</v>
+        <v>77.125</v>
       </c>
       <c r="AW6" t="n">
-        <v>77.18000000000001</v>
+        <v>77.14</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.001295672454003749</v>
+        <v>-0.0001944516463572299</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-08T20:11:44Z</t>
+          <t>2026-10-09T14:00:07Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7435017678180107</v>
+        <v>0.7958213676286936</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.4994439270854751</v>
+        <v>0.5173382872475525</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4921832066089715</v>
+        <v>0.4921706768785028</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.15299286272541</v>
+        <v>0.1679187469421297</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1914994222721327</v>
+        <v>0.1636435438065533</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.00486583714676958</v>
+        <v>0.01686644212959476</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.02967171717171713</v>
+        <v>0.006054567749846917</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09T14:00:09Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>65.11</v>
+        <v>65.63500000000001</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>63.36</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.02761994949494939</v>
+        <v>0.006054567749846917</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T20:13:57Z</t>
+          <t>2026-10-09T14:00:09Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,28 +2003,28 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.01733857326723887</v>
+        <v>0.01868762696450688</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01863585602339024</v>
+        <v>-0.02046731809851532</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.002771628173573681</v>
+        <v>-0.002359098979072272</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02582606741012483</v>
+        <v>-0.02747047488950127</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02629303695350149</v>
+        <v>-0.02542810028928311</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.02134831460674158</v>
+        <v>-0.01815103921753025</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.002686108979278679</v>
+        <v>-0.001148105625717433</v>
       </c>
       <c r="M8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09T13:59:39Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>104.51</v>
+        <v>104.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>104.24</v>
+        <v>104.52</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>0.002590176515733011</v>
+        <v>-0.001148105625717433</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-08T20:10:59Z</t>
+          <t>2026-10-09T13:59:39Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.05601618238491035</v>
+        <v>0.06325518132797625</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07882427822910487</v>
+        <v>0.07891374528621076</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.04159776759317979</v>
+        <v>0.04121026959450802</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05458515283842802</v>
+        <v>0.05849125364431496</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.02078196548080302</v>
+        <v>0.01912280701754399</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.03573981415296634</v>
+        <v>0.03621120228326791</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.002066115702479276</v>
+        <v>0.002242926155969771</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09T14:00:05Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
+        <v>29.045</v>
+      </c>
+      <c r="AW9" t="n">
         <v>28.98</v>
       </c>
-      <c r="AW9" t="n">
-        <v>29.04</v>
-      </c>
       <c r="AX9" s="4" t="n">
-        <v>-0.002066115702479276</v>
+        <v>0.002242926155969771</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-08T20:10:00Z</t>
+          <t>2026-10-09T14:00:05Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05966023577775803</v>
+        <v>0.05997664671707659</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03745531408093994</v>
+        <v>0.03766187155333811</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03455958491441069</v>
+        <v>0.03455961551286846</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01824846282228565</v>
+        <v>0.01814700024756633</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.008841057324690427</v>
+        <v>0.008941529166298201</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.002798996992298797</v>
+        <v>0.002998624722976295</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0</v>
+        <v>0.0002985965959987347</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09T14:00:10Z</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.48</v>
+        <v>100.5</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.47</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>9.953219866631891e-05</v>
+        <v>0.0002985965959987347</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-08T20:13:37Z</t>
+          <t>2026-10-09T14:00:10Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.01799905524877743</v>
+        <v>0.02655879725499566</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.02804490584804453</v>
+        <v>0.03842521604351568</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.1444484673503572</v>
+        <v>0.1479134002601734</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.04474175310578121</v>
+        <v>0.05868710248961784</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.03149366875459525</v>
+        <v>0.05415042871985998</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.2277837222880845</v>
+        <v>0.2291643770971514</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.04339144585566357</v>
+        <v>-0.0350622153788408</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.06713192386463396</v>
+        <v>-0.06440917889248798</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.08079949531138952</v>
+        <v>-0.08134837965646224</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.06131151605305574</v>
+        <v>-0.03075486931072757</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.004270443754807562</v>
+        <v>0.04641407675755183</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1353931173072093</v>
+        <v>-0.1211538901470958</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.01895152858287497</v>
+        <v>-0.0146509590817081</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01786378286693668</v>
+        <v>-0.01570869936574026</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01014187629785301</v>
+        <v>-0.006373850622725774</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.00486583714676958</v>
+        <v>0.01686644212959476</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1914994222721327</v>
+        <v>0.1636435438065533</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.15299286272541</v>
+        <v>0.1679187469421297</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.02134831460674158</v>
+        <v>-0.01815103921753025</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.02629303695350149</v>
+        <v>-0.02542810028928311</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.02582606741012483</v>
+        <v>-0.02747047488950127</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.03573981415296634</v>
+        <v>0.03621120228326791</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.02078196548080302</v>
+        <v>0.01912280701754399</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05458515283842802</v>
+        <v>0.05849125364431496</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.002798996992298797</v>
+        <v>0.002998624722976295</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.008841057324690427</v>
+        <v>0.008941529166298201</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01824846282228565</v>
+        <v>0.01814700024756633</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Survivor'!$A$1:$BA$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Weekly Review'!$A$17:$H$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Weekly History'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Weekly History'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.5889912796651864</v>
+        <v>0.594192058687294</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1653404770754798</v>
+        <v>0.1691547172617764</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0.1351911650765494</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1479134002601734</v>
+        <v>0.1516706004156583</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.03842521604351568</v>
+        <v>0.04182405378013754</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.02655879725499566</v>
+        <v>0.02991879538010389</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.002713423694649331</v>
+        <v>0.00599537425865404</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.1609548690014375</v>
+        <v>0.1609549765152376</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>3</v>
@@ -858,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512062651334</v>
+        <v>0.3464512254018678</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -867,24 +867,24 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09T14:00:07Z</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.3443143087082896</v>
+        <v>0.3443126610995251</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -895,26 +895,26 @@
         <v>1</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>0.3464512062651334</v>
+        <v>0.3464512254018678</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
           <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AE2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="AF2" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>0.3463971344821685</v>
+        <v>0.3443126610995251</v>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
@@ -941,26 +941,26 @@
       </c>
       <c r="AM2" s="2" t="n"/>
       <c r="AN2" s="3" t="n">
-        <v>0.1541615328928427</v>
+        <v>0.1351911650765494</v>
       </c>
       <c r="AO2" s="2" t="n">
         <v>3</v>
       </c>
       <c r="AP2" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR2" s="3" t="n">
-        <v>-0.01423490057071919</v>
+        <v>-0.01897026129460522</v>
       </c>
       <c r="AS2" s="3" t="n">
-        <v>0.0228523735523376</v>
+        <v>0.07056586290088451</v>
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +1.8%, 3m +2.8%, 6m +14.4%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +3.0%, 3m +4.2%, 6m +15.2%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>776.03</v>
+        <v>778.6</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>773.92999</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>0.002713436650775058</v>
+        <v>0.00603415045332456</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09T14:00:07Z</t>
+          <t>2026-10-09T20:15:05Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.8140202660761879</v>
+        <v>0.818303941259831</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2315542828101813</v>
+        <v>0.2344626898556437</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0.1632844869027379</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.2291643770971514</v>
+        <v>0.2320671402025043</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.05415042871985998</v>
+        <v>0.05663988336807102</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.05868710248961784</v>
+        <v>0.06118727083038711</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.002568287006072811</v>
+        <v>0.004935926589796358</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1057,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095554429965</v>
+        <v>0.358309537054902</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09T14:00:07Z</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.3565968482763557</v>
+        <v>0.3529527731412714</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1094,16 +1094,16 @@
         <v>1</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0.3583095554429965</v>
+        <v>0.358309537054902</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
           <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AE3" s="2" t="b">
@@ -1113,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>0.3542858821972162</v>
+        <v>0.3529527731412714</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1140,26 +1140,26 @@
       </c>
       <c r="AM3" s="2" t="n"/>
       <c r="AN3" s="3" t="n">
-        <v>0.1799928314412171</v>
+        <v>0.1632844869027379</v>
       </c>
       <c r="AO3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="AP3" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR3" s="3" t="n">
-        <v>-0.01773974908912357</v>
+        <v>-0.01670834453847925</v>
       </c>
       <c r="AS3" s="3" t="n">
-        <v>0.0228523735523376</v>
+        <v>0.07056586290088451</v>
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +4.5%, 3m +3.1%, 6m +22.8%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +6.1%, 3m +5.7%, 6m +23.2%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>749.5</v>
+        <v>751.27</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>747.58002</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>0.002568260184374616</v>
+        <v>0.004935899704756608</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09T14:00:07Z</t>
+          <t>2026-10-09T20:15:00Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.05988101685730907</v>
+        <v>-0.05570324846439068</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.08979096751387028</v>
+        <v>-0.08574603333338993</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.0567173894600016</v>
+        <v>-0.05671730508466388</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.08134837965646224</v>
+        <v>-0.07726592617238515</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.06440917889248798</v>
+        <v>-0.06025153307189046</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.0350622153788408</v>
+        <v>-0.0307741554098282</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.003017850263259292</v>
+        <v>0.001412610761525546</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.03802964211527826</v>
+        <v>-0.03802955588478829</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-09T14:00:04Z</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1297,14 +1297,14 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="AN4" s="4" t="n">
-        <v>-0.04348380153258791</v>
+        <v>-0.05671730508466388</v>
       </c>
       <c r="AO4" t="n">
         <v>8</v>
@@ -1350,14 +1350,14 @@
         <v>0</v>
       </c>
       <c r="AR4" s="4" t="n">
-        <v>-0.01880332514800176</v>
+        <v>-0.01323358907280725</v>
       </c>
       <c r="AS4" s="4" t="n">
-        <v>0.0228523735523376</v>
+        <v>0.07056586290088451</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -4.3%, 3m -6.7%, 6m -8.1%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -3.1%, 3m -6.0%, 6m -7.7%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>77.63500000000001</v>
+        <v>77.98</v>
       </c>
       <c r="AW4" t="n">
         <v>77.87</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>-0.003017850263259292</v>
+        <v>0.001412610761525546</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-09T14:00:04Z</t>
+          <t>2026-10-09T20:15:00Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3959665697674419</v>
+        <v>0.3974563953488373</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.03188289014235823</v>
+        <v>0.03298415256513554</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.06462530217566487</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1211538901470958</v>
+        <v>-0.1202159540640084</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.04641407675755183</v>
+        <v>0.04753084738376057</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.03075486931072757</v>
+        <v>-0.02972045615097396</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.0146584966457135</v>
+        <v>0.01574137657809938</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-09T14:00:07Z</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1494,19 +1494,19 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
       <c r="AF5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="4" t="n">
         <v>0</v>
@@ -1535,26 +1535,26 @@
         </is>
       </c>
       <c r="AN5" s="4" t="n">
-        <v>0.1313091593405051</v>
+        <v>0.06462530217566487</v>
       </c>
       <c r="AO5" t="n">
         <v>4</v>
       </c>
       <c r="AP5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AR5" s="4" t="n">
-        <v>-0.09588412971926408</v>
+        <v>-0.06668385716484027</v>
       </c>
       <c r="AS5" s="4" t="n">
-        <v>0.0228523735523376</v>
+        <v>0.07056586290088451</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -6.1%, 3m +0.4%, 6m -13.5%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -3.0%, 3m +4.8%, 6m -12.0%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>384.17</v>
+        <v>384.6</v>
       </c>
       <c r="AW5" t="n">
         <v>378.62</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>0.0146584966457135</v>
+        <v>0.01579419998943532</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-09T14:00:07Z</t>
+          <t>2026-10-09T20:14:49Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1116706343550791</v>
+        <v>0.1131837246970597</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01423156802463255</v>
+        <v>0.01561257330446653</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.02931197566237409</v>
+        <v>0.02931218220472731</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.006373850622725774</v>
+        <v>-0.005021101894237989</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01570869936574026</v>
+        <v>-0.01436856337595505</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.0146509590817081</v>
+        <v>-0.01330947902600077</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.0001944516463572299</v>
+        <v>0.001166709878143601</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715185591311232</v>
+        <v>0.03715175578024987</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1659,17 +1659,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-09T14:00:07Z</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1691,14 +1691,14 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="AN6" s="4" t="n">
-        <v>0.03176125469305457</v>
+        <v>0.02931218220472731</v>
       </c>
       <c r="AO6" t="n">
         <v>6</v>
@@ -1744,14 +1744,14 @@
         <v>0</v>
       </c>
       <c r="AR6" s="4" t="n">
-        <v>-0.007072183025119472</v>
+        <v>-0.002449175608860488</v>
       </c>
       <c r="AS6" s="4" t="n">
-        <v>0.0228523735523376</v>
+        <v>0.07056586290088451</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.9%, 3m -1.8%, 6m -1.0%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.3%, 3m -1.4%, 6m -0.5%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.125</v>
+        <v>77.2</v>
       </c>
       <c r="AW6" t="n">
         <v>77.14</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.0001944516463572299</v>
+        <v>0.0007778065854291416</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-09T14:00:07Z</t>
+          <t>2026-10-09T20:14:18Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7958213676286936</v>
+        <v>0.7809095851116703</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.5173382872475525</v>
+        <v>0.5047390739231079</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.4921706768785028</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.1679187469421297</v>
+        <v>0.158220937586093</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1636435438065533</v>
+        <v>0.1539812335852602</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.01686644212959476</v>
+        <v>0.008422895074507997</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.006054567749846917</v>
+        <v>-0.002299202942979583</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.4639559345596878</v>
+        <v>0.4639560631420809</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>1</v>
@@ -1847,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392382918702</v>
+        <v>0.2952392375432301</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1856,24 +1856,24 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09T14:00:09Z</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2990888430153547</v>
+        <v>0.3027345657592035</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -1884,16 +1884,16 @@
         <v>1</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.2952392382918702</v>
+        <v>0.2952392375432301</v>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
           <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AD7" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AE7" s="2" t="b">
@@ -1903,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2993169833206153</v>
+        <v>0.3027345657592035</v>
       </c>
       <c r="AH7" s="2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AM7" s="2" t="n"/>
       <c r="AN7" s="3" t="n">
-        <v>0.4900490316102593</v>
+        <v>0.4921706768785028</v>
       </c>
       <c r="AO7" s="2" t="n">
         <v>1</v>
@@ -1942,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="AR7" s="3" t="n">
-        <v>0.07692993235275614</v>
+        <v>0.002121514394037627</v>
       </c>
       <c r="AS7" s="3" t="n">
-        <v>0.0228523735523376</v>
+        <v>0.07056586290088451</v>
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +0.5%, 3m +19.1%, 6m +15.3%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +0.8%, 3m +15.4%, 6m +15.8%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>65.63500000000001</v>
+        <v>65.127</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>65.23999999999999</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.006054567749846917</v>
+        <v>-0.001732066217044803</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09T14:00:09Z</t>
+          <t>2026-10-09T20:13:38Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.01868762696450688</v>
+        <v>0.01888270200103648</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02046731809851532</v>
+        <v>-0.02027980842162591</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.002359098979072272</v>
+        <v>-0.002359241806851986</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02747047488950127</v>
+        <v>-0.02728416655135757</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02542810028928311</v>
+        <v>-0.02524140069163738</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.01815103921753025</v>
+        <v>-0.01796294554688227</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.001148105625717433</v>
+        <v>-0.0009567546880979716</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.004296411608788464</v>
+        <v>0.004296483646738736</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
@@ -2055,17 +2055,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-09T13:59:39Z</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2087,14 +2087,14 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="AN8" s="4" t="n">
-        <v>0.002883993594746892</v>
+        <v>-0.002359241806851986</v>
       </c>
       <c r="AO8" t="n">
         <v>7</v>
@@ -2140,14 +2140,14 @@
         <v>0</v>
       </c>
       <c r="AR8" s="4" t="n">
-        <v>-0.007445564518826053</v>
+        <v>-0.005243235401598878</v>
       </c>
       <c r="AS8" s="4" t="n">
-        <v>0.0228523735523376</v>
+        <v>0.07056586290088451</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -2.1%, 3m -2.6%, 6m -2.6%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.8%, 3m -2.5%, 6m -2.7%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>104.4</v>
+        <v>104.39</v>
       </c>
       <c r="AW8" t="n">
         <v>104.52</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>-0.001148105625717433</v>
+        <v>-0.001243781094527274</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-09T13:59:39Z</t>
+          <t>2026-10-09T20:12:49Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.06325518132797625</v>
+        <v>0.06234000213936541</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07891374528621076</v>
+        <v>0.07798508824946926</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.04121026959450802</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05849125364431496</v>
+        <v>0.05758017492711365</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01912280701754399</v>
+        <v>0.01824561403508773</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.03621120228326791</v>
+        <v>0.0353193007491972</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.002242926155969771</v>
+        <v>0.001380262249827346</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2252,17 +2252,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-09T14:00:05Z</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2284,14 +2284,14 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="AN9" s="4" t="n">
-        <v>0.05934818338039349</v>
+        <v>0.04121026959450802</v>
       </c>
       <c r="AO9" t="n">
         <v>5</v>
@@ -2337,14 +2337,14 @@
         <v>0</v>
       </c>
       <c r="AR9" s="4" t="n">
-        <v>0.006023869849343555</v>
+        <v>-0.01813791378588547</v>
       </c>
       <c r="AS9" s="4" t="n">
-        <v>0.0228523735523376</v>
+        <v>0.07056586290088451</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +3.6%, 3m +2.1%, 6m +5.5%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +3.5%, 3m +1.8%, 6m +5.8%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>29.045</v>
+        <v>29.02</v>
       </c>
       <c r="AW9" t="n">
         <v>28.98</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>0.002242926155969771</v>
+        <v>0.001380262249827346</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-09T14:00:05Z</t>
+          <t>2026-10-09T20:10:00Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05997664671707659</v>
+        <v>0.06008220233230976</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03766187155333811</v>
+        <v>0.03776512149080613</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0.03455961551286846</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01814700024756633</v>
+        <v>0.0182483871092407</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.008941529166298201</v>
+        <v>0.009041921358255101</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.002998624722976295</v>
+        <v>0.003098425581157693</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0002985965959987347</v>
+        <v>0.0003981287946650536</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-09T14:00:10Z</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="AC10" s="5" t="inlineStr">
         <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD10" s="5" t="inlineStr">
+        <is>
           <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AD10" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AE10" s="5" t="b">
@@ -2520,7 +2520,7 @@
       <c r="AQ10" s="5" t="n"/>
       <c r="AR10" s="6" t="n"/>
       <c r="AS10" s="6" t="n">
-        <v>0.0228523735523376</v>
+        <v>0.07056586290088451</v>
       </c>
       <c r="AT10" s="5" t="inlineStr">
         <is>
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.5</v>
+        <v>100.5115</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.47</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>0.0002985965959987347</v>
+        <v>0.0004130586244650569</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-09T14:00:10Z</t>
+          <t>2026-10-09T20:15:08Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02: QQQ 35.4%, SPY 34.6%, XLE 29.9%</t>
+          <t>2026-10-09: QQQ 35.3%, SPY 34.4%, XLE 30.3%</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25: QQQ 38.3%, GLD 30.9%, XLE 30.9%</t>
+          <t>2026-10-02: QQQ 35.4%, SPY 34.6%, XLE 29.9%</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>QQQ 35.7%, SPY 34.4%, XLE 29.9%</t>
+          <t>QQQ 35.3%, SPY 34.4%, XLE 30.3%</t>
         </is>
       </c>
     </row>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.02655879725499566</v>
+        <v>0.02991879538010389</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.03842521604351568</v>
+        <v>0.04182405378013754</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.1479134002601734</v>
+        <v>0.1516706004156583</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.05868710248961784</v>
+        <v>0.06118727083038711</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.05415042871985998</v>
+        <v>0.05663988336807102</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.2291643770971514</v>
+        <v>0.2320671402025043</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.0350622153788408</v>
+        <v>-0.0307741554098282</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.06440917889248798</v>
+        <v>-0.06025153307189046</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.08134837965646224</v>
+        <v>-0.07726592617238515</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.03075486931072757</v>
+        <v>-0.02972045615097396</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.04641407675755183</v>
+        <v>0.04753084738376057</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1211538901470958</v>
+        <v>-0.1202159540640084</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.0146509590817081</v>
+        <v>-0.01330947902600077</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01570869936574026</v>
+        <v>-0.01436856337595505</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.006373850622725774</v>
+        <v>-0.005021101894237989</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.01686644212959476</v>
+        <v>0.008422895074507997</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1636435438065533</v>
+        <v>0.1539812335852602</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.1679187469421297</v>
+        <v>0.158220937586093</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.01815103921753025</v>
+        <v>-0.01796294554688227</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.02542810028928311</v>
+        <v>-0.02524140069163738</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.02747047488950127</v>
+        <v>-0.02728416655135757</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.03621120228326791</v>
+        <v>0.0353193007491972</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.01912280701754399</v>
+        <v>0.01824561403508773</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05849125364431496</v>
+        <v>0.05758017492711365</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.002998624722976295</v>
+        <v>0.003098425581157693</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.008941529166298201</v>
+        <v>0.009041921358255101</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01814700024756633</v>
+        <v>0.0182483871092407</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.02933614706677878</v>
+        <v>0.02933625610116319</v>
       </c>
     </row>
     <row r="3">
@@ -3216,11 +3216,44 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.0228523735523376</v>
+        <v>0.02285226703064946</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>XLE, QQQ, SPY</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>QQQ 35.3%, SPY 34.4%, XLE 30.3%</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0.07056586290088451</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.594192058687294</v>
+        <v>0.4425156019719818</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1691547172617764</v>
+        <v>0.1724159500107416</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1351911650765494</v>
+        <v>0.1481941501433557</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1516706004156583</v>
+        <v>0.1403930872431869</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.04182405378013754</v>
+        <v>0.03801804373944129</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.02991879538010389</v>
+        <v>0.02109556111600264</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.00599537425865404</v>
+        <v>-0.0001155965423790262</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,12 +872,12 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12T14:00:09Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>778.6</v>
+        <v>778.48</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>773.92999</v>
+        <v>778.57001</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>0.00603415045332456</v>
+        <v>-0.0001156093849543627</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09T20:15:05Z</t>
+          <t>2026-10-12T14:00:09Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.818303941259831</v>
+        <v>0.6156508221856585</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2344626898556437</v>
+        <v>0.2300278067266641</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1632844869027379</v>
+        <v>0.1748670391393801</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.2320671402025043</v>
+        <v>0.2136033867715275</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.05663988336807102</v>
+        <v>0.03995341943039032</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.06118727083038711</v>
+        <v>0.04695064696656281</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.004935926589796358</v>
+        <v>-0.004798541137008061</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12T14:00:09Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>751.27</v>
+        <v>747.665</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>747.58002</v>
+        <v>751.27002</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>0.004935899704756608</v>
+        <v>-0.00479856763085007</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09T20:15:00Z</t>
+          <t>2026-10-12T14:00:09Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.05570324846439068</v>
+        <v>-0.06086613693928045</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.08574603333338993</v>
+        <v>-0.08467541932273182</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.05671730508466388</v>
+        <v>-0.05492528736023083</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.07726592617238515</v>
+        <v>-0.07967647019961377</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.06025153307189046</v>
+        <v>-0.06111872424211828</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.0307741554098282</v>
+        <v>-0.03147913235283095</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.001412610761525546</v>
+        <v>0.000385996409335565</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12T14:00:06Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
+        <v>78.01009999999999</v>
+      </c>
+      <c r="AW4" t="n">
         <v>77.98</v>
       </c>
-      <c r="AW4" t="n">
-        <v>77.87</v>
-      </c>
       <c r="AX4" s="4" t="n">
-        <v>0.001412610761525546</v>
+        <v>0.000385996409335565</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-09T20:15:00Z</t>
+          <t>2026-10-12T14:00:06Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3974563953488373</v>
+        <v>0.3400728852757726</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.03298415256513554</v>
+        <v>0.04652053744903273</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.06462530217566487</v>
+        <v>0.0912349834441617</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1202159540640084</v>
+        <v>-0.1215775450202131</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.04753084738376057</v>
+        <v>0.0276232701867527</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.02972045615097396</v>
+        <v>-0.04097600120370137</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.01574137657809938</v>
+        <v>-0.005590514327318052</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12T14:00:10Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>384.6</v>
+        <v>382.43</v>
       </c>
       <c r="AW5" t="n">
-        <v>378.62</v>
+        <v>384.57999</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>0.01579419998943532</v>
+        <v>-0.005590488470291977</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-09T20:14:49Z</t>
+          <t>2026-10-12T14:00:10Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1131837246970597</v>
+        <v>0.08406056721828903</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01561257330446653</v>
+        <v>0.01845108327875922</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.02931218220472731</v>
+        <v>0.03199325598799296</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.005021101894237989</v>
+        <v>-0.008804349278035639</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01436856337595505</v>
+        <v>-0.01641152386519484</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01330947902600077</v>
+        <v>-0.01312234613032315</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.001166709878143601</v>
+        <v>-6.474168069414699e-05</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12T13:59:42Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.2</v>
+        <v>77.22499999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>77.14</v>
+        <v>77.23</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>0.0007778065854291416</v>
+        <v>-6.474168069414699e-05</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-09T20:14:18Z</t>
+          <t>2026-10-12T13:59:42Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7809095851116703</v>
+        <v>0.682736428548965</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.5047390739231079</v>
+        <v>0.5531982722141466</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4921706768785028</v>
+        <v>0.5178073620032786</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.158220937586093</v>
+        <v>0.175619168466796</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1539812335852602</v>
+        <v>0.1704808185113009</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.008422895074507997</v>
+        <v>0.02331712910138828</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.002299202942979583</v>
+        <v>0.01820835894283968</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12T14:00:11Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>65.127</v>
+        <v>66.265</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>65.23999999999999</v>
+        <v>65.08</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>-0.001732066217044803</v>
+        <v>0.01820835894283968</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09T20:13:38Z</t>
+          <t>2026-10-12T14:00:11Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.01888270200103648</v>
+        <v>0.01722429721334429</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02027980842162591</v>
+        <v>-0.01866388124345386</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.002359241806851986</v>
+        <v>-0.005794823306280783</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02728416655135757</v>
+        <v>-0.02909210759261371</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02524140069163738</v>
+        <v>-0.02567758741782233</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.01796294554688227</v>
+        <v>-0.01294406651549518</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.0009567546880979716</v>
+        <v>0.0004788354721316779</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12T14:00:08Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>104.39</v>
+        <v>104.47</v>
       </c>
       <c r="AW8" t="n">
-        <v>104.52</v>
+        <v>104.42</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>-0.001243781094527274</v>
+        <v>0.0004788354721316779</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-09T20:12:49Z</t>
+          <t>2026-10-12T14:00:08Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.06234000213936541</v>
+        <v>0.06339683951109465</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07798508824946926</v>
+        <v>0.07326065173171492</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.04121026959450802</v>
+        <v>0.03562827411857139</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05758017492711365</v>
+        <v>0.06245434623812995</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01824561403508773</v>
+        <v>0.0246565692145122</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.0353193007491972</v>
+        <v>0.03633772711079453</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.001380262249827346</v>
+        <v>0.002412129565816601</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12T13:58:39Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="AW9" t="n">
         <v>29.02</v>
       </c>
-      <c r="AW9" t="n">
-        <v>28.98</v>
-      </c>
       <c r="AX9" s="4" t="n">
-        <v>0.001380262249827346</v>
+        <v>0.002412129565816601</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-09T20:10:00Z</t>
+          <t>2026-10-12T13:58:39Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2532,24 +2532,14 @@
           <t>SGOV fills vacancies only; reserve-weight changes cannot trigger an exception.</t>
         </is>
       </c>
-      <c r="AV10" s="5" t="n">
-        <v>100.5115</v>
-      </c>
-      <c r="AW10" s="5" t="n">
-        <v>100.47</v>
-      </c>
-      <c r="AX10" s="6" t="n">
-        <v>0.0004130586244650569</v>
-      </c>
-      <c r="AY10" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-09T20:15:08Z</t>
-        </is>
-      </c>
+      <c r="AV10" s="5" t="n"/>
+      <c r="AW10" s="5" t="n"/>
+      <c r="AX10" s="6" t="n"/>
+      <c r="AY10" s="5" t="n"/>
       <c r="AZ10" s="5" t="n"/>
       <c r="BA10" s="5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>UNAVAILABLE: 504 Server Error: Gateway Timeout for url: https://api.tradestation.com/v3/marketdata/quotes/SGOV</t>
         </is>
       </c>
     </row>
@@ -2791,13 +2781,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.02991879538010389</v>
+        <v>0.02109556111600264</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.04182405378013754</v>
+        <v>0.03801804373944129</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.1516706004156583</v>
+        <v>0.1403930872431869</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2815,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.06118727083038711</v>
+        <v>0.04695064696656281</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.05663988336807102</v>
+        <v>0.03995341943039032</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.2320671402025043</v>
+        <v>0.2136033867715275</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2849,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.0307741554098282</v>
+        <v>-0.03147913235283095</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.06025153307189046</v>
+        <v>-0.06111872424211828</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.07726592617238515</v>
+        <v>-0.07967647019961377</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2883,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.02972045615097396</v>
+        <v>-0.04097600120370137</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.04753084738376057</v>
+        <v>0.0276232701867527</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1202159540640084</v>
+        <v>-0.1215775450202131</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2917,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.01330947902600077</v>
+        <v>-0.01312234613032315</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01436856337595505</v>
+        <v>-0.01641152386519484</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.005021101894237989</v>
+        <v>-0.008804349278035639</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2951,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.008422895074507997</v>
+        <v>0.02331712910138828</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1539812335852602</v>
+        <v>0.1704808185113009</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.158220937586093</v>
+        <v>0.175619168466796</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2985,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.01796294554688227</v>
+        <v>-0.01294406651549518</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.02524140069163738</v>
+        <v>-0.02567758741782233</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.02728416655135757</v>
+        <v>-0.02909210759261371</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3019,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.0353193007491972</v>
+        <v>0.03633772711079453</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.01824561403508773</v>
+        <v>0.0246565692145122</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05758017492711365</v>
+        <v>0.06245434623812995</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4425156019719818</v>
+        <v>0.441644859750592</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1724159500107416</v>
+        <v>0.1717081148749577</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0.1481941501433557</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1403930872431869</v>
+        <v>0.1397045856105126</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.03801804373944129</v>
+        <v>0.03739135007928618</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.02109556111600264</v>
+        <v>0.02047908424604516</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.0001155965423790262</v>
+        <v>-0.0007192673748025458</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.1609549765152376</v>
+        <v>0.1609548690014375</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>3</v>
@@ -858,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512254018678</v>
+        <v>0.3464512030450774</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -867,24 +867,24 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T14:00:09Z</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.3443126610995251</v>
+        <v>0.3451433174288588</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>0.3464512254018678</v>
+        <v>0.3464512030450774</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +3.0%, 3m +4.2%, 6m +15.2%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +2.0%, 3m +3.7%, 6m +14.0%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>778.48</v>
+        <v>778.02</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>778.57001</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.0001156093849543627</v>
+        <v>-0.000706436149525036</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T14:00:09Z</t>
+          <t>2026-10-12T20:15:00Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.6156508221856585</v>
+        <v>0.6121395255346795</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2300278067266641</v>
+        <v>0.2273543001034053</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1748670391393801</v>
+        <v>0.1748669211680143</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.2136033867715275</v>
+        <v>0.2109657007711079</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.03995341943039032</v>
+        <v>0.03769315004961893</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.04695064696656281</v>
+        <v>0.0446751695785339</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.004798541137008061</v>
+        <v>-0.006961545116935364</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1057,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.358309537054902</v>
+        <v>0.358309549312061</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T14:00:09Z</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.3529527731412714</v>
+        <v>0.3529198503451894</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0.358309537054902</v>
+        <v>0.358309549312061</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +6.1%, 3m +5.7%, 6m +23.2%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +4.5%, 3m +3.8%, 6m +21.1%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>747.665</v>
+        <v>745.61</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>751.27002</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.00479856763085007</v>
+        <v>-0.007533935668030511</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T14:00:09Z</t>
+          <t>2026-10-12T20:14:58Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.06086613693928045</v>
+        <v>-0.06038579604577921</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.08467541932273182</v>
+        <v>-0.08420709225463763</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.05492528736023083</v>
+        <v>-0.05492511815624879</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.07967647019961377</v>
+        <v>-0.07920575026925813</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.06111872424211828</v>
+        <v>-0.06063851254000863</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.03147913235283095</v>
+        <v>-0.03098376082248899</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.000385996409335565</v>
+        <v>0.0008976660682225024</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.03802955588478829</v>
+        <v>-0.03802938342376228</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-12T14:00:06Z</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1350,14 +1350,14 @@
         <v>0</v>
       </c>
       <c r="AR4" s="4" t="n">
-        <v>-0.01323358907280725</v>
+        <v>-0.01323367459355407</v>
       </c>
       <c r="AS4" s="4" t="n">
         <v>0.07056586290088451</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -3.1%, 3m -6.0%, 6m -7.7%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -3.1%, 3m -6.1%, 6m -7.9%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>78.01009999999999</v>
+        <v>78.05</v>
       </c>
       <c r="AW4" t="n">
         <v>77.98</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>0.000385996409335565</v>
+        <v>0.0008976660682225024</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-12T14:00:06Z</t>
+          <t>2026-10-12T20:15:00Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3400728852757726</v>
+        <v>0.3390917373326792</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.04652053744903273</v>
+        <v>0.04575431683222497</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.0912349834441617</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1215775450202131</v>
+        <v>-0.122220690922455</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.0276232701867527</v>
+        <v>0.02687088539567384</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.04097600120370137</v>
+        <v>-0.04167816034305494</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.005590514327318052</v>
+        <v>-0.006318581309480487</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-12T14:00:10Z</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -3.0%, 3m +4.8%, 6m -12.0%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -4.2%, 3m +2.7%, 6m -12.2%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>382.43</v>
+        <v>382.15</v>
       </c>
       <c r="AW5" t="n">
         <v>384.57999</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.005590488470291977</v>
+        <v>-0.006318555471385934</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-12T14:00:10Z</t>
+          <t>2026-10-12T20:13:41Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.08406056721828903</v>
+        <v>0.08497290083247799</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01845108327875922</v>
+        <v>0.01930841238990189</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03199325598799296</v>
+        <v>0.03199335982430229</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.008804349278035639</v>
+        <v>-0.007969966380674043</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01641152386519484</v>
+        <v>-0.01558354538424334</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01312234613032315</v>
+        <v>-0.01229169481919934</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-6.474168069414699e-05</v>
+        <v>0.0007769001683284316</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715175578024987</v>
+        <v>0.03715195976610053</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1659,41 +1659,41 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>COMPLETED_SESSION</t>
+        </is>
+      </c>
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2026-10-12T13:59:42Z</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>LIVE_PRICE_OVERLAY</t>
-        </is>
-      </c>
-      <c r="X6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="AA6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
       <c r="AD6" t="inlineStr">
         <is>
           <t>2026-10-02</t>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="AN6" s="4" t="n">
-        <v>0.02931218220472731</v>
+        <v>0.0293120789335406</v>
       </c>
       <c r="AO6" t="n">
         <v>6</v>
@@ -1744,14 +1744,14 @@
         <v>0</v>
       </c>
       <c r="AR6" s="4" t="n">
-        <v>-0.002449175608860488</v>
+        <v>-0.002449382000601075</v>
       </c>
       <c r="AS6" s="4" t="n">
         <v>0.07056586290088451</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.3%, 3m -1.4%, 6m -0.5%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.2%, 3m -1.6%, 6m -0.8%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.22499999999999</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="AW6" t="n">
         <v>77.23</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>-6.474168069414699e-05</v>
+        <v>0.0007769001683284316</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-12T13:59:42Z</t>
+          <t>2026-10-12T20:10:00Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.682736428548965</v>
+        <v>0.6762609469330294</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.5531982722141466</v>
+        <v>0.5472212774293492</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.5178073620032786</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.175619168466796</v>
+        <v>0.1710951680448685</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1704808185113009</v>
+        <v>0.1659765914122233</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.02331712910138828</v>
+        <v>0.01937921515102459</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.01820835894283968</v>
+        <v>0.01429010448678558</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1847,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392375432301</v>
+        <v>0.2952392476428616</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1856,24 +1856,24 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T14:00:11Z</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.3027345657592035</v>
+        <v>0.3019368322259519</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>1</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.2952392375432301</v>
+        <v>0.2952392476428616</v>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +0.8%, 3m +15.4%, 6m +15.8%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +1.9%, 3m +16.6%, 6m +17.1%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>66.265</v>
+        <v>66.02</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>65.08</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.01820835894283968</v>
+        <v>0.01444376152427784</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T14:00:11Z</t>
+          <t>2026-10-12T20:14:23Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.01722429721334429</v>
+        <v>0.0175163315980511</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01866388124345386</v>
+        <v>-0.01838207705504857</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>-0.005794823306280783</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02909210759261371</v>
+        <v>-0.02881329801309584</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02567758741782233</v>
+        <v>-0.02539779731178737</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.01294406651549518</v>
+        <v>-0.01266061980347699</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0004788354721316779</v>
+        <v>0.0007661367554108178</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.004296483646738736</v>
+        <v>0.004296411608788464</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
@@ -2055,17 +2055,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-12T14:00:08Z</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2140,14 +2140,14 @@
         <v>0</v>
       </c>
       <c r="AR8" s="4" t="n">
-        <v>-0.005243235401598878</v>
+        <v>-0.005243163593030453</v>
       </c>
       <c r="AS8" s="4" t="n">
         <v>0.07056586290088451</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.8%, 3m -2.5%, 6m -2.7%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.3%, 3m -2.5%, 6m -2.9%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>104.47</v>
+        <v>104.5</v>
       </c>
       <c r="AW8" t="n">
         <v>104.42</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>0.0004788354721316779</v>
+        <v>0.0007661367554108178</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-12T14:00:08Z</t>
+          <t>2026-10-12T20:10:00Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.06339683951109465</v>
+        <v>0.0648590558596831</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07326065173171492</v>
+        <v>0.07473643124595597</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.03562827411857139</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.06245434623812995</v>
+        <v>0.06391526661796942</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.0246565692145122</v>
+        <v>0.02606551602676999</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.03633772711079453</v>
+        <v>0.03776273601710001</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.002412129565816601</v>
+        <v>0.003790489317711865</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2252,17 +2252,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-12T13:58:39Z</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +3.5%, 3m +1.8%, 6m +5.8%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +3.8%, 3m +2.6%, 6m +6.4%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>29.09</v>
+        <v>29.13</v>
       </c>
       <c r="AW9" t="n">
         <v>29.02</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>0.002412129565816601</v>
+        <v>0.003790489317711865</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-12T13:58:39Z</t>
+          <t>2026-10-12T20:10:00Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.06008220233230976</v>
+        <v>0.05997644544921044</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03776512149080613</v>
+        <v>0.03776498186211885</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03455961551286846</v>
+        <v>0.03466240463134262</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.0182483871092407</v>
+        <v>0.01824834816608645</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009041921358255101</v>
+        <v>0.009142313550212</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003098425581157693</v>
+        <v>0.002998637252971115</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0003981287946650536</v>
+        <v>9.949258780217463e-05</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
@@ -2532,14 +2532,24 @@
           <t>SGOV fills vacancies only; reserve-weight changes cannot trigger an exception.</t>
         </is>
       </c>
-      <c r="AV10" s="5" t="n"/>
-      <c r="AW10" s="5" t="n"/>
-      <c r="AX10" s="6" t="n"/>
-      <c r="AY10" s="5" t="n"/>
+      <c r="AV10" s="5" t="n">
+        <v>100.51</v>
+      </c>
+      <c r="AW10" s="5" t="n">
+        <v>100.51</v>
+      </c>
+      <c r="AX10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12T20:15:11Z</t>
+        </is>
+      </c>
       <c r="AZ10" s="5" t="n"/>
       <c r="BA10" s="5" t="inlineStr">
         <is>
-          <t>UNAVAILABLE: 504 Server Error: Gateway Timeout for url: https://api.tradestation.com/v3/marketdata/quotes/SGOV</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2605,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2653,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>QQQ 35.3%, SPY 34.4%, XLE 30.3%</t>
+          <t>QQQ 35.3%, SPY 34.5%, XLE 30.2%</t>
         </is>
       </c>
     </row>
@@ -2781,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.02109556111600264</v>
+        <v>0.02047908424604516</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.03801804373944129</v>
+        <v>0.03739135007928618</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.1403930872431869</v>
+        <v>0.1397045856105126</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2815,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.04695064696656281</v>
+        <v>0.0446751695785339</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.03995341943039032</v>
+        <v>0.03769315004961893</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.2136033867715275</v>
+        <v>0.2109657007711079</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2849,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.03147913235283095</v>
+        <v>-0.03098376082248899</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.06111872424211828</v>
+        <v>-0.06063851254000863</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.07967647019961377</v>
+        <v>-0.07920575026925813</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2883,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.04097600120370137</v>
+        <v>-0.04167816034305494</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.0276232701867527</v>
+        <v>0.02687088539567384</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1215775450202131</v>
+        <v>-0.122220690922455</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2917,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.01312234613032315</v>
+        <v>-0.01229169481919934</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01641152386519484</v>
+        <v>-0.01558354538424334</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.008804349278035639</v>
+        <v>-0.007969966380674043</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2951,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.02331712910138828</v>
+        <v>0.01937921515102459</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1704808185113009</v>
+        <v>0.1659765914122233</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.175619168466796</v>
+        <v>0.1710951680448685</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2985,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.01294406651549518</v>
+        <v>-0.01266061980347699</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.02567758741782233</v>
+        <v>-0.02539779731178737</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.02909210759261371</v>
+        <v>-0.02881329801309584</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3019,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.03633772711079453</v>
+        <v>0.03776273601710001</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.0246565692145122</v>
+        <v>0.02606551602676999</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.06245434623812995</v>
+        <v>0.06391526661796942</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3053,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003098425581157693</v>
+        <v>0.002998637252971115</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009041921358255101</v>
+        <v>0.009142313550212</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.0182483871092407</v>
+        <v>0.01824834816608645</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -3173,7 +3183,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.02933625610116319</v>
+        <v>0.02933614706677878</v>
       </c>
     </row>
     <row r="3">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.441644859750592</v>
+        <v>0.5077015768641757</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1717081148749577</v>
+        <v>0.2042488421456974</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1481941501433557</v>
+        <v>0.1748242391819608</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1397045856105126</v>
+        <v>0.1259773988310915</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.03739135007928618</v>
+        <v>0.03328907964258754</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.02047908424604516</v>
+        <v>0.02504596175528784</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.0007192673748025458</v>
+        <v>-0.0001220922760570842</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,12 +872,12 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13T14:00:07Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
@@ -960,7 +960,7 @@
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +2.0%, 3m +3.7%, 6m +14.0%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +2.1%, 3m +3.8%, 6m +14.0%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>778.02</v>
+        <v>778.005</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>778.57001</v>
+        <v>778.09998</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.000706436149525036</v>
+        <v>-0.0001220665755574668</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T20:15:00Z</t>
+          <t>2026-10-13T14:00:07Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.6121395255346795</v>
+        <v>0.6782011085297106</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2273543001034053</v>
+        <v>0.2673006615903133</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1748669211680143</v>
+        <v>0.2074137768771154</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.2109657007711079</v>
+        <v>0.1854484155523934</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.03769315004961893</v>
+        <v>0.03708144462883123</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.0446751695785339</v>
+        <v>0.04959930544116453</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.006961545116935364</v>
+        <v>-0.003297410326523975</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13T14:00:08Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>745.61</v>
+        <v>743.58</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>751.27002</v>
+        <v>746.03998</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.007533935668030511</v>
+        <v>-0.00329738360670695</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T20:14:58Z</t>
+          <t>2026-10-13T14:00:08Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.06038579604577921</v>
+        <v>-0.0308384916219393</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.08420709225463763</v>
+        <v>-0.09604598708000545</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.05492511815624879</v>
+        <v>-0.06925285671078485</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.07920575026925813</v>
+        <v>-0.08130476286022914</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.06063851254000863</v>
+        <v>-0.05959976103690789</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.03098376082248899</v>
+        <v>-0.02878669095296382</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.0008976660682225024</v>
+        <v>0.003010890454836712</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13T14:00:08Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
+        <v>78.285</v>
+      </c>
+      <c r="AW4" t="n">
         <v>78.05</v>
       </c>
-      <c r="AW4" t="n">
-        <v>77.98</v>
-      </c>
       <c r="AX4" s="4" t="n">
-        <v>0.0008976660682225024</v>
+        <v>0.003010890454836712</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-12T20:15:00Z</t>
+          <t>2026-10-13T14:00:08Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3390917373326792</v>
+        <v>0.3074055070976569</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.04575431683222497</v>
+        <v>0.03548981361074999</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.0912349834441617</v>
+        <v>0.06426094495015167</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.122220690922455</v>
+        <v>-0.1412523309892381</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.02687088539567384</v>
+        <v>0.02650731838324161</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.04167816034305494</v>
+        <v>-0.02703390693412067</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.006318581309480487</v>
+        <v>0.0001831741462776648</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13T14:00:08Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>382.15</v>
+        <v>382.22</v>
       </c>
       <c r="AW5" t="n">
-        <v>384.57999</v>
+        <v>382.14999</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.006318555471385934</v>
+        <v>0.0001832003188069198</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-12T20:13:41Z</t>
+          <t>2026-10-13T14:00:08Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.08497290083247799</v>
+        <v>0.1006993748912166</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01930841238990189</v>
+        <v>0.02317801006731468</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03199335982430229</v>
+        <v>0.03713548216353568</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.007969966380674043</v>
+        <v>-0.01297514147207113</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01558354538424334</v>
+        <v>-0.01922161880456519</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01229169481919934</v>
+        <v>-0.01345771341956659</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.0007769001683284316</v>
+        <v>-0.002070125501358655</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13T14:00:09Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
+        <v>77.13</v>
+      </c>
+      <c r="AW6" t="n">
         <v>77.29000000000001</v>
       </c>
-      <c r="AW6" t="n">
-        <v>77.23</v>
-      </c>
       <c r="AX6" s="4" t="n">
-        <v>0.0007769001683284316</v>
+        <v>-0.002070125501358655</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-12T20:10:00Z</t>
+          <t>2026-10-13T14:00:09Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.6762609469330294</v>
+        <v>0.8125663272351717</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.5472212774293492</v>
+        <v>0.610353703643945</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.5178073620032786</v>
+        <v>0.5484088074653759</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.1710951680448685</v>
+        <v>0.2081420318730405</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1659765914122233</v>
+        <v>0.1878151796657588</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.01937921515102459</v>
+        <v>0.04000551784510198</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.01429010448678558</v>
+        <v>0.01068019996970149</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13T14:00:08Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>66.02</v>
+        <v>66.715</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>65.08</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.01444376152427784</v>
+        <v>0.01068019996970149</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T20:14:23Z</t>
+          <t>2026-10-13T14:00:08Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.0175163315980511</v>
+        <v>0.02967352656844846</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01838207705504857</v>
+        <v>-0.0219089170497796</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.005794823306280783</v>
+        <v>-0.009459293733445118</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02881329801309584</v>
+        <v>-0.0310830258052045</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02539779731178737</v>
+        <v>-0.02603205419196397</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.01266061980347699</v>
+        <v>-0.01256851256851255</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0007661367554108178</v>
+        <v>-9.569377990437111e-05</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13T14:00:07Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
+        <v>104.49</v>
+      </c>
+      <c r="AW8" t="n">
         <v>104.5</v>
       </c>
-      <c r="AW8" t="n">
-        <v>104.42</v>
-      </c>
       <c r="AX8" s="4" t="n">
-        <v>0.0007661367554108178</v>
+        <v>-9.569377990437111e-05</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-12T20:10:00Z</t>
+          <t>2026-10-13T14:00:07Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.0648590558596831</v>
+        <v>0.08492674976986958</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07473643124595597</v>
+        <v>0.0775357324746957</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.03562827411857139</v>
+        <v>0.04453481017935923</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.06391526661796942</v>
+        <v>0.06368960468521223</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.02606551602676999</v>
+        <v>0.02867256637168136</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.03776273601710001</v>
+        <v>0.0315938942137024</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.003790489317711865</v>
+        <v>-0.002403020940611067</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13T13:59:54Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="AW9" t="n">
         <v>29.13</v>
       </c>
-      <c r="AW9" t="n">
-        <v>29.02</v>
-      </c>
       <c r="AX9" s="4" t="n">
-        <v>0.003790489317711865</v>
+        <v>-0.002403020940611067</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-12T20:10:00Z</t>
+          <t>2026-10-13T13:59:54Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05997644544921044</v>
+        <v>0.05997749994229196</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03776498186211885</v>
+        <v>0.03724978596082273</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03466240463134262</v>
+        <v>0.03425059365547645</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01824834816608645</v>
+        <v>0.01824936114693432</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009142313550212</v>
+        <v>0.008942591837899139</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.002998637252971115</v>
+        <v>0.002899870035119712</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>9.949258780217463e-05</v>
+        <v>9.948269001913701e-07</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13T14:00:11Z</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.51</v>
+        <v>100.5201</v>
       </c>
       <c r="AW10" s="5" t="n">
-        <v>100.51</v>
+        <v>100.52</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>0</v>
+        <v>9.948269001913701e-07</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-12T20:15:11Z</t>
+          <t>2026-10-13T14:00:11Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.02047908424604516</v>
+        <v>0.02504596175528784</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.03739135007928618</v>
+        <v>0.03328907964258754</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.1397045856105126</v>
+        <v>0.1259773988310915</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.0446751695785339</v>
+        <v>0.04959930544116453</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.03769315004961893</v>
+        <v>0.03708144462883123</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.2109657007711079</v>
+        <v>0.1854484155523934</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.03098376082248899</v>
+        <v>-0.02878669095296382</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.06063851254000863</v>
+        <v>-0.05959976103690789</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.07920575026925813</v>
+        <v>-0.08130476286022914</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.04167816034305494</v>
+        <v>-0.02703390693412067</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02687088539567384</v>
+        <v>0.02650731838324161</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.122220690922455</v>
+        <v>-0.1412523309892381</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.01229169481919934</v>
+        <v>-0.01345771341956659</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01558354538424334</v>
+        <v>-0.01922161880456519</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.007969966380674043</v>
+        <v>-0.01297514147207113</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.01937921515102459</v>
+        <v>0.04000551784510198</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1659765914122233</v>
+        <v>0.1878151796657588</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.1710951680448685</v>
+        <v>0.2081420318730405</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.01266061980347699</v>
+        <v>-0.01256851256851255</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.02539779731178737</v>
+        <v>-0.02603205419196397</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.02881329801309584</v>
+        <v>-0.0310830258052045</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.03776273601710001</v>
+        <v>0.0315938942137024</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.02606551602676999</v>
+        <v>0.02867256637168136</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.06391526661796942</v>
+        <v>0.06368960468521223</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.002998637252971115</v>
+        <v>0.002899870035119712</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009142313550212</v>
+        <v>0.008942591837899139</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01824834816608645</v>
+        <v>0.01824936114693432</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.5077015768641757</v>
+        <v>0.5076339284319713</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.2042488421456974</v>
+        <v>0.2041947805402633</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1748242391819608</v>
+        <v>0.1748243501727236</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1259773988310915</v>
+        <v>0.1259267446464023</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.03328907964258754</v>
+        <v>0.03324259521409734</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.02504596175528784</v>
+        <v>0.02499984815876677</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.0001220922760570842</v>
+        <v>-0.0001670736409201679</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -858,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512030450774</v>
+        <v>0.3464512197561446</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -867,24 +867,24 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T14:00:07Z</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.3451433174288588</v>
+        <v>0.3462425711427781</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>0.3464512030450774</v>
+        <v>0.3464512197561446</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -953,14 +953,14 @@
         <v>0</v>
       </c>
       <c r="AR2" s="3" t="n">
-        <v>-0.01897026129460522</v>
+        <v>-0.01897036781629335</v>
       </c>
       <c r="AS2" s="3" t="n">
         <v>0.07056586290088451</v>
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +2.1%, 3m +3.8%, 6m +14.0%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +2.5%, 3m +3.3%, 6m +12.6%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>778.005</v>
+        <v>778.01</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>778.09998</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.0001220665755574668</v>
+        <v>-0.0001156406661261267</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T14:00:07Z</t>
+          <t>2026-10-13T20:16:27Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.6782011085297106</v>
+        <v>0.6781786549083393</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2673006615903133</v>
+        <v>0.2672836183580911</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0.2074137768771154</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.1854484155523934</v>
+        <v>0.1854324731061798</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.03708144462883123</v>
+        <v>0.03706749748871685</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.04959930544116453</v>
+        <v>0.04958518995519889</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.003297410326523975</v>
+        <v>-0.003310814433542308</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.1982246540542743</v>
+        <v>0.1982245316673374</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>2</v>
@@ -1057,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.358309549312061</v>
+        <v>0.3583095304551976</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T14:00:08Z</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.3529198503451894</v>
+        <v>0.3551160176032208</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0.358309549312061</v>
+        <v>0.3583095304551976</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +4.5%, 3m +3.8%, 6m +21.1%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +5.0%, 3m +3.7%, 6m +18.5%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>743.58</v>
+        <v>743.66</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>746.03998</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.00329738360670695</v>
+        <v>-0.003190150747685139</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T14:00:08Z</t>
+          <t>2026-10-13T20:16:26Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.0308384916219393</v>
+        <v>-0.02978601572028527</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.09604598708000545</v>
+        <v>-0.09506457493079412</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.06925285671078485</v>
+        <v>-0.06925293870618987</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.08130476286022914</v>
+        <v>-0.08030726531718912</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.05959976103690789</v>
+        <v>-0.05857869671664384</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.02878669095296382</v>
+        <v>-0.02773217053054566</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.003010890454836712</v>
+        <v>0.004099935938500998</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.03802938342376228</v>
+        <v>-0.038029469654283</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-13T14:00:08Z</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1350,14 +1350,14 @@
         <v>0</v>
       </c>
       <c r="AR4" s="4" t="n">
-        <v>-0.01323367459355407</v>
+        <v>-0.01323358907280725</v>
       </c>
       <c r="AS4" s="4" t="n">
         <v>0.07056586290088451</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -3.1%, 3m -6.1%, 6m -7.9%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -2.8%, 3m -5.9%, 6m -8.0%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>78.285</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AW4" t="n">
         <v>78.05</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>0.003010890454836712</v>
+        <v>0.004484304932735439</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-13T14:00:08Z</t>
+          <t>2026-10-13T20:16:26Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3074055070976569</v>
+        <v>0.3055242004446725</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.03548981361074999</v>
+        <v>0.03399978326831388</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.06426094495015167</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1412523309892381</v>
+        <v>-0.1424880361275247</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.02650731838324161</v>
+        <v>0.02503021350879542</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.02703390693412067</v>
+        <v>-0.0284339680276956</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.0001831741462776648</v>
+        <v>-0.001256051288760829</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-13T14:00:08Z</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -4.2%, 3m +2.7%, 6m -12.2%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -2.8%, 3m +2.5%, 6m -14.2%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>382.22</v>
+        <v>381.46</v>
       </c>
       <c r="AW5" t="n">
         <v>382.14999</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>0.0001832003188069198</v>
+        <v>-0.001805547607105829</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-13T14:00:08Z</t>
+          <t>2026-10-13T20:16:10Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1006993748912166</v>
+        <v>0.1001284269654983</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.02317801006731468</v>
+        <v>0.02264728138299521</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03713548216353568</v>
+        <v>0.0371353771963856</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01297514147207113</v>
+        <v>-0.01348692113628724</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01922161880456519</v>
+        <v>-0.01973016022992669</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01345771341956659</v>
+        <v>-0.01396933913541276</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.002070125501358655</v>
+        <v>-0.002587656876698152</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715195976610053</v>
+        <v>0.03715185591311232</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1659,17 +1659,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-13T14:00:09Z</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="AN6" s="4" t="n">
-        <v>0.0293120789335406</v>
+        <v>0.02931218220472731</v>
       </c>
       <c r="AO6" t="n">
         <v>6</v>
@@ -1744,14 +1744,14 @@
         <v>0</v>
       </c>
       <c r="AR6" s="4" t="n">
-        <v>-0.002449382000601075</v>
+        <v>-0.002449381849988663</v>
       </c>
       <c r="AS6" s="4" t="n">
         <v>0.07056586290088451</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.2%, 3m -1.6%, 6m -0.8%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.4%, 3m -2.0%, 6m -1.3%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.13</v>
+        <v>77.09</v>
       </c>
       <c r="AW6" t="n">
         <v>77.29000000000001</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.002070125501358655</v>
+        <v>-0.002587656876698152</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-13T14:00:09Z</t>
+          <t>2026-10-13T20:13:10Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8125663272351717</v>
+        <v>0.8249281301114664</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.610353703643945</v>
+        <v>0.6213364052126775</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.5484088074653759</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2081420318730405</v>
+        <v>0.2163817115618032</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1878151796657588</v>
+        <v>0.1959161450670617</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.04000551784510198</v>
+        <v>0.04709841315529495</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.01068019996970149</v>
+        <v>0.01757309498560811</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.4639560631420809</v>
+        <v>0.4639559345596878</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>1</v>
@@ -1847,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392476428616</v>
+        <v>0.2952392497886577</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1856,24 +1856,24 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T14:00:08Z</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.3019368322259519</v>
+        <v>0.2986414112540011</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>1</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.2952392476428616</v>
+        <v>0.2952392497886577</v>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
@@ -1942,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="AR7" s="3" t="n">
-        <v>0.002121514394037627</v>
+        <v>0.002121645268243544</v>
       </c>
       <c r="AS7" s="3" t="n">
         <v>0.07056586290088451</v>
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +1.9%, 3m +16.6%, 6m +17.1%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +4.7%, 3m +19.6%, 6m +21.6%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>66.715</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>66.01000000000001</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.01068019996970149</v>
+        <v>0.01727011058930472</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T14:00:08Z</t>
+          <t>2026-10-13T20:15:58Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.02967352656844846</v>
+        <v>0.03036332604074055</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.0219089170497796</v>
+        <v>-0.02125360381933095</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.009459293733445118</v>
+        <v>-0.00945922299312929</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.0310830258052045</v>
+        <v>-0.03043399698982108</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02603205419196397</v>
+        <v>-0.02537957303389549</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.01256851256851255</v>
+        <v>-0.01190701190701182</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-9.569377990437111e-05</v>
+        <v>0.0005741626794257826</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.004296411608788464</v>
+        <v>0.004296483646738736</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
@@ -2055,17 +2055,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-13T14:00:07Z</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="AN8" s="4" t="n">
-        <v>-0.002359241806851986</v>
+        <v>-0.00235917039296718</v>
       </c>
       <c r="AO8" t="n">
         <v>7</v>
@@ -2140,14 +2140,14 @@
         <v>0</v>
       </c>
       <c r="AR8" s="4" t="n">
-        <v>-0.005243163593030453</v>
+        <v>-0.005243092179145648</v>
       </c>
       <c r="AS8" s="4" t="n">
         <v>0.07056586290088451</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.3%, 3m -2.5%, 6m -2.9%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.2%, 3m -2.5%, 6m -3.0%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>104.49</v>
+        <v>104.56</v>
       </c>
       <c r="AW8" t="n">
         <v>104.5</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>-9.569377990437111e-05</v>
+        <v>0.0005741626794257826</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-13T14:00:07Z</t>
+          <t>2026-10-13T20:10:00Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.08492674976986958</v>
+        <v>0.08343338879289797</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.0775357324746957</v>
+        <v>0.07605254495580427</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.04453481017935923</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.06368960468521223</v>
+        <v>0.0622254758418741</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.02867256637168136</v>
+        <v>0.02725663716814153</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.0315938942137024</v>
+        <v>0.03017394391196304</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.002403020940611067</v>
+        <v>-0.003776175763817391</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2252,17 +2252,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-13T13:59:54Z</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +3.8%, 3m +2.6%, 6m +6.4%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +3.0%, 3m +2.7%, 6m +6.2%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>29.06</v>
+        <v>29.02</v>
       </c>
       <c r="AW9" t="n">
         <v>29.13</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>-0.002403020940611067</v>
+        <v>-0.003776175763817391</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-13T13:59:54Z</t>
+          <t>2026-10-13T20:10:00Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05997749994229196</v>
+        <v>0.05997636017259067</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03724978596082273</v>
+        <v>0.03724883573674798</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03425059365547645</v>
+        <v>0.03425067507833002</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01824936114693432</v>
+        <v>0.01824842686070727</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.008942591837899139</v>
+        <v>0.008941588115666477</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.002899870035119712</v>
+        <v>0.002898872324343493</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>9.948269001913701e-07</v>
+        <v>0</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13T14:00:11Z</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.5201</v>
+        <v>100.5298</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.52</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>9.948269001913701e-07</v>
+        <v>9.749303621164884e-05</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13T14:00:11Z</t>
+          <t>2026-10-13T20:16:20Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>QQQ 35.3%, SPY 34.5%, XLE 30.2%</t>
+          <t>QQQ 35.5%, SPY 34.6%, XLE 29.9%</t>
         </is>
       </c>
     </row>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.02504596175528784</v>
+        <v>0.02499984815876677</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.03328907964258754</v>
+        <v>0.03324259521409734</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.1259773988310915</v>
+        <v>0.1259267446464023</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.04959930544116453</v>
+        <v>0.04958518995519889</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.03708144462883123</v>
+        <v>0.03706749748871685</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.1854484155523934</v>
+        <v>0.1854324731061798</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.02878669095296382</v>
+        <v>-0.02773217053054566</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.05959976103690789</v>
+        <v>-0.05857869671664384</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.08130476286022914</v>
+        <v>-0.08030726531718912</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.02703390693412067</v>
+        <v>-0.0284339680276956</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02650731838324161</v>
+        <v>0.02503021350879542</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1412523309892381</v>
+        <v>-0.1424880361275247</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.01345771341956659</v>
+        <v>-0.01396933913541276</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01922161880456519</v>
+        <v>-0.01973016022992669</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01297514147207113</v>
+        <v>-0.01348692113628724</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.04000551784510198</v>
+        <v>0.04709841315529495</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1878151796657588</v>
+        <v>0.1959161450670617</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.2081420318730405</v>
+        <v>0.2163817115618032</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.01256851256851255</v>
+        <v>-0.01190701190701182</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.02603205419196397</v>
+        <v>-0.02537957303389549</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.0310830258052045</v>
+        <v>-0.03043399698982108</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.0315938942137024</v>
+        <v>0.03017394391196304</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.02867256637168136</v>
+        <v>0.02725663716814153</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.06368960468521223</v>
+        <v>0.0622254758418741</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.002899870035119712</v>
+        <v>0.002898872324343493</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.008942591837899139</v>
+        <v>0.008941588115666477</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01824936114693432</v>
+        <v>0.01824842686070727</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.02933614706677878</v>
+        <v>0.02933603803237417</v>
       </c>
     </row>
     <row r="3">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.02285226703064946</v>
+        <v>0.0228523735523376</v>
       </c>
     </row>
     <row r="4">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.5076339284319713</v>
+        <v>0.4725039844992722</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.2041947805402633</v>
+        <v>0.1790298529062497</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1748243501727236</v>
+        <v>0.1517629222140719</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1259267446464023</v>
+        <v>0.1105493317623809</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.03324259521409734</v>
+        <v>0.03276920078504042</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.02499984815876677</v>
+        <v>0.02367408271813587</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.0001670736409201679</v>
+        <v>-0.005925373709849469</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,12 +872,12 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14T14:00:08Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>778.01</v>
+        <v>773.4</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>778.09998</v>
+        <v>778.01001</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.0001156406661261267</v>
+        <v>-0.005925386486993922</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T20:16:27Z</t>
+          <t>2026-10-14T14:00:08Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.6781786549083393</v>
+        <v>0.6312664835665531</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2672836183580911</v>
+        <v>0.2284823017995394</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.2074137768771154</v>
+        <v>0.1745876292366697</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.1854324731061798</v>
+        <v>0.1573216764925673</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.03706749748871685</v>
+        <v>0.04380975360211914</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.04958518995519889</v>
+        <v>0.0458839095707948</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.003310814433542308</v>
+        <v>-0.01004612881100642</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14T14:00:08Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>743.66</v>
+        <v>736.1</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>746.03998</v>
+        <v>743.57001</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.003190150747685139</v>
+        <v>-0.01004614212453248</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T20:16:26Z</t>
+          <t>2026-10-14T14:00:08Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.02978601572028527</v>
+        <v>-0.04057507192929999</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.09506457493079412</v>
+        <v>-0.09976387674416076</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.06925293870618987</v>
+        <v>-0.07127049489558868</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.08030726531718912</v>
+        <v>-0.08158646601696906</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.05857869671664384</v>
+        <v>-0.06365084156544187</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.02773217053054566</v>
+        <v>-0.03067995761087472</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.004099935938500998</v>
+        <v>-0.005741993109608323</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14T14:00:07Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>78.40000000000001</v>
+        <v>77.92</v>
       </c>
       <c r="AW4" t="n">
-        <v>78.05</v>
+        <v>78.37</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>0.004484304932735439</v>
+        <v>-0.005741993109608323</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-13T20:16:26Z</t>
+          <t>2026-10-14T14:00:07Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1387,7 +1387,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3055242004446725</v>
+        <v>0.2576108481858155</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.03399978326831388</v>
+        <v>-0.009019016636250599</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.06426094495015167</v>
+        <v>0.0424766589965353</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1424880361275247</v>
+        <v>-0.1493438677745992</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.02503021350879542</v>
+        <v>0.02663305567733465</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.0284339680276956</v>
+        <v>-0.04939743752378534</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.001256051288760829</v>
+        <v>-0.01831425053056313</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14T14:00:09Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>381.46</v>
+        <v>374.68</v>
       </c>
       <c r="AW5" t="n">
-        <v>382.14999</v>
+        <v>381.67001</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.001805547607105829</v>
+        <v>-0.01831427625136173</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-13T20:16:10Z</t>
+          <t>2026-10-14T14:00:09Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1001284269654983</v>
+        <v>0.09242041646416244</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.02264728138299521</v>
+        <v>0.0122047209544287</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0371353771963856</v>
+        <v>0.02872083243217571</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01348692113628724</v>
+        <v>-0.01696554859646937</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01973016022992669</v>
+        <v>-0.02354972997785687</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01396933913541276</v>
+        <v>-0.01605499855456249</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.002587656876698152</v>
+        <v>-0.00402127383577644</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14T14:00:10Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
+        <v>76.78</v>
+      </c>
+      <c r="AW6" t="n">
         <v>77.09</v>
       </c>
-      <c r="AW6" t="n">
-        <v>77.29000000000001</v>
-      </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.002587656876698152</v>
+        <v>-0.00402127383577644</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-13T20:13:10Z</t>
+          <t>2026-10-14T14:00:10Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8249281301114664</v>
+        <v>0.784495192274554</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6213364052126775</v>
+        <v>0.603135491682707</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.5484088074653759</v>
+        <v>0.5607573683842588</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2163817115618032</v>
+        <v>0.2232519919114404</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1959161450670617</v>
+        <v>0.1876561142535822</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.04709841315529495</v>
+        <v>0.02715228142239634</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.01757309498560811</v>
+        <v>0.001785714285714057</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14T14:00:10Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +4.7%, 3m +19.6%, 6m +21.6%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +4.8%, 3m +19.6%, 6m +21.7%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>67.15000000000001</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>66.01000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.01727011058930472</v>
+        <v>0.001785714285714057</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T20:15:58Z</t>
+          <t>2026-10-14T14:00:10Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.03036332604074055</v>
+        <v>0.02756832483803917</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02125360381933095</v>
+        <v>-0.02599261144360798</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.00945922299312929</v>
+        <v>-0.0122202786235851</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.03043399698982108</v>
+        <v>-0.0318376679993535</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02537957303389549</v>
+        <v>-0.02676273152783959</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.01190701190701182</v>
+        <v>-0.01394271670290204</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0005741626794257826</v>
+        <v>-0.002343152257077374</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14T14:00:11Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
+        <v>104.315</v>
+      </c>
+      <c r="AW8" t="n">
         <v>104.56</v>
       </c>
-      <c r="AW8" t="n">
-        <v>104.5</v>
-      </c>
       <c r="AX8" s="4" t="n">
-        <v>0.0005741626794257826</v>
+        <v>-0.002343152257077374</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-13T20:10:00Z</t>
+          <t>2026-10-14T14:00:11Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2177,7 +2177,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.08343338879289797</v>
+        <v>0.1008392682570802</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07605254495580427</v>
+        <v>0.07960123042221623</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.04453481017935923</v>
+        <v>0.04265032366470134</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.0622254758418741</v>
+        <v>0.07072554049102231</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.02725663716814153</v>
+        <v>0.03105504587155949</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.03017394391196304</v>
+        <v>0.0354394046775337</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.003776175763817391</v>
+        <v>0.006895244658855937</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14T14:00:09Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
+        <v>29.2201</v>
+      </c>
+      <c r="AW9" t="n">
         <v>29.02</v>
       </c>
-      <c r="AW9" t="n">
-        <v>29.13</v>
-      </c>
       <c r="AX9" s="4" t="n">
-        <v>-0.003776175763817391</v>
+        <v>0.006895244658855937</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-13T20:10:00Z</t>
+          <t>2026-10-14T14:00:09Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05997636017259067</v>
+        <v>0.05960723364016562</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03724883573674798</v>
+        <v>0.03750667528649232</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03425067507833002</v>
+        <v>0.03435341895380994</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01824842686070727</v>
+        <v>0.01819779009228628</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.008941588115666477</v>
+        <v>0.008991721443684764</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.002898872324343493</v>
+        <v>0.003048528940786444</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0</v>
+        <v>0.0001492240350178253</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14T14:00:12Z</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.5298</v>
+        <v>100.535</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.52</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>9.749303621164884e-05</v>
+        <v>0.0001492240350178253</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13T20:16:20Z</t>
+          <t>2026-10-14T14:00:12Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.02499984815876677</v>
+        <v>0.02367408271813587</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.03324259521409734</v>
+        <v>0.03276920078504042</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.1259267446464023</v>
+        <v>0.1105493317623809</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.04958518995519889</v>
+        <v>0.0458839095707948</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.03706749748871685</v>
+        <v>0.04380975360211914</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.1854324731061798</v>
+        <v>0.1573216764925673</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.02773217053054566</v>
+        <v>-0.03067995761087472</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.05857869671664384</v>
+        <v>-0.06365084156544187</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.08030726531718912</v>
+        <v>-0.08158646601696906</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.0284339680276956</v>
+        <v>-0.04939743752378534</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02503021350879542</v>
+        <v>0.02663305567733465</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1424880361275247</v>
+        <v>-0.1493438677745992</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.01396933913541276</v>
+        <v>-0.01605499855456249</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01973016022992669</v>
+        <v>-0.02354972997785687</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01348692113628724</v>
+        <v>-0.01696554859646937</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.04709841315529495</v>
+        <v>0.02715228142239634</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1959161450670617</v>
+        <v>0.1876561142535822</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.2163817115618032</v>
+        <v>0.2232519919114404</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.01190701190701182</v>
+        <v>-0.01394271670290204</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.02537957303389549</v>
+        <v>-0.02676273152783959</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.03043399698982108</v>
+        <v>-0.0318376679993535</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.03017394391196304</v>
+        <v>0.0354394046775337</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.02725663716814153</v>
+        <v>0.03105504587155949</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.0622254758418741</v>
+        <v>0.07072554049102231</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.002898872324343493</v>
+        <v>0.003048528940786444</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.008941588115666477</v>
+        <v>0.008991721443684764</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01824842686070727</v>
+        <v>0.01819779009228628</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4725039844992722</v>
+        <v>0.4647740049581979</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1790298529062497</v>
+        <v>0.1728404797451439</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0.1517629222140719</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1105493317623809</v>
+        <v>0.1047194503466125</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.03276920078504042</v>
+        <v>0.0273476298577231</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.02367408271813587</v>
+        <v>0.01830025704469973</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.005925373709849469</v>
+        <v>-0.0111438156321898</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -867,24 +867,24 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T14:00:08Z</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.3462425711427781</v>
+        <v>0.3449780561209737</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>0.3443126610995251</v>
+        <v>0.3443126487452514</v>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
@@ -953,14 +953,14 @@
         <v>0</v>
       </c>
       <c r="AR2" s="3" t="n">
-        <v>-0.01897036781629335</v>
+        <v>-0.01897026129460522</v>
       </c>
       <c r="AS2" s="3" t="n">
         <v>0.07056586290088451</v>
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +2.5%, 3m +3.3%, 6m +12.6%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +1.8%, 3m +2.7%, 6m +10.5%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>773.4</v>
+        <v>768.9400000000001</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>778.01001</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.005925386486993922</v>
+        <v>-0.01165796054474921</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T14:00:08Z</t>
+          <t>2026-10-14T20:15:07Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.6312664835665531</v>
+        <v>0.6154214144760752</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2284823017995394</v>
+        <v>0.2165494941980077</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1745876292366697</v>
+        <v>0.1745875095908531</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.1573216764925673</v>
+        <v>0.1460802011673101</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.04380975360211914</v>
+        <v>0.03367085978571493</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.0458839095707948</v>
+        <v>0.03572486874287595</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.01004612881100642</v>
+        <v>-0.01966190136772594</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T14:00:08Z</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.3551160176032208</v>
+        <v>0.3511620818355983</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>0.3529527731412714</v>
+        <v>0.3529527963579562</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="AM3" s="2" t="n"/>
       <c r="AN3" s="3" t="n">
-        <v>0.1632844869027379</v>
+        <v>0.1632846035697191</v>
       </c>
       <c r="AO3" s="2" t="n">
         <v>2</v>
@@ -1152,14 +1152,14 @@
         <v>0</v>
       </c>
       <c r="AR3" s="3" t="n">
-        <v>-0.01670834453847925</v>
+        <v>-0.01670822787149806</v>
       </c>
       <c r="AS3" s="3" t="n">
         <v>0.07056586290088451</v>
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +5.0%, 3m +3.7%, 6m +18.5%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +3.6%, 3m +3.4%, 6m +14.6%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>736.1</v>
+        <v>727.77</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>743.57001</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.01004614212453248</v>
+        <v>-0.0212488532182733</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T14:00:08Z</t>
+          <t>2026-10-14T20:15:06Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.04057507192929999</v>
+        <v>-0.028631420870743</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.09976387674416076</v>
+        <v>-0.08855729923500377</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.07127049489558868</v>
+        <v>-0.07127065862124093</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.08158646601696906</v>
+        <v>-0.0701533597112417</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.06365084156544187</v>
+        <v>-0.05199454429026829</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.03067995761087472</v>
+        <v>-0.01861321683678019</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.005741993109608323</v>
+        <v>0.006635192037769411</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-14T14:00:07Z</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="AN4" s="4" t="n">
-        <v>-0.05671730508466388</v>
+        <v>-0.05671722070931096</v>
       </c>
       <c r="AO4" t="n">
         <v>8</v>
@@ -1350,14 +1350,14 @@
         <v>0</v>
       </c>
       <c r="AR4" s="4" t="n">
-        <v>-0.01323358907280725</v>
+        <v>-0.01323350469745432</v>
       </c>
       <c r="AS4" s="4" t="n">
         <v>0.07056586290088451</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -2.8%, 3m -5.9%, 6m -8.0%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.9%, 3m -5.2%, 6m -7.0%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>77.92</v>
+        <v>78.78</v>
       </c>
       <c r="AW4" t="n">
         <v>78.37</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>-0.005741993109608323</v>
+        <v>0.00523159372208748</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-14T14:00:07Z</t>
+          <t>2026-10-14T20:15:01Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.2576108481858155</v>
+        <v>0.2620078541939381</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.009019016636250599</v>
+        <v>-0.005554233119098528</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.0424766589965353</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1493438677745992</v>
+        <v>-0.1463697043999455</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.02663305567733465</v>
+        <v>0.03022249013590539</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.04939743752378534</v>
+        <v>-0.04607382976024343</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.01831425053056313</v>
+        <v>-0.01488196609636594</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-14T14:00:09Z</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -2.8%, 3m +2.5%, 6m -14.2%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -4.6%, 3m +3.0%, 6m -14.6%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>374.68</v>
+        <v>375.81</v>
       </c>
       <c r="AW5" t="n">
         <v>381.67001</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.01831427625136173</v>
+        <v>-0.0153536034963816</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-14T14:00:09Z</t>
+          <t>2026-10-14T20:14:25Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.09242041646416244</v>
+        <v>0.09284749160330219</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.0122047209544287</v>
+        <v>0.01260052195833539</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.02872083243217571</v>
+        <v>0.0287211428375711</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01696554859646937</v>
+        <v>-0.01658154679983925</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.02354972997785687</v>
+        <v>-0.0231682995145327</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01605499855456249</v>
+        <v>-0.01567054492023889</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.00402127383577644</v>
+        <v>-0.003632118303281917</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1659,17 +1659,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-14T14:00:10Z</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="AN6" s="4" t="n">
-        <v>0.02931218220472731</v>
+        <v>0.02931197566237409</v>
       </c>
       <c r="AO6" t="n">
         <v>6</v>
@@ -1744,14 +1744,14 @@
         <v>0</v>
       </c>
       <c r="AR6" s="4" t="n">
-        <v>-0.002449381849988663</v>
+        <v>-0.002449485271767582</v>
       </c>
       <c r="AS6" s="4" t="n">
         <v>0.07056586290088451</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.4%, 3m -2.0%, 6m -1.3%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.6%, 3m -2.3%, 6m -1.7%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>76.78</v>
+        <v>76.81</v>
       </c>
       <c r="AW6" t="n">
         <v>77.09</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.00402127383577644</v>
+        <v>-0.003632118303281917</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-14T14:00:10Z</t>
+          <t>2026-10-14T20:10:00Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.784495192274554</v>
+        <v>0.7927129272686206</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.603135491682707</v>
+        <v>0.6105177258244425</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.5607573683842588</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2232519919114404</v>
+        <v>0.2288849110661129</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1876561142535822</v>
+        <v>0.1931251189389449</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.02715228142239634</v>
+        <v>0.03188218646162611</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.001785714285714057</v>
+        <v>0.006398809523809446</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1856,24 +1856,24 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T14:00:10Z</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2986414112540011</v>
+        <v>0.303859862043428</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.3027345657592035</v>
+        <v>0.3027345548967924</v>
       </c>
       <c r="AH7" s="2" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +4.8%, 3m +19.6%, 6m +21.7%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +3.2%, 3m +19.3%, 6m +22.9%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>67.31999999999999</v>
+        <v>67.73</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>67.2</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.001785714285714057</v>
+        <v>0.007886904761904789</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T14:00:10Z</t>
+          <t>2026-10-14T20:15:05Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.02756832483803917</v>
+        <v>0.0325427370926803</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02599261144360798</v>
+        <v>-0.02127747761551657</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.0122202786235851</v>
+        <v>-0.01222041935647289</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.0318376679993535</v>
+        <v>-0.02715082904259425</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02676273152783959</v>
+        <v>-0.02205118649041982</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.01394271670290204</v>
+        <v>-0.009169108611400079</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.002343152257077374</v>
+        <v>0.002486610558530833</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2055,17 +2055,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-14T14:00:11Z</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="AN8" s="4" t="n">
-        <v>-0.00235917039296718</v>
+        <v>-0.002359241806851986</v>
       </c>
       <c r="AO8" t="n">
         <v>7</v>
@@ -2140,14 +2140,14 @@
         <v>0</v>
       </c>
       <c r="AR8" s="4" t="n">
-        <v>-0.005243092179145648</v>
+        <v>-0.005243235401598878</v>
       </c>
       <c r="AS8" s="4" t="n">
         <v>0.07056586290088451</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.2%, 3m -2.5%, 6m -3.0%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -0.9%, 3m -2.2%, 6m -2.7%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>104.315</v>
+        <v>104.82</v>
       </c>
       <c r="AW8" t="n">
         <v>104.56</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>-0.002343152257077374</v>
+        <v>0.002486610558530833</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-14T14:00:11Z</t>
+          <t>2026-10-14T20:10:00Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1008392682570802</v>
+        <v>0.0970680966747608</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07960123042221623</v>
+        <v>0.07590281449738168</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.04265032366470134</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.07072554049102231</v>
+        <v>0.06705753023085381</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.03105504587155949</v>
+        <v>0.02752293577981657</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.0354394046775337</v>
+        <v>0.03189227498228209</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.006895244658855937</v>
+        <v>0.00344589937973816</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2252,17 +2252,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-14T14:00:09Z</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +3.0%, 3m +2.7%, 6m +6.2%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +3.2%, 3m +2.8%, 6m +6.7%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>29.2201</v>
+        <v>29.12</v>
       </c>
       <c r="AW9" t="n">
         <v>29.02</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>0.006895244658855937</v>
+        <v>0.00344589937973816</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-14T14:00:09Z</t>
+          <t>2026-10-14T20:10:00Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05960723364016562</v>
+        <v>0.05965976164778763</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03750667528649232</v>
+        <v>0.03755835625549975</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03435341895380994</v>
+        <v>0.03435350039285634</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01819779009228628</v>
+        <v>0.0182485077422776</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.008991721443684764</v>
+        <v>0.009041979823433355</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003048528940786444</v>
+        <v>0.00309841447960113</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0001492240350178253</v>
+        <v>0.0001989653800240632</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14T14:00:12Z</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.535</v>
+        <v>100.534</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.52</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>0.0001492240350178253</v>
+        <v>0.0001392757660167998</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14T14:00:12Z</t>
+          <t>2026-10-14T20:14:57Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>QQQ 35.5%, SPY 34.6%, XLE 29.9%</t>
+          <t>QQQ 35.1%, SPY 34.5%, XLE 30.4%</t>
         </is>
       </c>
     </row>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.02367408271813587</v>
+        <v>0.01830025704469973</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.03276920078504042</v>
+        <v>0.0273476298577231</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.1105493317623809</v>
+        <v>0.1047194503466125</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.0458839095707948</v>
+        <v>0.03572486874287595</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.04380975360211914</v>
+        <v>0.03367085978571493</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.1573216764925673</v>
+        <v>0.1460802011673101</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.03067995761087472</v>
+        <v>-0.01861321683678019</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.06365084156544187</v>
+        <v>-0.05199454429026829</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.08158646601696906</v>
+        <v>-0.0701533597112417</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.04939743752378534</v>
+        <v>-0.04607382976024343</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02663305567733465</v>
+        <v>0.03022249013590539</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1493438677745992</v>
+        <v>-0.1463697043999455</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.01605499855456249</v>
+        <v>-0.01567054492023889</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.02354972997785687</v>
+        <v>-0.0231682995145327</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01696554859646937</v>
+        <v>-0.01658154679983925</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.02715228142239634</v>
+        <v>0.03188218646162611</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1876561142535822</v>
+        <v>0.1931251189389449</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.2232519919114404</v>
+        <v>0.2288849110661129</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.01394271670290204</v>
+        <v>-0.009169108611400079</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.02676273152783959</v>
+        <v>-0.02205118649041982</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.0318376679993535</v>
+        <v>-0.02715082904259425</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.0354394046775337</v>
+        <v>0.03189227498228209</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.03105504587155949</v>
+        <v>0.02752293577981657</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.07072554049102231</v>
+        <v>0.06705753023085381</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003048528940786444</v>
+        <v>0.00309841447960113</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.008991721443684764</v>
+        <v>0.009041979823433355</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01819779009228628</v>
+        <v>0.0182485077422776</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.02933603803237417</v>
+        <v>0.02933602385378342</v>
       </c>
     </row>
     <row r="3">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.0228523735523376</v>
+        <v>0.02285226703064946</v>
       </c>
     </row>
     <row r="4">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4647740049581979</v>
+        <v>0.4435535389862164</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1728404797451439</v>
+        <v>0.1684901579315681</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1517629222140719</v>
+        <v>0.1480863433432313</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1047194503466125</v>
+        <v>0.09658257601647802</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.0273476298577231</v>
+        <v>0.03250552990519617</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.01830025704469973</v>
+        <v>0.01777202098661057</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.0111438156321898</v>
+        <v>-0.00526247401247415</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,12 +872,12 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15T14:00:08Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
@@ -960,7 +960,7 @@
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +1.8%, 3m +2.7%, 6m +10.5%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +1.9%, 3m +2.8%, 6m +10.5%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>768.9400000000001</v>
+        <v>765.55</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>778.01001</v>
+        <v>769.59998</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.01165796054474921</v>
+        <v>-0.005262448161706068</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T20:15:07Z</t>
+          <t>2026-10-15T14:00:08Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.6154214144760752</v>
+        <v>0.5792320508139734</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2165494941980077</v>
+        <v>0.2053863220496868</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1745875095908531</v>
+        <v>0.1827661853510243</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.1460802011673101</v>
+        <v>0.1225925493774125</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.03367085978571493</v>
+        <v>0.03288743524473992</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.03572486874287595</v>
+        <v>0.01912477459942719</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.01966190136772594</v>
+        <v>-0.01577611633170994</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15T14:00:08Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>727.77</v>
+        <v>717.45</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>743.57001</v>
+        <v>728.95001</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.0212488532182733</v>
+        <v>-0.01577612983364929</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T20:15:06Z</t>
+          <t>2026-10-15T14:00:08Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.028631420870743</v>
+        <v>-0.01680834662595854</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.08855729923500377</v>
+        <v>-0.07384618709576485</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.07127065862124093</v>
+        <v>-0.07228501576509827</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.0701533597112417</v>
+        <v>-0.04607742696112438</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.05199454429026829</v>
+        <v>-0.03715335878462822</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.01861321683678019</v>
+        <v>-0.001682813533462668</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.006635192037769411</v>
+        <v>0.01939409304094308</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15T14:00:08Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>78.78</v>
+        <v>80.42</v>
       </c>
       <c r="AW4" t="n">
-        <v>78.37</v>
+        <v>78.89</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>0.00523159372208748</v>
+        <v>0.01939409304094308</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-14T20:15:01Z</t>
+          <t>2026-10-15T14:00:08Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.2620078541939381</v>
+        <v>0.2849475070046921</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.005554233119098528</v>
+        <v>-0.0003939179075082011</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.0424766589965353</v>
+        <v>0.02875600724808947</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1463697043999455</v>
+        <v>-0.1350663515724414</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.03022249013590539</v>
+        <v>0.03319671018701986</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.04607382976024343</v>
+        <v>-0.02833512023280749</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.01488196609636594</v>
+        <v>0.01236735019548396</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15T14:00:07Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>375.81</v>
+        <v>380.64</v>
       </c>
       <c r="AW5" t="n">
-        <v>381.67001</v>
+        <v>375.98999</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.0153536034963816</v>
+        <v>0.01236737712086433</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-14T20:14:25Z</t>
+          <t>2026-10-15T14:00:07Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.09284749160330219</v>
+        <v>0.08958627519349771</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01260052195833539</v>
+        <v>0.01344426079009153</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0287211428375711</v>
+        <v>0.02809602700528835</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01658154679983925</v>
+        <v>-0.01331211972635293</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.0231682995145327</v>
+        <v>-0.01941739431342782</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01567054492023889</v>
+        <v>-0.01425135963016555</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.003632118303281917</v>
+        <v>0.001952870719958311</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15T14:00:09Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
+        <v>76.95999999999999</v>
+      </c>
+      <c r="AW6" t="n">
         <v>76.81</v>
       </c>
-      <c r="AW6" t="n">
-        <v>77.09</v>
-      </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.003632118303281917</v>
+        <v>0.001952870719958311</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-14T20:10:00Z</t>
+          <t>2026-10-15T14:00:09Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7927129272686206</v>
+        <v>0.7611480158209911</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6105177258244425</v>
+        <v>0.5877757274031872</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.5607573683842588</v>
+        <v>0.5157788080895356</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2288849110661129</v>
+        <v>0.1939735177836228</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1931251189389449</v>
+        <v>0.1628175498338233</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.03188218646162611</v>
+        <v>0.04749830181647363</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.006398809523809446</v>
+        <v>-0.0141209522401301</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15T14:00:10Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>67.73</v>
+        <v>66.675</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>67.2</v>
+        <v>67.63</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.007886904761904789</v>
+        <v>-0.0141209522401301</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T20:15:05Z</t>
+          <t>2026-10-15T14:00:10Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.0325427370926803</v>
+        <v>0.03484829904075726</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02127747761551657</v>
+        <v>-0.01330873968572344</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.01222041935647289</v>
+        <v>-0.01489776501968931</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02715082904259425</v>
+        <v>-0.0181679452922201</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02205118649041982</v>
+        <v>-0.01787598021824932</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.009169108611400079</v>
+        <v>0.001613056267198099</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.002486610558530833</v>
+        <v>0.007059721427208565</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15T14:00:04Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
+        <v>105.56</v>
+      </c>
+      <c r="AW8" t="n">
         <v>104.82</v>
       </c>
-      <c r="AW8" t="n">
-        <v>104.56</v>
-      </c>
       <c r="AX8" s="4" t="n">
-        <v>0.002486610558530833</v>
+        <v>0.007059721427208565</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-14T20:10:00Z</t>
+          <t>2026-10-15T14:00:04Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.0970680966747608</v>
+        <v>0.09501098117293472</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07590281449738168</v>
+        <v>0.07343248448644402</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.04265032366470134</v>
+        <v>0.05230850288452604</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.06705753023085381</v>
+        <v>0.05846181951041274</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.02752293577981657</v>
+        <v>0.02259442287327929</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.03189227498228209</v>
+        <v>0.0200739436619719</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.00344589937973816</v>
+        <v>-0.005147664835164933</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15T13:59:56Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
+        <v>28.9701</v>
+      </c>
+      <c r="AW9" t="n">
         <v>29.12</v>
       </c>
-      <c r="AW9" t="n">
-        <v>29.02</v>
-      </c>
       <c r="AX9" s="4" t="n">
-        <v>0.00344589937973816</v>
+        <v>-0.005147664835164933</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-14T20:10:00Z</t>
+          <t>2026-10-15T13:59:56Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05965976164778763</v>
+        <v>0.05960708463359055</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03755835625549975</v>
+        <v>0.0375067248185279</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03435350039285634</v>
+        <v>0.03445641929485777</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.0182485077422776</v>
+        <v>0.01829914671720001</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009041979823433355</v>
+        <v>0.008791130958750504</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.00309841447960113</v>
+        <v>0.002948703750854431</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0001989653800240632</v>
+        <v>4.973145016906599e-05</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15T14:00:11Z</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.534</v>
+        <v>100.545</v>
       </c>
       <c r="AW10" s="5" t="n">
-        <v>100.52</v>
+        <v>100.54</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>0.0001392757660167998</v>
+        <v>4.973145016906599e-05</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14T20:14:57Z</t>
+          <t>2026-10-15T14:00:11Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.01830025704469973</v>
+        <v>0.01777202098661057</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.0273476298577231</v>
+        <v>0.03250552990519617</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.1047194503466125</v>
+        <v>0.09658257601647802</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.03572486874287595</v>
+        <v>0.01912477459942719</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.03367085978571493</v>
+        <v>0.03288743524473992</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.1460802011673101</v>
+        <v>0.1225925493774125</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.01861321683678019</v>
+        <v>-0.001682813533462668</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.05199454429026829</v>
+        <v>-0.03715335878462822</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.0701533597112417</v>
+        <v>-0.04607742696112438</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.04607382976024343</v>
+        <v>-0.02833512023280749</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.03022249013590539</v>
+        <v>0.03319671018701986</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1463697043999455</v>
+        <v>-0.1350663515724414</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.01567054492023889</v>
+        <v>-0.01425135963016555</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.0231682995145327</v>
+        <v>-0.01941739431342782</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01658154679983925</v>
+        <v>-0.01331211972635293</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.03188218646162611</v>
+        <v>0.04749830181647363</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1931251189389449</v>
+        <v>0.1628175498338233</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.2288849110661129</v>
+        <v>0.1939735177836228</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.009169108611400079</v>
+        <v>0.001613056267198099</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.02205118649041982</v>
+        <v>-0.01787598021824932</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.02715082904259425</v>
+        <v>-0.0181679452922201</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.03189227498228209</v>
+        <v>0.0200739436619719</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.02752293577981657</v>
+        <v>0.02259442287327929</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.06705753023085381</v>
+        <v>0.05846181951041274</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.00309841447960113</v>
+        <v>0.002948703750854431</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009041979823433355</v>
+        <v>0.008791130958750504</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.0182485077422776</v>
+        <v>0.01829914671720001</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4435535389862164</v>
+        <v>0.4553201150529853</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1684901579315681</v>
+        <v>0.1780146339296047</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1480863433432313</v>
+        <v>0.1480864502994801</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.09658257601647802</v>
+        <v>0.1055208233867906</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.03250552990519617</v>
+        <v>0.04092148510943949</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.01777202098661057</v>
+        <v>0.02606788332212928</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.00526247401247415</v>
+        <v>0.002845634095633987</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.1609548690014375</v>
+        <v>0.1609549765152376</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>3</v>
@@ -858,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512197561446</v>
+        <v>0.3464512286219292</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -867,24 +867,24 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T14:00:08Z</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.3449780561209737</v>
+        <v>0.3443688144953474</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>0.3464512197561446</v>
+        <v>0.3464512286219292</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>0.3443126487452514</v>
+        <v>0.3443126584331728</v>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +1.9%, 3m +2.8%, 6m +10.5%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +2.6%, 3m +4.1%, 6m +10.6%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>765.55</v>
+        <v>771.79</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>769.59998</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.005262448161706068</v>
+        <v>0.002845660157111851</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T14:00:08Z</t>
+          <t>2026-10-15T20:15:05Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5792320508139734</v>
+        <v>0.602454433051185</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2053863220496868</v>
+        <v>0.2231111052774386</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1827661853510243</v>
+        <v>0.1827659427774506</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.1225925493774125</v>
+        <v>0.1391001128256413</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.03288743524473992</v>
+        <v>0.04807589777429877</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.01912477459942719</v>
+        <v>0.03411085916563228</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.01577611633170994</v>
+        <v>-0.001303244392619529</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.1982245316673374</v>
+        <v>0.1982246540542743</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>2</v>
@@ -1057,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095304551976</v>
+        <v>0.3583095431858343</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T14:00:08Z</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.3511620818355983</v>
+        <v>0.3544926612142901</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0.3583095304551976</v>
+        <v>0.3583095431858343</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>0.3529527963579562</v>
+        <v>0.3529527683766502</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="AM3" s="2" t="n"/>
       <c r="AN3" s="3" t="n">
-        <v>0.1632846035697191</v>
+        <v>0.1632844869027379</v>
       </c>
       <c r="AO3" s="2" t="n">
         <v>2</v>
@@ -1152,14 +1152,14 @@
         <v>0</v>
       </c>
       <c r="AR3" s="3" t="n">
-        <v>-0.01670822787149806</v>
+        <v>-0.01670834453847925</v>
       </c>
       <c r="AS3" s="3" t="n">
         <v>0.07056586290088451</v>
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +3.6%, 3m +3.4%, 6m +14.6%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +3.4%, 3m +4.8%, 6m +13.9%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>717.45</v>
+        <v>727.7</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>728.95001</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.01577612983364929</v>
+        <v>-0.001714808948284352</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T14:00:08Z</t>
+          <t>2026-10-15T20:15:05Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.01680834662595854</v>
+        <v>-0.02230991643469171</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.07384618709576485</v>
+        <v>-0.07902859465367218</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>-0.07228501576509827</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.04607742696112438</v>
+        <v>-0.05141521803134941</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.03715335878462822</v>
+        <v>-0.04254108557581104</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.001682813533462668</v>
+        <v>-0.007269020122743219</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.01939409304094308</v>
+        <v>0.013689948028901</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.038029469654283</v>
+        <v>-0.03802955588478829</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-15T14:00:08Z</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="AN4" s="4" t="n">
-        <v>-0.05671722070931096</v>
+        <v>-0.05671730508466388</v>
       </c>
       <c r="AO4" t="n">
         <v>8</v>
@@ -1350,14 +1350,14 @@
         <v>0</v>
       </c>
       <c r="AR4" s="4" t="n">
-        <v>-0.01323350469745432</v>
+        <v>-0.01323358907280725</v>
       </c>
       <c r="AS4" s="4" t="n">
         <v>0.07056586290088451</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.9%, 3m -5.2%, 6m -7.0%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -0.7%, 3m -4.3%, 6m -5.1%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>80.42</v>
+        <v>79.97</v>
       </c>
       <c r="AW4" t="n">
         <v>78.89</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>0.01939409304094308</v>
+        <v>0.013689948028901</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-15T14:00:08Z</t>
+          <t>2026-10-15T20:15:00Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.2849475070046921</v>
+        <v>0.291935320527968</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.0003939179075082011</v>
+        <v>0.005042149216103242</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.02875600724808947</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1350663515724414</v>
+        <v>-0.1303626613343029</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.03319671018701986</v>
+        <v>0.03881545017779087</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.02833512023280749</v>
+        <v>-0.02305100321641917</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.01236735019548396</v>
+        <v>0.01787281576637678</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-15T14:00:07Z</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -4.6%, 3m +3.0%, 6m -14.6%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -2.3%, 3m +3.9%, 6m -13.0%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>380.64</v>
+        <v>382.47</v>
       </c>
       <c r="AW5" t="n">
         <v>375.98999</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>0.01236737712086433</v>
+        <v>0.0172345279724071</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-15T14:00:07Z</t>
+          <t>2026-10-15T20:15:04Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.08958627519349771</v>
+        <v>0.09199310558308826</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01344426079009153</v>
+        <v>0.01568269397468303</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.02809602700528835</v>
+        <v>0.02809582042519621</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01331211972635293</v>
+        <v>-0.01113258568728692</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01941739431342782</v>
+        <v>-0.01725134645783111</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01425135963016555</v>
+        <v>-0.01207390031541933</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.001952870719958311</v>
+        <v>0.00416612420257767</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715185591311232</v>
+        <v>0.03715216747213934</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1659,17 +1659,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-15T14:00:09Z</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="AN6" s="4" t="n">
-        <v>0.02931197566237409</v>
+        <v>0.0293120789335406</v>
       </c>
       <c r="AO6" t="n">
         <v>6</v>
@@ -1744,14 +1744,14 @@
         <v>0</v>
       </c>
       <c r="AR6" s="4" t="n">
-        <v>-0.002449485271767582</v>
+        <v>-0.002449278880047201</v>
       </c>
       <c r="AS6" s="4" t="n">
         <v>0.07056586290088451</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.6%, 3m -2.3%, 6m -1.7%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.2%, 3m -1.7%, 6m -1.1%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>76.95999999999999</v>
+        <v>77.13</v>
       </c>
       <c r="AW6" t="n">
         <v>76.81</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>0.001952870719958311</v>
+        <v>0.00416612420257767</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-15T14:00:09Z</t>
+          <t>2026-10-15T20:10:00Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7611480158209911</v>
+        <v>0.7581102380222726</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.5877757274031872</v>
+        <v>0.5850371565947678</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.5157788080895356</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.1939735177836228</v>
+        <v>0.1919141708838086</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1628175498338233</v>
+        <v>0.1608119402615567</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.04749830181647363</v>
+        <v>0.04569159308443194</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.0141209522401301</v>
+        <v>-0.01582138104391528</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1847,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392497886577</v>
+        <v>0.2952392281922366</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1856,24 +1856,24 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T14:00:10Z</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.303859862043428</v>
+        <v>0.3011385242903626</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>1</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.2952392497886577</v>
+        <v>0.2952392281922366</v>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.3027345548967924</v>
+        <v>0.302734573190177</v>
       </c>
       <c r="AH7" s="2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AM7" s="2" t="n"/>
       <c r="AN7" s="3" t="n">
-        <v>0.4921706768785028</v>
+        <v>0.492170808484097</v>
       </c>
       <c r="AO7" s="2" t="n">
         <v>1</v>
@@ -1942,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="AR7" s="3" t="n">
-        <v>0.002121645268243544</v>
+        <v>0.002121776873837744</v>
       </c>
       <c r="AS7" s="3" t="n">
         <v>0.07056586290088451</v>
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +3.2%, 3m +19.3%, 6m +22.9%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +4.6%, 3m +16.1%, 6m +19.2%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>66.675</v>
+        <v>66.56</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>67.63</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>-0.0141209522401301</v>
+        <v>-0.01582138104391528</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T14:00:10Z</t>
+          <t>2026-10-15T20:10:00Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.03484829904075726</v>
+        <v>0.03220145467512769</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01330873968572344</v>
+        <v>-0.01583262617328896</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.01489776501968931</v>
+        <v>-0.01489790552191972</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.0181679452922201</v>
+        <v>-0.020679262597744</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.01787598021824932</v>
+        <v>-0.02038804430825569</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.001613056267198099</v>
+        <v>-0.0009488566277634503</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.007059721427208565</v>
+        <v>0.004483877122686719</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.004296483646738736</v>
+        <v>0.004296411608788464</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
@@ -2055,17 +2055,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-15T14:00:04Z</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2140,14 +2140,14 @@
         <v>0</v>
       </c>
       <c r="AR8" s="4" t="n">
-        <v>-0.005243235401598878</v>
+        <v>-0.005243163593030453</v>
       </c>
       <c r="AS8" s="4" t="n">
         <v>0.07056586290088451</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -0.9%, 3m -2.2%, 6m -2.7%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -0.1%, 3m -2.0%, 6m -2.1%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>105.56</v>
+        <v>105.2803</v>
       </c>
       <c r="AW8" t="n">
         <v>104.82</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>0.007059721427208565</v>
+        <v>0.004391337531005624</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-15T14:00:04Z</t>
+          <t>2026-10-15T20:12:48Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.09501098117293472</v>
+        <v>0.09614114048674693</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07343248448644402</v>
+        <v>0.07454037266377656</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.05230850288452604</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05846181951041274</v>
+        <v>0.05955425648520274</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.02259442287327929</v>
+        <v>0.02364984115778324</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.0200739436619719</v>
+        <v>0.02112676056338025</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.005147664835164933</v>
+        <v>-0.004120879120879106</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2252,17 +2252,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-15T13:59:56Z</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +3.2%, 3m +2.8%, 6m +6.7%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +2.1%, 3m +2.4%, 6m +6.0%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>28.9701</v>
+        <v>29</v>
       </c>
       <c r="AW9" t="n">
         <v>29.12</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>-0.005147664835164933</v>
+        <v>-0.004120879120879106</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-15T13:59:56Z</t>
+          <t>2026-10-15T20:10:00Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05960708463359055</v>
+        <v>0.05965969260976167</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.0375067248185279</v>
+        <v>0.03755823728341534</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03445641929485777</v>
+        <v>0.03445633785581292</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01829914671720001</v>
+        <v>0.01834978569212264</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.008791130958750504</v>
+        <v>0.008841297109775326</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.002948703750854431</v>
+        <v>0.002998579363950427</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>4.973145016906599e-05</v>
+        <v>9.946290033813199e-05</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15T14:00:11Z</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.545</v>
+        <v>100.54</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.54</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>4.973145016906599e-05</v>
+        <v>0</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15T14:00:11Z</t>
+          <t>2026-10-15T20:15:06Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>QQQ 35.1%, SPY 34.5%, XLE 30.4%</t>
+          <t>QQQ 35.4%, SPY 34.4%, XLE 30.1%</t>
         </is>
       </c>
     </row>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.01777202098661057</v>
+        <v>0.02606788332212928</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.03250552990519617</v>
+        <v>0.04092148510943949</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.09658257601647802</v>
+        <v>0.1055208233867906</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.01912477459942719</v>
+        <v>0.03411085916563228</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.03288743524473992</v>
+        <v>0.04807589777429877</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.1225925493774125</v>
+        <v>0.1391001128256413</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.001682813533462668</v>
+        <v>-0.007269020122743219</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.03715335878462822</v>
+        <v>-0.04254108557581104</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.04607742696112438</v>
+        <v>-0.05141521803134941</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.02833512023280749</v>
+        <v>-0.02305100321641917</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.03319671018701986</v>
+        <v>0.03881545017779087</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1350663515724414</v>
+        <v>-0.1303626613343029</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.01425135963016555</v>
+        <v>-0.01207390031541933</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01941739431342782</v>
+        <v>-0.01725134645783111</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01331211972635293</v>
+        <v>-0.01113258568728692</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.04749830181647363</v>
+        <v>0.04569159308443194</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1628175498338233</v>
+        <v>0.1608119402615567</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.1939735177836228</v>
+        <v>0.1919141708838086</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.001613056267198099</v>
+        <v>-0.0009488566277634503</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.01787598021824932</v>
+        <v>-0.02038804430825569</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.0181679452922201</v>
+        <v>-0.020679262597744</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.0200739436619719</v>
+        <v>0.02112676056338025</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.02259442287327929</v>
+        <v>0.02364984115778324</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05846181951041274</v>
+        <v>0.05955425648520274</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.002948703750854431</v>
+        <v>0.002998579363950427</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.008791130958750504</v>
+        <v>0.008841297109775326</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01829914671720001</v>
+        <v>0.01834978569212264</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.02933602385378342</v>
+        <v>0.02933603803237417</v>
       </c>
     </row>
     <row r="3">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4553201150529853</v>
+        <v>0.4583298240681015</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1780146339296047</v>
+        <v>0.1719417166613459</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1480864502994801</v>
+        <v>0.1559723322105802</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1055208233867906</v>
+        <v>0.09151270822776403</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.04092148510943949</v>
+        <v>0.04183467781612005</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.02606788332212928</v>
+        <v>0.0138146770521983</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.002845634095633987</v>
+        <v>-0.0007385428678784445</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,12 +872,12 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16T14:00:08Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>771.79</v>
+        <v>771.22</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>769.59998</v>
+        <v>771.78998</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>0.002845660157111851</v>
+        <v>-0.0007385169732314623</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T20:15:05Z</t>
+          <t>2026-10-16T14:00:08Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.602454433051185</v>
+        <v>0.5847512454474526</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2231111052774386</v>
+        <v>0.2024616817370763</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1827659427774506</v>
+        <v>0.1948102829331331</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.1391001128256413</v>
+        <v>0.1132064052273267</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.04807589777429877</v>
+        <v>0.03656443559978895</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.03411085916563228</v>
+        <v>0.00640386085827771</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.001303244392619529</v>
+        <v>-0.009945054945054932</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16T14:00:09Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>727.7</v>
+        <v>720.76</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>728.95001</v>
+        <v>728</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.001714808948284352</v>
+        <v>-0.009945054945054932</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T20:15:05Z</t>
+          <t>2026-10-16T14:00:09Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.02230991643469171</v>
+        <v>-0.0236289484545632</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.07902859465367218</v>
+        <v>-0.07497689686108067</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.07228501576509827</v>
+        <v>-0.05989223609562822</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.05141521803134941</v>
+        <v>-0.05796488940311506</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.04254108557581104</v>
+        <v>-0.03323977527487076</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.007269020122743219</v>
+        <v>-0.01604567193744277</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.013689948028901</v>
+        <v>0.002188320620232442</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16T14:00:09Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
+        <v>80.145</v>
+      </c>
+      <c r="AW4" t="n">
         <v>79.97</v>
       </c>
-      <c r="AW4" t="n">
-        <v>78.89</v>
-      </c>
       <c r="AX4" s="4" t="n">
-        <v>0.013689948028901</v>
+        <v>0.002188320620232442</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-15T20:15:00Z</t>
+          <t>2026-10-16T14:00:09Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1387,7 +1387,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.291935320527968</v>
+        <v>0.288635569883807</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.005042149216103242</v>
+        <v>-0.00944810139652541</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.02875600724808947</v>
+        <v>0.02831771599679911</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1303626613343029</v>
+        <v>-0.1394839997308995</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.03881545017779087</v>
+        <v>0.0438789445048966</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.02305100321641917</v>
+        <v>-0.03672582588613327</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.01787281576637678</v>
+        <v>0.002664942123278724</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16T14:00:09Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>382.47</v>
+        <v>383.7299</v>
       </c>
       <c r="AW5" t="n">
-        <v>375.98999</v>
+        <v>382.70999</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>0.0172345279724071</v>
+        <v>0.002664968322358074</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-15T20:15:04Z</t>
+          <t>2026-10-16T14:00:09Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1584,7 +1584,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.09199310558308826</v>
+        <v>0.08853352870612774</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01568269397468303</v>
+        <v>0.01195531989350851</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.02809582042519621</v>
+        <v>0.0287083197865643</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01113258568728692</v>
+        <v>-0.01525799800516547</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01725134645783111</v>
+        <v>-0.01806719409235669</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01207390031541933</v>
+        <v>-0.01628547137300473</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.00416612420257767</v>
+        <v>-0.0004537793335925855</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16T14:00:08Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
+        <v>77.095</v>
+      </c>
+      <c r="AW6" t="n">
         <v>77.13</v>
       </c>
-      <c r="AW6" t="n">
-        <v>76.81</v>
-      </c>
       <c r="AX6" s="4" t="n">
-        <v>0.00416612420257767</v>
+        <v>-0.0004537793335925855</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-15T20:10:00Z</t>
+          <t>2026-10-16T14:00:08Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7581102380222726</v>
+        <v>0.7746674250752679</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.5850371565947678</v>
+        <v>0.5986497126788617</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.5157788080895356</v>
+        <v>0.5274925994927393</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.1919141708838086</v>
+        <v>0.2353768473694551</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1608119402615567</v>
+        <v>0.1647178894572707</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.04569159308443194</v>
+        <v>0.04658426051278597</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.01582138104391528</v>
+        <v>0.007887620192307487</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16T14:00:11Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
+        <v>67.08499999999999</v>
+      </c>
+      <c r="AW7" s="2" t="n">
         <v>66.56</v>
       </c>
-      <c r="AW7" s="2" t="n">
-        <v>67.63</v>
-      </c>
       <c r="AX7" s="3" t="n">
-        <v>-0.01582138104391528</v>
+        <v>0.007887620192307487</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T20:10:00Z</t>
+          <t>2026-10-16T14:00:11Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.03220145467512769</v>
+        <v>0.03455146764745476</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01583262617328896</v>
+        <v>-0.01341758359725076</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.01489790552191972</v>
+        <v>-0.01164113686566881</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.020679262597744</v>
+        <v>-0.02109318918105085</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02038804430825569</v>
+        <v>-0.01624919549763071</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.0009488566277634503</v>
+        <v>-0.001797370163655221</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.004483877122686719</v>
+        <v>0.002184442967043232</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16T14:00:00Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>105.2803</v>
+        <v>105.52</v>
       </c>
       <c r="AW8" t="n">
-        <v>104.82</v>
+        <v>105.29</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>0.004391337531005624</v>
+        <v>0.002184442967043232</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-15T20:12:48Z</t>
+          <t>2026-10-16T14:00:00Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.09614114048674693</v>
+        <v>0.0858713581654249</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07454037266377656</v>
+        <v>0.07338562371257518</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.05230850288452604</v>
+        <v>0.05459028314822101</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05955425648520274</v>
+        <v>0.05576754385964922</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.02364984115778324</v>
+        <v>0.01746389573793583</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.02112676056338025</v>
+        <v>0.01782241014799157</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.004120879120879106</v>
+        <v>-0.003937931034482811</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16T14:00:06Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
+        <v>28.8858</v>
+      </c>
+      <c r="AW9" t="n">
         <v>29</v>
       </c>
-      <c r="AW9" t="n">
-        <v>29.12</v>
-      </c>
       <c r="AX9" s="4" t="n">
-        <v>-0.004120879120879106</v>
+        <v>-0.003937931034482811</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-15T20:10:00Z</t>
+          <t>2026-10-16T14:00:06Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05965969260976167</v>
+        <v>0.05986852340909121</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03755823728341534</v>
+        <v>0.03765927007429193</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03445633785581292</v>
+        <v>0.03435340054660352</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01834978569212264</v>
+        <v>0.01834761510946503</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.008841297109775326</v>
+        <v>0.009039975443613457</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.002998579363950427</v>
+        <v>0.003196073533418664</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>9.946290033813199e-05</v>
+        <v>0.0002963699651914453</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16T14:00:11Z</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.54</v>
+        <v>100.5798</v>
       </c>
       <c r="AW10" s="5" t="n">
-        <v>100.54</v>
+        <v>100.55</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>0</v>
+        <v>0.0002963699651914453</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15T20:15:06Z</t>
+          <t>2026-10-16T14:00:11Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.02606788332212928</v>
+        <v>0.0138146770521983</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.04092148510943949</v>
+        <v>0.04183467781612005</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.1055208233867906</v>
+        <v>0.09151270822776403</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.03411085916563228</v>
+        <v>0.00640386085827771</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.04807589777429877</v>
+        <v>0.03656443559978895</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.1391001128256413</v>
+        <v>0.1132064052273267</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.007269020122743219</v>
+        <v>-0.01604567193744277</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.04254108557581104</v>
+        <v>-0.03323977527487076</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.05141521803134941</v>
+        <v>-0.05796488940311506</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.02305100321641917</v>
+        <v>-0.03672582588613327</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.03881545017779087</v>
+        <v>0.0438789445048966</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1303626613343029</v>
+        <v>-0.1394839997308995</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.01207390031541933</v>
+        <v>-0.01628547137300473</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01725134645783111</v>
+        <v>-0.01806719409235669</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01113258568728692</v>
+        <v>-0.01525799800516547</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.04569159308443194</v>
+        <v>0.04658426051278597</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1608119402615567</v>
+        <v>0.1647178894572707</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.1919141708838086</v>
+        <v>0.2353768473694551</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.0009488566277634503</v>
+        <v>-0.001797370163655221</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.02038804430825569</v>
+        <v>-0.01624919549763071</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.020679262597744</v>
+        <v>-0.02109318918105085</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.02112676056338025</v>
+        <v>0.01782241014799157</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.02364984115778324</v>
+        <v>0.01746389573793583</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05955425648520274</v>
+        <v>0.05576754385964922</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.002998579363950427</v>
+        <v>0.003196073533418664</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.008841297109775326</v>
+        <v>0.009039975443613457</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01834978569212264</v>
+        <v>0.01834761510946503</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Survivor'!$A$1:$BA$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Weekly Review'!$A$17:$H$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Weekly History'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Weekly History'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4583298240681015</v>
+        <v>0.4421054026949163</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1719417166613459</v>
+        <v>0.1589034878486693</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1559723322105802</v>
+        <v>0.1559722249956661</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.09151270822776403</v>
+        <v>0.07936937813181943</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.04183467781612005</v>
+        <v>0.03024402724214337</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.0138146770521983</v>
+        <v>0.002535755435658427</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.0007385428678784445</v>
+        <v>-0.01185555656331383</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.1609549765152376</v>
+        <v>0.1609548690014375</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>3</v>
@@ -858,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512286219292</v>
+        <v>0.3464512197561446</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -867,24 +867,24 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T14:00:08Z</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.3443688144953474</v>
+        <v>0.3444390211106695</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -895,16 +895,16 @@
         <v>1</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>0.3464512286219292</v>
+        <v>0.3464512197561446</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AE2" s="2" t="b">
@@ -914,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>0.3443126584331728</v>
+        <v>0.3444390211106695</v>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
       </c>
       <c r="AM2" s="2" t="n"/>
       <c r="AN2" s="3" t="n">
-        <v>0.1351911650765494</v>
+        <v>0.1559722249956661</v>
       </c>
       <c r="AO2" s="2" t="n">
         <v>3</v>
@@ -953,14 +953,14 @@
         <v>0</v>
       </c>
       <c r="AR2" s="3" t="n">
-        <v>-0.01897026129460522</v>
+        <v>0.02078105991911672</v>
       </c>
       <c r="AS2" s="3" t="n">
-        <v>0.07056586290088451</v>
+        <v>0.1013819418474451</v>
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +2.6%, 3m +4.1%, 6m +10.6%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +0.3%, 3m +3.0%, 6m +7.9%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>771.22</v>
+        <v>762.85</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>771.78998</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.0007385169732314623</v>
+        <v>-0.01158343620890234</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T14:00:08Z</t>
+          <t>2026-10-16T20:15:09Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5847512454474526</v>
+        <v>0.560829144400685</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2024616817370763</v>
+        <v>0.1843104300335037</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1948102829331331</v>
+        <v>0.1948104045964485</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.1132064052273267</v>
+        <v>0.09640235715463508</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.03656443559978895</v>
+        <v>0.02091731164822996</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.00640386085827771</v>
+        <v>-0.008787983869701144</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.009945054945054932</v>
+        <v>-0.02489010989010987</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.1982246540542743</v>
+        <v>0.1982245316673374</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>2</v>
@@ -1057,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095431858343</v>
+        <v>0.3583095304551976</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T14:00:09Z</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.3544926612142901</v>
+        <v>0.3554859723629458</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1094,16 +1094,16 @@
         <v>1</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0.3583095431858343</v>
+        <v>0.3583095304551976</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AE3" s="2" t="b">
@@ -1113,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>0.3529527683766502</v>
+        <v>0.3554859723629458</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="AM3" s="2" t="n"/>
       <c r="AN3" s="3" t="n">
-        <v>0.1632844869027379</v>
+        <v>0.1948104045964485</v>
       </c>
       <c r="AO3" s="2" t="n">
         <v>2</v>
@@ -1152,14 +1152,14 @@
         <v>0</v>
       </c>
       <c r="AR3" s="3" t="n">
-        <v>-0.01670834453847925</v>
+        <v>0.03152580102672942</v>
       </c>
       <c r="AS3" s="3" t="n">
-        <v>0.07056586290088451</v>
+        <v>0.1013819418474451</v>
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +3.4%, 3m +4.8%, 6m +13.9%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -0.9%, 3m +2.1%, 6m +9.6%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>720.76</v>
+        <v>709.53</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>728</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.009945054945054932</v>
+        <v>-0.02537087912087921</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T14:00:09Z</t>
+          <t>2026-10-16T20:15:10Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.0236289484545632</v>
+        <v>-0.02503012377757641</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.07497689686108067</v>
+        <v>-0.07630429315179832</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.05989223609562822</v>
+        <v>-0.05989231887913193</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.05796488940311506</v>
+        <v>-0.05931669922977556</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.03323977527487076</v>
+        <v>-0.03462688994763918</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.01604567193744277</v>
+        <v>-0.01745754726001048</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.002188320620232442</v>
+        <v>0.0007502813555082533</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.03802955588478829</v>
+        <v>-0.03802938342376228</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-16T14:00:09Z</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1297,14 +1297,14 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="AN4" s="4" t="n">
-        <v>-0.05671730508466388</v>
+        <v>-0.05989231887913193</v>
       </c>
       <c r="AO4" t="n">
         <v>8</v>
@@ -1350,14 +1350,14 @@
         <v>0</v>
       </c>
       <c r="AR4" s="4" t="n">
-        <v>-0.01323358907280725</v>
+        <v>-0.003175013794468051</v>
       </c>
       <c r="AS4" s="4" t="n">
-        <v>0.07056586290088451</v>
+        <v>0.1013819418474451</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -0.7%, 3m -4.3%, 6m -5.1%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.7%, 3m -3.5%, 6m -5.9%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>80.145</v>
+        <v>80.02</v>
       </c>
       <c r="AW4" t="n">
         <v>79.97</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>0.002188320620232442</v>
+        <v>0.0006252344629236184</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-16T14:00:09Z</t>
+          <t>2026-10-16T20:15:01Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.288635569883807</v>
+        <v>0.2828598294042584</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.00944810139652541</v>
+        <v>-0.01388781331474742</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.02831771599679911</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1394839997308995</v>
+        <v>-0.1433408830982441</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.0438789445048966</v>
+        <v>0.0392002176278563</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.03672582588613327</v>
+        <v>-0.04104327743749381</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.002664942123278724</v>
+        <v>-0.001829061169031365</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-16T14:00:09Z</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1494,14 +1494,14 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
@@ -1535,26 +1535,26 @@
         </is>
       </c>
       <c r="AN5" s="4" t="n">
-        <v>0.06462530217566487</v>
+        <v>0.02831771599679911</v>
       </c>
       <c r="AO5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AP5" t="n">
         <v>4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AR5" s="4" t="n">
-        <v>-0.06668385716484027</v>
+        <v>-0.03630758617886576</v>
       </c>
       <c r="AS5" s="4" t="n">
-        <v>0.07056586290088451</v>
+        <v>0.1013819418474451</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -2.3%, 3m +3.9%, 6m -13.0%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -4.1%, 3m +3.9%, 6m -14.3%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>383.7299</v>
+        <v>381.89</v>
       </c>
       <c r="AW5" t="n">
         <v>382.70999</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>0.002664968322358074</v>
+        <v>-0.002142588438833304</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-16T14:00:09Z</t>
+          <t>2026-10-16T20:10:31Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.08853352870612774</v>
+        <v>0.0852154746267979</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01195531989350851</v>
+        <v>0.008870387440722327</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0287083197865643</v>
+        <v>0.02870801072958273</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01525799800516547</v>
+        <v>-0.01825967607078305</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01806719409235669</v>
+        <v>-0.02106030920213409</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01628547137300473</v>
+        <v>-0.01928401750734998</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.0004537793335925855</v>
+        <v>-0.003500583430571691</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715216747213934</v>
+        <v>0.03715195976610053</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1659,17 +1659,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-16T14:00:08Z</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1691,14 +1691,14 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
@@ -1732,26 +1732,26 @@
         </is>
       </c>
       <c r="AN6" s="4" t="n">
-        <v>0.0293120789335406</v>
+        <v>0.02870801072958273</v>
       </c>
       <c r="AO6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP6" t="n">
         <v>6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR6" s="4" t="n">
-        <v>-0.002449278880047201</v>
+        <v>-0.000604171475144577</v>
       </c>
       <c r="AS6" s="4" t="n">
-        <v>0.07056586290088451</v>
+        <v>0.1013819418474451</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.2%, 3m -1.7%, 6m -1.1%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.9%, 3m -2.1%, 6m -1.8%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.095</v>
+        <v>76.86</v>
       </c>
       <c r="AW6" t="n">
         <v>77.13</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.0004537793335925855</v>
+        <v>-0.003500583430571691</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-16T14:00:08Z</t>
+          <t>2026-10-16T20:10:00Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7746674250752679</v>
+        <v>0.8052216272574668</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.5986497126788617</v>
+        <v>0.6261734586898218</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.5274925994927393</v>
+        <v>0.5274924606359737</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2353768473694551</v>
+        <v>0.2566461972487892</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1647178894572707</v>
+        <v>0.1847707949103996</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.04658426051278597</v>
+        <v>0.06460326358191115</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.007887620192307487</v>
+        <v>0.02524038461538458</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1847,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392281922366</v>
+        <v>0.2952392497886577</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1856,24 +1856,24 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T14:00:11Z</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.3011385242903626</v>
+        <v>0.3000750065263847</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -1884,16 +1884,16 @@
         <v>1</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.2952392281922366</v>
+        <v>0.2952392497886577</v>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AD7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AE7" s="2" t="b">
@@ -1903,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.302734573190177</v>
+        <v>0.3000750065263847</v>
       </c>
       <c r="AH7" s="2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AM7" s="2" t="n"/>
       <c r="AN7" s="3" t="n">
-        <v>0.492170808484097</v>
+        <v>0.5274924606359737</v>
       </c>
       <c r="AO7" s="2" t="n">
         <v>1</v>
@@ -1942,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="AR7" s="3" t="n">
-        <v>0.002121776873837744</v>
+        <v>0.0353219153630413</v>
       </c>
       <c r="AS7" s="3" t="n">
-        <v>0.07056586290088451</v>
+        <v>0.1013819418474451</v>
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +4.6%, 3m +16.1%, 6m +19.2%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +6.5%, 3m +18.5%, 6m +25.7%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>67.08499999999999</v>
+        <v>68.1657</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>66.56</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.007887620192307487</v>
+        <v>0.02412409855769226</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T14:00:11Z</t>
+          <t>2026-10-16T20:14:03Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.03455146764745476</v>
+        <v>0.03474755397566698</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01341758359725076</v>
+        <v>-0.01323065959337422</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.01164113686566881</v>
+        <v>-0.01164120736797036</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02109318918105085</v>
+        <v>-0.02090764960356428</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.01624919549763071</v>
+        <v>-0.01606273780155354</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.001797370163655221</v>
+        <v>-0.001608173304323057</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.002184442967043232</v>
+        <v>0.00237439452939503</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2055,17 +2055,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-16T14:00:00Z</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2087,14 +2087,14 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="AN8" s="4" t="n">
-        <v>-0.002359241806851986</v>
+        <v>-0.01164120736797036</v>
       </c>
       <c r="AO8" t="n">
         <v>7</v>
@@ -2140,14 +2140,14 @@
         <v>0</v>
       </c>
       <c r="AR8" s="4" t="n">
-        <v>-0.005243163593030453</v>
+        <v>-0.009282036975003183</v>
       </c>
       <c r="AS8" s="4" t="n">
-        <v>0.07056586290088451</v>
+        <v>0.1013819418474451</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -0.1%, 3m -2.0%, 6m -2.1%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -0.2%, 3m -1.6%, 6m -2.1%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>105.52</v>
+        <v>105.56</v>
       </c>
       <c r="AW8" t="n">
         <v>105.29</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>0.002184442967043232</v>
+        <v>0.002564346091746605</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-16T14:00:00Z</t>
+          <t>2026-10-16T20:14:27Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.0858713581654249</v>
+        <v>0.08715700026116946</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07338562371257518</v>
+        <v>0.07465648303899064</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.05459028314822101</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05576754385964922</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01746389573793583</v>
+        <v>0.01866854526241646</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.01782241014799157</v>
+        <v>0.01902748414376321</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.003937931034482811</v>
+        <v>-0.002758620689655156</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2252,17 +2252,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-16T14:00:06Z</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2284,14 +2284,14 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
@@ -2325,26 +2325,26 @@
         </is>
       </c>
       <c r="AN9" s="4" t="n">
-        <v>0.04121026959450802</v>
+        <v>0.05459028314822101</v>
       </c>
       <c r="AO9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP9" t="n">
         <v>5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR9" s="4" t="n">
-        <v>-0.01813791378588547</v>
+        <v>0.01338001355371299</v>
       </c>
       <c r="AS9" s="4" t="n">
-        <v>0.07056586290088451</v>
+        <v>0.1013819418474451</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +2.1%, 3m +2.4%, 6m +6.0%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +1.9%, 3m +1.9%, 6m +5.7%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>28.8858</v>
+        <v>28.92</v>
       </c>
       <c r="AW9" t="n">
         <v>29</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>-0.003937931034482811</v>
+        <v>-0.002758620689655156</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-16T14:00:06Z</t>
+          <t>2026-10-16T20:10:00Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05986852340909121</v>
+        <v>0.05997600680972215</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03765927007429193</v>
+        <v>0.03776458287306617</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03435340054660352</v>
+        <v>0.03435348196134758</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01834761510946503</v>
+        <v>0.01845080912006103</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009039975443613457</v>
+        <v>0.009142304218869635</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003196073533418664</v>
+        <v>0.003297809666817475</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0002963699651914453</v>
+        <v>0.0003978120338141711</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16T14:00:11Z</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="AC10" s="5" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AD10" s="5" t="inlineStr">
+        <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AD10" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AE10" s="5" t="b">
@@ -2520,7 +2520,7 @@
       <c r="AQ10" s="5" t="n"/>
       <c r="AR10" s="6" t="n"/>
       <c r="AS10" s="6" t="n">
-        <v>0.07056586290088451</v>
+        <v>0.1013819418474451</v>
       </c>
       <c r="AT10" s="5" t="inlineStr">
         <is>
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.5798</v>
+        <v>100.5868</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.55</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>0.0002963699651914453</v>
+        <v>0.0003659870711087976</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16T14:00:11Z</t>
+          <t>2026-10-16T20:15:15Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>2026-10-09: QQQ 35.3%, SPY 34.4%, XLE 30.3%</t>
+          <t>2026-10-16: QQQ 35.5%, SPY 34.4%, XLE 30.0%</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02: QQQ 35.4%, SPY 34.6%, XLE 29.9%</t>
+          <t>2026-10-09: QQQ 35.3%, SPY 34.4%, XLE 30.3%</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>QQQ 35.4%, SPY 34.4%, XLE 30.1%</t>
+          <t>QQQ 35.5%, SPY 34.4%, XLE 30.0%</t>
         </is>
       </c>
     </row>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.0138146770521983</v>
+        <v>0.002535755435658427</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.04183467781612005</v>
+        <v>0.03024402724214337</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.09151270822776403</v>
+        <v>0.07936937813181943</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.00640386085827771</v>
+        <v>-0.008787983869701144</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.03656443559978895</v>
+        <v>0.02091731164822996</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.1132064052273267</v>
+        <v>0.09640235715463508</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.01604567193744277</v>
+        <v>-0.01745754726001048</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.03323977527487076</v>
+        <v>-0.03462688994763918</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.05796488940311506</v>
+        <v>-0.05931669922977556</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.03672582588613327</v>
+        <v>-0.04104327743749381</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.0438789445048966</v>
+        <v>0.0392002176278563</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1394839997308995</v>
+        <v>-0.1433408830982441</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.01628547137300473</v>
+        <v>-0.01928401750734998</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01806719409235669</v>
+        <v>-0.02106030920213409</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01525799800516547</v>
+        <v>-0.01825967607078305</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.04658426051278597</v>
+        <v>0.06460326358191115</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1647178894572707</v>
+        <v>0.1847707949103996</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.2353768473694551</v>
+        <v>0.2566461972487892</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.001797370163655221</v>
+        <v>-0.001608173304323057</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.01624919549763071</v>
+        <v>-0.01606273780155354</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.02109318918105085</v>
+        <v>-0.02090764960356428</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.01782241014799157</v>
+        <v>0.01902748414376321</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.01746389573793583</v>
+        <v>0.01866854526241646</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05576754385964922</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003196073533418664</v>
+        <v>0.003297809666817475</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009039975443613457</v>
+        <v>0.009142304218869635</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01834761510946503</v>
+        <v>0.01845080912006103</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.02285226703064946</v>
+        <v>0.0228523735523376</v>
       </c>
     </row>
     <row r="4">
@@ -3252,8 +3252,41 @@
         <v>0.07056586290088451</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>XLE, QQQ, SPY</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>QQQ 35.5%, SPY 34.4%, XLE 30.0%</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0.1013819418474451</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4421054026949163</v>
+        <v>0.4822089291877185</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1589034878486693</v>
+        <v>0.172641087717323</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1559722249956661</v>
+        <v>0.165396470761533</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.07936937813181943</v>
+        <v>0.08689980334505654</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.03024402724214337</v>
+        <v>0.0267923445498206</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.002535755435658427</v>
+        <v>0.006216439758957026</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.01185555656331383</v>
+        <v>0.004159842777595735</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,12 +872,12 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19T14:00:09Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
@@ -960,7 +960,7 @@
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +0.3%, 3m +3.0%, 6m +7.9%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +0.3%, 3m +3.1%, 6m +8.0%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>762.85</v>
+        <v>766.425</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>771.78998</v>
+        <v>763.25</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.01158343620890234</v>
+        <v>0.004159842777595735</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T20:15:09Z</t>
+          <t>2026-10-19T14:00:09Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.560829144400685</v>
+        <v>0.6270175155989941</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1843104300335037</v>
+        <v>0.2017567278047836</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1948104045964485</v>
+        <v>0.2068289048638279</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.09640235715463508</v>
+        <v>0.1119642645389296</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.02091731164822996</v>
+        <v>0.01332610752731167</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.008787983869701144</v>
+        <v>-0.004202896565206782</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.02489010989010987</v>
+        <v>0.01108763031839954</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19T14:00:09Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>709.53</v>
+        <v>717.67</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>728</v>
+        <v>709.79999</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.02537087912087921</v>
+        <v>0.0110876445630832</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T20:15:10Z</t>
+          <t>2026-10-19T14:00:09Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.02503012377757641</v>
+        <v>-0.03165132313120045</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.07630429315179832</v>
+        <v>-0.08432653597396167</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.05989231887913193</v>
+        <v>-0.07293841410493662</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.05931669922977556</v>
+        <v>-0.06027617265992624</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.03462688994763918</v>
+        <v>-0.03318248476682206</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.01745754726001048</v>
+        <v>-0.01228410500692889</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.0007502813555082533</v>
+        <v>-0.00149906308557135</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19T14:00:08Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.7%, 3m -3.5%, 6m -5.9%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.7%, 3m -3.4%, 6m -5.9%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>80.02</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>79.97</v>
+        <v>80.05</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>0.0006252344629236184</v>
+        <v>-0.00149906308557135</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-16T20:15:01Z</t>
+          <t>2026-10-19T14:00:08Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.2828598294042584</v>
+        <v>0.2383321950108952</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.01388781331474742</v>
+        <v>-0.03960146298398282</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.02831771599679911</v>
+        <v>0.01190566275696825</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1433408830982441</v>
+        <v>-0.1387500282747857</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.0392002176278563</v>
+        <v>0.0158480296683654</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.04104327743749381</v>
+        <v>-0.05090111424084554</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.001829061169031365</v>
+        <v>-0.003298342975314728</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19T14:00:10Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>381.89</v>
+        <v>380.75</v>
       </c>
       <c r="AW5" t="n">
-        <v>382.70999</v>
+        <v>382.01001</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.002142588438833304</v>
+        <v>-0.003298369066297546</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-16T20:10:31Z</t>
+          <t>2026-10-19T14:00:10Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.0852154746267979</v>
+        <v>0.08627362334682487</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.008870387440722327</v>
+        <v>0.01336068679441715</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.02870801072958273</v>
+        <v>0.02992161545668948</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01825967607078305</v>
+        <v>-0.01657600444509688</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.02106030920213409</v>
+        <v>-0.01986334534252121</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01928401750734998</v>
+        <v>-0.0160797952132784</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.003500583430571691</v>
+        <v>0.0008456934686442708</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19T14:00:10Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
+        <v>76.925</v>
+      </c>
+      <c r="AW6" t="n">
         <v>76.86</v>
       </c>
-      <c r="AW6" t="n">
-        <v>77.13</v>
-      </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.003500583430571691</v>
+        <v>0.0008456934686442708</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-16T20:10:00Z</t>
+          <t>2026-10-19T14:00:10Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8052216272574668</v>
+        <v>0.7943992420975741</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6261734586898218</v>
+        <v>0.6493818858098435</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.5274924606359737</v>
+        <v>0.5420441967578147</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2566461972487892</v>
+        <v>0.2580811276997146</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1847707949103996</v>
+        <v>0.1758368304802527</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.06460326358191115</v>
+        <v>0.06960740118714415</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.02524038461538458</v>
+        <v>0.002051582649472472</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19T14:00:11Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>68.1657</v>
+        <v>68.38</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>66.56</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.02412409855769226</v>
+        <v>0.002051582649472472</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T20:14:03Z</t>
+          <t>2026-10-19T14:00:11Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.03474755397566698</v>
+        <v>0.03131698198861277</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01323065959337422</v>
+        <v>-0.01607378044915353</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.01164120736797036</v>
+        <v>-0.01804198735205753</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02090764960356428</v>
+        <v>-0.02084013499452231</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.01606273780155354</v>
+        <v>-0.01506318992386702</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.001608173304323057</v>
+        <v>0.002004369715968402</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.00237439452939503</v>
+        <v>-0.0005590297517530374</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19T14:00:05Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>105.56</v>
+        <v>105.481</v>
       </c>
       <c r="AW8" t="n">
-        <v>105.29</v>
+        <v>105.54</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>0.002564346091746605</v>
+        <v>-0.0005590297517530374</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-16T20:14:27Z</t>
+          <t>2026-10-19T14:00:05Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.08715700026116946</v>
+        <v>0.09764974592661479</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07465648303899064</v>
+        <v>0.08022670989357361</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.05459028314822101</v>
+        <v>0.05914820562523082</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05701754385964919</v>
+        <v>0.05984626647144942</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01866854526241646</v>
+        <v>0.01667837078651679</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.01902748414376321</v>
+        <v>0.01990137372314194</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.002758620689655156</v>
+        <v>0.001210235131396731</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19T14:00:11Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
+        <v>28.955</v>
+      </c>
+      <c r="AW9" t="n">
         <v>28.92</v>
       </c>
-      <c r="AW9" t="n">
-        <v>29</v>
-      </c>
       <c r="AX9" s="4" t="n">
-        <v>-0.002758620689655156</v>
+        <v>0.001210235131396731</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-16T20:10:00Z</t>
+          <t>2026-10-19T14:00:11Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05997600680972215</v>
+        <v>0.05981743748203416</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03776458287306617</v>
+        <v>0.03771294633047528</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03435348196134758</v>
+        <v>0.03455913398014943</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01845080912006103</v>
+        <v>0.01840020990177216</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009142304218869635</v>
+        <v>0.00909215754149173</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003297809666817475</v>
+        <v>0.003048460205645975</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0003978120338141711</v>
+        <v>4.970673029114359e-05</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19T14:00:12Z</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.5868</v>
+        <v>100.595</v>
       </c>
       <c r="AW10" s="5" t="n">
-        <v>100.55</v>
+        <v>100.59</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>0.0003659870711087976</v>
+        <v>4.970673029114359e-05</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16T20:15:15Z</t>
+          <t>2026-10-19T14:00:12Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.002535755435658427</v>
+        <v>0.006216439758957026</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.03024402724214337</v>
+        <v>0.0267923445498206</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.07936937813181943</v>
+        <v>0.08689980334505654</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.008787983869701144</v>
+        <v>-0.004202896565206782</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.02091731164822996</v>
+        <v>0.01332610752731167</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.09640235715463508</v>
+        <v>0.1119642645389296</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.01745754726001048</v>
+        <v>-0.01228410500692889</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.03462688994763918</v>
+        <v>-0.03318248476682206</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.05931669922977556</v>
+        <v>-0.06027617265992624</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.04104327743749381</v>
+        <v>-0.05090111424084554</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.0392002176278563</v>
+        <v>0.0158480296683654</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1433408830982441</v>
+        <v>-0.1387500282747857</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.01928401750734998</v>
+        <v>-0.0160797952132784</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.02106030920213409</v>
+        <v>-0.01986334534252121</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01825967607078305</v>
+        <v>-0.01657600444509688</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.06460326358191115</v>
+        <v>0.06960740118714415</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1847707949103996</v>
+        <v>0.1758368304802527</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.2566461972487892</v>
+        <v>0.2580811276997146</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.001608173304323057</v>
+        <v>0.002004369715968402</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.01606273780155354</v>
+        <v>-0.01506318992386702</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.02090764960356428</v>
+        <v>-0.02084013499452231</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.01902748414376321</v>
+        <v>0.01990137372314194</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.01866854526241646</v>
+        <v>0.01667837078651679</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05701754385964919</v>
+        <v>0.05984626647144942</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003297809666817475</v>
+        <v>0.003048460205645975</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009142304218869635</v>
+        <v>0.00909215754149173</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01845080912006103</v>
+        <v>0.01840020990177216</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4822089291877185</v>
+        <v>0.4823154700645542</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.172641087717323</v>
+        <v>0.1727253480096029</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.165396470761533</v>
+        <v>0.1653965795916847</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.08689980334505654</v>
+        <v>0.08697780117809173</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.0267923445498206</v>
+        <v>0.02686602896636536</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.006216439758957026</v>
+        <v>0.006288647612545661</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.004159842777595735</v>
+        <v>0.004231903046184149</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -867,24 +867,24 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T14:00:09Z</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.3444390211106695</v>
+        <v>0.344733947081772</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +0.3%, 3m +3.1%, 6m +8.0%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +0.6%, 3m +2.7%, 6m +8.7%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>766.425</v>
+        <v>766.86</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>763.25</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>0.004159842777595735</v>
+        <v>0.004729773992794062</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T14:00:09Z</t>
+          <t>2026-10-19T20:15:02Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.6270175155989941</v>
+        <v>0.6285818029257089</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2017567278047836</v>
+        <v>0.2029121504115323</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0.2068289048638279</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.1119642645389296</v>
+        <v>0.1130333566600048</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.01332610752731167</v>
+        <v>0.01430036451756322</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.004202896565206782</v>
+        <v>-0.00324549274260022</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.01108763031839954</v>
+        <v>0.01205973513665826</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T14:00:09Z</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.3554859723629458</v>
+        <v>0.3561651602097869</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -0.9%, 3m +2.1%, 6m +9.6%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -0.3%, 3m +1.4%, 6m +11.3%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>717.67</v>
+        <v>718.6900000000001</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>709.79999</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>0.0110876445630832</v>
+        <v>0.01252466909727645</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T14:00:09Z</t>
+          <t>2026-10-19T20:15:06Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.03165132313120045</v>
+        <v>-0.03734535388471405</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.08432653597396167</v>
+        <v>-0.08971074927034883</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.07293841410493662</v>
+        <v>-0.07293833307797926</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.06027617265992624</v>
+        <v>-0.06580188514397289</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.03318248476682206</v>
+        <v>-0.03886751206770533</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.01228410500692889</v>
+        <v>-0.01809201781371927</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.00149906308557135</v>
+        <v>-0.007370393504059991</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.03802938342376228</v>
+        <v>-0.03802955588478829</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-19T14:00:08Z</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1350,14 +1350,14 @@
         <v>0</v>
       </c>
       <c r="AR4" s="4" t="n">
-        <v>-0.003175013794468051</v>
+        <v>-0.003174929419130335</v>
       </c>
       <c r="AS4" s="4" t="n">
         <v>0.1013819418474451</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.7%, 3m -3.4%, 6m -5.9%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.8%, 3m -3.9%, 6m -6.6%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>79.93000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="AW4" t="n">
         <v>80.05</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>-0.00149906308557135</v>
+        <v>-0.006870705808869393</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-19T14:00:08Z</t>
+          <t>2026-10-19T20:15:01Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.2383321950108952</v>
+        <v>0.2348847041987836</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.03960146298398282</v>
+        <v>-0.04227519233194599</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.01190566275696825</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1387500282747857</v>
+        <v>-0.1411477301002058</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.0158480296683654</v>
+        <v>0.01301993009791635</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.05090111424084554</v>
+        <v>-0.05354338559712846</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.003298342975314728</v>
+        <v>-0.006073139446611364</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-19T14:00:10Z</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -4.1%, 3m +3.9%, 6m -14.3%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -5.4%, 3m +1.3%, 6m -14.1%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>380.75</v>
+        <v>379.42</v>
       </c>
       <c r="AW5" t="n">
         <v>382.01001</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.003298369066297546</v>
+        <v>-0.006779953226880076</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-19T14:00:10Z</t>
+          <t>2026-10-19T20:14:52Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.08627362334682487</v>
+        <v>0.0849318751868946</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01336068679441715</v>
+        <v>0.01210921763295514</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>0.02992161545668948</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01657600444509688</v>
+        <v>-0.0177902153157562</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01986334534252121</v>
+        <v>-0.02107378385006042</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.0160797952132784</v>
+        <v>-0.01729490628841313</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.0008456934686442708</v>
+        <v>-0.0003903200624512104</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715195976610053</v>
+        <v>0.03715185591311232</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1659,17 +1659,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-19T14:00:10Z</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.9%, 3m -2.1%, 6m -1.8%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.7%, 3m -2.1%, 6m -1.8%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>76.925</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="AW6" t="n">
         <v>76.86</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>0.0008456934686442708</v>
+        <v>-0.0009107468123861207</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-19T14:00:10Z</t>
+          <t>2026-10-19T20:13:04Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7943992420975741</v>
+        <v>0.7791791256831753</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6493818858098435</v>
+        <v>0.6353918083929131</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.5420441967578147</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2580811276997146</v>
+        <v>0.2474100681199276</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1758368304802527</v>
+        <v>0.1658633680397943</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.06960740118714415</v>
+        <v>0.06053497807090347</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.002051582649472472</v>
+        <v>-0.00644783118405623</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1856,24 +1856,24 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T14:00:11Z</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.3000750065263847</v>
+        <v>0.2991008927084411</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +6.5%, 3m +18.5%, 6m +25.7%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +6.1%, 3m +16.6%, 6m +24.7%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>68.38</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>68.23999999999999</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.002051582649472472</v>
+        <v>-0.004982415005861496</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T14:00:11Z</t>
+          <t>2026-10-19T20:12:17Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.03131698198861277</v>
+        <v>0.02915620371556393</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01607378044915353</v>
+        <v>-0.01813533717637739</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.01804198735205753</v>
+        <v>-0.01804205723501096</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02084013499452231</v>
+        <v>-0.02289170475166113</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.01506318992386702</v>
+        <v>-0.01712679412772189</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.002004369715968402</v>
+        <v>-9.499382540123502e-05</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.0005590297517530374</v>
+        <v>-0.002653022550691664</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.004296411608788464</v>
+        <v>0.004296483646738736</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
@@ -2055,41 +2055,41 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>COMPLETED_SESSION</t>
+        </is>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>2026-10-19T14:00:05Z</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>LIVE_PRICE_OVERLAY</t>
-        </is>
-      </c>
-      <c r="X8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="AA8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
       <c r="AD8" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="AN8" s="4" t="n">
-        <v>-0.01164120736797036</v>
+        <v>-0.01164113686566881</v>
       </c>
       <c r="AO8" t="n">
         <v>7</v>
@@ -2140,14 +2140,14 @@
         <v>0</v>
       </c>
       <c r="AR8" s="4" t="n">
-        <v>-0.009282036975003183</v>
+        <v>-0.00928196647270163</v>
       </c>
       <c r="AS8" s="4" t="n">
         <v>0.1013819418474451</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -0.2%, 3m -1.6%, 6m -2.1%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -0.0%, 3m -1.7%, 6m -2.3%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>105.481</v>
+        <v>105.26</v>
       </c>
       <c r="AW8" t="n">
         <v>105.54</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>-0.0005590297517530374</v>
+        <v>-0.002653022550691664</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-19T14:00:05Z</t>
+          <t>2026-10-19T20:10:00Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.09764974592661479</v>
+        <v>0.09935564261342877</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.08022670989357361</v>
+        <v>0.08190552881760094</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.05914820562523082</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05984626647144942</v>
+        <v>0.06149341142020504</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01667837078651679</v>
+        <v>0.01825842696629221</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.01990137372314194</v>
+        <v>0.02148643888693202</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.001210235131396731</v>
+        <v>0.002766251728907321</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2252,17 +2252,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-19T14:00:11Z</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +1.9%, 3m +1.9%, 6m +5.7%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +2.1%, 3m +1.8%, 6m +6.1%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>28.955</v>
+        <v>29.019</v>
       </c>
       <c r="AW9" t="n">
         <v>28.92</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>0.001210235131396731</v>
+        <v>0.003423236514522809</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-19T14:00:11Z</t>
+          <t>2026-10-19T20:12:14Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05981743748203416</v>
+        <v>0.05976510077405428</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03771294633047528</v>
+        <v>0.03766128590975848</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03455913398014943</v>
+        <v>0.03455905255731895</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01840020990177216</v>
+        <v>0.01834951241782035</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.00909215754149173</v>
+        <v>0.009042001362877361</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003048460205645975</v>
+        <v>0.002998604424533369</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>4.970673029114359e-05</v>
+        <v>0</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-19T14:00:12Z</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.595</v>
+        <v>100.59</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.59</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>4.970673029114359e-05</v>
+        <v>0</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-19T14:00:12Z</t>
+          <t>2026-10-19T20:15:01Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>QQQ 35.5%, SPY 34.4%, XLE 30.0%</t>
+          <t>QQQ 35.6%, SPY 34.5%, XLE 29.9%</t>
         </is>
       </c>
     </row>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.006216439758957026</v>
+        <v>0.006288647612545661</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.0267923445498206</v>
+        <v>0.02686602896636536</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.08689980334505654</v>
+        <v>0.08697780117809173</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.004202896565206782</v>
+        <v>-0.00324549274260022</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.01332610752731167</v>
+        <v>0.01430036451756322</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.1119642645389296</v>
+        <v>0.1130333566600048</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.01228410500692889</v>
+        <v>-0.01809201781371927</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.03318248476682206</v>
+        <v>-0.03886751206770533</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.06027617265992624</v>
+        <v>-0.06580188514397289</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.05090111424084554</v>
+        <v>-0.05354338559712846</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.0158480296683654</v>
+        <v>0.01301993009791635</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1387500282747857</v>
+        <v>-0.1411477301002058</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.0160797952132784</v>
+        <v>-0.01729490628841313</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01986334534252121</v>
+        <v>-0.02107378385006042</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01657600444509688</v>
+        <v>-0.0177902153157562</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.06960740118714415</v>
+        <v>0.06053497807090347</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1758368304802527</v>
+        <v>0.1658633680397943</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.2580811276997146</v>
+        <v>0.2474100681199276</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.002004369715968402</v>
+        <v>-9.499382540123502e-05</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.01506318992386702</v>
+        <v>-0.01712679412772189</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.02084013499452231</v>
+        <v>-0.02289170475166113</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.01990137372314194</v>
+        <v>0.02148643888693202</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.01667837078651679</v>
+        <v>0.01825842696629221</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05984626647144942</v>
+        <v>0.06149341142020504</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003048460205645975</v>
+        <v>0.002998604424533369</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.00909215754149173</v>
+        <v>0.009042001362877361</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01840020990177216</v>
+        <v>0.01834951241782035</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.02933603803237417</v>
+        <v>0.02933602385378342</v>
       </c>
     </row>
     <row r="3">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.0228523735523376</v>
+        <v>0.02285226703064946</v>
       </c>
     </row>
     <row r="4">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4823154700645542</v>
+        <v>0.4826369105941555</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1727253480096029</v>
+        <v>0.1680232327190643</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1653965795916847</v>
+        <v>0.1767863736527941</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.08697780117809173</v>
+        <v>0.09593971523045774</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.02686602896636536</v>
+        <v>0.02975135535958184</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.006288647612545661</v>
+        <v>-0.007446670976082759</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.004231903046184149</v>
+        <v>0.001643878509550056</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,12 +872,12 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20T14:00:08Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>766.86</v>
+        <v>767.74</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>763.25</v>
+        <v>766.47998</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>0.004729773992794062</v>
+        <v>0.001643904645754812</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T20:15:02Z</t>
+          <t>2026-10-20T14:00:08Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.6285818029257089</v>
+        <v>0.6232970562682081</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2029121504115323</v>
+        <v>0.1909719848882525</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.2068289048638279</v>
+        <v>0.2335102634936339</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.1130333566600048</v>
+        <v>0.1134566407903004</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.01430036451756322</v>
+        <v>0.01601476124033163</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.00324549274260022</v>
+        <v>-0.03448554897703215</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.01205973513665826</v>
+        <v>-0.003424466841138174</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20T14:00:09Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>718.6900000000001</v>
+        <v>715.9</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>709.79999</v>
+        <v>718.35999</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>0.01252466909727645</v>
+        <v>-0.0034244529682117</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T20:15:06Z</t>
+          <t>2026-10-20T14:00:09Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.03734535388471405</v>
+        <v>-0.02063841028012225</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.08971074927034883</v>
+        <v>-0.08068344249889614</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.07293833307797926</v>
+        <v>-0.0652300322070003</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.06580188514397289</v>
+        <v>-0.0527605704339853</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.03886751206770533</v>
+        <v>-0.02826835050155885</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.01809201781371927</v>
+        <v>-0.01653177875235057</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.007370393504059991</v>
+        <v>0.008368990687138256</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20T14:00:09Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>79.5</v>
+        <v>80.125</v>
       </c>
       <c r="AW4" t="n">
-        <v>80.05</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>-0.006870705808869393</v>
+        <v>0.008368990687138256</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-19T20:15:01Z</t>
+          <t>2026-10-20T14:00:09Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.2348847041987836</v>
+        <v>0.2358225532470926</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.04227519233194599</v>
+        <v>-0.0274557186560066</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.01190566275696825</v>
+        <v>0.02413943803182605</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1411477301002058</v>
+        <v>-0.1193286309565379</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.01301993009791635</v>
+        <v>-0.002136526693395258</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.05354338559712846</v>
+        <v>-0.05037903509212305</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.006073139446611364</v>
+        <v>-0.003634543970080895</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20T14:00:09Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>379.42</v>
+        <v>378.31</v>
       </c>
       <c r="AW5" t="n">
-        <v>382.01001</v>
+        <v>379.69</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.006779953226880076</v>
+        <v>-0.003634543970080895</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-19T20:14:52Z</t>
+          <t>2026-10-20T14:00:09Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.0849318751868946</v>
+        <v>0.07858442683221778</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01210921763295514</v>
+        <v>0.009410393311476195</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.02992161545668948</v>
+        <v>0.02920428742943937</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.0177902153157562</v>
+        <v>-0.015287910537228</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.02107378385006042</v>
+        <v>-0.01953728967185997</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01729490628841313</v>
+        <v>-0.01923223052966561</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.0003903200624512104</v>
+        <v>-6.507874528172142e-05</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20T14:00:10Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>76.79000000000001</v>
+        <v>76.825</v>
       </c>
       <c r="AW6" t="n">
-        <v>76.86</v>
+        <v>76.83</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.0009107468123861207</v>
+        <v>-6.507874528172142e-05</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-19T20:13:04Z</t>
+          <t>2026-10-20T14:00:10Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7791791256831753</v>
+        <v>0.7442444134385289</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6353918083929131</v>
+        <v>0.6261420759561402</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.5420441967578147</v>
+        <v>0.4943207811725563</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2474100681199276</v>
+        <v>0.2326295074075597</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1658633680397943</v>
+        <v>0.1549647908310172</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.06053497807090347</v>
+        <v>0.08821485750880553</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.00644783118405623</v>
+        <v>0.002505899705014691</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20T14:00:09Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>67.90000000000001</v>
+        <v>67.9699</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>68.23999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>-0.004982415005861496</v>
+        <v>0.002505899705014691</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T20:12:17Z</t>
+          <t>2026-10-20T14:00:09Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.02915620371556393</v>
+        <v>0.02899135198432035</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01813533717637739</v>
+        <v>-0.01409806845463935</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.01804205723501096</v>
+        <v>-0.01227552613439142</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02289170475166113</v>
+        <v>-0.01913018169972902</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.01712679412772189</v>
+        <v>-0.01402048250008814</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-9.499382540123502e-05</v>
+        <v>-0.001845193035579173</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.002653022550691664</v>
+        <v>0.002137564126923674</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20T14:00:02Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
+        <v>105.485</v>
+      </c>
+      <c r="AW8" t="n">
         <v>105.26</v>
       </c>
-      <c r="AW8" t="n">
-        <v>105.54</v>
-      </c>
       <c r="AX8" s="4" t="n">
-        <v>-0.002653022550691664</v>
+        <v>0.002137564126923674</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-19T20:10:00Z</t>
+          <t>2026-10-20T14:00:02Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.09935564261342877</v>
+        <v>0.09476212873627055</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.08190552881760094</v>
+        <v>0.07700926828321708</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.05914820562523082</v>
+        <v>0.0613572304742569</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.06149341142020504</v>
+        <v>0.05205678922460866</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01825842696629221</v>
+        <v>0.01581722319859402</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.02148643888693202</v>
+        <v>0.01474719101123578</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.002766251728907321</v>
+        <v>-0.003448275862068972</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20T14:00:09Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>29.019</v>
+        <v>28.9</v>
       </c>
       <c r="AW9" t="n">
-        <v>28.92</v>
+        <v>29</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>0.003423236514522809</v>
+        <v>-0.003448275862068972</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-19T20:12:14Z</t>
+          <t>2026-10-20T14:00:09Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05976510077405428</v>
+        <v>0.05950799418556274</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03766128590975848</v>
+        <v>0.03751280710351557</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03455905255731895</v>
+        <v>0.03435343298636173</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01834951241782035</v>
+        <v>0.01830503744926437</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009042001362877361</v>
+        <v>0.009198488640153935</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.002998604424533369</v>
+        <v>0.00305444349716355</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0</v>
+        <v>0.0001550849985088032</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20T14:00:12Z</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.59</v>
+        <v>100.6056</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.59</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>0</v>
+        <v>0.0001550849985088032</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-19T20:15:01Z</t>
+          <t>2026-10-20T14:00:12Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.006288647612545661</v>
+        <v>-0.007446670976082759</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.02686602896636536</v>
+        <v>0.02975135535958184</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.08697780117809173</v>
+        <v>0.09593971523045774</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.00324549274260022</v>
+        <v>-0.03448554897703215</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.01430036451756322</v>
+        <v>0.01601476124033163</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.1130333566600048</v>
+        <v>0.1134566407903004</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.01809201781371927</v>
+        <v>-0.01653177875235057</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.03886751206770533</v>
+        <v>-0.02826835050155885</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.06580188514397289</v>
+        <v>-0.0527605704339853</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.05354338559712846</v>
+        <v>-0.05037903509212305</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.01301993009791635</v>
+        <v>-0.002136526693395258</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1411477301002058</v>
+        <v>-0.1193286309565379</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.01729490628841313</v>
+        <v>-0.01923223052966561</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.02107378385006042</v>
+        <v>-0.01953728967185997</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.0177902153157562</v>
+        <v>-0.015287910537228</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.06053497807090347</v>
+        <v>0.08821485750880553</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1658633680397943</v>
+        <v>0.1549647908310172</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.2474100681199276</v>
+        <v>0.2326295074075597</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-9.499382540123502e-05</v>
+        <v>-0.001845193035579173</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.01712679412772189</v>
+        <v>-0.01402048250008814</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.02289170475166113</v>
+        <v>-0.01913018169972902</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.02148643888693202</v>
+        <v>0.01474719101123578</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.01825842696629221</v>
+        <v>0.01581722319859402</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.06149341142020504</v>
+        <v>0.05205678922460866</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.002998604424533369</v>
+        <v>0.00305444349716355</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009042001362877361</v>
+        <v>0.009198488640153935</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01834951241782035</v>
+        <v>0.01830503744926437</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4826369105941555</v>
+        <v>0.4854757313649547</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1680232327190643</v>
+        <v>0.1702595506440561</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1767863736527941</v>
+        <v>0.1767862643792688</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.09593971523045774</v>
+        <v>0.09803812274001666</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.02975135535958184</v>
+        <v>0.03172303130766152</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-0.007446670976082759</v>
+        <v>-0.005546218487394894</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.001643878509550056</v>
+        <v>0.003561736770691937</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -867,24 +867,24 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20T14:00:08Z</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.344733947081772</v>
+        <v>0.3451870399306671</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>0.3444390211106695</v>
+        <v>0.3444390384706972</v>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
       </c>
       <c r="AM2" s="2" t="n"/>
       <c r="AN2" s="3" t="n">
-        <v>0.1559722249956661</v>
+        <v>0.1559723322105802</v>
       </c>
       <c r="AO2" s="2" t="n">
         <v>3</v>
@@ -953,14 +953,14 @@
         <v>0</v>
       </c>
       <c r="AR2" s="3" t="n">
-        <v>0.02078105991911672</v>
+        <v>0.02078116713403078</v>
       </c>
       <c r="AS2" s="3" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.1013820490623591</v>
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +0.6%, 3m +2.7%, 6m +8.7%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -0.6%, 3m +3.2%, 6m +9.8%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>767.74</v>
+        <v>769.67</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>766.47998</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>0.001643904645754812</v>
+        <v>0.00416190909513392</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20T14:00:08Z</t>
+          <t>2026-10-20T20:14:51Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.6232970562682081</v>
+        <v>0.6281268128401474</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1909719848882525</v>
+        <v>0.1945154551045005</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0.2335102634936339</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.1134566407903004</v>
+        <v>0.1167694814731937</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.01601476124033163</v>
+        <v>0.01903768544963724</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.03448554897703215</v>
+        <v>-0.03161287712247296</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.003424466841138174</v>
+        <v>-0.0004593796982015341</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20T14:00:09Z</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.3561651602097869</v>
+        <v>0.3619880633257918</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>0.3554859723629458</v>
+        <v>0.3554859562725387</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1152,14 +1152,14 @@
         <v>0</v>
       </c>
       <c r="AR3" s="3" t="n">
-        <v>0.03152580102672942</v>
+        <v>0.03152603436066848</v>
       </c>
       <c r="AS3" s="3" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.1013820490623591</v>
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -0.3%, 3m +1.4%, 6m +11.3%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -3.2%, 3m +1.9%, 6m +11.7%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>715.9</v>
+        <v>718.7</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>718.35999</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.0034244529682117</v>
+        <v>0.0004733142223023457</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20T14:00:09Z</t>
+          <t>2026-10-20T20:15:06Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.02063841028012225</v>
+        <v>-0.02057747834148038</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.08068344249889614</v>
+        <v>-0.08062623580776529</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.0652300322070003</v>
+        <v>-0.06523019585918166</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.0527605704339853</v>
+        <v>-0.05270137488770732</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.02826835050155885</v>
+        <v>-0.02820771202109096</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.01653177875235057</v>
+        <v>-0.01647040788050991</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.008368990687138256</v>
+        <v>0.008431915429146786</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.03802955588478829</v>
+        <v>-0.03802929719322601</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-20T14:00:09Z</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="AN4" s="4" t="n">
-        <v>-0.05989231887913193</v>
+        <v>-0.05989215331210995</v>
       </c>
       <c r="AO4" t="n">
         <v>8</v>
@@ -1350,14 +1350,14 @@
         <v>0</v>
       </c>
       <c r="AR4" s="4" t="n">
-        <v>-0.003174929419130335</v>
+        <v>-0.00317484822744607</v>
       </c>
       <c r="AS4" s="4" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.1013820490623591</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.8%, 3m -3.9%, 6m -6.6%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.6%, 3m -2.8%, 6m -5.3%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>80.125</v>
+        <v>80.13</v>
       </c>
       <c r="AW4" t="n">
         <v>79.45999999999999</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>0.008368990687138256</v>
+        <v>0.008431915429146786</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-20T14:00:09Z</t>
+          <t>2026-10-20T20:15:00Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.2358225532470926</v>
+        <v>0.2336665359989545</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.0274557186560066</v>
+        <v>-0.02915242037070365</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.02413943803182605</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1193286309565379</v>
+        <v>-0.1208650510976093</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>-0.002136526693395258</v>
+        <v>-0.003877400295421052</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.05037903509212305</v>
+        <v>-0.05203574476630357</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.003634543970080895</v>
+        <v>-0.005372804129684772</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-20T14:00:09Z</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1550,11 +1550,11 @@
         <v>-0.03630758617886576</v>
       </c>
       <c r="AS5" s="4" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.1013820490623591</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -5.4%, 3m +1.3%, 6m -14.1%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -5.2%, 3m -0.4%, 6m -12.1%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>378.31</v>
+        <v>377.99</v>
       </c>
       <c r="AW5" t="n">
         <v>379.69</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.003634543970080895</v>
+        <v>-0.004477336774737273</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-20T14:00:09Z</t>
+          <t>2026-10-20T20:14:56Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07858442683221778</v>
+        <v>0.07865450878397739</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.009410393311476195</v>
+        <v>0.009476088748723743</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>0.02920428742943937</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.015287910537228</v>
+        <v>-0.0152239188409814</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01953728967185997</v>
+        <v>-0.01947347823610812</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01923223052966561</v>
+        <v>-0.01916839923975544</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-6.507874528172142e-05</v>
+        <v>0</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715185591311232</v>
+        <v>0.03715206361910939</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1659,17 +1659,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-20T14:00:10Z</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1744,14 +1744,14 @@
         <v>1</v>
       </c>
       <c r="AR6" s="4" t="n">
-        <v>-0.000604171475144577</v>
+        <v>-0.0006039649327913565</v>
       </c>
       <c r="AS6" s="4" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.1013820490623591</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.7%, 3m -2.1%, 6m -1.8%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.9%, 3m -1.9%, 6m -1.5%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>76.825</v>
+        <v>76.83</v>
       </c>
       <c r="AW6" t="n">
         <v>76.83</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>-6.507874528172142e-05</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-20T14:00:10Z</t>
+          <t>2026-10-20T20:10:00Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7442444134385289</v>
+        <v>0.7442468088905456</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6261420759561402</v>
+        <v>0.6261447652191587</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4943207811725563</v>
+        <v>0.494321053929508</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2326295074075597</v>
+        <v>0.2326313209007493</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1549647908310172</v>
+        <v>0.1549664900608099</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.08821485750880553</v>
+        <v>0.08821645853346127</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.002505899705014691</v>
+        <v>0.002507374631268489</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1856,24 +1856,24 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20T14:00:09Z</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2991008927084411</v>
+        <v>0.2928248967435412</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.3000750065263847</v>
+        <v>0.3000750052567641</v>
       </c>
       <c r="AH7" s="2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AM7" s="2" t="n"/>
       <c r="AN7" s="3" t="n">
-        <v>0.5274924606359737</v>
+        <v>0.5274925994927393</v>
       </c>
       <c r="AO7" s="2" t="n">
         <v>1</v>
@@ -1942,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="AR7" s="3" t="n">
-        <v>0.0353219153630413</v>
+        <v>0.0353217910086423</v>
       </c>
       <c r="AS7" s="3" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.1013820490623591</v>
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +6.1%, 3m +16.6%, 6m +24.7%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +8.8%, 3m +15.5%, 6m +23.3%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>67.9699</v>
+        <v>68</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>67.8</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.002505899705014691</v>
+        <v>0.002949852507374784</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20T14:00:09Z</t>
+          <t>2026-10-20T20:13:39Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.02899135198432035</v>
+        <v>0.02894257768693276</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01409806845463935</v>
+        <v>-0.01414473001047434</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.01227552613439142</v>
+        <v>-0.01227545570256849</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.01913018169972902</v>
+        <v>-0.01917674461413543</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.01402048250008814</v>
+        <v>-0.01406721803203581</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.001845193035579173</v>
+        <v>-0.001892505677517087</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.002137564126923674</v>
+        <v>0.002090062701880946</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2055,17 +2055,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-20T14:00:02Z</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="AN8" s="4" t="n">
-        <v>-0.01164113686566881</v>
+        <v>-0.01164120736797036</v>
       </c>
       <c r="AO8" t="n">
         <v>7</v>
@@ -2140,14 +2140,14 @@
         <v>0</v>
       </c>
       <c r="AR8" s="4" t="n">
-        <v>-0.00928196647270163</v>
+        <v>-0.009282036975003183</v>
       </c>
       <c r="AS8" s="4" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.1013820490623591</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -0.0%, 3m -1.7%, 6m -2.3%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -0.2%, 3m -1.4%, 6m -1.9%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>105.485</v>
+        <v>105.48</v>
       </c>
       <c r="AW8" t="n">
         <v>105.26</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>0.002137564126923674</v>
+        <v>0.002090062701880946</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-20T14:00:02Z</t>
+          <t>2026-10-20T20:12:29Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2252,17 +2252,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-20T14:00:09Z</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2340,11 +2340,11 @@
         <v>0.01338001355371299</v>
       </c>
       <c r="AS9" s="4" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.1013820490623591</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +2.1%, 3m +1.8%, 6m +6.1%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +1.5%, 3m +1.6%, 6m +5.2%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-20T14:00:09Z</t>
+          <t>2026-10-20T20:10:00Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05950799418556274</v>
+        <v>0.05955407651857203</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03751280710351557</v>
+        <v>0.03755801960236282</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03435343298636173</v>
+        <v>0.03435327022164225</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01830503744926437</v>
+        <v>0.01834965180249437</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009198488640153935</v>
+        <v>0.009242626077334615</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.00305444349716355</v>
+        <v>0.00309831222366963</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0001550849985088032</v>
+        <v>0.0001988269211650184</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-20T14:00:12Z</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2520,7 +2520,7 @@
       <c r="AQ10" s="5" t="n"/>
       <c r="AR10" s="6" t="n"/>
       <c r="AS10" s="6" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.1013820490623591</v>
       </c>
       <c r="AT10" s="5" t="inlineStr">
         <is>
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.6056</v>
+        <v>100.6</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.59</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>0.0001550849985088032</v>
+        <v>9.941346058250922e-05</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-20T14:00:12Z</t>
+          <t>2026-10-20T20:14:58Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>QQQ 35.6%, SPY 34.5%, XLE 29.9%</t>
+          <t>QQQ 36.2%, SPY 34.5%, XLE 29.3%</t>
         </is>
       </c>
     </row>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>-0.007446670976082759</v>
+        <v>-0.005546218487394894</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.02975135535958184</v>
+        <v>0.03172303130766152</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.09593971523045774</v>
+        <v>0.09803812274001666</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.03448554897703215</v>
+        <v>-0.03161287712247296</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.01601476124033163</v>
+        <v>0.01903768544963724</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.1134566407903004</v>
+        <v>0.1167694814731937</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.01653177875235057</v>
+        <v>-0.01647040788050991</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.02826835050155885</v>
+        <v>-0.02820771202109096</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.0527605704339853</v>
+        <v>-0.05270137488770732</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.05037903509212305</v>
+        <v>-0.05203574476630357</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-0.002136526693395258</v>
+        <v>-0.003877400295421052</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1193286309565379</v>
+        <v>-0.1208650510976093</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.01923223052966561</v>
+        <v>-0.01916839923975544</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01953728967185997</v>
+        <v>-0.01947347823610812</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.015287910537228</v>
+        <v>-0.0152239188409814</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.08821485750880553</v>
+        <v>0.08821645853346127</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1549647908310172</v>
+        <v>0.1549664900608099</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.2326295074075597</v>
+        <v>0.2326313209007493</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.001845193035579173</v>
+        <v>-0.001892505677517087</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.01402048250008814</v>
+        <v>-0.01406721803203581</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.01913018169972902</v>
+        <v>-0.01917674461413543</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.00305444349716355</v>
+        <v>0.00309831222366963</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009198488640153935</v>
+        <v>0.009242626077334615</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01830503744926437</v>
+        <v>0.01834965180249437</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.02933602385378342</v>
+        <v>0.02933614706677878</v>
       </c>
     </row>
     <row r="3">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.02285226703064946</v>
+        <v>0.0228523735523376</v>
       </c>
     </row>
     <row r="4">
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.1013820490623591</v>
       </c>
     </row>
   </sheetData>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4854757313649547</v>
+        <v>0.5244065227188084</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1702595506440561</v>
+        <v>0.1602763237777178</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1767862643792688</v>
+        <v>0.1644923347130882</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.09803812274001666</v>
+        <v>0.08896617767994863</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.03172303130766152</v>
+        <v>0.0464839018069132</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-0.005546218487394894</v>
+        <v>-0.003620471178463314</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.003561736770691937</v>
+        <v>0.001989467524868394</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,12 +872,12 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21T14:00:07Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>769.67</v>
+        <v>770.58</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>766.47998</v>
+        <v>769.04999</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>0.00416190909513392</v>
+        <v>0.001989480553793443</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20T20:14:51Z</t>
+          <t>2026-10-21T14:00:07Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.6281268128401474</v>
+        <v>0.6799079755993951</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1945154551045005</v>
+        <v>0.1870477266904447</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.2335102634936339</v>
+        <v>0.2280014247003765</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.1167694814731937</v>
+        <v>0.1052801155309062</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.01903768544963724</v>
+        <v>0.0452702221284913</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.03161287712247296</v>
+        <v>-0.03334987825435487</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.0004593796982015341</v>
+        <v>0.00683123615233483</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21T14:00:07Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -3.2%, 3m +1.9%, 6m +11.7%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -3.2%, 3m +1.8%, 6m +11.6%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>718.7</v>
+        <v>722.5323</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>718.35999</v>
+        <v>717.63</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>0.0004733142223023457</v>
+        <v>0.00683123615233483</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20T20:15:06Z</t>
+          <t>2026-10-21T14:00:07Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.02057747834148038</v>
+        <v>-0.0004159825846918874</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.08062623580776529</v>
+        <v>-0.0816264119270449</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.06523019585918166</v>
+        <v>-0.06937297244713325</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.05270137488770732</v>
+        <v>-0.05196214804925703</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.02820771202109096</v>
+        <v>-0.02237622162998432</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.01647040788050991</v>
+        <v>-0.01316686397141575</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.008431915429146786</v>
+        <v>0.002745538499937528</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21T14:00:08Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="AW4" t="n">
         <v>80.13</v>
       </c>
-      <c r="AW4" t="n">
-        <v>79.45999999999999</v>
-      </c>
       <c r="AX4" s="4" t="n">
-        <v>0.008431915429146786</v>
+        <v>0.002745538499937528</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-20T20:15:00Z</t>
+          <t>2026-10-21T14:00:08Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,28 +1410,28 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.2336665359989545</v>
+        <v>0.1988218891599862</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.02915242037070365</v>
+        <v>-0.06154979536152783</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.02413943803182605</v>
+        <v>-0.007639836289222379</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1208650510976093</v>
+        <v>-0.1307811423057482</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>-0.003877400295421052</v>
+        <v>0.01834679155900099</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.05203574476630357</v>
+        <v>-0.05432499312620287</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.005372804129684772</v>
+        <v>0.001817026347146866</v>
       </c>
       <c r="M5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21T14:00:08Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>377.99</v>
+        <v>378.3362</v>
       </c>
       <c r="AW5" t="n">
-        <v>379.69</v>
+        <v>377.64999</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.004477336774737273</v>
+        <v>0.001817052874806269</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-20T20:14:56Z</t>
+          <t>2026-10-21T14:00:08Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07865450878397739</v>
+        <v>0.08669662640769404</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.009476088748723743</v>
+        <v>0.00898700941221442</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.02920428742943937</v>
+        <v>0.0270376424527583</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.0152239188409814</v>
+        <v>-0.01534256787979404</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01947347823610812</v>
+        <v>-0.01441154388049948</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01916839923975544</v>
+        <v>-0.01757543472061607</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0</v>
+        <v>0.001496811141481036</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21T14:00:10Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>76.83</v>
+        <v>76.94499999999999</v>
       </c>
       <c r="AW6" t="n">
         <v>76.83</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>0</v>
+        <v>0.001496811141481036</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-20T20:10:00Z</t>
+          <t>2026-10-21T14:00:10Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7442468088905456</v>
+        <v>0.7895133530488292</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6261447652191587</v>
+        <v>0.607745332761384</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.494321053929508</v>
+        <v>0.4624043972025662</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2326313209007493</v>
+        <v>0.2171286186224006</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1549664900608099</v>
+        <v>0.150618386883959</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.08821645853346127</v>
+        <v>0.09938491421171891</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.002507374631268489</v>
+        <v>-0.0007356186552890387</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21T14:00:09Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>68</v>
+        <v>67.92</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>67.8</v>
+        <v>67.97</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.002949852507374784</v>
+        <v>-0.0007356186552890387</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20T20:13:39Z</t>
+          <t>2026-10-21T14:00:09Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.02894257768693276</v>
+        <v>0.03587236995737419</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01414473001047434</v>
+        <v>-0.01348606136022412</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.01227545570256849</v>
+        <v>-0.01427979210739039</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.01917674461413543</v>
+        <v>-0.01914169440908875</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.01406721803203581</v>
+        <v>-0.009952654761349544</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.001892505677517087</v>
+        <v>0.0008052292535050132</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.002090062701880946</v>
+        <v>0.00156427758816835</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21T14:00:09Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
+        <v>105.645</v>
+      </c>
+      <c r="AW8" t="n">
         <v>105.48</v>
       </c>
-      <c r="AW8" t="n">
-        <v>105.26</v>
-      </c>
       <c r="AX8" s="4" t="n">
-        <v>0.002090062701880946</v>
+        <v>0.00156427758816835</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-20T20:12:29Z</t>
+          <t>2026-10-21T14:00:09Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.09476212873627055</v>
+        <v>0.1060460018771643</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07700926828321708</v>
+        <v>0.07503534890088082</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0613572304742569</v>
+        <v>0.05868666922651911</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05205678922460866</v>
+        <v>0.05239446870451236</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01581722319859402</v>
+        <v>0.01259803921568636</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.01474719101123578</v>
+        <v>0.015442415730337</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.003448275862068972</v>
+        <v>0.0006851211072664842</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21T13:59:54Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
+        <v>28.9198</v>
+      </c>
+      <c r="AW9" t="n">
         <v>28.9</v>
       </c>
-      <c r="AW9" t="n">
-        <v>29</v>
-      </c>
       <c r="AX9" s="4" t="n">
-        <v>-0.003448275862068972</v>
+        <v>0.0006851211072664842</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-20T20:10:00Z</t>
+          <t>2026-10-21T13:59:54Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2398,22 +2398,22 @@
         <v>0.05955407651857203</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03755801960236282</v>
+        <v>0.03745494751513179</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03435327022164225</v>
+        <v>0.03435331836104849</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01834965180249437</v>
+        <v>0.01824839535128508</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009242626077334615</v>
+        <v>0.009142323219453186</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.00309831222366963</v>
+        <v>0.002998616719283032</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0001988269211650184</v>
+        <v>0</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21T14:00:11Z</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.6</v>
+        <v>100.61</v>
       </c>
       <c r="AW10" s="5" t="n">
-        <v>100.59</v>
+        <v>100.61</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>9.941346058250922e-05</v>
+        <v>0</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-20T20:14:58Z</t>
+          <t>2026-10-21T14:00:11Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>-0.005546218487394894</v>
+        <v>-0.003620471178463314</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.03172303130766152</v>
+        <v>0.0464839018069132</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.09803812274001666</v>
+        <v>0.08896617767994863</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.03161287712247296</v>
+        <v>-0.03334987825435487</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.01903768544963724</v>
+        <v>0.0452702221284913</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.1167694814731937</v>
+        <v>0.1052801155309062</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.01647040788050991</v>
+        <v>-0.01316686397141575</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.02820771202109096</v>
+        <v>-0.02237622162998432</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.05270137488770732</v>
+        <v>-0.05196214804925703</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.05203574476630357</v>
+        <v>-0.05432499312620287</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-0.003877400295421052</v>
+        <v>0.01834679155900099</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1208650510976093</v>
+        <v>-0.1307811423057482</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.01916839923975544</v>
+        <v>-0.01757543472061607</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01947347823610812</v>
+        <v>-0.01441154388049948</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.0152239188409814</v>
+        <v>-0.01534256787979404</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.08821645853346127</v>
+        <v>0.09938491421171891</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1549664900608099</v>
+        <v>0.150618386883959</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.2326313209007493</v>
+        <v>0.2171286186224006</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-0.001892505677517087</v>
+        <v>0.0008052292535050132</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.01406721803203581</v>
+        <v>-0.009952654761349544</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.01917674461413543</v>
+        <v>-0.01914169440908875</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.01474719101123578</v>
+        <v>0.015442415730337</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.01581722319859402</v>
+        <v>0.01259803921568636</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05205678922460866</v>
+        <v>0.05239446870451236</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.00309831222366963</v>
+        <v>0.002998616719283032</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009242626077334615</v>
+        <v>0.009142323219453186</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01834965180249437</v>
+        <v>0.01824839535128508</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.5244065227188084</v>
+        <v>0.529371859509042</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1602763237777178</v>
+        <v>0.1640557834163989</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1644923347130882</v>
+        <v>0.1644924417319775</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.08896617767994863</v>
+        <v>0.09251325274804878</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.0464839018069132</v>
+        <v>0.04989259992201522</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-0.003620471178463314</v>
+        <v>-0.000374977372055052</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.001989467524868394</v>
+        <v>0.00525323451010995</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -858,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512197561446</v>
+        <v>0.3464512062651334</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -867,24 +867,24 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T14:00:07Z</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.3451870399306671</v>
+        <v>0.3439623359746363</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>0.3464512197561446</v>
+        <v>0.3464512062651334</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>0.3444390384706972</v>
+        <v>0.3444390530219004</v>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -0.6%, 3m +3.2%, 6m +9.8%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -0.0%, 3m +5.0%, 6m +9.3%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>770.58</v>
+        <v>773.24</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>769.04999</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>0.001989480553793443</v>
+        <v>0.00544829341978148</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T14:00:07Z</t>
+          <t>2026-10-21T20:14:48Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.6799079755993951</v>
+        <v>0.6861103337017975</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1870477266904447</v>
+        <v>0.1914303693756236</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.2280014247003765</v>
+        <v>0.2280013015630222</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.1052801155309062</v>
+        <v>0.1093609791327161</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.0452702221284913</v>
+        <v>0.04912952000565518</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.03334987825435487</v>
+        <v>-0.02978085783854656</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.00683123615233483</v>
+        <v>0.01054861140141861</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.1982245316673374</v>
+        <v>0.1982246540542743</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>2</v>
@@ -1057,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095304551976</v>
+        <v>0.3583095554429965</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T14:00:07Z</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.3619880633257918</v>
+        <v>0.3640161653056022</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0.3583095304551976</v>
+        <v>0.3583095554429965</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>0.3554859562725387</v>
+        <v>0.3554859392185158</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="AM3" s="2" t="n"/>
       <c r="AN3" s="3" t="n">
-        <v>0.1948104045964485</v>
+        <v>0.1948102829331331</v>
       </c>
       <c r="AO3" s="2" t="n">
         <v>2</v>
@@ -1152,14 +1152,14 @@
         <v>0</v>
       </c>
       <c r="AR3" s="3" t="n">
-        <v>0.03152603436066848</v>
+        <v>0.03152579603039518</v>
       </c>
       <c r="AS3" s="3" t="n">
         <v>0.1013820490623591</v>
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -3.2%, 3m +1.8%, 6m +11.6%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -3.0%, 3m +4.9%, 6m +10.9%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>722.5323</v>
+        <v>724.28</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>717.63</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>0.00683123615233483</v>
+        <v>0.009266613714588257</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T14:00:07Z</t>
+          <t>2026-10-21T20:15:08Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.0004159825846918874</v>
+        <v>-0.00178442367885101</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.0816264119270449</v>
+        <v>-0.08288367508433203</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>-0.06937297244713325</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.05196214804925703</v>
+        <v>-0.05326010712133689</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.02237622162998432</v>
+        <v>-0.02371459892457928</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.01316686397141575</v>
+        <v>-0.01451784897406849</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.002745538499937528</v>
+        <v>0.001372769249968764</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.03802929719322601</v>
+        <v>-0.03802938342376228</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-21T14:00:08Z</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1350,14 +1350,14 @@
         <v>0</v>
       </c>
       <c r="AR4" s="4" t="n">
-        <v>-0.00317484822744607</v>
+        <v>-0.003174763852108353</v>
       </c>
       <c r="AS4" s="4" t="n">
         <v>0.1013820490623591</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.6%, 3m -2.8%, 6m -5.3%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.5%, 3m -2.4%, 6m -5.3%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>80.34999999999999</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="AW4" t="n">
         <v>80.13</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>0.002745538499937528</v>
+        <v>0.001372769249968764</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-21T14:00:08Z</t>
+          <t>2026-10-21T20:15:00Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.1988218891599862</v>
+        <v>0.2007668177065181</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.06154979536152783</v>
+        <v>-0.06002728512960431</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>-0.007639836289222379</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1307811423057482</v>
+        <v>-0.1293709506961357</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.01834679155900099</v>
+        <v>0.01999892334194664</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.05432499312620287</v>
+        <v>-0.05279076161671714</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.001817026347146866</v>
+        <v>0.00344234079173833</v>
       </c>
       <c r="M5" t="b">
         <v>0</v>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-21T14:00:08Z</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -5.2%, 3m -0.4%, 6m -12.1%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -5.3%, 3m +2.0%, 6m -12.9%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>378.3362</v>
+        <v>378.9</v>
       </c>
       <c r="AW5" t="n">
         <v>377.64999</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>0.001817052874806269</v>
+        <v>0.003309969636170251</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-21T14:00:08Z</t>
+          <t>2026-10-21T20:11:04Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.08669662640769404</v>
+        <v>0.08719081535046924</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.00898700941221442</v>
+        <v>0.009446068688387266</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0270376424527583</v>
+        <v>0.02703774520271884</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01534256787979404</v>
+        <v>-0.01489477257563154</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01441154388049948</v>
+        <v>-0.0139632289027336</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01757543472061607</v>
+        <v>-0.01712855890302178</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.001496811141481036</v>
+        <v>0.001952362358453863</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715206361910939</v>
+        <v>0.03715195976610053</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1659,17 +1659,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-21T14:00:10Z</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1744,14 +1744,14 @@
         <v>1</v>
       </c>
       <c r="AR6" s="4" t="n">
-        <v>-0.0006039649327913565</v>
+        <v>-0.000604171475144577</v>
       </c>
       <c r="AS6" s="4" t="n">
         <v>0.1013820490623591</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.9%, 3m -1.9%, 6m -1.5%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.7%, 3m -1.4%, 6m -1.5%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>76.94499999999999</v>
+        <v>76.98</v>
       </c>
       <c r="AW6" t="n">
         <v>76.83</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>0.001496811141481036</v>
+        <v>0.001952362358453863</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-21T14:00:10Z</t>
+          <t>2026-10-21T20:10:00Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7895133530488292</v>
+        <v>0.7961000149411712</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.607745332761384</v>
+        <v>0.6136629775693438</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4624043972025662</v>
+        <v>0.4624042651347229</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2171286186224006</v>
+        <v>0.2216086267887081</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.150618386883959</v>
+        <v>0.1548535841266119</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.09938491421171891</v>
+        <v>0.1034315312398835</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.0007356186552890387</v>
+        <v>0.002942474621156377</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1847,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392497886577</v>
+        <v>0.2952392382918702</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1856,24 +1856,24 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T14:00:09Z</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2928248967435412</v>
+        <v>0.2920214987197616</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>1</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.2952392497886577</v>
+        <v>0.2952392382918702</v>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.3000750052567641</v>
+        <v>0.3000750077595838</v>
       </c>
       <c r="AH7" s="2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AM7" s="2" t="n"/>
       <c r="AN7" s="3" t="n">
-        <v>0.5274925994927393</v>
+        <v>0.5274924606359737</v>
       </c>
       <c r="AO7" s="2" t="n">
         <v>1</v>
@@ -1942,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="AR7" s="3" t="n">
-        <v>0.0353217910086423</v>
+        <v>0.03532178375747086</v>
       </c>
       <c r="AS7" s="3" t="n">
         <v>0.1013820490623591</v>
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +8.8%, 3m +15.5%, 6m +23.3%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +10.3%, 3m +15.5%, 6m +22.2%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>67.92</v>
+        <v>68.1187</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>67.97</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>-0.0007356186552890387</v>
+        <v>0.002187729880829936</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T14:00:09Z</t>
+          <t>2026-10-21T20:14:12Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.03587236995737419</v>
+        <v>0.03494102898804585</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01348606136022412</v>
+        <v>-0.01437317219529233</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>-0.01427979210739039</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.01914169440908875</v>
+        <v>-0.02002371948392567</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.009952654761349544</v>
+        <v>-0.0108429429699507</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.0008052292535050132</v>
+        <v>-9.473285335359627e-05</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.00156427758816835</v>
+        <v>0.0006636329161926469</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.004296483646738736</v>
+        <v>0.004296411608788464</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
@@ -2055,17 +2055,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-21T14:00:09Z</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2140,14 +2140,14 @@
         <v>0</v>
       </c>
       <c r="AR8" s="4" t="n">
-        <v>-0.009282036975003183</v>
+        <v>-0.009281894147243896</v>
       </c>
       <c r="AS8" s="4" t="n">
         <v>0.1013820490623591</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -0.2%, 3m -1.4%, 6m -1.9%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -0.0%, 3m -1.1%, 6m -2.0%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>105.645</v>
+        <v>105.55</v>
       </c>
       <c r="AW8" t="n">
         <v>105.48</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>0.00156427758816835</v>
+        <v>0.0006636329161926469</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-21T14:00:09Z</t>
+          <t>2026-10-21T20:09:59Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1060460018771643</v>
+        <v>0.1060536509342247</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07503534890088082</v>
+        <v>0.0750427834982772</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.05868666922651911</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05239446870451236</v>
+        <v>0.05240174672489095</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01259803921568636</v>
+        <v>0.0126050420168069</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.015442415730337</v>
+        <v>0.0154494382022472</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.0006851211072664842</v>
+        <v>0.0006920415224913601</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2252,17 +2252,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-21T13:59:54Z</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +1.5%, 3m +1.6%, 6m +5.2%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +1.5%, 3m +1.3%, 6m +5.2%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>28.9198</v>
+        <v>28.92</v>
       </c>
       <c r="AW9" t="n">
         <v>28.9</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>0.0006851211072664842</v>
+        <v>0.0006920415224913601</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-21T13:59:54Z</t>
+          <t>2026-10-21T20:10:00Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05955407651857203</v>
+        <v>0.05965938951693395</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03745494751513179</v>
+        <v>0.03755814562572279</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03435331836104849</v>
+        <v>0.03435339973531915</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01824839535128508</v>
+        <v>0.01834952419319147</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009142323219453186</v>
+        <v>0.009242625607209787</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.002998616719283032</v>
+        <v>0.003098308461328525</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0</v>
+        <v>9.93936984394761e-05</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21T14:00:11Z</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.61</v>
+        <v>100.62</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.61</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>0</v>
+        <v>9.93936984394761e-05</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21T14:00:11Z</t>
+          <t>2026-10-21T20:15:08Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>QQQ 36.2%, SPY 34.5%, XLE 29.3%</t>
+          <t>QQQ 36.4%, SPY 34.4%, XLE 29.2%</t>
         </is>
       </c>
     </row>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>-0.003620471178463314</v>
+        <v>-0.000374977372055052</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.0464839018069132</v>
+        <v>0.04989259992201522</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.08896617767994863</v>
+        <v>0.09251325274804878</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.03334987825435487</v>
+        <v>-0.02978085783854656</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.0452702221284913</v>
+        <v>0.04912952000565518</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.1052801155309062</v>
+        <v>0.1093609791327161</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.01316686397141575</v>
+        <v>-0.01451784897406849</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.02237622162998432</v>
+        <v>-0.02371459892457928</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.05196214804925703</v>
+        <v>-0.05326010712133689</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.05432499312620287</v>
+        <v>-0.05279076161671714</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.01834679155900099</v>
+        <v>0.01999892334194664</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1307811423057482</v>
+        <v>-0.1293709506961357</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.01757543472061607</v>
+        <v>-0.01712855890302178</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01441154388049948</v>
+        <v>-0.0139632289027336</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01534256787979404</v>
+        <v>-0.01489477257563154</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.09938491421171891</v>
+        <v>0.1034315312398835</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.150618386883959</v>
+        <v>0.1548535841266119</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.2171286186224006</v>
+        <v>0.2216086267887081</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.0008052292535050132</v>
+        <v>-9.473285335359627e-05</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.009952654761349544</v>
+        <v>-0.0108429429699507</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.01914169440908875</v>
+        <v>-0.02002371948392567</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.015442415730337</v>
+        <v>0.0154494382022472</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.01259803921568636</v>
+        <v>0.0126050420168069</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05239446870451236</v>
+        <v>0.05240174672489095</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.002998616719283032</v>
+        <v>0.003098308461328525</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009142323219453186</v>
+        <v>0.009242625607209787</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01824839535128508</v>
+        <v>0.01834952419319147</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.02933614706677878</v>
+        <v>0.02933627027979946</v>
       </c>
     </row>
     <row r="3">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.0228523735523376</v>
+        <v>0.02285226703064946</v>
       </c>
     </row>
     <row r="4">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.529371859509042</v>
+        <v>0.478732607512953</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1640557834163989</v>
+        <v>0.154812942414025</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1644924417319775</v>
+        <v>0.1561227862709389</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.09251325274804878</v>
+        <v>0.08804473274724334</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.04989259992201522</v>
+        <v>0.04048365057261338</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-0.000374977372055052</v>
+        <v>-0.001132962581888664</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.00525323451010995</v>
+        <v>-0.007954959965851272</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,12 +872,12 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22T14:00:08Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>773.24</v>
+        <v>766.9401</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>769.04999</v>
+        <v>773.09003</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>0.00544829341978148</v>
+        <v>-0.007954998462468721</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T20:14:48Z</t>
+          <t>2026-10-22T14:00:08Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.6861103337017975</v>
+        <v>0.6177179229521428</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1914303693756236</v>
+        <v>0.1734189648447113</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.2280013015630222</v>
+        <v>0.2180517763917773</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.1093609791327161</v>
+        <v>0.09849191267532276</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.04912952000565518</v>
+        <v>0.04466923921934285</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.02978085783854656</v>
+        <v>-0.03664278679456578</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.01054861140141861</v>
+        <v>-0.01537506894649765</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22T14:00:09Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>724.28</v>
+        <v>714.05</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>717.63</v>
+        <v>725.20001</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>0.009266613714588257</v>
+        <v>-0.0153750825237855</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T20:15:08Z</t>
+          <t>2026-10-22T14:00:09Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.00178442367885101</v>
+        <v>0.003314412077746187</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.08288367508433203</v>
+        <v>-0.07758810906216296</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.06937297244713325</v>
+        <v>-0.0885382404377415</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.05326010712133689</v>
+        <v>-0.04101254721666547</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.02371459892457928</v>
+        <v>-0.01419921079842912</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-0.01451784897406849</v>
+        <v>0.01201381326281581</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.001372769249968764</v>
+        <v>0.01071784646061813</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22T14:00:09Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="AW4" t="n">
         <v>80.23999999999999</v>
       </c>
-      <c r="AW4" t="n">
-        <v>80.13</v>
-      </c>
       <c r="AX4" s="4" t="n">
-        <v>0.001372769249968764</v>
+        <v>0.01071784646061813</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-21T20:15:00Z</t>
+          <t>2026-10-22T14:00:09Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1387,7 +1387,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1410,28 +1410,28 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.2007668177065181</v>
+        <v>0.1955578412780046</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.06002728512960431</v>
+        <v>-0.01402290319160227</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.007639836289222379</v>
+        <v>0.04145901813169339</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1293709506961357</v>
+        <v>-0.1370870452858204</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.01999892334194664</v>
+        <v>0.00013444474321056</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.05279076161671714</v>
+        <v>-0.05327326410099775</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.00344234079173833</v>
+        <v>-0.01847209394379201</v>
       </c>
       <c r="M5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22T14:00:10Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>378.9</v>
+        <v>371.95</v>
       </c>
       <c r="AW5" t="n">
-        <v>377.64999</v>
+        <v>378.95001</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>0.003309969636170251</v>
+        <v>-0.01847211984504249</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-21T20:11:04Z</t>
+          <t>2026-10-22T14:00:10Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1584,7 +1584,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.08719081535046924</v>
+        <v>0.08291796417089214</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.009446068688387266</v>
+        <v>0.01088037409869957</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.02703774520271884</v>
+        <v>0.02111144685141775</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01489477257563154</v>
+        <v>-0.01336546356386226</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.0139632289027336</v>
+        <v>-0.01402727389955749</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01712855890302178</v>
+        <v>-0.01001954564730956</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.001952362358453863</v>
+        <v>-6.495193556776968e-05</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22T14:00:08Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
+        <v>76.97499999999999</v>
+      </c>
+      <c r="AW6" t="n">
         <v>76.98</v>
       </c>
-      <c r="AW6" t="n">
-        <v>76.83</v>
-      </c>
       <c r="AX6" s="4" t="n">
-        <v>0.001952362358453863</v>
+        <v>-6.495193556776968e-05</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-21T20:10:00Z</t>
+          <t>2026-10-22T14:00:08Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7961000149411712</v>
+        <v>0.7304597044027681</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6136629775693438</v>
+        <v>0.5979302118136096</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4624042651347229</v>
+        <v>0.4797759066193739</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2216086267887081</v>
+        <v>0.1975944365963009</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1548535841266119</v>
+        <v>0.1363691448586488</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1034315312398835</v>
+        <v>0.07984607984607983</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.002942474621156377</v>
+        <v>-0.01188380281690149</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22T14:00:10Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +10.3%, 3m +15.5%, 6m +22.2%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +10.3%, 3m +15.5%, 6m +22.1%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>68.1187</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>67.97</v>
+        <v>68.16</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.002187729880829936</v>
+        <v>-0.01188380281690149</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T20:14:12Z</t>
+          <t>2026-10-22T14:00:10Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.03494102898804585</v>
+        <v>0.03509516121468437</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01437317219529233</v>
+        <v>-0.01271106700324809</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.01427979210739039</v>
+        <v>-0.02338017962918626</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02002371948392567</v>
+        <v>-0.01785054634786332</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.0108429429699507</v>
+        <v>-0.007139910452140352</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-9.473285335359627e-05</v>
+        <v>0.01092453010208949</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0006636329161926469</v>
+        <v>0.003837044054950223</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22T14:00:10Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
+        <v>105.955</v>
+      </c>
+      <c r="AW8" t="n">
         <v>105.55</v>
       </c>
-      <c r="AW8" t="n">
-        <v>105.48</v>
-      </c>
       <c r="AX8" s="4" t="n">
-        <v>0.0006636329161926469</v>
+        <v>0.003837044054950223</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-21T20:09:59Z</t>
+          <t>2026-10-22T14:00:10Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1060536509342247</v>
+        <v>0.1012830348925162</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.0750427834982772</v>
+        <v>0.07210470152818282</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.05868666922651911</v>
+        <v>0.06081159381047962</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05240174672489095</v>
+        <v>0.05176171449328004</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.0126050420168069</v>
+        <v>0.01312106368089583</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.0154494382022472</v>
+        <v>0.0106457242582898</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.0006920415224913601</v>
+        <v>0.001210235131396731</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22T13:54:12Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
+        <v>28.955</v>
+      </c>
+      <c r="AW9" t="n">
         <v>28.92</v>
       </c>
-      <c r="AW9" t="n">
-        <v>28.9</v>
-      </c>
       <c r="AX9" s="4" t="n">
-        <v>0.0006920415224913601</v>
+        <v>0.001210235131396731</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-21T20:10:00Z</t>
+          <t>2026-10-22T13:54:12Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05965938951693395</v>
+        <v>0.0596067544359733</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03755814562572279</v>
+        <v>0.03740334849194027</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03435339973531915</v>
+        <v>0.03425047338202991</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01834952419319147</v>
+        <v>0.01829895515185753</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009242625607209787</v>
+        <v>0.00899194366862921</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003098308461328525</v>
+        <v>0.003048463782279409</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>9.93936984394761e-05</v>
+        <v>4.969191015691266e-05</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22T14:00:11Z</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
+        <v>100.625</v>
+      </c>
+      <c r="AW10" s="5" t="n">
         <v>100.62</v>
       </c>
-      <c r="AW10" s="5" t="n">
-        <v>100.61</v>
-      </c>
       <c r="AX10" s="6" t="n">
-        <v>9.93936984394761e-05</v>
+        <v>4.969191015691266e-05</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21T20:15:08Z</t>
+          <t>2026-10-22T14:00:11Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>-0.000374977372055052</v>
+        <v>-0.001132962581888664</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.04989259992201522</v>
+        <v>0.04048365057261338</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.09251325274804878</v>
+        <v>0.08804473274724334</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.02978085783854656</v>
+        <v>-0.03664278679456578</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.04912952000565518</v>
+        <v>0.04466923921934285</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.1093609791327161</v>
+        <v>0.09849191267532276</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-0.01451784897406849</v>
+        <v>0.01201381326281581</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.02371459892457928</v>
+        <v>-0.01419921079842912</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.05326010712133689</v>
+        <v>-0.04101254721666547</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.05279076161671714</v>
+        <v>-0.05327326410099775</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.01999892334194664</v>
+        <v>0.00013444474321056</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1293709506961357</v>
+        <v>-0.1370870452858204</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.01712855890302178</v>
+        <v>-0.01001954564730956</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.0139632289027336</v>
+        <v>-0.01402727389955749</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01489477257563154</v>
+        <v>-0.01336546356386226</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1034315312398835</v>
+        <v>0.07984607984607983</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1548535841266119</v>
+        <v>0.1363691448586488</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.2216086267887081</v>
+        <v>0.1975944365963009</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-9.473285335359627e-05</v>
+        <v>0.01092453010208949</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.0108429429699507</v>
+        <v>-0.007139910452140352</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.02002371948392567</v>
+        <v>-0.01785054634786332</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.0154494382022472</v>
+        <v>0.0106457242582898</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.0126050420168069</v>
+        <v>0.01312106368089583</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05240174672489095</v>
+        <v>0.05176171449328004</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003098308461328525</v>
+        <v>0.003048463782279409</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009242625607209787</v>
+        <v>0.00899194366862921</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01834952419319147</v>
+        <v>0.01829895515185753</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.478732607512953</v>
+        <v>0.4729865212311557</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.154812942414025</v>
+        <v>0.1503256844786425</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0.1561227862709389</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.08804473274724334</v>
+        <v>0.08381691611846098</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.04048365057261338</v>
+        <v>0.03644064209376152</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-0.001132962581888664</v>
+        <v>-0.005014261340696158</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.007954959965851272</v>
+        <v>-0.01180975048183264</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.1609548690014375</v>
+        <v>0.1609549765152376</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>3</v>
@@ -858,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512062651334</v>
+        <v>0.3464512286219292</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -867,24 +867,24 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22T14:00:08Z</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.3439623359746363</v>
+        <v>0.3429858175160105</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>0.3464512062651334</v>
+        <v>0.3464512286219292</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>0.3444390530219004</v>
+        <v>0.3444390303983334</v>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
       </c>
       <c r="AM2" s="2" t="n"/>
       <c r="AN2" s="3" t="n">
-        <v>0.1559723322105802</v>
+        <v>0.1559722249956661</v>
       </c>
       <c r="AO2" s="2" t="n">
         <v>3</v>
@@ -953,14 +953,14 @@
         <v>0</v>
       </c>
       <c r="AR2" s="3" t="n">
-        <v>0.02078116713403078</v>
+        <v>0.02078105991911672</v>
       </c>
       <c r="AS2" s="3" t="n">
-        <v>0.1013820490623591</v>
+        <v>0.1013819418474451</v>
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -0.0%, 3m +5.0%, 6m +9.3%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -0.5%, 3m +3.6%, 6m +8.4%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>766.9401</v>
+        <v>763.97</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>773.09003</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.007954998462468721</v>
+        <v>-0.01179685372478534</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22T14:00:08Z</t>
+          <t>2026-10-22T20:15:07Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.6177179229521428</v>
+        <v>0.5960140381982282</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1734189648447113</v>
+        <v>0.1576759905842553</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.2180517763917773</v>
+        <v>0.2180518985633964</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.09849191267532276</v>
+        <v>0.0837540756563051</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.04466923921934285</v>
+        <v>0.03065351019235418</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.03664278679456578</v>
+        <v>-0.04956759892608031</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.01537506894649765</v>
+        <v>-0.02858521787093216</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1057,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095554429965</v>
+        <v>0.3583095431858343</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22T14:00:09Z</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.3640161653056022</v>
+        <v>0.3620243500926276</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0.3583095554429965</v>
+        <v>0.3583095431858343</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>0.3554859392185158</v>
+        <v>0.3554859448097056</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1155,11 +1155,11 @@
         <v>0.03152579603039518</v>
       </c>
       <c r="AS3" s="3" t="n">
-        <v>0.1013820490623591</v>
+        <v>0.1013819418474451</v>
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -3.0%, 3m +4.9%, 6m +10.9%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -5.0%, 3m +3.1%, 6m +8.4%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>714.05</v>
+        <v>704.64</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>725.20001</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.0153750825237855</v>
+        <v>-0.02835081317773291</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22T14:00:09Z</t>
+          <t>2026-10-22T20:15:08Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.003314412077746187</v>
+        <v>0.01123177338180614</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.07758810906216296</v>
+        <v>-0.07030898369161387</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.0885382404377415</v>
+        <v>-0.08853831952973601</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.04101254721666547</v>
+        <v>-0.0334446182206436</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.01419921079842912</v>
+        <v>-0.006419679628646868</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.01201381326281581</v>
+        <v>0.02000011215909447</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.01071784646061813</v>
+        <v>0.01869391824526412</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-22T14:00:09Z</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="AN4" s="4" t="n">
-        <v>-0.05989215331210995</v>
+        <v>-0.05989223609562822</v>
       </c>
       <c r="AO4" t="n">
         <v>8</v>
@@ -1350,14 +1350,14 @@
         <v>0</v>
       </c>
       <c r="AR4" s="4" t="n">
-        <v>-0.003174763852108353</v>
+        <v>-0.003174931010964333</v>
       </c>
       <c r="AS4" s="4" t="n">
-        <v>0.1013820490623591</v>
+        <v>0.1013819418474451</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.5%, 3m -2.4%, 6m -5.3%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +2.0%, 3m -0.6%, 6m -3.3%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>81.09999999999999</v>
+        <v>81.64</v>
       </c>
       <c r="AW4" t="n">
         <v>80.23999999999999</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>0.01071784646061813</v>
+        <v>0.01744765702891327</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-22T14:00:09Z</t>
+          <t>2026-10-22T20:15:07Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.1955578412780046</v>
+        <v>0.1860756645559447</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.01402290319160227</v>
+        <v>-0.02184285865761848</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.04145901813169339</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1370870452858204</v>
+        <v>-0.1439309576837416</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.00013444474321056</v>
+        <v>-0.007797795106211258</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.05327326410099775</v>
+        <v>-0.06078191814294442</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.01847209394379201</v>
+        <v>-0.02625676210581873</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-22T14:00:10Z</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1550,11 +1550,11 @@
         <v>-0.03630758617886576</v>
       </c>
       <c r="AS5" s="4" t="n">
-        <v>0.1013820490623591</v>
+        <v>0.1013819418474451</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -5.3%, 3m +2.0%, 6m -12.9%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -6.1%, 3m -0.8%, 6m -14.4%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>371.95</v>
+        <v>368.61</v>
       </c>
       <c r="AW5" t="n">
         <v>378.95001</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.01847211984504249</v>
+        <v>-0.02728594729420908</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-22T14:00:10Z</t>
+          <t>2026-10-22T20:14:38Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.08291796417089214</v>
+        <v>0.08467651883826921</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01088037409869957</v>
+        <v>0.01252184519689803</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.02111144685141775</v>
+        <v>0.02111134454256147</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01336546356386226</v>
+        <v>-0.01176326392690852</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01402727389955749</v>
+        <v>-0.01242614897896566</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01001954564730956</v>
+        <v>-0.008411912561319568</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-6.495193556776968e-05</v>
+        <v>0.001558846453624252</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715195976610053</v>
+        <v>0.03715206361910939</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1659,17 +1659,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-22T14:00:08Z</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1747,11 +1747,11 @@
         <v>-0.000604171475144577</v>
       </c>
       <c r="AS6" s="4" t="n">
-        <v>0.1013820490623591</v>
+        <v>0.1013819418474451</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.7%, 3m -1.4%, 6m -1.5%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -0.8%, 3m -1.2%, 6m -1.2%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>76.97499999999999</v>
+        <v>77.10209999999999</v>
       </c>
       <c r="AW6" t="n">
         <v>76.98</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>-6.495193556776968e-05</v>
+        <v>0.001586126266562626</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-22T14:00:08Z</t>
+          <t>2026-10-22T20:10:47Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7304597044027681</v>
+        <v>0.7361124526843925</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.5979302118136096</v>
+        <v>0.6031498799145596</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.4797759066193739</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.1975944365963009</v>
+        <v>0.2015064006059697</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1363691448586488</v>
+        <v>0.140081115339256</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.07984607984607983</v>
+        <v>0.08337341670674991</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.01188380281690149</v>
+        <v>-0.008656103286384997</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1847,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392382918702</v>
+        <v>0.2952392281922366</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1856,24 +1856,24 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22T14:00:10Z</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2920214987197616</v>
+        <v>0.2949898323913618</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>1</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.2952392382918702</v>
+        <v>0.2952392281922366</v>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.3000750077595838</v>
+        <v>0.3000750247919609</v>
       </c>
       <c r="AH7" s="2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AM7" s="2" t="n"/>
       <c r="AN7" s="3" t="n">
-        <v>0.5274924606359737</v>
+        <v>0.5274925994927393</v>
       </c>
       <c r="AO7" s="2" t="n">
         <v>1</v>
@@ -1942,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="AR7" s="3" t="n">
-        <v>0.03532178375747086</v>
+        <v>0.0353219226142365</v>
       </c>
       <c r="AS7" s="3" t="n">
-        <v>0.1013820490623591</v>
+        <v>0.1013819418474451</v>
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +10.3%, 3m +15.5%, 6m +22.1%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +8.3%, 3m +14.0%, 6m +20.2%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>67.34999999999999</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>68.16</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>-0.01188380281690149</v>
+        <v>-0.008656103286384997</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22T14:00:10Z</t>
+          <t>2026-10-22T20:10:00Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.03509516121468437</v>
+        <v>0.03875845486759921</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01271106700324809</v>
+        <v>-0.009216745707731899</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.02338017962918626</v>
+        <v>-0.02338011020057729</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.01785054634786332</v>
+        <v>-0.01437448533026564</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.007139910452140352</v>
+        <v>-0.003625941941164501</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.01092453010208949</v>
+        <v>0.01450243297395293</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.003837044054950223</v>
+        <v>0.007389862624348709</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.004296411608788464</v>
+        <v>0.004296483646738736</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
@@ -2055,17 +2055,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-22T14:00:10Z</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2140,14 +2140,14 @@
         <v>0</v>
       </c>
       <c r="AR8" s="4" t="n">
-        <v>-0.009281894147243896</v>
+        <v>-0.009282036975003183</v>
       </c>
       <c r="AS8" s="4" t="n">
-        <v>0.1013820490623591</v>
+        <v>0.1013819418474451</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -0.0%, 3m -1.1%, 6m -2.0%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +1.5%, 3m -0.4%, 6m -1.4%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>105.955</v>
+        <v>106.33</v>
       </c>
       <c r="AW8" t="n">
         <v>105.55</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>0.003837044054950223</v>
+        <v>0.007389862624348709</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-22T14:00:10Z</t>
+          <t>2026-10-22T20:10:00Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1012830348925162</v>
+        <v>0.09919114862350953</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07210470152818282</v>
+        <v>0.07006823948072816</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.06081159381047962</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05176171449328004</v>
+        <v>0.04976389393389025</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01312106368089583</v>
+        <v>0.01119664100769779</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.0106457242582898</v>
+        <v>0.008726003490401313</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.001210235131396731</v>
+        <v>-0.0006915629322269412</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2252,17 +2252,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-22T13:54:12Z</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2340,11 +2340,11 @@
         <v>0.01338001355371299</v>
       </c>
       <c r="AS9" s="4" t="n">
-        <v>0.1013820490623591</v>
+        <v>0.1013819418474451</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +1.5%, 3m +1.3%, 6m +5.2%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +0.9%, 3m +1.1%, 6m +5.0%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>28.955</v>
+        <v>28.9</v>
       </c>
       <c r="AW9" t="n">
         <v>28.92</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>0.001210235131396731</v>
+        <v>-0.0006915629322269412</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-22T13:54:12Z</t>
+          <t>2026-10-22T20:10:00Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.0596067544359733</v>
+        <v>0.05955410316867216</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03740334849194027</v>
+        <v>0.03735180049946862</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0.03425047338202991</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01829895515185753</v>
+        <v>0.01824835644601164</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.00899194366862921</v>
+        <v>0.008941807422981229</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003048463782279409</v>
+        <v>0.002998622864824441</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>4.969191015691266e-05</v>
+        <v>0</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-22T14:00:11Z</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2520,7 +2520,7 @@
       <c r="AQ10" s="5" t="n"/>
       <c r="AR10" s="6" t="n"/>
       <c r="AS10" s="6" t="n">
-        <v>0.1013820490623591</v>
+        <v>0.1013819418474451</v>
       </c>
       <c r="AT10" s="5" t="inlineStr">
         <is>
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.625</v>
+        <v>100.6215</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.62</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>4.969191015691266e-05</v>
+        <v>1.490757304711821e-05</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-22T14:00:11Z</t>
+          <t>2026-10-22T20:15:11Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>QQQ 36.4%, SPY 34.4%, XLE 29.2%</t>
+          <t>QQQ 36.2%, SPY 34.3%, XLE 29.5%</t>
         </is>
       </c>
     </row>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>-0.001132962581888664</v>
+        <v>-0.005014261340696158</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.04048365057261338</v>
+        <v>0.03644064209376152</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.08804473274724334</v>
+        <v>0.08381691611846098</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.03664278679456578</v>
+        <v>-0.04956759892608031</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.04466923921934285</v>
+        <v>0.03065351019235418</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.09849191267532276</v>
+        <v>0.0837540756563051</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.01201381326281581</v>
+        <v>0.02000011215909447</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.01419921079842912</v>
+        <v>-0.006419679628646868</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.04101254721666547</v>
+        <v>-0.0334446182206436</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.05327326410099775</v>
+        <v>-0.06078191814294442</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.00013444474321056</v>
+        <v>-0.007797795106211258</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1370870452858204</v>
+        <v>-0.1439309576837416</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.01001954564730956</v>
+        <v>-0.008411912561319568</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01402727389955749</v>
+        <v>-0.01242614897896566</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01336546356386226</v>
+        <v>-0.01176326392690852</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.07984607984607983</v>
+        <v>0.08337341670674991</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1363691448586488</v>
+        <v>0.140081115339256</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.1975944365963009</v>
+        <v>0.2015064006059697</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.01092453010208949</v>
+        <v>0.01450243297395293</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.007139910452140352</v>
+        <v>-0.003625941941164501</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.01785054634786332</v>
+        <v>-0.01437448533026564</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.0106457242582898</v>
+        <v>0.008726003490401313</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.01312106368089583</v>
+        <v>0.01119664100769779</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05176171449328004</v>
+        <v>0.04976389393389025</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003048463782279409</v>
+        <v>0.002998622864824441</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.00899194366862921</v>
+        <v>0.008941807422981229</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01829895515185753</v>
+        <v>0.01824835644601164</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.02933627027979946</v>
+        <v>0.02933614706677878</v>
       </c>
     </row>
     <row r="3">
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1013820490623591</v>
+        <v>0.1013819418474451</v>
       </c>
     </row>
   </sheetData>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4729865212311557</v>
+        <v>0.4451921129447352</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1503256844786425</v>
+        <v>0.1520978314599208</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1561227862709389</v>
+        <v>0.1612112769334948</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.08381691611846098</v>
+        <v>0.07153955033950954</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.03644064209376152</v>
+        <v>0.03241702213598785</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-0.005014261340696158</v>
+        <v>-0.007848223363487006</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.01180975048183264</v>
+        <v>-0.003666422325776297</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,12 +872,12 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23T14:00:08Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>763.97</v>
+        <v>761.159</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>773.09003</v>
+        <v>763.96002</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.01179685372478534</v>
+        <v>-0.003666448409171963</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22T20:15:07Z</t>
+          <t>2026-10-23T14:00:08Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5960140381982282</v>
+        <v>0.5633467212914678</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1576759905842553</v>
+        <v>0.1709784593427488</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.2180518985633964</v>
+        <v>0.2297182035126981</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.0837540756563051</v>
+        <v>0.06527036575707079</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.03065351019235418</v>
+        <v>0.03564670721177077</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.04956759892608031</v>
+        <v>-0.04776683308595331</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.02858521787093216</v>
+        <v>0.001745993441878424</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23T14:00:08Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>704.64</v>
+        <v>705.7</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>725.20001</v>
+        <v>704.46997</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.02835081317773291</v>
+        <v>0.001746036101439641</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22T20:15:08Z</t>
+          <t>2026-10-23T14:00:08Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.01123177338180614</v>
+        <v>-0.001497550680284565</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.07030898369161387</v>
+        <v>-0.07369963188724638</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.08853831952973601</v>
+        <v>-0.1009058975858805</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.0334446182206436</v>
+        <v>-0.03811978178390418</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.006419679628646868</v>
+        <v>-0.01531187530611</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.02000011215909447</v>
+        <v>0.03025964203923004</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.01869391824526412</v>
+        <v>-0.002997308539270715</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23T14:00:08Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>81.64</v>
+        <v>81.495</v>
       </c>
       <c r="AW4" t="n">
-        <v>80.23999999999999</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>0.01744765702891327</v>
+        <v>-0.002997308539270715</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-22T20:15:07Z</t>
+          <t>2026-10-23T14:00:08Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.1860756645559447</v>
+        <v>0.2139305121027499</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.02184285865761848</v>
+        <v>-0.02298027989821871</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.04145901813169339</v>
+        <v>0.03819444444444442</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1439309576837416</v>
+        <v>-0.1491979226774379</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>-0.007797795106211258</v>
+        <v>-0.01606918826575554</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.06078191814294442</v>
+        <v>-0.05892414919962208</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.02625676210581873</v>
+        <v>-0.001056910569105618</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23T14:00:07Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1566,14 +1566,14 @@
         <v>368.61</v>
       </c>
       <c r="AW5" t="n">
-        <v>378.95001</v>
+        <v>369</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.02728594729420908</v>
+        <v>-0.001056910569105618</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-22T20:14:38Z</t>
+          <t>2026-10-23T14:00:07Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.08467651883826921</v>
+        <v>0.07645371556410518</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01252184519689803</v>
+        <v>0.01089681668316955</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.02111134454256147</v>
+        <v>0.01937561378969899</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01176326392690852</v>
+        <v>-0.01567390303012262</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01242614897896566</v>
+        <v>-0.01548496541404143</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.008411912561319568</v>
+        <v>-0.008317637769465702</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.001558846453624252</v>
+        <v>-0.002594033722438271</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23T14:00:10Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.10209999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>76.98</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>0.001586126266562626</v>
+        <v>-0.002594033722438271</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-22T20:10:47Z</t>
+          <t>2026-10-23T14:00:10Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7361124526843925</v>
+        <v>0.7756044981712304</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6031498799145596</v>
+        <v>0.6158930116928252</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4797759066193739</v>
+        <v>0.4666252367940658</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2015064006059697</v>
+        <v>0.2287942145430006</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.140081115339256</v>
+        <v>0.1888479791095801</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.08337341670674991</v>
+        <v>0.101776357827476</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.008656103286384997</v>
+        <v>0.02073701346751511</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23T14:00:10Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
+        <v>68.9712</v>
+      </c>
+      <c r="AW7" s="2" t="n">
         <v>67.56999999999999</v>
       </c>
-      <c r="AW7" s="2" t="n">
-        <v>68.16</v>
-      </c>
       <c r="AX7" s="3" t="n">
-        <v>-0.008656103286384997</v>
+        <v>0.02073701346751511</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22T20:10:00Z</t>
+          <t>2026-10-23T14:00:10Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.03875845486759921</v>
+        <v>0.03566579787444013</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.009216745707731899</v>
+        <v>-0.0108527576889923</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.02338011020057729</v>
+        <v>-0.02969144252962053</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.01437448533026564</v>
+        <v>-0.01644854028295339</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.003625941941164501</v>
+        <v>-0.00265225129904112</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.01450243297395293</v>
+        <v>0.01941514860977955</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.007389862624348709</v>
+        <v>-4.702341766193996e-05</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23T14:00:10Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
+        <v>106.325</v>
+      </c>
+      <c r="AW8" t="n">
         <v>106.33</v>
       </c>
-      <c r="AW8" t="n">
-        <v>105.55</v>
-      </c>
       <c r="AX8" s="4" t="n">
-        <v>0.007389862624348709</v>
+        <v>-4.702341766193996e-05</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-22T20:10:00Z</t>
+          <t>2026-10-23T14:00:10Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.09919114862350953</v>
+        <v>0.09030723785690498</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07006823948072816</v>
+        <v>0.07233087601338317</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.06081159381047962</v>
+        <v>0.06343494064375976</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.04976389393389025</v>
+        <v>0.05276564774381365</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01119664100769779</v>
+        <v>0.0115384615384615</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.008726003490401313</v>
+        <v>0.008365284071104817</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.0006915629322269412</v>
+        <v>0.001038062283737151</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23T13:59:50Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
+        <v>28.93</v>
+      </c>
+      <c r="AW9" t="n">
         <v>28.9</v>
       </c>
-      <c r="AW9" t="n">
-        <v>28.92</v>
-      </c>
       <c r="AX9" s="4" t="n">
-        <v>-0.0006915629322269412</v>
+        <v>0.001038062283737151</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-22T20:10:00Z</t>
+          <t>2026-10-23T13:59:50Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05955410316867216</v>
+        <v>0.05960682341651768</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03735180049946862</v>
+        <v>0.03760941651675931</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03425047338202991</v>
+        <v>0.03414759782888854</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01824835644601164</v>
+        <v>0.01829890339281959</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.008941807422981229</v>
+        <v>0.009192415964769829</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.002998622864824441</v>
+        <v>0.003347509287009443</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0</v>
+        <v>0.0003478433710990547</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23T14:00:11Z</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.6215</v>
+        <v>100.655</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.62</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>1.490757304711821e-05</v>
+        <v>0.0003478433710990547</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-22T20:15:11Z</t>
+          <t>2026-10-23T14:00:11Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>-0.005014261340696158</v>
+        <v>-0.007848223363487006</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.03644064209376152</v>
+        <v>0.03241702213598785</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.08381691611846098</v>
+        <v>0.07153955033950954</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.04956759892608031</v>
+        <v>-0.04776683308595331</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.03065351019235418</v>
+        <v>0.03564670721177077</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.0837540756563051</v>
+        <v>0.06527036575707079</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.02000011215909447</v>
+        <v>0.03025964203923004</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.006419679628646868</v>
+        <v>-0.01531187530611</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.0334446182206436</v>
+        <v>-0.03811978178390418</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.06078191814294442</v>
+        <v>-0.05892414919962208</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-0.007797795106211258</v>
+        <v>-0.01606918826575554</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1439309576837416</v>
+        <v>-0.1491979226774379</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.008411912561319568</v>
+        <v>-0.008317637769465702</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01242614897896566</v>
+        <v>-0.01548496541404143</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01176326392690852</v>
+        <v>-0.01567390303012262</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.08337341670674991</v>
+        <v>0.101776357827476</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.140081115339256</v>
+        <v>0.1888479791095801</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.2015064006059697</v>
+        <v>0.2287942145430006</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.01450243297395293</v>
+        <v>0.01941514860977955</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.003625941941164501</v>
+        <v>-0.00265225129904112</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.01437448533026564</v>
+        <v>-0.01644854028295339</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.008726003490401313</v>
+        <v>0.008365284071104817</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.01119664100769779</v>
+        <v>0.0115384615384615</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.04976389393389025</v>
+        <v>0.05276564774381365</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.002998622864824441</v>
+        <v>0.003347509287009443</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.008941807422981229</v>
+        <v>0.009192415964769829</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01824835644601164</v>
+        <v>0.01829890339281959</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Survivor'!$A$1:$BA$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Weekly Review'!$A$17:$H$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Weekly History'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Weekly History'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4451921129447352</v>
+        <v>0.4429344234212957</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1520978314599208</v>
+        <v>0.1502980429678882</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1612112769334948</v>
+        <v>0.1612111696568344</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.07153955033950954</v>
+        <v>0.06986570752170995</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.03241702213598785</v>
+        <v>0.03080429228674508</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-0.007848223363487006</v>
+        <v>-0.009398055215203649</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.003666422325776297</v>
+        <v>-0.005222786533326418</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -858,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512286219292</v>
+        <v>0.3464512421129409</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -867,24 +867,24 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:00:08Z</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.3429858175160105</v>
+        <v>0.3430182189724962</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -895,16 +895,16 @@
         <v>1</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>0.3464512286219292</v>
+        <v>0.3464512421129409</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
           <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AE2" s="2" t="b">
@@ -914,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>0.3444390303983334</v>
+        <v>0.3430182189724962</v>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
       </c>
       <c r="AM2" s="2" t="n"/>
       <c r="AN2" s="3" t="n">
-        <v>0.1559722249956661</v>
+        <v>0.1612111696568344</v>
       </c>
       <c r="AO2" s="2" t="n">
         <v>3</v>
@@ -953,14 +953,14 @@
         <v>0</v>
       </c>
       <c r="AR2" s="3" t="n">
-        <v>0.02078105991911672</v>
+        <v>0.005238837446254196</v>
       </c>
       <c r="AS2" s="3" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.09777622901307459</v>
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -0.5%, 3m +3.6%, 6m +8.4%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -0.9%, 3m +3.1%, 6m +7.0%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>761.159</v>
+        <v>760.5</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>763.96002</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.003666448409171963</v>
+        <v>-0.004529058994474533</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:00:08Z</t>
+          <t>2026-10-23T20:15:07Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5633467212914678</v>
+        <v>0.5604668137703128</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1709784593427488</v>
+        <v>0.1688213500935696</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0.2297182035126981</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.06527036575707079</v>
+        <v>0.06330798588533448</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.03564670721177077</v>
+        <v>0.03373889834203103</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.04776683308595331</v>
+        <v>-0.04952098232357316</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.001745993441878424</v>
+        <v>-9.936548043221194e-05</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.1982246540542743</v>
+        <v>0.1982245316673374</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>2</v>
@@ -1057,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095431858343</v>
+        <v>0.3583095181980359</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:00:08Z</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.3620243500926276</v>
+        <v>0.3644891959458457</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1094,16 +1094,16 @@
         <v>1</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0.3583095431858343</v>
+        <v>0.3583095181980359</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
           <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AE3" s="2" t="b">
@@ -1113,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>0.3554859448097056</v>
+        <v>0.3644891959458457</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="AM3" s="2" t="n"/>
       <c r="AN3" s="3" t="n">
-        <v>0.1948102829331331</v>
+        <v>0.2297182035126981</v>
       </c>
       <c r="AO3" s="2" t="n">
         <v>2</v>
@@ -1152,14 +1152,14 @@
         <v>0</v>
       </c>
       <c r="AR3" s="3" t="n">
-        <v>0.03152579603039518</v>
+        <v>0.0349080422428556</v>
       </c>
       <c r="AS3" s="3" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.09777622901307459</v>
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -5.0%, 3m +3.1%, 6m +8.4%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -5.0%, 3m +3.4%, 6m +6.3%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>705.7</v>
+        <v>705.3354</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>704.46997</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>0.001746036101439641</v>
+        <v>0.00122848387703467</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:00:08Z</t>
+          <t>2026-10-23T20:15:04Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.001497550680284565</v>
+        <v>-0.003396752738537678</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.07369963188724638</v>
+        <v>-0.07546157586772473</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1009058975858805</v>
+        <v>-0.1009060535217502</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.03811978178390418</v>
+        <v>-0.03994932321855171</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.01531187530611</v>
+        <v>-0.01718461934996662</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.03025964203923004</v>
+        <v>0.0283001323206451</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.002997308539270715</v>
+        <v>-0.004893564962074715</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.03802938342376228</v>
+        <v>-0.038029469654283</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-23T14:00:08Z</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1297,14 +1297,14 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="AN4" s="4" t="n">
-        <v>-0.05989223609562822</v>
+        <v>-0.1009060535217502</v>
       </c>
       <c r="AO4" t="n">
         <v>8</v>
@@ -1350,14 +1350,14 @@
         <v>0</v>
       </c>
       <c r="AR4" s="4" t="n">
-        <v>-0.003174931010964333</v>
+        <v>-0.04101373464261826</v>
       </c>
       <c r="AS4" s="4" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.09777622901307459</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +2.0%, 3m -0.6%, 6m -3.3%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +2.8%, 3m -1.7%, 6m -4.0%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>81.495</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="AW4" t="n">
         <v>81.73999999999999</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>-0.002997308539270715</v>
+        <v>-0.005138243210178639</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-23T14:00:08Z</t>
+          <t>2026-10-23T20:15:03Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.2139305121027499</v>
+        <v>0.2073439815577147</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.02298027989821871</v>
+        <v>-0.02828138252756562</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.03819444444444442</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1491979226774379</v>
+        <v>-0.1538141950375072</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>-0.01606918826575554</v>
+        <v>-0.02140778901849816</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.05892414919962208</v>
+        <v>-0.06403022798641778</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.001056910569105618</v>
+        <v>-0.006476964769647653</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-23T14:00:07Z</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1494,14 +1494,14 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
@@ -1535,26 +1535,26 @@
         </is>
       </c>
       <c r="AN5" s="4" t="n">
-        <v>0.02831771599679911</v>
+        <v>0.03819444444444442</v>
       </c>
       <c r="AO5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP5" t="n">
         <v>6</v>
       </c>
-      <c r="AP5" t="n">
-        <v>4</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AR5" s="4" t="n">
-        <v>-0.03630758617886576</v>
+        <v>0.009876728447645311</v>
       </c>
       <c r="AS5" s="4" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.09777622901307459</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -6.1%, 3m -0.8%, 6m -14.4%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -6.4%, 3m -2.1%, 6m -15.4%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>368.61</v>
+        <v>366.3242</v>
       </c>
       <c r="AW5" t="n">
         <v>369</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.001056910569105618</v>
+        <v>-0.007251490514905146</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-23T14:00:07Z</t>
+          <t>2026-10-23T20:13:50Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07645371556410518</v>
+        <v>0.07855331503758345</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01089681668316955</v>
+        <v>0.01286855544419319</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.01937561378969899</v>
+        <v>0.01937551155348527</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01567390303012262</v>
+        <v>-0.01375379482376504</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01548496541404143</v>
+        <v>-0.01356458498246949</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.008317637769465702</v>
+        <v>-0.006383276854841857</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.002594033722438271</v>
+        <v>-0.0006485084306095956</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715206361910939</v>
+        <v>0.03715195976610053</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1659,17 +1659,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-23T14:00:10Z</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1691,14 +1691,14 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
@@ -1732,26 +1732,26 @@
         </is>
       </c>
       <c r="AN6" s="4" t="n">
-        <v>0.02870801072958273</v>
+        <v>0.01937551155348527</v>
       </c>
       <c r="AO6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP6" t="n">
         <v>5</v>
       </c>
-      <c r="AP6" t="n">
-        <v>6</v>
-      </c>
       <c r="AQ6" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AR6" s="4" t="n">
-        <v>-0.000604171475144577</v>
+        <v>-0.009332602195070594</v>
       </c>
       <c r="AS6" s="4" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.09777622901307459</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -0.8%, 3m -1.2%, 6m -1.2%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -0.6%, 3m -1.4%, 6m -1.4%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>76.90000000000001</v>
+        <v>76.9812</v>
       </c>
       <c r="AW6" t="n">
         <v>77.09999999999999</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.002594033722438271</v>
+        <v>-0.001540856031128301</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-23T14:00:10Z</t>
+          <t>2026-10-23T20:12:31Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7756044981712304</v>
+        <v>0.784841146440072</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6158930116928252</v>
+        <v>0.6242991640085076</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.4666252367940658</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2287942145430006</v>
+        <v>0.2351866125899831</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1888479791095801</v>
+        <v>0.1950325699954067</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.101776357827476</v>
+        <v>0.1075079872204472</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.02073701346751511</v>
+        <v>0.02604706230575715</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1847,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392281922366</v>
+        <v>0.2952392396890233</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1856,24 +1856,24 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:00:10Z</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2949898323913618</v>
+        <v>0.2924925850816581</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -1884,16 +1884,16 @@
         <v>1</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.2952392281922366</v>
+        <v>0.2952392396890233</v>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
           <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AD7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AE7" s="2" t="b">
@@ -1903,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.3000750247919609</v>
+        <v>0.2924925850816581</v>
       </c>
       <c r="AH7" s="2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AM7" s="2" t="n"/>
       <c r="AN7" s="3" t="n">
-        <v>0.5274925994927393</v>
+        <v>0.4666252367940658</v>
       </c>
       <c r="AO7" s="2" t="n">
         <v>1</v>
@@ -1942,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="AR7" s="3" t="n">
-        <v>0.0353219226142365</v>
+        <v>-0.0608672238419079</v>
       </c>
       <c r="AS7" s="3" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.09777622901307459</v>
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +8.3%, 3m +14.0%, 6m +20.2%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +10.8%, 3m +19.5%, 6m +23.5%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>68.9712</v>
+        <v>69.31</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>67.56999999999999</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.02073701346751511</v>
+        <v>0.02575107296137347</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:00:10Z</t>
+          <t>2026-10-23T20:14:11Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.03566579787444013</v>
+        <v>0.03483754205590017</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.0108527576889923</v>
+        <v>-0.01164351729958657</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>-0.02969144252962053</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.01644854028295339</v>
+        <v>-0.01723468770761294</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.00265225129904112</v>
+        <v>-0.003449566687139693</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.01941514860977955</v>
+        <v>0.01860019175455419</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-4.702341766193996e-05</v>
+        <v>-0.0008464215179159185</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.004296483646738736</v>
+        <v>0.004296411608788464</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
@@ -2055,17 +2055,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-23T14:00:10Z</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2087,14 +2087,14 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="AN8" s="4" t="n">
-        <v>-0.01164120736797036</v>
+        <v>-0.02969144252962053</v>
       </c>
       <c r="AO8" t="n">
         <v>7</v>
@@ -2140,14 +2140,14 @@
         <v>0</v>
       </c>
       <c r="AR8" s="4" t="n">
-        <v>-0.009282036975003183</v>
+        <v>-0.01805023516165016</v>
       </c>
       <c r="AS8" s="4" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.09777622901307459</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +1.5%, 3m -0.4%, 6m -1.4%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +1.9%, 3m -0.3%, 6m -1.7%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>106.325</v>
+        <v>106.24</v>
       </c>
       <c r="AW8" t="n">
         <v>106.33</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>-4.702341766193996e-05</v>
+        <v>-0.0008464215179159185</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-23T14:00:10Z</t>
+          <t>2026-10-23T20:10:00Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.09030723785690498</v>
+        <v>0.0914378710105761</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07233087601338317</v>
+        <v>0.07344286793458621</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.06343494064375976</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05276564774381365</v>
+        <v>0.05385735080058218</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.0115384615384615</v>
+        <v>0.01258741258741258</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.008365284071104817</v>
+        <v>0.00941094457999303</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.001038062283737151</v>
+        <v>0.00207612456747408</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2252,17 +2252,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-23T13:59:50Z</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2284,14 +2284,14 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
@@ -2325,26 +2325,26 @@
         </is>
       </c>
       <c r="AN9" s="4" t="n">
-        <v>0.05459028314822101</v>
+        <v>0.06343494064375976</v>
       </c>
       <c r="AO9" t="n">
         <v>4</v>
       </c>
       <c r="AP9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR9" s="4" t="n">
-        <v>0.01338001355371299</v>
+        <v>0.008844657495538755</v>
       </c>
       <c r="AS9" s="4" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.09777622901307459</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +0.9%, 3m +1.1%, 6m +5.0%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +0.9%, 3m +1.3%, 6m +5.4%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>28.93</v>
+        <v>28.96</v>
       </c>
       <c r="AW9" t="n">
         <v>28.9</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>0.001038062283737151</v>
+        <v>0.00207612456747408</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-23T13:59:50Z</t>
+          <t>2026-10-23T20:10:00Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05960682341651768</v>
+        <v>0.05965928878048277</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03760941651675931</v>
+        <v>0.0376609593818189</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0.03414759782888854</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01829890339281959</v>
+        <v>0.01834948701526229</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009192415964769829</v>
+        <v>0.009242624427048263</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003347509287009443</v>
+        <v>0.003397350204464411</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0003478433710990547</v>
+        <v>0.0003975352812561894</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23T14:00:11Z</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="AC10" s="5" t="inlineStr">
         <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AD10" s="5" t="inlineStr">
+        <is>
           <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AD10" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AE10" s="5" t="b">
@@ -2520,7 +2520,7 @@
       <c r="AQ10" s="5" t="n"/>
       <c r="AR10" s="6" t="n"/>
       <c r="AS10" s="6" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.09777622901307459</v>
       </c>
       <c r="AT10" s="5" t="inlineStr">
         <is>
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.655</v>
+        <v>100.66</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.62</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>0.0003478433710990547</v>
+        <v>0.0003975352812561894</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23T14:00:11Z</t>
+          <t>2026-10-23T20:15:09Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>2026-10-16: QQQ 35.5%, SPY 34.4%, XLE 30.0%</t>
+          <t>2026-10-23: QQQ 36.4%, SPY 34.3%, XLE 29.2%</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-09: QQQ 35.3%, SPY 34.4%, XLE 30.3%</t>
+          <t>2026-10-16: QQQ 35.5%, SPY 34.4%, XLE 30.0%</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>QQQ 36.2%, SPY 34.3%, XLE 29.5%</t>
+          <t>QQQ 36.4%, SPY 34.3%, XLE 29.2%</t>
         </is>
       </c>
     </row>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>-0.007848223363487006</v>
+        <v>-0.009398055215203649</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.03241702213598785</v>
+        <v>0.03080429228674508</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.07153955033950954</v>
+        <v>0.06986570752170995</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.04776683308595331</v>
+        <v>-0.04952098232357316</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.03564670721177077</v>
+        <v>0.03373889834203103</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.06527036575707079</v>
+        <v>0.06330798588533448</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.03025964203923004</v>
+        <v>0.0283001323206451</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.01531187530611</v>
+        <v>-0.01718461934996662</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.03811978178390418</v>
+        <v>-0.03994932321855171</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.05892414919962208</v>
+        <v>-0.06403022798641778</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-0.01606918826575554</v>
+        <v>-0.02140778901849816</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1491979226774379</v>
+        <v>-0.1538141950375072</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.008317637769465702</v>
+        <v>-0.006383276854841857</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01548496541404143</v>
+        <v>-0.01356458498246949</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01567390303012262</v>
+        <v>-0.01375379482376504</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.101776357827476</v>
+        <v>0.1075079872204472</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1888479791095801</v>
+        <v>0.1950325699954067</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.2287942145430006</v>
+        <v>0.2351866125899831</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.01941514860977955</v>
+        <v>0.01860019175455419</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.00265225129904112</v>
+        <v>-0.003449566687139693</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.01644854028295339</v>
+        <v>-0.01723468770761294</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.008365284071104817</v>
+        <v>0.00941094457999303</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.0115384615384615</v>
+        <v>0.01258741258741258</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05276564774381365</v>
+        <v>0.05385735080058218</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003347509287009443</v>
+        <v>0.003397350204464411</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009192415964769829</v>
+        <v>0.009242624427048263</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01829890339281959</v>
+        <v>0.01834948701526229</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3282,11 +3282,44 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.1013820490623591</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>XLE, QQQ, SPY</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>QQQ 36.4%, SPY 34.3%, XLE 29.2%</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0.09777622901307459</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>760.5</v>
+        <v>761.12</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>763.96002</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.004529058994474533</v>
+        <v>-0.00371749820101841</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T20:15:07Z</t>
+          <t>2026-10-23T21:34:26Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>705.3354</v>
+        <v>705.55</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>704.46997</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>0.00122848387703467</v>
+        <v>0.001533110062874599</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T20:15:04Z</t>
+          <t>2026-10-23T21:35:16Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>81.31999999999999</v>
+        <v>81.27</v>
       </c>
       <c r="AW4" t="n">
         <v>81.73999999999999</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>-0.005138243210178639</v>
+        <v>-0.005749938830437951</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-23T20:15:03Z</t>
+          <t>2026-10-23T21:35:09Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>366.3242</v>
+        <v>366.35</v>
       </c>
       <c r="AW5" t="n">
         <v>369</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.007251490514905146</v>
+        <v>-0.007181571815718102</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-23T20:13:50Z</t>
+          <t>2026-10-23T21:34:31Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>76.9812</v>
+        <v>77.05</v>
       </c>
       <c r="AW6" t="n">
         <v>77.09999999999999</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.001540856031128301</v>
+        <v>-0.0006485084306095956</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-23T20:12:31Z</t>
+          <t>2026-10-23T20:23:31Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>69.31</v>
+        <v>69.3501</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>67.56999999999999</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.02575107296137347</v>
+        <v>0.02634453159686267</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T20:14:11Z</t>
+          <t>2026-10-23T21:29:42Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-23T20:10:00Z</t>
+          <t>2026-10-23T21:27:42Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23T20:15:09Z</t>
+          <t>2026-10-23T21:33:15Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4429344234212957</v>
+        <v>0.4187669860268044</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1502980429678882</v>
+        <v>0.1480311926615299</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1612111696568344</v>
+        <v>0.1606404713939882</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.06986570752170995</v>
+        <v>0.07224158929056812</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.03080429228674508</v>
+        <v>0.03240099962459375</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-0.009398055215203649</v>
+        <v>-0.010864069488559</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.005222786533326418</v>
+        <v>0.003947524244378053</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,12 +872,12 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26T14:00:07Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>761.12</v>
+        <v>762.97</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>763.96002</v>
+        <v>759.96997</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.00371749820101841</v>
+        <v>0.003947563875451587</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T21:34:26Z</t>
+          <t>2026-10-26T14:00:07Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5604668137703128</v>
+        <v>0.5225878691689898</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1688213500935696</v>
+        <v>0.1627636594718558</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.2297182035126981</v>
+        <v>0.2250616218679902</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.06330798588533448</v>
+        <v>0.06612722591819042</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.03373889834203103</v>
+        <v>0.04720471928361825</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.04952098232357316</v>
+        <v>-0.0508529214237744</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-9.936548043221194e-05</v>
+        <v>0.003180011357183377</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26T14:00:08Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>705.55</v>
+        <v>706.64</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>704.46997</v>
+        <v>704.40002</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>0.001533110062874599</v>
+        <v>0.003179982873935616</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T21:35:16Z</t>
+          <t>2026-10-26T14:00:08Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.003396752738537678</v>
+        <v>-0.008816313132574805</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.07546157586772473</v>
+        <v>-0.06439859311739082</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1009060535217502</v>
+        <v>-0.09585055134711762</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.03994932321855171</v>
+        <v>-0.03030137666494359</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.01718461934996662</v>
+        <v>-0.0179762843336112</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.0283001323206451</v>
+        <v>0.0347862383553823</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.004893564962074715</v>
+        <v>0.005040570445045356</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26T14:00:09Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>81.27</v>
+        <v>81.75</v>
       </c>
       <c r="AW4" t="n">
-        <v>81.73999999999999</v>
+        <v>81.34</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>-0.005749938830437951</v>
+        <v>0.005040570445045356</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-23T21:35:09Z</t>
+          <t>2026-10-26T14:00:09Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.2073439815577147</v>
+        <v>0.1884312007011395</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.02828138252756562</v>
+        <v>-0.033448612687769</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.03819444444444442</v>
+        <v>0.03859658385913045</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1538141950375072</v>
+        <v>-0.1483402730931168</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>-0.02140778901849816</v>
+        <v>-0.008798765465522385</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.06403022798641778</v>
+        <v>-0.06936783508299238</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.006476964769647653</v>
+        <v>-0.001336570197212339</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26T14:00:09Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>366.35</v>
+        <v>366.12</v>
       </c>
       <c r="AW5" t="n">
-        <v>369</v>
+        <v>366.60999</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.007181571815718102</v>
+        <v>-0.00133654295672625</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-23T21:34:31Z</t>
+          <t>2026-10-26T14:00:09Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07855331503758345</v>
+        <v>0.07069423387940388</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01286855544419319</v>
+        <v>0.01225360717425894</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.01937551155348527</v>
+        <v>0.01671474821253449</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01375379482376504</v>
+        <v>-0.01252198477223865</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01356458498246949</v>
+        <v>-0.01383034762369439</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.006383276854841857</v>
+        <v>-0.004387800064982517</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.0006485084306095956</v>
+        <v>0.001622323166774908</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26T14:00:08Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
+        <v>77.175</v>
+      </c>
+      <c r="AW6" t="n">
         <v>77.05</v>
       </c>
-      <c r="AW6" t="n">
-        <v>77.09999999999999</v>
-      </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.0006485084306095956</v>
+        <v>0.001622323166774908</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-23T20:23:31Z</t>
+          <t>2026-10-26T14:00:08Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.784841146440072</v>
+        <v>0.7686393718297435</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6242991640085076</v>
+        <v>0.6136238761160056</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4666252367940658</v>
+        <v>0.4342295884561174</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2351866125899831</v>
+        <v>0.2457507195333128</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1950325699954067</v>
+        <v>0.2196437918330723</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1075079872204472</v>
+        <v>0.1250805931656995</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.02604706230575715</v>
+        <v>0.006779172075580542</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26T14:00:10Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>69.3501</v>
+        <v>69.8</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>67.56999999999999</v>
+        <v>69.33</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.02634453159686267</v>
+        <v>0.006779172075580542</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T21:29:42Z</t>
+          <t>2026-10-26T14:00:10Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.03483754205590017</v>
+        <v>0.03048401904855069</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01164351729958657</v>
+        <v>-0.008629729104638217</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.02969144252962053</v>
+        <v>-0.02554794678763461</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.01723468770761294</v>
+        <v>-0.01590688657971739</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.003449566687139693</v>
+        <v>-0.004872780170781188</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.01860019175455419</v>
+        <v>0.01736177539697725</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.0008464215179159185</v>
+        <v>0.001082454819277157</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26T14:00:06Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
+        <v>106.355</v>
+      </c>
+      <c r="AW8" t="n">
         <v>106.24</v>
       </c>
-      <c r="AW8" t="n">
-        <v>106.33</v>
-      </c>
       <c r="AX8" s="4" t="n">
-        <v>-0.0008464215179159185</v>
+        <v>0.001082454819277157</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-23T21:27:42Z</t>
+          <t>2026-10-26T14:00:06Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.0914378710105761</v>
+        <v>0.09863563211306792</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07344286793458621</v>
+        <v>0.07541112089679713</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.06343494064375976</v>
+        <v>0.06046018847025136</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05385735080058218</v>
+        <v>0.05732240437158476</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01258741258741258</v>
+        <v>0.01551784464660599</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.00941094457999303</v>
+        <v>0.0140985324947589</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.00207612456747408</v>
+        <v>0.002192679558010946</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26T13:59:39Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
+        <v>29.0235</v>
+      </c>
+      <c r="AW9" t="n">
         <v>28.96</v>
       </c>
-      <c r="AW9" t="n">
-        <v>28.9</v>
-      </c>
       <c r="AX9" s="4" t="n">
-        <v>0.00207612456747408</v>
+        <v>0.002192679558010946</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-23T20:10:00Z</t>
+          <t>2026-10-26T13:59:39Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05965928878048277</v>
+        <v>0.05977298161098976</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.0376609593818189</v>
+        <v>0.03766923957854051</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03414759782888854</v>
+        <v>0.03445594913144046</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01834948701526229</v>
+        <v>0.01845874763973843</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009242624427048263</v>
+        <v>0.009250644162933641</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003397350204464411</v>
+        <v>0.003106261266898835</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0003975352812561894</v>
+        <v>0.0001072918736340078</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26T14:00:11Z</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
+        <v>100.6708</v>
+      </c>
+      <c r="AW10" s="5" t="n">
         <v>100.66</v>
       </c>
-      <c r="AW10" s="5" t="n">
-        <v>100.62</v>
-      </c>
       <c r="AX10" s="6" t="n">
-        <v>0.0003975352812561894</v>
+        <v>0.0001072918736340078</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23T21:33:15Z</t>
+          <t>2026-10-26T14:00:11Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>-0.009398055215203649</v>
+        <v>-0.010864069488559</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.03080429228674508</v>
+        <v>0.03240099962459375</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.06986570752170995</v>
+        <v>0.07224158929056812</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.04952098232357316</v>
+        <v>-0.0508529214237744</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.03373889834203103</v>
+        <v>0.04720471928361825</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.06330798588533448</v>
+        <v>0.06612722591819042</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.0283001323206451</v>
+        <v>0.0347862383553823</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.01718461934996662</v>
+        <v>-0.0179762843336112</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.03994932321855171</v>
+        <v>-0.03030137666494359</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.06403022798641778</v>
+        <v>-0.06936783508299238</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-0.02140778901849816</v>
+        <v>-0.008798765465522385</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1538141950375072</v>
+        <v>-0.1483402730931168</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.006383276854841857</v>
+        <v>-0.004387800064982517</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01356458498246949</v>
+        <v>-0.01383034762369439</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01375379482376504</v>
+        <v>-0.01252198477223865</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1075079872204472</v>
+        <v>0.1250805931656995</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1950325699954067</v>
+        <v>0.2196437918330723</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.2351866125899831</v>
+        <v>0.2457507195333128</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.01860019175455419</v>
+        <v>0.01736177539697725</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.003449566687139693</v>
+        <v>-0.004872780170781188</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.01723468770761294</v>
+        <v>-0.01590688657971739</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.00941094457999303</v>
+        <v>0.0140985324947589</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.01258741258741258</v>
+        <v>0.01551784464660599</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05385735080058218</v>
+        <v>0.05732240437158476</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003397350204464411</v>
+        <v>0.003106261266898835</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009242624427048263</v>
+        <v>0.009250644162933641</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01834948701526229</v>
+        <v>0.01845874763973843</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4187669860268044</v>
+        <v>0.4230439091926714</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1480311926615299</v>
+        <v>0.1514920789722281</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1606404713939882</v>
+        <v>0.1606405779858457</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.07224158929056812</v>
+        <v>0.07547389941464666</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.03240099962459375</v>
+        <v>0.03551320888463882</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-0.010864069488559</v>
+        <v>-0.007882284306734988</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.003947524244378053</v>
+        <v>0.006973959498401294</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.1609549765152376</v>
+        <v>0.1609548690014375</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>3</v>
@@ -858,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512421129409</v>
+        <v>0.3464512062651334</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -867,24 +867,24 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26T14:00:07Z</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.3430182189724962</v>
+        <v>0.3440562879571546</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>0.3464512421129409</v>
+        <v>0.3464512062651334</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>0.3430182189724962</v>
+        <v>0.3430182213596835</v>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
@@ -953,14 +953,14 @@
         <v>0</v>
       </c>
       <c r="AR2" s="3" t="n">
-        <v>0.005238837446254196</v>
+        <v>0.005238944661168254</v>
       </c>
       <c r="AS2" s="3" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -0.9%, 3m +3.1%, 6m +7.0%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -0.8%, 3m +3.6%, 6m +7.5%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>762.97</v>
+        <v>765.11</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>759.96997</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>0.003947563875451587</v>
+        <v>0.006763464614266246</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26T14:00:07Z</t>
+          <t>2026-10-26T20:15:03Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5225878691689898</v>
+        <v>0.5345679276889994</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1627636594718558</v>
+        <v>0.1719124237318355</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.2250616218679902</v>
+        <v>0.2250614988322823</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.06612722591819042</v>
+        <v>0.07451575101739971</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.04720471928361825</v>
+        <v>0.05544435791038294</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.0508529214237744</v>
+        <v>-0.04338482202820682</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.003180011357183377</v>
+        <v>0.01107325383304958</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.1982245316673374</v>
+        <v>0.1982246540542743</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>2</v>
@@ -1057,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095181980359</v>
+        <v>0.3583095554429965</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26T14:00:08Z</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.3644891959458457</v>
+        <v>0.3655939642989111</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0.3583095181980359</v>
+        <v>0.3583095554429965</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>0.3644891959458457</v>
+        <v>0.364489203625325</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1152,14 +1152,14 @@
         <v>0</v>
       </c>
       <c r="AR3" s="3" t="n">
-        <v>0.0349080422428556</v>
+        <v>0.03490779891624962</v>
       </c>
       <c r="AS3" s="3" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -5.0%, 3m +3.4%, 6m +6.3%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -4.3%, 3m +5.5%, 6m +7.5%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>706.64</v>
+        <v>712.4472</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>704.40002</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>0.003179982873935616</v>
+        <v>0.01142416208335706</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26T14:00:08Z</t>
+          <t>2026-10-26T20:15:06Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.008816313132574805</v>
+        <v>-0.009665124718181484</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.06439859311739082</v>
+        <v>-0.06519980132721492</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.09585055134711762</v>
+        <v>-0.09585063029370489</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.03030137666494359</v>
+        <v>-0.03113169964516926</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.0179762843336112</v>
+        <v>-0.01881716090971697</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.0347862383553823</v>
+        <v>0.03390018286076635</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.005040570445045356</v>
+        <v>0.00417998524711094</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.038029469654283</v>
+        <v>-0.03802938342376228</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -1265,41 +1265,41 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>COMPLETED_SESSION</t>
+        </is>
+      </c>
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>2026-10-26T14:00:09Z</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>LIVE_PRICE_OVERLAY</t>
-        </is>
-      </c>
-      <c r="X4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="AA4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
       <c r="AD4" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="AN4" s="4" t="n">
-        <v>-0.1009060535217502</v>
+        <v>-0.1009058975858805</v>
       </c>
       <c r="AO4" t="n">
         <v>8</v>
@@ -1350,14 +1350,14 @@
         <v>0</v>
       </c>
       <c r="AR4" s="4" t="n">
-        <v>-0.04101373464261826</v>
+        <v>-0.04101366149025232</v>
       </c>
       <c r="AS4" s="4" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +2.8%, 3m -1.7%, 6m -4.0%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +3.4%, 3m -1.9%, 6m -3.1%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>81.75</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="AW4" t="n">
         <v>81.34</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>0.005040570445045356</v>
+        <v>0.00417998524711094</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-26T14:00:09Z</t>
+          <t>2026-10-26T20:15:00Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.1884312007011395</v>
+        <v>0.1939494270782613</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.033448612687769</v>
+        <v>-0.02896063782042824</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.03859658385913045</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1483402730931168</v>
+        <v>-0.1443857731047478</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>-0.008798765465522385</v>
+        <v>-0.004196334298941506</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.06936783508299238</v>
+        <v>-0.06504664345085287</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.001336570197212339</v>
+        <v>0.003300510078830365</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-26T14:00:09Z</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -6.4%, 3m -2.1%, 6m -15.4%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -6.5%, 3m -0.4%, 6m -14.4%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>366.12</v>
+        <v>367.72</v>
       </c>
       <c r="AW5" t="n">
         <v>366.60999</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.00133654295672625</v>
+        <v>0.003027768010358978</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-26T14:00:09Z</t>
+          <t>2026-10-26T20:12:23Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07069423387940388</v>
+        <v>0.07104107360531242</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01225360717425894</v>
+        <v>0.0125813130386867</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.01671474821253449</v>
+        <v>0.01671454472781697</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01252198477223865</v>
+        <v>-0.01220200560396312</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01383034762369439</v>
+        <v>-0.01351088871459927</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.004387800064982517</v>
+        <v>-0.004065282345534715</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.001622323166774908</v>
+        <v>0.001946787800129801</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715195976610053</v>
+        <v>0.03715185963322809</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1659,17 +1659,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-26T14:00:08Z</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1744,14 +1744,14 @@
         <v>-1</v>
       </c>
       <c r="AR6" s="4" t="n">
-        <v>-0.009332602195070594</v>
+        <v>-0.009332499176097464</v>
       </c>
       <c r="AS6" s="4" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -0.6%, 3m -1.4%, 6m -1.4%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -0.4%, 3m -1.4%, 6m -1.2%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.175</v>
+        <v>77.2</v>
       </c>
       <c r="AW6" t="n">
         <v>77.05</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>0.001622323166774908</v>
+        <v>0.001946787800129801</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-26T14:00:08Z</t>
+          <t>2026-10-26T20:10:00Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7686393718297435</v>
+        <v>0.7645853547216279</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6136238761160056</v>
+        <v>0.6099251668152594</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4342295884561174</v>
+        <v>0.4342297149514458</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2457507195333128</v>
+        <v>0.2428951304914027</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.2196437918330723</v>
+        <v>0.2168480467515066</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1250805931656995</v>
+        <v>0.122501611863314</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.006779172075580542</v>
+        <v>0.004471368815808452</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1847,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392396890233</v>
+        <v>0.2952392382918702</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1856,24 +1856,24 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26T14:00:10Z</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2924925850816581</v>
+        <v>0.2903497477439342</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>1</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.2952392396890233</v>
+        <v>0.2952392382918702</v>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2924925850816581</v>
+        <v>0.2924925750149914</v>
       </c>
       <c r="AH7" s="2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AM7" s="2" t="n"/>
       <c r="AN7" s="3" t="n">
-        <v>0.4666252367940658</v>
+        <v>0.4666251057178188</v>
       </c>
       <c r="AO7" s="2" t="n">
         <v>1</v>
@@ -1942,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="AR7" s="3" t="n">
-        <v>-0.0608672238419079</v>
+        <v>-0.06086749377492051</v>
       </c>
       <c r="AS7" s="3" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +10.8%, 3m +19.5%, 6m +23.5%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +12.3%, 3m +21.7%, 6m +24.3%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>69.8</v>
+        <v>69.7</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>69.33</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.006779172075580542</v>
+        <v>0.005336795038223041</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26T14:00:10Z</t>
+          <t>2026-10-26T20:14:21Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.03048401904855069</v>
+        <v>0.03004800963801824</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.008629729104638217</v>
+        <v>-0.009049259519761321</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.02554794678763461</v>
+        <v>-0.02554801608687662</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.01590688657971739</v>
+        <v>-0.01632319803309723</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.004872780170781188</v>
+        <v>-0.005293829720800725</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.01736177539697725</v>
+        <v>0.01693131815572979</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.001082454819277157</v>
+        <v>0.0006588855421687523</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2055,17 +2055,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-26T14:00:06Z</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +1.9%, 3m -0.3%, 6m -1.7%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +1.7%, 3m -0.5%, 6m -1.6%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>106.355</v>
+        <v>106.31</v>
       </c>
       <c r="AW8" t="n">
         <v>106.24</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>0.001082454819277157</v>
+        <v>0.0006588855421687523</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-26T14:00:06Z</t>
+          <t>2026-10-26T20:10:00Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.09863563211306792</v>
+        <v>0.09812461238651804</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07541112089679713</v>
+        <v>0.07491090382676413</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.06046018847025136</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05732240437158476</v>
+        <v>0.05683060109289628</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01551784464660599</v>
+        <v>0.01504548635409386</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.0140985324947589</v>
+        <v>0.01362683438155132</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.002192679558010946</v>
+        <v>0.001726519337016619</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2252,17 +2252,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-26T13:59:39Z</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +0.9%, 3m +1.3%, 6m +5.4%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +1.4%, 3m +1.5%, 6m +5.7%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>29.0235</v>
+        <v>29.01</v>
       </c>
       <c r="AW9" t="n">
         <v>28.96</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>0.002192679558010946</v>
+        <v>0.001726519337016619</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-26T13:59:39Z</t>
+          <t>2026-10-26T20:10:00Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05977298161098976</v>
+        <v>0.05976447480432223</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03766923957854051</v>
+        <v>0.03766099353905683</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0.03445594913144046</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01845874763973843</v>
+        <v>0.01845065426014747</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009250644162933641</v>
+        <v>0.009242623957319784</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003106261266898835</v>
+        <v>0.003098289888812999</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0001072918736340078</v>
+        <v>9.934432743885502e-05</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-26T14:00:11Z</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.6708</v>
+        <v>100.675</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.66</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>0.0001072918736340078</v>
+        <v>0.0001490164911583935</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-26T14:00:11Z</t>
+          <t>2026-10-26T20:14:44Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>QQQ 36.4%, SPY 34.3%, XLE 29.2%</t>
+          <t>QQQ 36.6%, SPY 34.4%, XLE 29.0%</t>
         </is>
       </c>
     </row>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>-0.010864069488559</v>
+        <v>-0.007882284306734988</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.03240099962459375</v>
+        <v>0.03551320888463882</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.07224158929056812</v>
+        <v>0.07547389941464666</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.0508529214237744</v>
+        <v>-0.04338482202820682</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.04720471928361825</v>
+        <v>0.05544435791038294</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.06612722591819042</v>
+        <v>0.07451575101739971</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.0347862383553823</v>
+        <v>0.03390018286076635</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.0179762843336112</v>
+        <v>-0.01881716090971697</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.03030137666494359</v>
+        <v>-0.03113169964516926</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.06936783508299238</v>
+        <v>-0.06504664345085287</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-0.008798765465522385</v>
+        <v>-0.004196334298941506</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1483402730931168</v>
+        <v>-0.1443857731047478</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.004387800064982517</v>
+        <v>-0.004065282345534715</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01383034762369439</v>
+        <v>-0.01351088871459927</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01252198477223865</v>
+        <v>-0.01220200560396312</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1250805931656995</v>
+        <v>0.122501611863314</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.2196437918330723</v>
+        <v>0.2168480467515066</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.2457507195333128</v>
+        <v>0.2428951304914027</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.01736177539697725</v>
+        <v>0.01693131815572979</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.004872780170781188</v>
+        <v>-0.005293829720800725</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.01590688657971739</v>
+        <v>-0.01632319803309723</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.0140985324947589</v>
+        <v>0.01362683438155132</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.01551784464660599</v>
+        <v>0.01504548635409386</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05732240437158476</v>
+        <v>0.05683060109289628</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003106261266898835</v>
+        <v>0.003098289888812999</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009250644162933641</v>
+        <v>0.009242623957319784</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01845874763973843</v>
+        <v>0.01845065426014747</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.02933614706677878</v>
+        <v>0.02933625610116319</v>
       </c>
     </row>
     <row r="3">
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1013820490623591</v>
+        <v>0.1013819418474451</v>
       </c>
     </row>
     <row r="6">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4230439091926714</v>
+        <v>0.4144788606720533</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1514920789722281</v>
+        <v>0.1434860332773134</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1606405779858457</v>
+        <v>0.1426651638527774</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.07547389941464666</v>
+        <v>0.08198963303561846</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.03551320888463882</v>
+        <v>0.05291928791635159</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-0.007882284306734988</v>
+        <v>0.0007183814213502782</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.006973959498401294</v>
+        <v>0.00103218051399967</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,12 +872,12 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27T14:00:08Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
@@ -960,7 +960,7 @@
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -0.8%, 3m +3.6%, 6m +7.5%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -0.8%, 3m +3.6%, 6m +7.6%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>765.11</v>
+        <v>766.16</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>759.96997</v>
+        <v>765.37</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>0.006763464614266246</v>
+        <v>0.00103218051399967</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26T20:15:03Z</t>
+          <t>2026-10-27T14:00:08Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5345679276889994</v>
+        <v>0.5242977830135354</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1719124237318355</v>
+        <v>0.1646101229314871</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.2250614988322823</v>
+        <v>0.199142053686082</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.07451575101739971</v>
+        <v>0.09018671830958636</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.05544435791038294</v>
+        <v>0.08211113968027117</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.04338482202820682</v>
+        <v>-0.02879719767015587</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.01107325383304958</v>
+        <v>0.004380791912384163</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27T14:00:08Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>712.4472</v>
+        <v>715.3200000000001</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>704.40002</v>
+        <v>712.20001</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>0.01142416208335706</v>
+        <v>0.004380777809873893</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26T20:15:06Z</t>
+          <t>2026-10-27T14:00:08Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.009665124718181484</v>
+        <v>-0.01871216460416969</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.06519980132721492</v>
+        <v>-0.06732416725823109</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.09585063029370489</v>
+        <v>-0.1042213018522242</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.03113169964516926</v>
+        <v>-0.03391870646144945</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.01881716090971697</v>
+        <v>-0.004187683902438288</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.03390018286076635</v>
+        <v>0.04119001118276899</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.00417998524711094</v>
+        <v>-0.001836434867776737</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27T14:00:08Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
+        <v>81.53</v>
+      </c>
+      <c r="AW4" t="n">
         <v>81.68000000000001</v>
       </c>
-      <c r="AW4" t="n">
-        <v>81.34</v>
-      </c>
       <c r="AX4" s="4" t="n">
-        <v>0.00417998524711094</v>
+        <v>-0.001836434867776737</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-26T20:15:00Z</t>
+          <t>2026-10-27T14:00:08Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1387,7 +1387,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.1939494270782613</v>
+        <v>0.2111213205132412</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.02896063782042824</v>
+        <v>-0.02239616444161896</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.03859658385913045</v>
+        <v>0.00103305785123986</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1443857731047478</v>
+        <v>-0.1252518309592093</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>-0.004196334298941506</v>
+        <v>-0.005430095936186263</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.06504664345085287</v>
+        <v>-0.02340504352888262</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.003300510078830365</v>
+        <v>0.003384807786417365</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27T14:00:07Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>367.72</v>
+        <v>369.065</v>
       </c>
       <c r="AW5" t="n">
-        <v>366.60999</v>
+        <v>367.82001</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>0.003027768010358978</v>
+        <v>0.003384780507183383</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-26T20:12:23Z</t>
+          <t>2026-10-27T14:00:07Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1584,7 +1584,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07104107360531242</v>
+        <v>0.07161392197810912</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.0125813130386867</v>
+        <v>0.01127255838923458</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.01671454472781697</v>
+        <v>0.009788415790381144</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01220200560396312</v>
+        <v>-0.009441228979861216</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01351088871459927</v>
+        <v>-0.009861246495925569</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.004065282345534715</v>
+        <v>0.001469756015859636</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.001946787800129801</v>
+        <v>0.001424870466321337</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27T14:00:09Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
+        <v>77.31</v>
+      </c>
+      <c r="AW6" t="n">
         <v>77.2</v>
       </c>
-      <c r="AW6" t="n">
-        <v>77.05</v>
-      </c>
       <c r="AX6" s="4" t="n">
-        <v>0.001946787800129801</v>
+        <v>0.001424870466321337</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-26T20:10:00Z</t>
+          <t>2026-10-27T14:00:09Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7645853547216279</v>
+        <v>0.7537498400454361</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6099251668152594</v>
+        <v>0.6136474285148719</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4342297149514458</v>
+        <v>0.4502859152004277</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2428951304914027</v>
+        <v>0.2130820193271685</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.2168480467515066</v>
+        <v>0.1850929750536248</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.122501611863314</v>
+        <v>0.1126409017713366</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.004471368815808452</v>
+        <v>-0.007825962090752481</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27T14:00:10Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>69.7</v>
+        <v>69.095</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>69.33</v>
+        <v>69.64</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.005336795038223041</v>
+        <v>-0.007825962090752481</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26T20:14:21Z</t>
+          <t>2026-10-27T14:00:10Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.03004800963801824</v>
+        <v>0.02873141959560988</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.009049259519761321</v>
+        <v>-0.009776375890002797</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.02554801608687662</v>
+        <v>-0.02965589179684514</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.01632319803309723</v>
+        <v>-0.0167810014199361</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.005293829720800725</v>
+        <v>-0.007126991537807492</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.01693131815572979</v>
+        <v>0.02048707848976838</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0006588855421687523</v>
+        <v>-0.000823064622330949</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27T14:00:05Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
+        <v>106.2225</v>
+      </c>
+      <c r="AW8" t="n">
         <v>106.31</v>
       </c>
-      <c r="AW8" t="n">
-        <v>106.24</v>
-      </c>
       <c r="AX8" s="4" t="n">
-        <v>0.0006588855421687523</v>
+        <v>-0.000823064622330949</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-26T20:10:00Z</t>
+          <t>2026-10-27T14:00:05Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.09812461238651804</v>
+        <v>0.09814990287323466</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07491090382676413</v>
+        <v>0.0776898875491705</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.06046018847025136</v>
+        <v>0.0634244377741513</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05683060109289628</v>
+        <v>0.056483835815474</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01504548635409386</v>
+        <v>0.02339901477832518</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.01362683438155132</v>
+        <v>0.01341463414634148</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.001726519337016619</v>
+        <v>0.002585315408479838</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27T14:00:00Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
+        <v>29.085</v>
+      </c>
+      <c r="AW9" t="n">
         <v>29.01</v>
       </c>
-      <c r="AW9" t="n">
-        <v>28.96</v>
-      </c>
       <c r="AX9" s="4" t="n">
-        <v>0.001726519337016619</v>
+        <v>0.002585315408479838</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-26T20:10:00Z</t>
+          <t>2026-10-27T14:00:00Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05976447480432223</v>
+        <v>0.05950117403252841</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03766099353905683</v>
+        <v>0.03750628700062508</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03445594913144046</v>
+        <v>0.03425043944690431</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01845065426014747</v>
+        <v>0.0184000413101264</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009242623957319784</v>
+        <v>0.009192430214416403</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003098289888812999</v>
+        <v>0.003148026270563653</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>9.934432743885502e-05</v>
+        <v>0.0001490016886858125</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27T14:00:12Z</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.675</v>
+        <v>100.685</v>
       </c>
       <c r="AW10" s="5" t="n">
-        <v>100.66</v>
+        <v>100.67</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>0.0001490164911583935</v>
+        <v>0.0001490016886858125</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-26T20:14:44Z</t>
+          <t>2026-10-27T14:00:12Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>-0.007882284306734988</v>
+        <v>0.0007183814213502782</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.03551320888463882</v>
+        <v>0.05291928791635159</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.07547389941464666</v>
+        <v>0.08198963303561846</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.04338482202820682</v>
+        <v>-0.02879719767015587</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.05544435791038294</v>
+        <v>0.08211113968027117</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.07451575101739971</v>
+        <v>0.09018671830958636</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.03390018286076635</v>
+        <v>0.04119001118276899</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.01881716090971697</v>
+        <v>-0.004187683902438288</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.03113169964516926</v>
+        <v>-0.03391870646144945</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.06504664345085287</v>
+        <v>-0.02340504352888262</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-0.004196334298941506</v>
+        <v>-0.005430095936186263</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1443857731047478</v>
+        <v>-0.1252518309592093</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-0.004065282345534715</v>
+        <v>0.001469756015859636</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01351088871459927</v>
+        <v>-0.009861246495925569</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01220200560396312</v>
+        <v>-0.009441228979861216</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.122501611863314</v>
+        <v>0.1126409017713366</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.2168480467515066</v>
+        <v>0.1850929750536248</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.2428951304914027</v>
+        <v>0.2130820193271685</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.01693131815572979</v>
+        <v>0.02048707848976838</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.005293829720800725</v>
+        <v>-0.007126991537807492</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.01632319803309723</v>
+        <v>-0.0167810014199361</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.01362683438155132</v>
+        <v>0.01341463414634148</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.01504548635409386</v>
+        <v>0.02339901477832518</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05683060109289628</v>
+        <v>0.056483835815474</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003098289888812999</v>
+        <v>0.003148026270563653</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009242623957319784</v>
+        <v>0.009192430214416403</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01845065426014747</v>
+        <v>0.0184000413101264</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4144788606720533</v>
+        <v>0.4207836081258425</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1434860332773134</v>
+        <v>0.1485828861587508</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0.1426651638527774</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.08198963303561846</v>
+        <v>0.08681237841101863</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.05291928791635159</v>
+        <v>0.05761245823095229</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.0007183814213502782</v>
+        <v>0.00517887697391628</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.00103218051399967</v>
+        <v>0.005494074761226653</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27T14:00:08Z</t>
+          <t>2026-10-27T17:40:07Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>766.16</v>
+        <v>769.575</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>765.37</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>0.00103218051399967</v>
+        <v>0.005494074761226653</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27T14:00:08Z</t>
+          <t>2026-10-27T17:40:07Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5242977830135354</v>
+        <v>0.5365080194065726</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1646101229314871</v>
+        <v>0.1739391169542983</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0.199142053686082</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.09018671830958636</v>
+        <v>0.09891955102209793</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.08211113968027117</v>
+        <v>0.09077928377014399</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.02879719767015587</v>
+        <v>-0.02101747382998653</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.004380791912384163</v>
+        <v>0.01242628475147423</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27T14:00:08Z</t>
+          <t>2026-10-27T17:40:08Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>715.3200000000001</v>
+        <v>721.05</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>712.20001</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>0.004380777809873893</v>
+        <v>0.01242627053599721</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27T14:00:08Z</t>
+          <t>2026-10-27T17:40:08Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.01871216460416969</v>
+        <v>-0.01678641882147214</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.06732416725823109</v>
+        <v>-0.06549382096559431</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>-0.1042213018522242</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.03391870646144945</v>
+        <v>-0.03202280302754579</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.004187683902438288</v>
+        <v>-0.002233434294004577</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.04119001118276899</v>
+        <v>0.04323331305679368</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.001836434867776737</v>
+        <v>0.0001224289911849752</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-27T14:00:08Z</t>
+          <t>2026-10-27T17:40:04Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>81.53</v>
+        <v>81.69</v>
       </c>
       <c r="AW4" t="n">
         <v>81.68000000000001</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>-0.001836434867776737</v>
+        <v>0.0001224289911849752</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-27T14:00:08Z</t>
+          <t>2026-10-27T17:40:04Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.2111213205132412</v>
+        <v>0.2223279624585699</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.02239616444161896</v>
+        <v>-0.01335028607755873</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.00103305785123986</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1252518309592093</v>
+        <v>-0.1171576876585054</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>-0.005430095936186263</v>
+        <v>0.00377277137005505</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.02340504352888262</v>
+        <v>-0.01436850043661186</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.003384807786417365</v>
+        <v>0.01266924038932093</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-27T14:00:07Z</t>
+          <t>2026-10-27T17:40:04Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>369.065</v>
+        <v>372.48</v>
       </c>
       <c r="AW5" t="n">
         <v>367.82001</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>0.003384780507183383</v>
+        <v>0.01266921285766909</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-27T14:00:07Z</t>
+          <t>2026-10-27T17:40:04Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07161392197810912</v>
+        <v>0.07459409263165062</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01127255838923458</v>
+        <v>0.01408491901597997</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>0.009788415790381144</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.009441228979861216</v>
+        <v>-0.006686473634248347</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.009861246495925569</v>
+        <v>-0.007107659223860141</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.001469756015859636</v>
+        <v>0.004254854936353913</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.001424870466321337</v>
+        <v>0.004209844559585507</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-27T14:00:09Z</t>
+          <t>2026-10-27T17:40:08Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.31</v>
+        <v>77.52500000000001</v>
       </c>
       <c r="AW6" t="n">
         <v>77.2</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>0.001424870466321337</v>
+        <v>0.004209844559585507</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-27T14:00:09Z</t>
+          <t>2026-10-27T17:40:08Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7537498400454361</v>
+        <v>0.7303986590216021</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6136474285148719</v>
+        <v>0.5921617112526434</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.4502859152004277</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2130820193271685</v>
+        <v>0.1969298309230727</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1850929750536248</v>
+        <v>0.1693134608044125</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1126409017713366</v>
+        <v>0.09782608695652173</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.007825962090752481</v>
+        <v>-0.02103676048248138</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27T14:00:10Z</t>
+          <t>2026-10-27T17:40:09Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>69.095</v>
+        <v>68.175</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>69.64</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>-0.007825962090752481</v>
+        <v>-0.02103676048248138</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27T14:00:10Z</t>
+          <t>2026-10-27T17:40:09Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.02873141959560988</v>
+        <v>0.03015991058754075</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.009776375890002797</v>
+        <v>-0.008401356618603306</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>-0.02965589179684514</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.0167810014199361</v>
+        <v>-0.01541570873438858</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.007126991537807492</v>
+        <v>-0.005748293345351208</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.02048707848976838</v>
+        <v>0.02190412143337506</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.000823064622330949</v>
+        <v>0.0005643871695983904</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-27T14:00:05Z</t>
+          <t>2026-10-27T17:40:07Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>106.2225</v>
+        <v>106.37</v>
       </c>
       <c r="AW8" t="n">
         <v>106.31</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>-0.000823064622330949</v>
+        <v>0.0005643871695983904</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-27T14:00:05Z</t>
+          <t>2026-10-27T17:40:07Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.09814990287323466</v>
+        <v>0.09852746859538453</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.0776898875491705</v>
+        <v>0.07806041871215785</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.0634244377741513</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.056483835815474</v>
+        <v>0.05684707591718108</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.02339901477832518</v>
+        <v>0.02375087966220968</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.01341463414634148</v>
+        <v>0.01376306620209067</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.002585315408479838</v>
+        <v>0.002930024129610409</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-27T14:00:00Z</t>
+          <t>2026-10-27T17:36:31Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>29.085</v>
+        <v>29.095</v>
       </c>
       <c r="AW9" t="n">
         <v>29.01</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>0.002585315408479838</v>
+        <v>0.002930024129610409</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-27T14:00:00Z</t>
+          <t>2026-10-27T17:36:31Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27T14:00:12Z</t>
+          <t>2026-10-27T17:40:07Z</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27T14:00:12Z</t>
+          <t>2026-10-27T17:40:07Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.0007183814213502782</v>
+        <v>0.00517887697391628</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.05291928791635159</v>
+        <v>0.05761245823095229</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.08198963303561846</v>
+        <v>0.08681237841101863</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.02879719767015587</v>
+        <v>-0.02101747382998653</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.08211113968027117</v>
+        <v>0.09077928377014399</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.09018671830958636</v>
+        <v>0.09891955102209793</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.04119001118276899</v>
+        <v>0.04323331305679368</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.004187683902438288</v>
+        <v>-0.002233434294004577</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.03391870646144945</v>
+        <v>-0.03202280302754579</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.02340504352888262</v>
+        <v>-0.01436850043661186</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-0.005430095936186263</v>
+        <v>0.00377277137005505</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1252518309592093</v>
+        <v>-0.1171576876585054</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.001469756015859636</v>
+        <v>0.004254854936353913</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.009861246495925569</v>
+        <v>-0.007107659223860141</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.009441228979861216</v>
+        <v>-0.006686473634248347</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1126409017713366</v>
+        <v>0.09782608695652173</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1850929750536248</v>
+        <v>0.1693134608044125</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.2130820193271685</v>
+        <v>0.1969298309230727</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.02048707848976838</v>
+        <v>0.02190412143337506</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.007126991537807492</v>
+        <v>-0.005748293345351208</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.0167810014199361</v>
+        <v>-0.01541570873438858</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.01341463414634148</v>
+        <v>0.01376306620209067</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.02339901477832518</v>
+        <v>0.02375087966220968</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.056483835815474</v>
+        <v>0.05684707591718108</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4207836081258425</v>
+        <v>0.4209405344899924</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1485828861587508</v>
+        <v>0.1487096431561274</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1426651638527774</v>
+        <v>0.1426650597624441</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.08681237841101863</v>
+        <v>0.08693241746135794</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.05761245823095229</v>
+        <v>0.05772927213336532</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.00517887697391628</v>
+        <v>0.005289899557215705</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.005494074761226653</v>
+        <v>0.005605132158302384</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -858,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512062651334</v>
+        <v>0.3464512030450774</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -867,24 +867,24 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27T17:40:07Z</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.3440562879571546</v>
+        <v>0.342772830089295</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>0.3464512062651334</v>
+        <v>0.3464512030450774</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>0.3430182213596835</v>
+        <v>0.3430182189724962</v>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -0.8%, 3m +3.6%, 6m +7.6%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +0.5%, 3m +5.8%, 6m +8.7%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>769.575</v>
+        <v>769.9</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>765.37</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>0.005494074761226653</v>
+        <v>0.005918705985340278</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27T17:40:07Z</t>
+          <t>2026-10-27T20:15:07Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5365080194065726</v>
+        <v>0.5369341057199584</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1739391169542983</v>
+        <v>0.1742648529799553</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.199142053686082</v>
+        <v>0.1991421728462064</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.09891955102209793</v>
+        <v>0.09922436193701989</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09077928377014399</v>
+        <v>0.09108183679247817</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.02101747382998653</v>
+        <v>-0.02074593024045179</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.01242628475147423</v>
+        <v>0.01270710474585779</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1057,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095554429965</v>
+        <v>0.358309549312061</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27T17:40:08Z</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.3655939642989111</v>
+        <v>0.3613293294474164</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0.3583095554429965</v>
+        <v>0.358309549312061</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>0.364489203625325</v>
+        <v>0.3644891959458457</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1152,14 +1152,14 @@
         <v>0</v>
       </c>
       <c r="AR3" s="3" t="n">
-        <v>0.03490779891624962</v>
+        <v>0.03490792057956504</v>
       </c>
       <c r="AS3" s="3" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -4.3%, 3m +5.5%, 6m +7.5%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -2.1%, 3m +9.1%, 6m +9.9%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>721.05</v>
+        <v>720.88</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>712.20001</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>0.01242627053599721</v>
+        <v>0.01218757354412281</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27T17:40:08Z</t>
+          <t>2026-10-27T20:15:07Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.01678641882147214</v>
+        <v>-0.01750857348998369</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.06549382096559431</v>
+        <v>-0.06618060833342942</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1042213018522242</v>
+        <v>-0.1042216927596267</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.03202280302754579</v>
+        <v>-0.0327336793707883</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.002233434294004577</v>
+        <v>-0.002966277897167191</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.04323331305679368</v>
+        <v>0.04246707485403434</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.0001224289911849752</v>
+        <v>-0.0006121449559256531</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.03802938342376228</v>
+        <v>-0.03802955588478829</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-27T17:40:04Z</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1350,14 +1350,14 @@
         <v>0</v>
       </c>
       <c r="AR4" s="4" t="n">
-        <v>-0.04101366149025232</v>
+        <v>-0.0410135787067486</v>
       </c>
       <c r="AS4" s="4" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +3.4%, 3m -1.9%, 6m -3.1%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +4.2%, 3m -0.3%, 6m -3.3%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>81.69</v>
+        <v>81.63</v>
       </c>
       <c r="AW4" t="n">
         <v>81.68000000000001</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>0.0001224289911849752</v>
+        <v>-0.0006121449559256531</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-27T17:40:04Z</t>
+          <t>2026-10-27T20:15:00Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.2223279624585699</v>
+        <v>0.2216060118793686</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.01335028607755873</v>
+        <v>-0.01393303666030932</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.00103305785123986</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1171576876585054</v>
+        <v>-0.1176791258799271</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.00377277137005505</v>
+        <v>0.003179907297617746</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.01436850043661186</v>
+        <v>-0.01495064962557235</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.01266924038932093</v>
+        <v>0.01207112174433145</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-27T17:40:04Z</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -6.5%, 3m -0.4%, 6m -14.4%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.5%, 3m +0.3%, 6m -11.8%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>372.48</v>
+        <v>372.2585</v>
       </c>
       <c r="AW5" t="n">
         <v>367.82001</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>0.01266921285766909</v>
+        <v>0.01206701614738148</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-27T17:40:04Z</t>
+          <t>2026-10-27T20:14:16Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07459409263165062</v>
+        <v>0.07563380079719617</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01408491901597997</v>
+        <v>0.01506607635031054</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.009788415790381144</v>
+        <v>0.009788516565435446</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.006686473634248347</v>
+        <v>-0.005725415272833656</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.007107659223860141</v>
+        <v>-0.006147008412364596</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.004254854936353913</v>
+        <v>0.005226401071410036</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.004209844559585507</v>
+        <v>0.005181347150258864</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715185963322809</v>
+        <v>0.03715196348622696</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1659,17 +1659,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-27T17:40:08Z</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="AN6" s="4" t="n">
-        <v>0.01937551155348527</v>
+        <v>0.01937540931729198</v>
       </c>
       <c r="AO6" t="n">
         <v>6</v>
@@ -1744,14 +1744,14 @@
         <v>-1</v>
       </c>
       <c r="AR6" s="4" t="n">
-        <v>-0.009332499176097464</v>
+        <v>-0.009332704431263883</v>
       </c>
       <c r="AS6" s="4" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -0.4%, 3m -1.4%, 6m -1.2%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +0.5%, 3m -0.6%, 6m -0.6%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.52500000000001</v>
+        <v>77.6097</v>
       </c>
       <c r="AW6" t="n">
         <v>77.2</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>0.004209844559585507</v>
+        <v>0.005306994818652822</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-27T17:40:08Z</t>
+          <t>2026-10-27T20:11:55Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7303986590216021</v>
+        <v>0.7312871868190052</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.5921617112526434</v>
+        <v>0.5929789607378571</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4502859152004277</v>
+        <v>0.4502857859818346</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.1969298309230727</v>
+        <v>0.1975443163514892</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1693134608044125</v>
+        <v>0.1699137684117193</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.09782608695652173</v>
+        <v>0.09838969404186781</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.02103676048248138</v>
+        <v>-0.02053417576105698</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.4639559345596878</v>
+        <v>0.4639560631420809</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>1</v>
@@ -1847,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392382918702</v>
+        <v>0.2952392476428616</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1856,24 +1856,24 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27T17:40:09Z</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2903497477439342</v>
+        <v>0.2958978404632886</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>1</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.2952392382918702</v>
+        <v>0.2952392476428616</v>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2924925750149914</v>
+        <v>0.2924925850816581</v>
       </c>
       <c r="AH7" s="2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AM7" s="2" t="n"/>
       <c r="AN7" s="3" t="n">
-        <v>0.4666251057178188</v>
+        <v>0.4666252367940658</v>
       </c>
       <c r="AO7" s="2" t="n">
         <v>1</v>
@@ -1942,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="AR7" s="3" t="n">
-        <v>-0.06086749377492051</v>
+        <v>-0.0608672238419079</v>
       </c>
       <c r="AS7" s="3" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +12.3%, 3m +21.7%, 6m +24.3%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +9.8%, 3m +17.0%, 6m +19.8%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>68.175</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>69.64</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>-0.02103676048248138</v>
+        <v>-0.02053417576105698</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27T17:40:09Z</t>
+          <t>2026-10-27T20:10:59Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.03015991058754075</v>
+        <v>0.02957905772755653</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.008401356618603306</v>
+        <v>-0.008960827462023424</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.02965589179684514</v>
+        <v>-0.02965602982336579</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.01541570873438858</v>
+        <v>-0.01597108203020448</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.005748293345351208</v>
+        <v>-0.006309119728723278</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.02190412143337506</v>
+        <v>0.02132769718512817</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0005643871695983904</v>
+        <v>0</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.004296411608788464</v>
+        <v>0.004296483646738736</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
@@ -2055,17 +2055,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-27T17:40:07Z</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="AN8" s="4" t="n">
-        <v>-0.02969144252962053</v>
+        <v>-0.02969137366034236</v>
       </c>
       <c r="AO8" t="n">
         <v>7</v>
@@ -2140,14 +2140,14 @@
         <v>0</v>
       </c>
       <c r="AR8" s="4" t="n">
-        <v>-0.01805023516165016</v>
+        <v>-0.01805009579008054</v>
       </c>
       <c r="AS8" s="4" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +1.7%, 3m -0.5%, 6m -1.6%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +2.1%, 3m -0.6%, 6m -1.6%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>106.37</v>
+        <v>106.31</v>
       </c>
       <c r="AW8" t="n">
         <v>106.31</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>0.0005643871695983904</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-27T17:40:07Z</t>
+          <t>2026-10-27T20:10:00Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.09852746859538453</v>
+        <v>0.09947138290075963</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07806041871215785</v>
+        <v>0.07898674661962679</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.0634244377741513</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05684707591718108</v>
+        <v>0.05775517617144943</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.02375087966220968</v>
+        <v>0.02463054187192126</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.01376306620209067</v>
+        <v>0.01463414634146343</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.002930024129610409</v>
+        <v>0.00379179593243717</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2252,17 +2252,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-27T17:36:31Z</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +1.4%, 3m +1.5%, 6m +5.7%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +1.5%, 3m +2.5%, 6m +5.8%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>29.095</v>
+        <v>29.12</v>
       </c>
       <c r="AW9" t="n">
         <v>29.01</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>0.002930024129610409</v>
+        <v>0.00379179593243717</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-27T17:36:31Z</t>
+          <t>2026-10-27T20:10:00Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05950117403252841</v>
+        <v>0.05944855938416804</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03750628700062508</v>
+        <v>0.03745476461461927</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0.03425043944690431</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.0184000413101264</v>
+        <v>0.01834946773703661</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009192430214416403</v>
+        <v>0.009142313889729969</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003148026270563653</v>
+        <v>0.003098210109950372</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0001490016886858125</v>
+        <v>9.933445912402306e-05</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27T17:40:07Z</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.685</v>
+        <v>100.6826</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.67</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>0.0001490016886858125</v>
+        <v>0.0001251614184960559</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27T17:40:07Z</t>
+          <t>2026-10-27T20:14:16Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>QQQ 36.6%, SPY 34.4%, XLE 29.0%</t>
+          <t>QQQ 36.1%, SPY 34.3%, XLE 29.6%</t>
         </is>
       </c>
     </row>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.00517887697391628</v>
+        <v>0.005289899557215705</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.05761245823095229</v>
+        <v>0.05772927213336532</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.08681237841101863</v>
+        <v>0.08693241746135794</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.02101747382998653</v>
+        <v>-0.02074593024045179</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.09077928377014399</v>
+        <v>0.09108183679247817</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.09891955102209793</v>
+        <v>0.09922436193701989</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.04323331305679368</v>
+        <v>0.04246707485403434</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.002233434294004577</v>
+        <v>-0.002966277897167191</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.03202280302754579</v>
+        <v>-0.0327336793707883</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.01436850043661186</v>
+        <v>-0.01495064962557235</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.00377277137005505</v>
+        <v>0.003179907297617746</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1171576876585054</v>
+        <v>-0.1176791258799271</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.004254854936353913</v>
+        <v>0.005226401071410036</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.007107659223860141</v>
+        <v>-0.006147008412364596</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.006686473634248347</v>
+        <v>-0.005725415272833656</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.09782608695652173</v>
+        <v>0.09838969404186781</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1693134608044125</v>
+        <v>0.1699137684117193</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.1969298309230727</v>
+        <v>0.1975443163514892</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.02190412143337506</v>
+        <v>0.02132769718512817</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.005748293345351208</v>
+        <v>-0.006309119728723278</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.01541570873438858</v>
+        <v>-0.01597108203020448</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.01376306620209067</v>
+        <v>0.01463414634146343</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.02375087966220968</v>
+        <v>0.02463054187192126</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05684707591718108</v>
+        <v>0.05775517617144943</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003148026270563653</v>
+        <v>0.003098210109950372</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009192430214416403</v>
+        <v>0.009142313889729969</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.0184000413101264</v>
+        <v>0.01834946773703661</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.02933625610116319</v>
+        <v>0.02933614706677878</v>
       </c>
     </row>
     <row r="3">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4209405344899924</v>
+        <v>0.4218199964036251</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1487096431561274</v>
+        <v>0.1364514123445437</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1426650597624441</v>
+        <v>0.12726161924341</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.08693241746135794</v>
+        <v>0.08818812375466578</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.05772927213336532</v>
+        <v>0.04132878868212497</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.005289899557215705</v>
+        <v>0.008152316147605143</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.005605132158302384</v>
+        <v>0.001000441753501446</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,12 +872,12 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28T14:00:07Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>769.9</v>
+        <v>770.4299999999999</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>765.37</v>
+        <v>769.65997</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>0.005918705985340278</v>
+        <v>0.001000480770748657</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27T20:15:07Z</t>
+          <t>2026-10-28T14:00:07Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5369341057199584</v>
+        <v>0.5394472549303559</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1742648529799553</v>
+        <v>0.1552376705115435</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1991421728462064</v>
+        <v>0.1803995211860747</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.09922436193701989</v>
+        <v>0.09398405093396645</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09108183679247817</v>
+        <v>0.05764401190524282</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.02074593024045179</v>
+        <v>-0.02131638502296951</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.01270710474585779</v>
+        <v>0.001317157712305006</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28T14:00:08Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>720.88</v>
+        <v>722.2</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>712.20001</v>
+        <v>721.25</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>0.01218757354412281</v>
+        <v>0.001317157712305006</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27T20:15:07Z</t>
+          <t>2026-10-28T14:00:08Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.01750857348998369</v>
+        <v>-0.022222949451846</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.06618060833342942</v>
+        <v>-0.06796546912824308</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1042216927596267</v>
+        <v>-0.1116758925697279</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.0327336793707883</v>
+        <v>-0.0237374088121951</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.002966277897167191</v>
+        <v>-0.0008963832461361676</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.04246707485403434</v>
+        <v>0.04920549051396295</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.0006121449559256531</v>
+        <v>0.001471272816366609</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28T14:00:08Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
+        <v>81.7501</v>
+      </c>
+      <c r="AW4" t="n">
         <v>81.63</v>
       </c>
-      <c r="AW4" t="n">
-        <v>81.68000000000001</v>
-      </c>
       <c r="AX4" s="4" t="n">
-        <v>-0.0006121449559256531</v>
+        <v>0.001471272816366609</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-27T20:15:00Z</t>
+          <t>2026-10-28T14:00:08Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1387,7 +1387,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.2216060118793686</v>
+        <v>0.2006665156760603</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.01393303666030932</v>
+        <v>0.01111686330072748</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.00103305785123986</v>
+        <v>0.04326857578812571</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1176791258799271</v>
+        <v>-0.1109700294674302</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.003179907297617746</v>
+        <v>-0.01609396542581409</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.01495064962557235</v>
+        <v>-0.03081825067251698</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.01207112174433145</v>
+        <v>-0.00319651874932847</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28T14:00:08Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>372.2585</v>
+        <v>371.09</v>
       </c>
       <c r="AW5" t="n">
-        <v>367.82001</v>
+        <v>372.28</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>0.01206701614738148</v>
+        <v>-0.00319651874932847</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-27T20:14:16Z</t>
+          <t>2026-10-28T14:00:08Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1584,7 +1584,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07563380079719617</v>
+        <v>0.07640377952550548</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01506607635031054</v>
+        <v>0.0138082399984516</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.009788516565435446</v>
+        <v>0.004965663170520607</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.005725415272833656</v>
+        <v>-0.001153981643128299</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.006147008412364596</v>
+        <v>-0.007810147875399687</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.005226401071410036</v>
+        <v>0.008798884531073359</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.005181347150258864</v>
+        <v>0.001224226804123596</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28T14:00:09Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.6097</v>
+        <v>77.69499999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>77.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>0.005306994818652822</v>
+        <v>0.001224226804123596</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-27T20:11:55Z</t>
+          <t>2026-10-28T14:00:09Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7312871868190052</v>
+        <v>0.7190603882971747</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.5929789607378571</v>
+        <v>0.5892535266058916</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4502857859818346</v>
+        <v>0.4339514995576066</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.1975443163514892</v>
+        <v>0.170679545587809</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1699137684117193</v>
+        <v>0.1636772724855422</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.09838969404186781</v>
+        <v>0.1083035424114398</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.02053417576105698</v>
+        <v>-7.330303474561983e-05</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28T14:00:10Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
+        <v>68.205</v>
+      </c>
+      <c r="AW7" s="2" t="n">
         <v>68.20999999999999</v>
       </c>
-      <c r="AW7" s="2" t="n">
-        <v>69.64</v>
-      </c>
       <c r="AX7" s="3" t="n">
-        <v>-0.02053417576105698</v>
+        <v>-7.330303474561983e-05</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27T20:10:59Z</t>
+          <t>2026-10-28T14:00:10Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.02957905772755653</v>
+        <v>0.02564272698357972</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.008960827462023424</v>
+        <v>-0.009068284913850144</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.02965602982336579</v>
+        <v>-0.03014201857428755</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.01597108203020448</v>
+        <v>-0.01333896775416421</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.006309119728723278</v>
+        <v>-0.00640637127159116</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.02132769718512817</v>
+        <v>0.02172867993462169</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0</v>
+        <v>-0.0003762581130656306</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28T14:00:08Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>106.31</v>
+        <v>106.27</v>
       </c>
       <c r="AW8" t="n">
         <v>106.31</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>0</v>
+        <v>-0.0003762581130656306</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-27T20:10:00Z</t>
+          <t>2026-10-28T14:00:08Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.09947138290075963</v>
+        <v>0.1065279480657968</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07898674661962679</v>
+        <v>0.08033327857469019</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0634244377741513</v>
+        <v>0.06642340803510183</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05775517617144943</v>
+        <v>0.05487142339731976</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.02463054187192126</v>
+        <v>0.03500355366026997</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.01463414634146343</v>
+        <v>0.01304347826086949</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.00379179593243717</v>
+        <v>0.0001717032967032406</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28T14:00:01Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
+        <v>29.125</v>
+      </c>
+      <c r="AW9" t="n">
         <v>29.12</v>
       </c>
-      <c r="AW9" t="n">
-        <v>29.01</v>
-      </c>
       <c r="AX9" s="4" t="n">
-        <v>0.00379179593243717</v>
+        <v>0.0001717032967032406</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-27T20:10:00Z</t>
+          <t>2026-10-28T14:00:01Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05944855938416804</v>
+        <v>0.05955378868088879</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03745476461461927</v>
+        <v>0.03745465611882293</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03425043944690431</v>
+        <v>0.03425033515224207</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01834946773703661</v>
+        <v>0.01834934163531554</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009142313889729969</v>
+        <v>0.009142323381512663</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003098210109950372</v>
+        <v>0.003098206360367506</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>9.933445912402306e-05</v>
+        <v>9.932459276917882e-05</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28T14:00:10Z</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.6826</v>
+        <v>100.69</v>
       </c>
       <c r="AW10" s="5" t="n">
-        <v>100.67</v>
+        <v>100.68</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>0.0001251614184960559</v>
+        <v>9.932459276917882e-05</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27T20:14:16Z</t>
+          <t>2026-10-28T14:00:10Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.005289899557215705</v>
+        <v>0.008152316147605143</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.05772927213336532</v>
+        <v>0.04132878868212497</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.08693241746135794</v>
+        <v>0.08818812375466578</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.02074593024045179</v>
+        <v>-0.02131638502296951</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.09108183679247817</v>
+        <v>0.05764401190524282</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.09922436193701989</v>
+        <v>0.09398405093396645</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.04246707485403434</v>
+        <v>0.04920549051396295</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.002966277897167191</v>
+        <v>-0.0008963832461361676</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.0327336793707883</v>
+        <v>-0.0237374088121951</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.01495064962557235</v>
+        <v>-0.03081825067251698</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.003179907297617746</v>
+        <v>-0.01609396542581409</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1176791258799271</v>
+        <v>-0.1109700294674302</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.005226401071410036</v>
+        <v>0.008798884531073359</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.006147008412364596</v>
+        <v>-0.007810147875399687</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.005725415272833656</v>
+        <v>-0.001153981643128299</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.09838969404186781</v>
+        <v>0.1083035424114398</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1699137684117193</v>
+        <v>0.1636772724855422</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.1975443163514892</v>
+        <v>0.170679545587809</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.02132769718512817</v>
+        <v>0.02172867993462169</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.006309119728723278</v>
+        <v>-0.00640637127159116</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.01597108203020448</v>
+        <v>-0.01333896775416421</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.01463414634146343</v>
+        <v>0.01304347826086949</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.02463054187192126</v>
+        <v>0.03500355366026997</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05775517617144943</v>
+        <v>0.05487142339731976</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003098210109950372</v>
+        <v>0.003098206360367506</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009142313889729969</v>
+        <v>0.009142323381512663</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01834946773703661</v>
+        <v>0.01834934163531554</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4218199964036251</v>
+        <v>0.42300110928565</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1364514123445437</v>
+        <v>0.1373954681366345</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0.12726161924341</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.08818812375466578</v>
+        <v>0.08909208699493831</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.04132878868212497</v>
+        <v>0.04219382564168872</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.008152316147605143</v>
+        <v>0.008989793247840883</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.001000441753501446</v>
+        <v>0.001831977756411973</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T14:00:07Z</t>
+          <t>2026-10-28T17:40:08Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>770.4299999999999</v>
+        <v>771.0700000000001</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>769.65997</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>0.001000480770748657</v>
+        <v>0.001832016806070813</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T14:00:07Z</t>
+          <t>2026-10-28T17:40:08Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5394472549303559</v>
+        <v>0.5390635655009908</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1552376705115435</v>
+        <v>0.154949740878904</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0.1803995211860747</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.09398405093396645</v>
+        <v>0.09371138805779888</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.05764401190524282</v>
+        <v>0.05738040636364339</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.02131638502296951</v>
+        <v>-0.02156031059856622</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.001317157712305006</v>
+        <v>0.00106759098786835</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T14:00:08Z</t>
+          <t>2026-10-28T17:40:07Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>722.2</v>
+        <v>722.02</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>721.25</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>0.001317157712305006</v>
+        <v>0.00106759098786835</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T14:00:08Z</t>
+          <t>2026-10-28T17:40:07Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.022222949451846</v>
+        <v>-0.02563290536763418</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.06796546912824308</v>
+        <v>-0.07121589995036492</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>-0.1116758925697279</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.0237374088121951</v>
+        <v>-0.02714208311531696</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.0008963832461361676</v>
+        <v>-0.004380714655351836</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.04920549051396295</v>
+        <v>0.04554643094895283</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.001471272816366609</v>
+        <v>-0.002021315692759873</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-28T14:00:08Z</t>
+          <t>2026-10-28T17:40:10Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>81.7501</v>
+        <v>81.465</v>
       </c>
       <c r="AW4" t="n">
         <v>81.63</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>0.001471272816366609</v>
+        <v>-0.002021315692759873</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-28T14:00:08Z</t>
+          <t>2026-10-28T17:40:10Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.2006665156760603</v>
+        <v>0.1978030866793929</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.01111686330072748</v>
+        <v>0.008705484864172552</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.04326857578812571</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1109700294674302</v>
+        <v>-0.1130902469993532</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>-0.01609396542581409</v>
+        <v>-0.01844044967652991</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.03081825067251698</v>
+        <v>-0.03312961947295567</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.00319651874932847</v>
+        <v>-0.005573761684753431</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-28T14:00:08Z</t>
+          <t>2026-10-28T17:40:11Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>371.09</v>
+        <v>370.205</v>
       </c>
       <c r="AW5" t="n">
         <v>372.28</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.00319651874932847</v>
+        <v>-0.005573761684753431</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-28T14:00:08Z</t>
+          <t>2026-10-28T17:40:11Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07640377952550548</v>
+        <v>0.07456809510839846</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.0138082399984516</v>
+        <v>0.01207930516609701</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>0.004965663170520607</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.001153981643128299</v>
+        <v>-0.002857400105478192</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.007810147875399687</v>
+        <v>-0.009502215002068159</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.008798884531073359</v>
+        <v>0.007078492585641083</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.001224226804123596</v>
+        <v>-0.0004832474226803551</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-28T14:00:09Z</t>
+          <t>2026-10-28T17:40:11Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.69499999999999</v>
+        <v>77.5625</v>
       </c>
       <c r="AW6" t="n">
         <v>77.59999999999999</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>0.001224226804123596</v>
+        <v>-0.0004832474226803551</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-28T14:00:09Z</t>
+          <t>2026-10-28T17:40:11Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7190603882971747</v>
+        <v>0.729898244275003</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.5892535266058916</v>
+        <v>0.5992730122219101</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.4339514995576066</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.170679545587809</v>
+        <v>0.178060121859384</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1636772724855422</v>
+        <v>0.1710137027643897</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1083035424114398</v>
+        <v>0.1152908677283069</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-7.330303474561983e-05</v>
+        <v>0.006230757953379351</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T14:00:10Z</t>
+          <t>2026-10-28T17:40:10Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>68.205</v>
+        <v>68.63500000000001</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>68.20999999999999</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>-7.330303474561983e-05</v>
+        <v>0.006230757953379351</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T14:00:10Z</t>
+          <t>2026-10-28T17:40:10Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.02564272698357972</v>
+        <v>0.02491888013570387</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.009068284913850144</v>
+        <v>-0.009767634482227505</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>-0.03014201857428755</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.01333896775416421</v>
+        <v>-0.01403530329023694</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.00640637127159116</v>
+        <v>-0.007107599484206473</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.02172867993462169</v>
+        <v>0.02100759542351693</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.0003762581130656306</v>
+        <v>-0.001081742075063619</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-28T14:00:08Z</t>
+          <t>2026-10-28T17:39:15Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>106.27</v>
+        <v>106.195</v>
       </c>
       <c r="AW8" t="n">
         <v>106.31</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>-0.0003762581130656306</v>
+        <v>-0.001081742075063619</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-28T14:00:08Z</t>
+          <t>2026-10-28T17:39:15Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1065279480657968</v>
+        <v>0.1059580624273078</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.08033327857469019</v>
+        <v>0.07977688375310654</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.06642340803510183</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05487142339731976</v>
+        <v>0.05432814197754432</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.03500355366026997</v>
+        <v>0.0344705046197582</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.01304347826086949</v>
+        <v>0.01252173913043486</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.0001717032967032406</v>
+        <v>-0.0003434065934065922</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-28T14:00:01Z</t>
+          <t>2026-10-28T17:39:33Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>29.125</v>
+        <v>29.11</v>
       </c>
       <c r="AW9" t="n">
         <v>29.12</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>0.0001717032967032406</v>
+        <v>-0.0003434065934065922</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-28T14:00:01Z</t>
+          <t>2026-10-28T17:39:33Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05955378868088879</v>
+        <v>0.05965901797760953</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03745465611882293</v>
+        <v>0.03755769064619607</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0.03425033515224207</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01834934163531554</v>
+        <v>0.0184504787235702</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009142323381512663</v>
+        <v>0.00924254607725028</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003098206360367506</v>
+        <v>0.003197828786264845</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>9.932459276917882e-05</v>
+        <v>0.0001986491855383576</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-28T14:00:10Z</t>
+          <t>2026-10-28T17:40:12Z</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.69</v>
+        <v>100.7</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.68</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>9.932459276917882e-05</v>
+        <v>0.0001986491855383576</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-28T14:00:10Z</t>
+          <t>2026-10-28T17:40:12Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.008152316147605143</v>
+        <v>0.008989793247840883</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.04132878868212497</v>
+        <v>0.04219382564168872</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.08818812375466578</v>
+        <v>0.08909208699493831</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.02131638502296951</v>
+        <v>-0.02156031059856622</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.05764401190524282</v>
+        <v>0.05738040636364339</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.09398405093396645</v>
+        <v>0.09371138805779888</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.04920549051396295</v>
+        <v>0.04554643094895283</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.0008963832461361676</v>
+        <v>-0.004380714655351836</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.0237374088121951</v>
+        <v>-0.02714208311531696</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.03081825067251698</v>
+        <v>-0.03312961947295567</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-0.01609396542581409</v>
+        <v>-0.01844044967652991</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1109700294674302</v>
+        <v>-0.1130902469993532</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.008798884531073359</v>
+        <v>0.007078492585641083</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.007810147875399687</v>
+        <v>-0.009502215002068159</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.001153981643128299</v>
+        <v>-0.002857400105478192</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1083035424114398</v>
+        <v>0.1152908677283069</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1636772724855422</v>
+        <v>0.1710137027643897</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.170679545587809</v>
+        <v>0.178060121859384</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.02172867993462169</v>
+        <v>0.02100759542351693</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.00640637127159116</v>
+        <v>-0.007107599484206473</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.01333896775416421</v>
+        <v>-0.01403530329023694</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.01304347826086949</v>
+        <v>0.01252173913043486</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.03500355366026997</v>
+        <v>0.0344705046197582</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05487142339731976</v>
+        <v>0.05432814197754432</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003098206360367506</v>
+        <v>0.003197828786264845</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009142323381512663</v>
+        <v>0.00924254607725028</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01834934163531554</v>
+        <v>0.0184504787235702</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.42300110928565</v>
+        <v>0.4252893549503975</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1373954681366345</v>
+        <v>0.1392244736669503</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.12726161924341</v>
+        <v>0.127261517753601</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.08909208699493831</v>
+        <v>0.09084351577296568</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.04219382564168872</v>
+        <v>0.04386983475084305</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.008989793247840883</v>
+        <v>0.01061240512954709</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.001831977756411973</v>
+        <v>0.003443078762050744</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.1609548690014375</v>
+        <v>0.1609549765152376</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>3</v>
@@ -858,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512030450774</v>
+        <v>0.3464512453330066</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -867,24 +867,24 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T17:40:08Z</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.342772830089295</v>
+        <v>0.3418200038008798</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>0.3464512030450774</v>
+        <v>0.3464512453330066</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>0.3430182189724962</v>
+        <v>0.3430182213596835</v>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
@@ -953,14 +953,14 @@
         <v>0</v>
       </c>
       <c r="AR2" s="3" t="n">
-        <v>0.005238944661168254</v>
+        <v>0.005238837446254196</v>
       </c>
       <c r="AS2" s="3" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +0.5%, 3m +5.8%, 6m +8.7%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +1.1%, 3m +4.4%, 6m +9.1%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>771.0700000000001</v>
+        <v>771.77</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>769.65997</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>0.001832016806070813</v>
+        <v>0.002741509344704518</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T17:40:08Z</t>
+          <t>2026-10-28T20:15:02Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5390635655009908</v>
+        <v>0.5467160380088834</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.154949740878904</v>
+        <v>0.1606923374409872</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0.1803995211860747</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.09371138805779888</v>
+        <v>0.09914949764358272</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.05738040636364339</v>
+        <v>0.06263787244331653</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.02156031059856622</v>
+        <v>-0.01669535050750059</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.00106759098786835</v>
+        <v>0.006045060658578905</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.1982246540542743</v>
+        <v>0.1982245316673374</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>2</v>
@@ -1057,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.358309549312061</v>
+        <v>0.3583095243289641</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T17:40:07Z</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.3613293294474164</v>
+        <v>0.3600718930386608</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0.358309549312061</v>
+        <v>0.3583095243289641</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>0.3644891959458457</v>
+        <v>0.364489203625325</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1152,14 +1152,14 @@
         <v>0</v>
       </c>
       <c r="AR3" s="3" t="n">
-        <v>0.03490792057956504</v>
+        <v>0.0349080422428556</v>
       </c>
       <c r="AS3" s="3" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -2.1%, 3m +9.1%, 6m +9.9%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.7%, 3m +6.3%, 6m +9.9%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>722.02</v>
+        <v>723.52</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>721.25</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>0.00106759098786835</v>
+        <v>0.003147313691507669</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T17:40:07Z</t>
+          <t>2026-10-28T20:15:11Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.02563290536763418</v>
+        <v>-0.02904184243077024</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.07121589995036492</v>
+        <v>-0.07446502965908253</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1116758925697279</v>
+        <v>-0.11167573803172</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.02714208311531696</v>
+        <v>-0.0305455632148951</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.004380714655351836</v>
+        <v>-0.007863823920965629</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.04554643094895283</v>
+        <v>0.04188865481416548</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.002021315692759873</v>
+        <v>-0.005512679162072653</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.03802955588478829</v>
+        <v>-0.03802938342376228</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-28T17:40:10Z</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1350,14 +1350,14 @@
         <v>0</v>
       </c>
       <c r="AR4" s="4" t="n">
-        <v>-0.0410135787067486</v>
+        <v>-0.04101366149025232</v>
       </c>
       <c r="AS4" s="4" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +4.2%, 3m -0.3%, 6m -3.3%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +4.2%, 3m -0.8%, 6m -3.1%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>81.465</v>
+        <v>81</v>
       </c>
       <c r="AW4" t="n">
         <v>81.63</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>-0.002021315692759873</v>
+        <v>-0.007717750826901848</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-28T17:40:10Z</t>
+          <t>2026-10-28T20:15:04Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.1978030866793929</v>
+        <v>0.2086905878927103</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.008705484864172552</v>
+        <v>0.01787417236587552</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.04326857578812571</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1130902469993532</v>
+        <v>-0.1050286289259961</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>-0.01844044967652991</v>
+        <v>-0.009518506734542465</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.03312961947295567</v>
+        <v>-0.02434119459897099</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.005573761684753431</v>
+        <v>0.00346513377028046</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-28T17:40:11Z</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.5%, 3m +0.3%, 6m -11.8%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -2.4%, 3m -1.0%, 6m -10.5%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>370.205</v>
+        <v>372.9955</v>
       </c>
       <c r="AW5" t="n">
         <v>372.28</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.005573761684753431</v>
+        <v>0.001921940474911343</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-28T17:40:11Z</t>
+          <t>2026-10-28T20:14:49Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07456809510839846</v>
+        <v>0.07494931345667788</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01207930516609701</v>
+        <v>0.01243793911558044</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.004965663170520607</v>
+        <v>0.004965463076570309</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.002857400105478192</v>
+        <v>-0.002503762586779867</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.009502215002068159</v>
+        <v>-0.009151031258797238</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.007078492585641083</v>
+        <v>0.007435555064881694</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.0004832474226803551</v>
+        <v>-0.0001288659793813318</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1659,17 +1659,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-28T17:40:11Z</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="AN6" s="4" t="n">
-        <v>0.01937540931729198</v>
+        <v>0.01937561378969899</v>
       </c>
       <c r="AO6" t="n">
         <v>6</v>
@@ -1744,14 +1744,14 @@
         <v>-1</v>
       </c>
       <c r="AR6" s="4" t="n">
-        <v>-0.009332704431263883</v>
+        <v>-0.009332190901998993</v>
       </c>
       <c r="AS6" s="4" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +0.5%, 3m -0.6%, 6m -0.6%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +0.7%, 3m -0.9%, 6m -0.3%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.5625</v>
+        <v>77.59</v>
       </c>
       <c r="AW6" t="n">
         <v>77.59999999999999</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.0004832474226803551</v>
+        <v>-0.0001288659793813318</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-28T17:40:11Z</t>
+          <t>2026-10-28T20:13:46Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.729898244275003</v>
+        <v>0.7206985033923081</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.5992730122219101</v>
+        <v>0.5907681000129639</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.4339514995576066</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.178060121859384</v>
+        <v>0.1717952908184039</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1710137027643897</v>
+        <v>0.1647862677602516</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1152908677283069</v>
+        <v>0.1093597660058498</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.006230757953379351</v>
+        <v>0.00087963641694766</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.4639560631420809</v>
+        <v>0.4639558059773172</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>1</v>
@@ -1847,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392476428616</v>
+        <v>0.2952392303380292</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1856,24 +1856,24 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T17:40:10Z</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2958978404632886</v>
+        <v>0.2981081031604594</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>1</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.2952392476428616</v>
+        <v>0.2952392303380292</v>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2924925850816581</v>
+        <v>0.2924925750149914</v>
       </c>
       <c r="AH7" s="2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AM7" s="2" t="n"/>
       <c r="AN7" s="3" t="n">
-        <v>0.4666252367940658</v>
+        <v>0.4666251057178188</v>
       </c>
       <c r="AO7" s="2" t="n">
         <v>1</v>
@@ -1942,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="AR7" s="3" t="n">
-        <v>-0.0608672238419079</v>
+        <v>-0.06086749377492051</v>
       </c>
       <c r="AS7" s="3" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +9.8%, 3m +17.0%, 6m +19.8%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +10.9%, 3m +16.5%, 6m +17.2%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>68.63500000000001</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>68.20999999999999</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.006230757953379351</v>
+        <v>0.006890485266090263</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T17:40:10Z</t>
+          <t>2026-10-28T20:14:57Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.02491888013570387</v>
+        <v>0.02554606304141482</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.009767634482227505</v>
+        <v>-0.009161461033211693</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.03014201857428755</v>
+        <v>-0.03014194957711602</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.01403530329023694</v>
+        <v>-0.01343174260882929</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.007107599484206473</v>
+        <v>-0.006499868366606432</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.02100759542351693</v>
+        <v>0.02163253533314102</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.001081742075063619</v>
+        <v>-0.000470322641331955</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.004296483646738736</v>
+        <v>0.004296411608788464</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
@@ -2055,17 +2055,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-28T17:39:15Z</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="AN8" s="4" t="n">
-        <v>-0.02969137366034236</v>
+        <v>-0.02969144252962053</v>
       </c>
       <c r="AO8" t="n">
         <v>7</v>
@@ -2140,14 +2140,14 @@
         <v>0</v>
       </c>
       <c r="AR8" s="4" t="n">
-        <v>-0.01805009579008054</v>
+        <v>-0.01805023516165016</v>
       </c>
       <c r="AS8" s="4" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +2.1%, 3m -0.6%, 6m -1.6%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +2.2%, 3m -0.6%, 6m -1.3%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>106.195</v>
+        <v>106.26</v>
       </c>
       <c r="AW8" t="n">
         <v>106.31</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>-0.001081742075063619</v>
+        <v>-0.000470322641331955</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-28T17:39:15Z</t>
+          <t>2026-10-28T20:10:00Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1059580624273078</v>
+        <v>0.1040584436323451</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07977688375310654</v>
+        <v>0.07792223434782808</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.06642340803510183</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05432814197754432</v>
+        <v>0.05251720391162618</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.0344705046197582</v>
+        <v>0.03269367448471927</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.01252173913043486</v>
+        <v>0.01078260869565217</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.0003434065934065922</v>
+        <v>-0.002060439560439664</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2252,17 +2252,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-28T17:39:33Z</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +1.5%, 3m +2.5%, 6m +5.8%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +1.1%, 3m +3.3%, 6m +5.3%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>29.11</v>
+        <v>29.06</v>
       </c>
       <c r="AW9" t="n">
         <v>29.12</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>-0.0003434065934065922</v>
+        <v>-0.002060439560439664</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-28T17:39:33Z</t>
+          <t>2026-10-28T20:10:00Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05965901797760953</v>
+        <v>0.0596588478311959</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>0.03755769064619607</v>
@@ -2404,10 +2404,10 @@
         <v>0.03425033515224207</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.0184504787235702</v>
+        <v>0.01845055730871858</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.00924254607725028</v>
+        <v>0.009242468906688783</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>0.003197828786264845</v>
@@ -2441,17 +2441,17 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-28T17:40:12Z</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.7</v>
+        <v>100.697</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.68</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>0.0001986491855383576</v>
+        <v>0.0001688518077076484</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-28T17:40:12Z</t>
+          <t>2026-10-28T20:15:15Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>QQQ 36.1%, SPY 34.3%, XLE 29.6%</t>
+          <t>QQQ 36.0%, SPY 34.2%, XLE 29.8%</t>
         </is>
       </c>
     </row>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.008989793247840883</v>
+        <v>0.01061240512954709</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.04219382564168872</v>
+        <v>0.04386983475084305</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.08909208699493831</v>
+        <v>0.09084351577296568</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.02156031059856622</v>
+        <v>-0.01669535050750059</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.05738040636364339</v>
+        <v>0.06263787244331653</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.09371138805779888</v>
+        <v>0.09914949764358272</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.04554643094895283</v>
+        <v>0.04188865481416548</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.004380714655351836</v>
+        <v>-0.007863823920965629</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.02714208311531696</v>
+        <v>-0.0305455632148951</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.03312961947295567</v>
+        <v>-0.02434119459897099</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-0.01844044967652991</v>
+        <v>-0.009518506734542465</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1130902469993532</v>
+        <v>-0.1050286289259961</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.007078492585641083</v>
+        <v>0.007435555064881694</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.009502215002068159</v>
+        <v>-0.009151031258797238</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.002857400105478192</v>
+        <v>-0.002503762586779867</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1152908677283069</v>
+        <v>0.1093597660058498</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1710137027643897</v>
+        <v>0.1647862677602516</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.178060121859384</v>
+        <v>0.1717952908184039</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.02100759542351693</v>
+        <v>0.02163253533314102</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.007107599484206473</v>
+        <v>-0.006499868366606432</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.01403530329023694</v>
+        <v>-0.01343174260882929</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.01252173913043486</v>
+        <v>0.01078260869565217</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.0344705046197582</v>
+        <v>0.03269367448471927</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05432814197754432</v>
+        <v>0.05251720391162618</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3066,10 +3066,10 @@
         <v>0.003197828786264845</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.00924254607725028</v>
+        <v>0.009242468906688783</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.0184504787235702</v>
+        <v>0.01845055730871858</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1013819418474451</v>
+        <v>0.1013820490623591</v>
       </c>
     </row>
     <row r="6">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4252893549503975</v>
+        <v>0.4100859776700978</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1392244736669503</v>
+        <v>0.1311679881964611</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.127261517753601</v>
+        <v>0.1219657592985519</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.09084351577296568</v>
+        <v>0.07530686851277157</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.04386983475084305</v>
+        <v>0.03181166372139765</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.01061240512954709</v>
+        <v>0.008201880335156009</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.003443078762050744</v>
+        <v>-0.004434747704937125</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,12 +872,12 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29T14:00:08Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>771.77</v>
+        <v>768.885</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>769.65997</v>
+        <v>772.3099999999999</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>0.002741509344704518</v>
+        <v>-0.004434747704937125</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T20:15:02Z</t>
+          <t>2026-10-29T14:00:08Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5467160380088834</v>
+        <v>0.5144176518925518</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1606923374409872</v>
+        <v>0.1352306280665514</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1803995211860747</v>
+        <v>0.1743124683280328</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.09914949764358272</v>
+        <v>0.07329497574119603</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.06263787244331653</v>
+        <v>0.04056043235844453</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.01669535050750059</v>
+        <v>-0.03328061424496809</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.006045060658578905</v>
+        <v>-0.01441545733934213</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29T14:00:08Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>723.52</v>
+        <v>715.15</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>721.25</v>
+        <v>725.60999</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>0.003147313691507669</v>
+        <v>-0.01441544375650072</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T20:15:11Z</t>
+          <t>2026-10-29T14:00:08Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.02904184243077024</v>
+        <v>-0.03414986461407654</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.07446502965908253</v>
+        <v>-0.07403608004660367</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.11167573803172</v>
+        <v>-0.1190891666484106</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.0305455632148951</v>
+        <v>-0.02665134983834938</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.007863823920965629</v>
+        <v>0.001846333837173031</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.04188865481416548</v>
+        <v>0.0511437535969379</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.005512679162072653</v>
+        <v>0.005432769477713428</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29T14:00:09Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +4.2%, 3m -0.8%, 6m -3.1%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +3.9%, 3m -1.0%, 6m -3.3%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>81</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>81.63</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>-0.007717750826901848</v>
+        <v>0.005432769477713428</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-28T20:15:04Z</t>
+          <t>2026-10-29T14:00:09Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.2086905878927103</v>
+        <v>0.2050251584656604</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.01787417236587552</v>
+        <v>0.0121576376310446</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.04326857578812571</v>
+        <v>0.0451726219880344</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1050286289259961</v>
+        <v>-0.1294670254449323</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>-0.009518506734542465</v>
+        <v>-0.007347795661301615</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.02434119459897099</v>
+        <v>-0.03158806848020157</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.00346513377028046</v>
+        <v>-0.01258333110224619</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29T14:00:08Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>372.9955</v>
+        <v>368.81</v>
       </c>
       <c r="AW5" t="n">
-        <v>372.28</v>
+        <v>373.51001</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>0.001921940474911343</v>
+        <v>-0.01258335753839646</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-28T20:14:49Z</t>
+          <t>2026-10-29T14:00:08Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07494931345667788</v>
+        <v>0.07216149091337387</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01243793911558044</v>
+        <v>0.01350072438681371</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.004965463076570309</v>
+        <v>0.004005135679763461</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.002503762586779867</v>
+        <v>-0.005542224213649249</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.009151031258797238</v>
+        <v>-0.009211969265486508</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.007435555064881694</v>
+        <v>0.009457709298091643</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.0001288659793813318</v>
+        <v>6.444129398119891e-05</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29T14:00:08Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
+        <v>77.595</v>
+      </c>
+      <c r="AW6" t="n">
         <v>77.59</v>
       </c>
-      <c r="AW6" t="n">
-        <v>77.59999999999999</v>
-      </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.0001288659793813318</v>
+        <v>6.444129398119891e-05</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-28T20:13:46Z</t>
+          <t>2026-10-29T14:00:08Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7206985033923081</v>
+        <v>0.7423728409065469</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.5907681000129639</v>
+        <v>0.6230615150135663</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4339514995576066</v>
+        <v>0.4481108831181535</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.1717952908184039</v>
+        <v>0.1708262543633019</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1647862677602516</v>
+        <v>0.1643949932636282</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1093597660058498</v>
+        <v>0.1208130081300813</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.00087963641694766</v>
+        <v>0.0070124178232287</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29T14:00:10Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +10.9%, 3m +16.5%, 6m +17.2%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +11.2%, 3m +16.8%, 6m +17.5%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>68.68000000000001</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>68.20999999999999</v>
+        <v>68.45</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.006890485266090263</v>
+        <v>0.0070124178232287</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T20:14:57Z</t>
+          <t>2026-10-29T14:00:10Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.02554606304141482</v>
+        <v>0.02585241185526033</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.009161461033211693</v>
+        <v>-0.007954266595279869</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.03014194957711602</v>
+        <v>-0.03064157686379809</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.01343174260882929</v>
+        <v>-0.01294191407832135</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.006499868366606432</v>
+        <v>-0.003472247751530211</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.02163253533314102</v>
+        <v>0.02340445982314487</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.000470322641331955</v>
+        <v>0.002023338979860512</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29T14:00:03Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
+        <v>106.475</v>
+      </c>
+      <c r="AW8" t="n">
         <v>106.26</v>
       </c>
-      <c r="AW8" t="n">
-        <v>106.31</v>
-      </c>
       <c r="AX8" s="4" t="n">
-        <v>-0.000470322641331955</v>
+        <v>0.002023338979860512</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-28T20:10:00Z</t>
+          <t>2026-10-29T14:00:03Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1040584436323451</v>
+        <v>0.1017453505263002</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07792223434782808</v>
+        <v>0.07999517810531365</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.06642340803510183</v>
+        <v>0.06793130345729081</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05251720391162618</v>
+        <v>0.06341374269005851</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.03269367448471927</v>
+        <v>0.03283635072772451</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.01078260869565217</v>
+        <v>0.01129648939867911</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.002060439560439664</v>
+        <v>0.001204404679972404</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29T13:57:32Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
+        <v>29.095</v>
+      </c>
+      <c r="AW9" t="n">
         <v>29.06</v>
       </c>
-      <c r="AW9" t="n">
-        <v>29.12</v>
-      </c>
       <c r="AX9" s="4" t="n">
-        <v>-0.002060439560439664</v>
+        <v>0.001204404679972404</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-28T20:10:00Z</t>
+          <t>2026-10-29T13:57:32Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.0596588478311959</v>
+        <v>0.0595546974140837</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03755769064619607</v>
+        <v>0.03745574389873019</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03425033515224207</v>
+        <v>0.03414768641485089</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01845055730871858</v>
+        <v>0.01845156867967912</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009242468906688783</v>
+        <v>0.009043065151826069</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003197828786264845</v>
+        <v>0.003198825010523931</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0001986491855383576</v>
+        <v>9.930486595255417e-07</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29T14:00:11Z</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.697</v>
+        <v>100.7001</v>
       </c>
       <c r="AW10" s="5" t="n">
-        <v>100.68</v>
+        <v>100.7</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>0.0001688518077076484</v>
+        <v>9.930486595255417e-07</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-28T20:15:15Z</t>
+          <t>2026-10-29T14:00:11Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.01061240512954709</v>
+        <v>0.008201880335156009</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.04386983475084305</v>
+        <v>0.03181166372139765</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.09084351577296568</v>
+        <v>0.07530686851277157</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.01669535050750059</v>
+        <v>-0.03328061424496809</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.06263787244331653</v>
+        <v>0.04056043235844453</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.09914949764358272</v>
+        <v>0.07329497574119603</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.04188865481416548</v>
+        <v>0.0511437535969379</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.007863823920965629</v>
+        <v>0.001846333837173031</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.0305455632148951</v>
+        <v>-0.02665134983834938</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.02434119459897099</v>
+        <v>-0.03158806848020157</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-0.009518506734542465</v>
+        <v>-0.007347795661301615</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1050286289259961</v>
+        <v>-0.1294670254449323</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.007435555064881694</v>
+        <v>0.009457709298091643</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.009151031258797238</v>
+        <v>-0.009211969265486508</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.002503762586779867</v>
+        <v>-0.005542224213649249</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1093597660058498</v>
+        <v>0.1208130081300813</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1647862677602516</v>
+        <v>0.1643949932636282</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.1717952908184039</v>
+        <v>0.1708262543633019</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.02163253533314102</v>
+        <v>0.02340445982314487</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.006499868366606432</v>
+        <v>-0.003472247751530211</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.01343174260882929</v>
+        <v>-0.01294191407832135</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.01078260869565217</v>
+        <v>0.01129648939867911</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.03269367448471927</v>
+        <v>0.03283635072772451</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05251720391162618</v>
+        <v>0.06341374269005851</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003197828786264845</v>
+        <v>0.003198825010523931</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009242468906688783</v>
+        <v>0.009043065151826069</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01845055730871858</v>
+        <v>0.01845156867967912</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4100859776700978</v>
+        <v>0.4087563739792845</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1311679881964611</v>
+        <v>0.130101382928518</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0.1219657592985519</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.07530686851277157</v>
+        <v>0.07429293602654585</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.03181166372139765</v>
+        <v>0.03083874390088082</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.008201880335156009</v>
+        <v>0.007251222742352015</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.004434747704937125</v>
+        <v>-0.00537348991985076</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T14:00:08Z</t>
+          <t>2026-10-29T17:40:08Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>768.885</v>
+        <v>768.16</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>772.3099999999999</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.004434747704937125</v>
+        <v>-0.00537348991985076</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T14:00:08Z</t>
+          <t>2026-10-29T17:40:08Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5144176518925518</v>
+        <v>0.5126388490853229</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1352306280665514</v>
+        <v>0.1338972102834626</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0.1743124683280328</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.07329497574119603</v>
+        <v>0.07203430625979701</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.04056043235844453</v>
+        <v>0.0393382121764112</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.03328061424496809</v>
+        <v>-0.03441610230206693</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.01441545733934213</v>
+        <v>-0.01557310400904077</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T14:00:08Z</t>
+          <t>2026-10-29T17:40:08Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>715.15</v>
+        <v>714.3099999999999</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>725.60999</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.01441544375650072</v>
+        <v>-0.01557309044215349</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T14:00:08Z</t>
+          <t>2026-10-29T17:40:08Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.03414986461407654</v>
+        <v>-0.0368779197674447</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.07403608004660367</v>
+        <v>-0.07665147611180423</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>-0.1190891666484106</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.02665134983834938</v>
+        <v>-0.02940058463556394</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.001846333837173031</v>
+        <v>-0.0009833930052997042</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.0511437535969379</v>
+        <v>0.04817478560814625</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.005432769477713428</v>
+        <v>0.002592912705272399</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-29T14:00:09Z</t>
+          <t>2026-10-29T17:40:07Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>81.43000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="AW4" t="n">
         <v>80.98999999999999</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>0.005432769477713428</v>
+        <v>0.002592912705272399</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-29T14:00:09Z</t>
+          <t>2026-10-29T17:40:07Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.2050251584656604</v>
+        <v>0.2022152519113898</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.0121576376310446</v>
+        <v>0.009797464185740123</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.0451726219880344</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1294670254449323</v>
+        <v>-0.1314969551055092</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>-0.007347795661301615</v>
+        <v>-0.009662485869623816</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.03158806848020157</v>
+        <v>-0.03384623463921854</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.01258333110224619</v>
+        <v>-0.01488581296350833</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-29T14:00:08Z</t>
+          <t>2026-10-29T17:40:07Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>368.81</v>
+        <v>367.95</v>
       </c>
       <c r="AW5" t="n">
         <v>373.51001</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.01258335753839646</v>
+        <v>-0.01488583933801413</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-29T14:00:08Z</t>
+          <t>2026-10-29T17:40:07Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07216149091337387</v>
+        <v>0.07057248941256788</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01350072438681371</v>
+        <v>0.01199866132470317</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>0.004005135679763461</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.005542224213649249</v>
+        <v>-0.007016064592738513</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.009211969265486508</v>
+        <v>-0.01068037088330298</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.009457709298091643</v>
+        <v>0.007961638203700661</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.444129398119891e-05</v>
+        <v>-0.001417708467586043</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-29T14:00:08Z</t>
+          <t>2026-10-29T17:40:00Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.595</v>
+        <v>77.48</v>
       </c>
       <c r="AW6" t="n">
         <v>77.59</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>6.444129398119891e-05</v>
+        <v>-0.001417708467586043</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-29T14:00:08Z</t>
+          <t>2026-10-29T17:40:00Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7423728409065469</v>
+        <v>0.7256897410226308</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6230615150135663</v>
+        <v>0.6075208128532739</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.4481108831181535</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.1708262543633019</v>
+        <v>0.1596156736599827</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1643949932636282</v>
+        <v>0.1532459914421569</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1208130081300813</v>
+        <v>0.1100813008130082</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.0070124178232287</v>
+        <v>-0.002629656683710846</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T14:00:10Z</t>
+          <t>2026-10-29T17:40:10Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>68.93000000000001</v>
+        <v>68.27</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>68.45</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.0070124178232287</v>
+        <v>-0.002629656683710846</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T14:00:10Z</t>
+          <t>2026-10-29T17:40:10Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.02585241185526033</v>
+        <v>0.02445538344747433</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.007954266595279869</v>
+        <v>-0.009305256323795197</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>-0.03064157686379809</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.01294191407832135</v>
+        <v>-0.01428611151864667</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.003472247751530211</v>
+        <v>-0.004829341192018832</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.02340445982314487</v>
+        <v>0.02201076509034983</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.002023338979860512</v>
+        <v>0.0006587615283266679</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-29T14:00:03Z</t>
+          <t>2026-10-29T17:40:07Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>106.475</v>
+        <v>106.33</v>
       </c>
       <c r="AW8" t="n">
         <v>106.26</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>0.002023338979860512</v>
+        <v>0.0006587615283266679</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-29T14:00:03Z</t>
+          <t>2026-10-29T17:40:07Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1017453505263002</v>
+        <v>0.09909464853156424</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07999517810531365</v>
+        <v>0.07739680510420111</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.06793130345729081</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.06341374269005851</v>
+        <v>0.06085526315789469</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.03283635072772451</v>
+        <v>0.03035143769968029</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.01129648939867911</v>
+        <v>0.008863399374348324</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.001204404679972404</v>
+        <v>-0.001204404679972515</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-29T13:57:32Z</t>
+          <t>2026-10-29T17:38:59Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>29.095</v>
+        <v>29.025</v>
       </c>
       <c r="AW9" t="n">
         <v>29.06</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>0.001204404679972404</v>
+        <v>-0.001204404679972515</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-29T13:57:32Z</t>
+          <t>2026-10-29T17:38:59Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.0595546974140837</v>
+        <v>0.05955574960241061</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03745574389873019</v>
+        <v>0.03745677414174264</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0.03414768641485089</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01845156867967912</v>
+        <v>0.01845258005063966</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009043065151826069</v>
+        <v>0.009044067179694082</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003198825010523931</v>
+        <v>0.003199821234782796</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>9.930486595255417e-07</v>
+        <v>1.986097318606994e-06</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-29T14:00:11Z</t>
+          <t>2026-10-29T17:40:09Z</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.7001</v>
+        <v>100.7002</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.7</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>9.930486595255417e-07</v>
+        <v>1.986097318606994e-06</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-29T14:00:11Z</t>
+          <t>2026-10-29T17:40:09Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.008201880335156009</v>
+        <v>0.007251222742352015</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.03181166372139765</v>
+        <v>0.03083874390088082</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.07530686851277157</v>
+        <v>0.07429293602654585</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.03328061424496809</v>
+        <v>-0.03441610230206693</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.04056043235844453</v>
+        <v>0.0393382121764112</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.07329497574119603</v>
+        <v>0.07203430625979701</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.0511437535969379</v>
+        <v>0.04817478560814625</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.001846333837173031</v>
+        <v>-0.0009833930052997042</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.02665134983834938</v>
+        <v>-0.02940058463556394</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.03158806848020157</v>
+        <v>-0.03384623463921854</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-0.007347795661301615</v>
+        <v>-0.009662485869623816</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1294670254449323</v>
+        <v>-0.1314969551055092</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.009457709298091643</v>
+        <v>0.007961638203700661</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.009211969265486508</v>
+        <v>-0.01068037088330298</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.005542224213649249</v>
+        <v>-0.007016064592738513</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1208130081300813</v>
+        <v>0.1100813008130082</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1643949932636282</v>
+        <v>0.1532459914421569</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.1708262543633019</v>
+        <v>0.1596156736599827</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.02340445982314487</v>
+        <v>0.02201076509034983</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.003472247751530211</v>
+        <v>-0.004829341192018832</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.01294191407832135</v>
+        <v>-0.01428611151864667</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.01129648939867911</v>
+        <v>0.008863399374348324</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.03283635072772451</v>
+        <v>0.03035143769968029</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.06341374269005851</v>
+        <v>0.06085526315789469</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003198825010523931</v>
+        <v>0.003199821234782796</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009043065151826069</v>
+        <v>0.009044067179694082</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01845156867967912</v>
+        <v>0.01845258005063966</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4087563739792845</v>
+        <v>0.4109569393947285</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.130101382928518</v>
+        <v>0.131866798544424</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0.1219657592985519</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.07429293602654585</v>
+        <v>0.07597116910719559</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.03083874390088082</v>
+        <v>0.0324490939486326</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.007251222742352015</v>
+        <v>0.008824724964924036</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.00537348991985076</v>
+        <v>-0.003819709702062579</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.1609549765152376</v>
+        <v>0.1609548690014375</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>3</v>
@@ -858,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512453330066</v>
+        <v>0.3464512165360852</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -867,24 +867,24 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T17:40:08Z</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.3418200038008798</v>
+        <v>0.3411078150596467</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>0.3464512453330066</v>
+        <v>0.3464512165360852</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>0.3430182213596835</v>
+        <v>0.3430182165853097</v>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
@@ -953,14 +953,14 @@
         <v>0</v>
       </c>
       <c r="AR2" s="3" t="n">
-        <v>0.005238837446254196</v>
+        <v>0.005238944661168254</v>
       </c>
       <c r="AS2" s="3" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +1.1%, 3m +4.4%, 6m +9.1%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +0.9%, 3m +3.2%, 6m +7.6%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>768.16</v>
+        <v>765.45</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>772.3099999999999</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.00537348991985076</v>
+        <v>-0.008882443578355659</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T17:40:08Z</t>
+          <t>2026-10-29T20:15:06Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5126388490853229</v>
+        <v>0.5148199022517757</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1338972102834626</v>
+        <v>0.1355321244511831</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1743124683280328</v>
+        <v>0.1743123545520335</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.07203430625979701</v>
+        <v>0.07358012717151263</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.0393382121764112</v>
+        <v>0.04083688692342813</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.03441610230206693</v>
+        <v>-0.03302377766062414</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.01557310400904077</v>
+        <v>-0.01415360868786264</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1057,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095243289641</v>
+        <v>0.3583095243242682</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T17:40:08Z</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.3600718930386608</v>
+        <v>0.3586446953345716</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0.3583095243289641</v>
+        <v>0.3583095243242682</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>0.364489203625325</v>
+        <v>0.3644891882663687</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1152,14 +1152,14 @@
         <v>0</v>
       </c>
       <c r="AR3" s="3" t="n">
-        <v>0.0349080422428556</v>
+        <v>0.03490779891624962</v>
       </c>
       <c r="AS3" s="3" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -1.7%, 3m +6.3%, 6m +9.9%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -3.3%, 3m +4.1%, 6m +7.4%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>714.3099999999999</v>
+        <v>705.8099999999999</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>725.60999</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.01557309044215349</v>
+        <v>-0.02728737238030599</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T17:40:08Z</t>
+          <t>2026-10-29T20:15:06Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.0368779197674447</v>
+        <v>-0.03296375367782967</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.07665147611180423</v>
+        <v>-0.07289895132260349</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>-0.1190891666484106</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.02940058463556394</v>
+        <v>-0.02545611923544844</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.0009833930052997042</v>
+        <v>0.00307664985563938</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.04817478560814625</v>
+        <v>0.05243460924423848</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.002592912705272399</v>
+        <v>0.006667489813557248</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-29T17:40:07Z</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +3.9%, 3m -1.0%, 6m -3.3%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +5.2%, 3m +0.3%, 6m -2.5%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>81.2</v>
+        <v>81.73</v>
       </c>
       <c r="AW4" t="n">
         <v>80.98999999999999</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>0.002592912705272399</v>
+        <v>0.009136930485245109</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-29T17:40:07Z</t>
+          <t>2026-10-29T20:14:49Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.2022152519113898</v>
+        <v>0.2042409984970266</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.009797464185740123</v>
+        <v>0.01149898457654097</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.0451726219880344</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1314969551055092</v>
+        <v>-0.1300335174432329</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>-0.009662485869623816</v>
+        <v>-0.007993755719438056</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.03384623463921854</v>
+        <v>-0.03221825438504355</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.01488581296350833</v>
+        <v>-0.01322588417980775</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-29T17:40:07Z</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -2.4%, 3m -1.0%, 6m -10.5%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -3.2%, 3m -0.8%, 6m -13.0%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>367.95</v>
+        <v>368.9348</v>
       </c>
       <c r="AW5" t="n">
         <v>373.51001</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.01488583933801413</v>
+        <v>-0.01224922994701005</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-29T17:40:07Z</t>
+          <t>2026-10-29T20:14:55Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07057248941256788</v>
+        <v>0.0719544558555707</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01199866132470317</v>
+        <v>0.01330480311784288</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>0.004005135679763461</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.007016064592738513</v>
+        <v>-0.005734464263095762</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01068037088330298</v>
+        <v>-0.009403499911288749</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.007961638203700661</v>
+        <v>0.009262569590127612</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.001417708467586043</v>
+        <v>-0.0001288825879623978</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715196348622696</v>
+        <v>0.0371520673392467</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1659,17 +1659,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-29T17:40:00Z</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1744,14 +1744,14 @@
         <v>-1</v>
       </c>
       <c r="AR6" s="4" t="n">
-        <v>-0.009332190901998993</v>
+        <v>-0.009332293920931045</v>
       </c>
       <c r="AS6" s="4" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +0.7%, 3m -0.9%, 6m -0.3%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +0.9%, 3m -0.9%, 6m -0.6%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.48</v>
+        <v>77.55</v>
       </c>
       <c r="AW6" t="n">
         <v>77.59</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.001417708467586043</v>
+        <v>-0.0005155303518495913</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-29T17:40:00Z</t>
+          <t>2026-10-29T20:14:35Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7256897410226308</v>
+        <v>0.7368116401183575</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6075208128532739</v>
+        <v>0.6178812809601353</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.4481108831181535</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.1596156736599827</v>
+        <v>0.1670893185068314</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1532459914421569</v>
+        <v>0.1606786593231375</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1100813008130082</v>
+        <v>0.1172357723577235</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.002629656683710846</v>
+        <v>0.003798392987582</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.4639558059773172</v>
+        <v>0.4639560631420809</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>1</v>
@@ -1847,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392303380292</v>
+        <v>0.2952392591396466</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1856,24 +1856,24 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T17:40:10Z</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2981081031604594</v>
+        <v>0.3002474896057817</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>1</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.2952392303380292</v>
+        <v>0.2952392591396466</v>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2924925750149914</v>
+        <v>0.2924925951483215</v>
       </c>
       <c r="AH7" s="2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AM7" s="2" t="n"/>
       <c r="AN7" s="3" t="n">
-        <v>0.4666251057178188</v>
+        <v>0.4666253678703363</v>
       </c>
       <c r="AO7" s="2" t="n">
         <v>1</v>
@@ -1942,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="AR7" s="3" t="n">
-        <v>-0.06086749377492051</v>
+        <v>-0.06086723162240304</v>
       </c>
       <c r="AS7" s="3" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +11.2%, 3m +16.8%, 6m +17.5%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +11.7%, 3m +16.1%, 6m +16.7%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>68.27</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>68.45</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>-0.002629656683710846</v>
+        <v>0.009495982468955333</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T17:40:10Z</t>
+          <t>2026-10-29T20:13:34Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.02445538344747433</v>
+        <v>0.0255153488662887</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.009305256323795197</v>
+        <v>-0.008280297068460785</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.03064157686379809</v>
+        <v>-0.0306415079575596</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.01428611151864667</v>
+        <v>-0.01326644531812371</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.004829341192018832</v>
+        <v>-0.00379982203026874</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.02201076509034983</v>
+        <v>0.02306805074971163</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0006587615283266679</v>
+        <v>0.001693958215697178</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.004296411608788464</v>
+        <v>0.004296483646738736</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
@@ -2055,17 +2055,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-29T17:40:07Z</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="AN8" s="4" t="n">
-        <v>-0.02969144252962053</v>
+        <v>-0.02969137366034236</v>
       </c>
       <c r="AO8" t="n">
         <v>7</v>
@@ -2140,14 +2140,14 @@
         <v>0</v>
       </c>
       <c r="AR8" s="4" t="n">
-        <v>-0.01805023516165016</v>
+        <v>-0.01805023679467355</v>
       </c>
       <c r="AS8" s="4" t="n">
         <v>0.09777622901307459</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +2.2%, 3m -0.6%, 6m -1.3%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +2.3%, 3m -0.4%, 6m -1.3%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>106.33</v>
+        <v>106.6</v>
       </c>
       <c r="AW8" t="n">
         <v>106.26</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>0.0006587615283266679</v>
+        <v>0.003199698851872768</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-29T17:40:07Z</t>
+          <t>2026-10-29T20:05:05Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.09909464853156424</v>
+        <v>0.09966265610186475</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07739680510420111</v>
+        <v>0.07795359931872525</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.06793130345729081</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.06085526315789469</v>
+        <v>0.06140350877192979</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.03035143769968029</v>
+        <v>0.03088391906283272</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.008863399374348324</v>
+        <v>0.00938477580813335</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.001204404679972515</v>
+        <v>-0.0006882312456985007</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2252,17 +2252,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-29T17:38:59Z</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +1.1%, 3m +3.3%, 6m +5.3%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +0.9%, 3m +3.1%, 6m +6.1%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>29.025</v>
+        <v>29.015</v>
       </c>
       <c r="AW9" t="n">
         <v>29.06</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>-0.001204404679972515</v>
+        <v>-0.00154852030282171</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-29T17:38:59Z</t>
+          <t>2026-10-29T20:12:03Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05955574960241061</v>
+        <v>0.05965903418797103</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03745677414174264</v>
+        <v>0.03755765640358799</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03414768641485089</v>
+        <v>0.0341476051294991</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01845258005063966</v>
+        <v>0.018551694404777</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009044067179694082</v>
+        <v>0.009142343058342606</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003199821234782796</v>
+        <v>0.003297451212162184</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>1.986097318606994e-06</v>
+        <v>9.930486593834331e-05</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-29T17:40:09Z</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AT10" s="5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +0.3%, 3m +0.9%, 6m +1.8%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +0.3%, 3m +0.9%, 6m +1.9%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU10" s="5" t="inlineStr">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.7002</v>
+        <v>100.7</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.7</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>1.986097318606994e-06</v>
+        <v>0</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-29T17:40:09Z</t>
+          <t>2026-10-29T20:15:06Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>QQQ 36.0%, SPY 34.2%, XLE 29.8%</t>
+          <t>QQQ 35.9%, SPY 34.1%, XLE 30.0%</t>
         </is>
       </c>
     </row>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.007251222742352015</v>
+        <v>0.008824724964924036</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.03083874390088082</v>
+        <v>0.0324490939486326</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.07429293602654585</v>
+        <v>0.07597116910719559</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.03441610230206693</v>
+        <v>-0.03302377766062414</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.0393382121764112</v>
+        <v>0.04083688692342813</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.07203430625979701</v>
+        <v>0.07358012717151263</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.04817478560814625</v>
+        <v>0.05243460924423848</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.0009833930052997042</v>
+        <v>0.00307664985563938</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.02940058463556394</v>
+        <v>-0.02545611923544844</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.03384623463921854</v>
+        <v>-0.03221825438504355</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-0.009662485869623816</v>
+        <v>-0.007993755719438056</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1314969551055092</v>
+        <v>-0.1300335174432329</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.007961638203700661</v>
+        <v>0.009262569590127612</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01068037088330298</v>
+        <v>-0.009403499911288749</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.007016064592738513</v>
+        <v>-0.005734464263095762</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1100813008130082</v>
+        <v>0.1172357723577235</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1532459914421569</v>
+        <v>0.1606786593231375</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.1596156736599827</v>
+        <v>0.1670893185068314</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.02201076509034983</v>
+        <v>0.02306805074971163</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.004829341192018832</v>
+        <v>-0.00379982203026874</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.01428611151864667</v>
+        <v>-0.01326644531812371</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.008863399374348324</v>
+        <v>0.00938477580813335</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.03035143769968029</v>
+        <v>0.03088391906283272</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.06085526315789469</v>
+        <v>0.06140350877192979</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003199821234782796</v>
+        <v>0.003297451212162184</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009044067179694082</v>
+        <v>0.009142343058342606</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01845258005063966</v>
+        <v>0.018551694404777</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.02933614706677878</v>
+        <v>0.02933625610116319</v>
       </c>
     </row>
     <row r="3">
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1013820490623591</v>
+        <v>0.1013819418474451</v>
       </c>
     </row>
     <row r="6">

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.4109569393947285</v>
+        <v>0.3951265820093859</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.131866798544424</v>
+        <v>0.1190743006084971</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1219657592985519</v>
+        <v>0.1234269015963703</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.07597116910719559</v>
+        <v>0.06138248131775303</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.0324490939486326</v>
+        <v>0.006928839601132664</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.008824724964924036</v>
+        <v>-0.00387439626173125</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.003819709702062579</v>
+        <v>-0.01082718103358637</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,12 +872,12 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30T14:00:08Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>765.45</v>
+        <v>761.03</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>772.3099999999999</v>
+        <v>769.35999</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.008882443578355659</v>
+        <v>-0.01082716817649965</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T20:15:06Z</t>
+          <t>2026-10-30T14:00:08Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5148199022517757</v>
+        <v>0.4785621476730058</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1355321244511831</v>
+        <v>0.1032450522878894</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1743123545520335</v>
+        <v>0.1726196068772043</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.07358012717151263</v>
+        <v>0.03778906109170888</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.04083688692342813</v>
+        <v>-0.001732060261481649</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.03302377766062414</v>
+        <v>-0.0591620284894141</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.01415360868786264</v>
+        <v>-0.02405848966924828</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30T14:00:09Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>705.8099999999999</v>
+        <v>698.13</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>725.60999</v>
+        <v>715.34003</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.02728737238030599</v>
+        <v>-0.02405853059837848</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T20:15:06Z</t>
+          <t>2026-10-30T14:00:09Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.03296375367782967</v>
+        <v>-0.02369840477227203</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.07289895132260349</v>
+        <v>-0.06211260603708535</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1190891666484106</v>
+        <v>-0.1073154585723792</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.02545611923544844</v>
+        <v>-0.02755840931384756</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.00307664985563938</v>
+        <v>0.001191616655901617</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.05243460924423848</v>
+        <v>0.05063698365718694</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.006667489813557248</v>
+        <v>0.001902073874094912</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30T14:00:09Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +5.2%, 3m +0.3%, 6m -2.5%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +5.2%, 3m +0.3%, 6m -2.6%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>81.73</v>
+        <v>81.645</v>
       </c>
       <c r="AW4" t="n">
-        <v>80.98999999999999</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>0.009136930485245109</v>
+        <v>0.001902073874094912</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-29T20:14:49Z</t>
+          <t>2026-10-30T14:00:09Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.2042409984970266</v>
+        <v>0.1828521578826086</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.01149898457654097</v>
+        <v>-0.01015151515151513</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.0451726219880344</v>
+        <v>0.05443526170798885</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1300335174432329</v>
+        <v>-0.1509168675268208</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>-0.007993755719438056</v>
+        <v>-0.03334588792338111</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.03221825438504355</v>
+        <v>-0.0612524819730379</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.01322588417980775</v>
+        <v>-0.02511056244404042</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30T14:00:09Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>368.9348</v>
+        <v>359.315</v>
       </c>
       <c r="AW5" t="n">
-        <v>373.51001</v>
+        <v>368.57001</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.01224922994701005</v>
+        <v>-0.02511058889463103</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-29T20:14:55Z</t>
+          <t>2026-10-30T14:00:09Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.0719544558555707</v>
+        <v>0.07552943489882424</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01330480311784288</v>
+        <v>0.01440363991016125</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.004005135679763461</v>
+        <v>0.007525216778707211</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.005734464263095762</v>
+        <v>-0.00894793241791525</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.009403499911288749</v>
+        <v>-0.01405018897500487</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.009262569590127612</v>
+        <v>0.006827048114434131</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.0001288825879623978</v>
+        <v>-0.001997937612786771</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30T14:00:08Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.55</v>
+        <v>77.425</v>
       </c>
       <c r="AW6" t="n">
-        <v>77.59</v>
+        <v>77.58</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.0005155303518495913</v>
+        <v>-0.001997937612786771</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-29T20:14:35Z</t>
+          <t>2026-10-30T14:00:08Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7368116401183575</v>
+        <v>0.8222930502678218</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6178812809601353</v>
+        <v>0.6391690013067177</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4481108831181535</v>
+        <v>0.4652964981740975</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.1670893185068314</v>
+        <v>0.2075744455390687</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1606786593231375</v>
+        <v>0.2001516441617484</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1172357723577235</v>
+        <v>0.1186602870813396</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.003798392987582</v>
+        <v>0.02081210886333884</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30T14:00:10Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>69.09999999999999</v>
+        <v>70.14</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>68.45</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.009495982468955333</v>
+        <v>0.02081210886333884</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T20:13:34Z</t>
+          <t>2026-10-30T14:00:10Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.0255153488662887</v>
+        <v>0.02647437214963588</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.008280297068460785</v>
+        <v>-0.0009224015767244076</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.0306415079575596</v>
+        <v>-0.0229805063373002</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.01326644531812371</v>
+        <v>-0.014297605103892</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.00379982203026874</v>
+        <v>-0.001824817518248145</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.02306805074971163</v>
+        <v>0.02257693413862527</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.001693958215697178</v>
+        <v>0.002113866967305533</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30T14:00:09Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>106.6</v>
+        <v>106.665</v>
       </c>
       <c r="AW8" t="n">
-        <v>106.26</v>
+        <v>106.44</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>0.003199698851872768</v>
+        <v>0.002113866967305533</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-29T20:05:05Z</t>
+          <t>2026-10-30T14:00:09Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.09966265610186475</v>
+        <v>0.09546215153879389</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07795359931872525</v>
+        <v>0.07161377565529925</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.06793130345729081</v>
+        <v>0.06884570149741576</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.06140350877192979</v>
+        <v>0.05928493250638445</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.03088391906283272</v>
+        <v>0.03070642527511525</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.00938477580813335</v>
+        <v>0.002589779005524928</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.0006882312456985007</v>
+        <v>-0.0001721763085399397</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30T14:00:05Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>29.015</v>
+        <v>29.035</v>
       </c>
       <c r="AW9" t="n">
-        <v>29.06</v>
+        <v>29.04</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>-0.00154852030282171</v>
+        <v>-0.0001721763085399397</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-29T20:12:03Z</t>
+          <t>2026-10-30T14:00:05Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05965903418797103</v>
+        <v>0.05960640875185041</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03755765640358799</v>
+        <v>0.03771214033825476</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.0341476051294991</v>
+        <v>0.03436418336590208</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.018551694404777</v>
+        <v>0.01841906598617715</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.009142343058342606</v>
+        <v>0.00922194543339061</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003297451212162184</v>
+        <v>0.003236729409421324</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>9.930486593834331e-05</v>
+        <v>0.0002482375136532156</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30T14:00:12Z</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>COMPLETED_SESSION</t>
+          <t>LIVE_PRICE_OVERLAY</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.7</v>
+        <v>100.735</v>
       </c>
       <c r="AW10" s="5" t="n">
-        <v>100.7</v>
+        <v>100.71</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>0</v>
+        <v>0.0002482375136532156</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-29T20:15:06Z</t>
+          <t>2026-10-30T14:00:12Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.008824724964924036</v>
+        <v>-0.00387439626173125</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.0324490939486326</v>
+        <v>0.006928839601132664</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.07597116910719559</v>
+        <v>0.06138248131775303</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.03302377766062414</v>
+        <v>-0.0591620284894141</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.04083688692342813</v>
+        <v>-0.001732060261481649</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.07358012717151263</v>
+        <v>0.03778906109170888</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.05243460924423848</v>
+        <v>0.05063698365718694</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.00307664985563938</v>
+        <v>0.001191616655901617</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.02545611923544844</v>
+        <v>-0.02755840931384756</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.03221825438504355</v>
+        <v>-0.0612524819730379</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-0.007993755719438056</v>
+        <v>-0.03334588792338111</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1300335174432329</v>
+        <v>-0.1509168675268208</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.009262569590127612</v>
+        <v>0.006827048114434131</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.009403499911288749</v>
+        <v>-0.01405018897500487</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.005734464263095762</v>
+        <v>-0.00894793241791525</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1172357723577235</v>
+        <v>0.1186602870813396</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1606786593231375</v>
+        <v>0.2001516441617484</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.1670893185068314</v>
+        <v>0.2075744455390687</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.02306805074971163</v>
+        <v>0.02257693413862527</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.00379982203026874</v>
+        <v>-0.001824817518248145</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.01326644531812371</v>
+        <v>-0.014297605103892</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.00938477580813335</v>
+        <v>0.002589779005524928</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.03088391906283272</v>
+        <v>0.03070642527511525</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.06140350877192979</v>
+        <v>0.05928493250638445</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003297451212162184</v>
+        <v>0.003236729409421324</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.009142343058342606</v>
+        <v>0.00922194543339061</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.018551694404777</v>
+        <v>0.01841906598617715</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.3951265820093859</v>
+        <v>0.3844206450043601</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1190743006084971</v>
+        <v>0.1104867364972879</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0.1234269015963703</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.06138248131775303</v>
+        <v>0.05323763329481612</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.006928839601132664</v>
+        <v>-0.0007981414945803511</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-0.00387439626173125</v>
+        <v>-0.01151847537271422</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.01082718103358637</v>
+        <v>-0.01841790579182689</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T14:00:08Z</t>
+          <t>2026-10-30T17:40:07Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>761.03</v>
+        <v>755.1900000000001</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>769.35999</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.01082716817649965</v>
+        <v>-0.01841789303340302</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T14:00:08Z</t>
+          <t>2026-10-30T17:40:07Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4785621476730058</v>
+        <v>0.458886954869542</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1032450522878894</v>
+        <v>0.0885641955194445</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0.1726196068772043</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.03778906109170888</v>
+        <v>0.02397922570640532</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0.001732060261481649</v>
+        <v>-0.01501598898560297</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.0591620284894141</v>
+        <v>-0.07168173793512389</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.02405848966924828</v>
+        <v>-0.03704532110604752</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T14:00:09Z</t>
+          <t>2026-10-30T17:40:08Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>698.13</v>
+        <v>688.84</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>715.34003</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.02405853059837848</v>
+        <v>-0.03704536149053472</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T14:00:09Z</t>
+          <t>2026-10-30T17:40:08Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.02369840477227203</v>
+        <v>-0.02549208765896627</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.06211260603708535</v>
+        <v>-0.06383571350348782</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>-0.1073154585723792</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.02755840931384756</v>
+        <v>-0.02934500051481403</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.001191616655901617</v>
+        <v>-0.0006477947287315544</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.05063698365718694</v>
+        <v>0.04870673015055993</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.001902073874094912</v>
+        <v>6.135722174516189e-05</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-30T14:00:09Z</t>
+          <t>2026-10-30T17:39:58Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>81.645</v>
+        <v>81.495</v>
       </c>
       <c r="AW4" t="n">
         <v>81.48999999999999</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>0.001902073874094912</v>
+        <v>6.135722174516189e-05</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-30T14:00:09Z</t>
+          <t>2026-10-30T17:39:58Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.1828521578826086</v>
+        <v>0.1719063765348785</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.01015151515151513</v>
+        <v>-0.01931129476584015</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.05443526170798885</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1509168675268208</v>
+        <v>-0.1587740441419727</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>-0.03334588792338111</v>
+        <v>-0.04229103333243645</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.0612524819730379</v>
+        <v>-0.06993938760581042</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.02511056244404042</v>
+        <v>-0.03413191523998149</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-30T14:00:09Z</t>
+          <t>2026-10-30T17:40:09Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>359.315</v>
+        <v>355.99</v>
       </c>
       <c r="AW5" t="n">
         <v>368.57001</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.02511058889463103</v>
+        <v>-0.03413194144580567</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-30T14:00:09Z</t>
+          <t>2026-10-30T17:40:09Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07552943489882424</v>
+        <v>0.07483487278393963</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01440363991016125</v>
+        <v>0.01374855199287994</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>0.007525216778707211</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.00894793241791525</v>
+        <v>-0.009587940210993739</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01405018897500487</v>
+        <v>-0.01468690180098164</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.006827048114434131</v>
+        <v>0.006176853055916753</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.001997937612786771</v>
+        <v>-0.002642433616911521</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-30T14:00:08Z</t>
+          <t>2026-10-30T17:40:09Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.425</v>
+        <v>77.375</v>
       </c>
       <c r="AW6" t="n">
         <v>77.58</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.001997937612786771</v>
+        <v>-0.002642433616911521</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-30T14:00:08Z</t>
+          <t>2026-10-30T17:40:09Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8222930502678218</v>
+        <v>0.8120306357417915</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6391690013067177</v>
+        <v>0.629937867067822</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.4652964981740975</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2075744455390687</v>
+        <v>0.2007738765914222</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.2001516441617484</v>
+        <v>0.1933928774174671</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1186602870813396</v>
+        <v>0.1123604465709729</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.02081210886333884</v>
+        <v>0.01506330956192703</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T14:00:10Z</t>
+          <t>2026-10-30T17:40:08Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>70.14</v>
+        <v>69.745</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>68.70999999999999</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.02081210886333884</v>
+        <v>0.01506330956192703</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T14:00:10Z</t>
+          <t>2026-10-30T17:40:08Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.02647437214963588</v>
+        <v>0.02643972809826245</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.0009224015767244076</v>
+        <v>-0.0009561209725368336</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>-0.0229805063373002</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.014297605103892</v>
+        <v>-0.01433087307953185</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.001824817518248145</v>
+        <v>-0.001858506457046549</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.02257693413862527</v>
+        <v>0.02254242162784004</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.002113866967305533</v>
+        <v>0.002080045095828709</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-30T14:00:09Z</t>
+          <t>2026-10-30T17:39:52Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>106.665</v>
+        <v>106.6614</v>
       </c>
       <c r="AW8" t="n">
         <v>106.44</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>0.002113866967305533</v>
+        <v>0.002080045095828709</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-30T14:00:09Z</t>
+          <t>2026-10-30T17:39:52Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.09546215153879389</v>
+        <v>0.09508486131956229</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07161377565529925</v>
+        <v>0.0712446991009148</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.06884570149741576</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05928493250638445</v>
+        <v>0.05892010215249899</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.03070642527511525</v>
+        <v>0.03035143769968029</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.002589779005524928</v>
+        <v>0.002244475138121427</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.0001721763085399397</v>
+        <v>-0.0005165289256198191</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-30T14:00:05Z</t>
+          <t>2026-10-30T17:39:35Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>29.035</v>
+        <v>29.025</v>
       </c>
       <c r="AW9" t="n">
         <v>29.04</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>-0.0001721763085399397</v>
+        <v>-0.0005165289256198191</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-30T14:00:05Z</t>
+          <t>2026-10-30T17:39:35Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-30T14:00:12Z</t>
+          <t>2026-10-30T17:40:07Z</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-30T14:00:12Z</t>
+          <t>2026-10-30T17:40:07Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>-0.00387439626173125</v>
+        <v>-0.01151847537271422</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.006928839601132664</v>
+        <v>-0.0007981414945803511</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.06138248131775303</v>
+        <v>0.05323763329481612</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.0591620284894141</v>
+        <v>-0.07168173793512389</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>-0.001732060261481649</v>
+        <v>-0.01501598898560297</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.03778906109170888</v>
+        <v>0.02397922570640532</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.05063698365718694</v>
+        <v>0.04870673015055993</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.001191616655901617</v>
+        <v>-0.0006477947287315544</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.02755840931384756</v>
+        <v>-0.02934500051481403</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.0612524819730379</v>
+        <v>-0.06993938760581042</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-0.03334588792338111</v>
+        <v>-0.04229103333243645</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1509168675268208</v>
+        <v>-0.1587740441419727</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.006827048114434131</v>
+        <v>0.006176853055916753</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01405018897500487</v>
+        <v>-0.01468690180098164</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.00894793241791525</v>
+        <v>-0.009587940210993739</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1186602870813396</v>
+        <v>0.1123604465709729</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.2001516441617484</v>
+        <v>0.1933928774174671</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.2075744455390687</v>
+        <v>0.2007738765914222</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.02257693413862527</v>
+        <v>0.02254242162784004</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.001824817518248145</v>
+        <v>-0.001858506457046549</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.014297605103892</v>
+        <v>-0.01433087307953185</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.002589779005524928</v>
+        <v>0.002244475138121427</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.03070642527511525</v>
+        <v>0.03035143769968029</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05928493250638445</v>
+        <v>0.05892010215249899</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>

--- a/Survivor_LATEST.xlsx
+++ b/Survivor_LATEST.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Survivor'!$A$1:$BA$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Weekly Review'!$A$17:$H$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Weekly History'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Weekly History'!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -815,25 +815,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.3844206450043601</v>
+        <v>0.3853924004635183</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1104867364972879</v>
+        <v>0.1112660873498461</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0.1234269015963703</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.05323763329481612</v>
+        <v>0.05397680614621292</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>-0.0007981414945803511</v>
+        <v>-9.689149788039142e-05</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-0.01151847537271422</v>
+        <v>-0.01082474901503949</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.01841790579182689</v>
+        <v>-0.01772902152438394</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>1</v>
@@ -858,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512165360852</v>
+        <v>0.3464512030450774</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -867,24 +867,24 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T17:40:07Z</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.3411078150596467</v>
+        <v>0.3413469661631208</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -895,16 +895,16 @@
         <v>1</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>0.3464512165360852</v>
+        <v>0.3464512030450774</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
           <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AE2" s="2" t="b">
@@ -914,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>0.3430182165853097</v>
+        <v>0.3413469661631208</v>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
       </c>
       <c r="AM2" s="2" t="n"/>
       <c r="AN2" s="3" t="n">
-        <v>0.1612111696568344</v>
+        <v>0.1234269015963703</v>
       </c>
       <c r="AO2" s="2" t="n">
         <v>3</v>
@@ -953,14 +953,14 @@
         <v>0</v>
       </c>
       <c r="AR2" s="3" t="n">
-        <v>0.005238944661168254</v>
+        <v>-0.03778426806046409</v>
       </c>
       <c r="AS2" s="3" t="n">
-        <v>0.09777622901307459</v>
+        <v>0.05458120009895451</v>
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +0.9%, 3m +3.2%, 6m +7.6%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -1.1%, 3m -0.0%, 6m +5.4%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>755.1900000000001</v>
+        <v>755.5841</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>769.35999</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>-0.01841789303340302</v>
+        <v>-0.01790564908372738</v>
       </c>
       <c r="AY2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T17:40:07Z</t>
+          <t>2026-10-30T20:15:08Z</t>
         </is>
       </c>
       <c r="AZ2" s="2" t="n"/>
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.458886954869542</v>
+        <v>0.464266488661129</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.0885641955194445</v>
+        <v>0.09257822729498555</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.1726196068772043</v>
+        <v>0.1726197199798927</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.02397922570640532</v>
+        <v>0.0277550041648198</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0.01501598898560297</v>
+        <v>-0.01138399986189276</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.07168173793512389</v>
+        <v>-0.06825869574006438</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.03704532110604752</v>
+        <v>-0.03349456202644896</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.1982245316673374</v>
+        <v>0.1982246540542743</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>2</v>
@@ -1057,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095243242682</v>
+        <v>0.358309549312061</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T17:40:08Z</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.3586446953345716</v>
+        <v>0.3572781867289219</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1094,16 +1094,16 @@
         <v>1</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0.3583095243242682</v>
+        <v>0.358309549312061</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
           <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AE3" s="2" t="b">
@@ -1113,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>0.3644891882663687</v>
+        <v>0.3572781867289219</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="AM3" s="2" t="n"/>
       <c r="AN3" s="3" t="n">
-        <v>0.2297182035126981</v>
+        <v>0.1726197199798927</v>
       </c>
       <c r="AO3" s="2" t="n">
         <v>2</v>
@@ -1152,14 +1152,14 @@
         <v>0</v>
       </c>
       <c r="AR3" s="3" t="n">
-        <v>0.03490779891624962</v>
+        <v>-0.05709848353280544</v>
       </c>
       <c r="AS3" s="3" t="n">
-        <v>0.09777622901307459</v>
+        <v>0.05458120009895451</v>
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -3.3%, 3m +4.1%, 6m +7.4%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -6.8%, 3m -1.1%, 6m +2.8%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>688.84</v>
+        <v>690.4853000000001</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>715.34003</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>-0.03704536149053472</v>
+        <v>-0.03474533642413369</v>
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T17:40:08Z</t>
+          <t>2026-10-30T20:15:08Z</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="n"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.02549208765896627</v>
+        <v>-0.0213664384552944</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.06383571350348782</v>
+        <v>-0.05987248393631173</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1073154585723792</v>
+        <v>-0.107315380335909</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.02934500051481403</v>
+        <v>-0.02523584075259078</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.0006477947287315544</v>
+        <v>0.003582851455925073</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.04870673015055993</v>
+        <v>0.05314631321580254</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>6.135722174516189e-05</v>
+        <v>0.004295005522150008</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-30T17:39:58Z</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X4" t="b">
@@ -1297,14 +1297,14 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="AN4" s="4" t="n">
-        <v>-0.1009058975858805</v>
+        <v>-0.107315380335909</v>
       </c>
       <c r="AO4" t="n">
         <v>8</v>
@@ -1350,14 +1350,14 @@
         <v>0</v>
       </c>
       <c r="AR4" s="4" t="n">
-        <v>-0.04101366149025232</v>
+        <v>-0.006409560717983709</v>
       </c>
       <c r="AS4" s="4" t="n">
-        <v>0.09777622901307459</v>
+        <v>0.05458120009895451</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +5.2%, 3m +0.3%, 6m -2.6%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +5.3%, 3m +0.4%, 6m -2.5%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1366,17 +1366,17 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>81.495</v>
+        <v>81.63</v>
       </c>
       <c r="AW4" t="n">
         <v>81.48999999999999</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>6.135722174516189e-05</v>
+        <v>0.001718002208860092</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2026-10-30T17:39:58Z</t>
+          <t>2026-10-30T20:15:01Z</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.1719063765348785</v>
+        <v>0.171215064028706</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.01931129476584015</v>
+        <v>-0.01988980716253452</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.05443526170798885</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.1587740441419727</v>
+        <v>-0.1592702868755613</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>-0.04229103333243645</v>
+        <v>-0.0428559898845875</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.06993938760581042</v>
+        <v>-0.07048803427735395</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.03413191523998149</v>
+        <v>-0.03470168489025161</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-30T17:40:09Z</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X5" t="b">
@@ -1494,14 +1494,14 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
@@ -1535,26 +1535,26 @@
         </is>
       </c>
       <c r="AN5" s="4" t="n">
-        <v>0.03819444444444442</v>
+        <v>0.05443526170798885</v>
       </c>
       <c r="AO5" t="n">
         <v>5</v>
       </c>
       <c r="AP5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR5" s="4" t="n">
-        <v>0.009876728447645311</v>
+        <v>0.01624081726354443</v>
       </c>
       <c r="AS5" s="4" t="n">
-        <v>0.09777622901307459</v>
+        <v>0.05458120009895451</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m -3.2%, 3m -0.8%, 6m -13.0%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m -7.0%, 3m -4.3%, 6m -15.9%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1563,17 +1563,17 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>355.99</v>
+        <v>355.78</v>
       </c>
       <c r="AW5" t="n">
         <v>368.57001</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>-0.03413194144580567</v>
+        <v>-0.03470171108061681</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2026-10-30T17:40:09Z</t>
+          <t>2026-10-30T20:14:38Z</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1607,25 +1607,25 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07483487278393963</v>
+        <v>0.07559877711645058</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.01374855199287994</v>
+        <v>0.01446894589232728</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.007525216778707211</v>
+        <v>0.007525015357354503</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.009587940210993739</v>
+        <v>-0.008884028428457813</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01468690180098164</v>
+        <v>-0.01398651769240711</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.006176853055916753</v>
+        <v>0.006892067620286157</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.002642433616911521</v>
+        <v>-0.001933488012374251</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.0371520673392467</v>
+        <v>0.03715195976610053</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1659,17 +1659,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-30T17:40:09Z</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X6" t="b">
@@ -1691,14 +1691,14 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
@@ -1732,26 +1732,26 @@
         </is>
       </c>
       <c r="AN6" s="4" t="n">
-        <v>0.01937561378969899</v>
+        <v>0.007525015357354503</v>
       </c>
       <c r="AO6" t="n">
         <v>6</v>
       </c>
       <c r="AP6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AR6" s="4" t="n">
-        <v>-0.009332293920931045</v>
+        <v>-0.01185070066857885</v>
       </c>
       <c r="AS6" s="4" t="n">
-        <v>0.09777622901307459</v>
+        <v>0.05458120009895451</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +0.9%, 3m -0.9%, 6m -0.6%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +0.7%, 3m -1.4%, 6m -0.9%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1760,17 +1760,17 @@
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>77.375</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="AW6" t="n">
         <v>77.58</v>
       </c>
       <c r="AX6" s="4" t="n">
-        <v>-0.002642433616911521</v>
+        <v>-0.001933488012374251</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2026-10-30T17:40:09Z</t>
+          <t>2026-10-30T20:12:09Z</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8120306357417915</v>
+        <v>0.81917535471561</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.629937867067822</v>
+        <v>0.6363644601975456</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4652964981740975</v>
+        <v>0.4652963675290791</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2007738765914222</v>
+        <v>0.2055084499094038</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1933928774174671</v>
+        <v>0.1980983479356375</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1123604465709729</v>
+        <v>0.1167464114832535</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.01506330956192703</v>
+        <v>0.01906563818949203</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1847,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392591396466</v>
+        <v>0.2952392476428616</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1856,24 +1856,24 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T17:40:08Z</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.3002474896057817</v>
+        <v>0.3013748471079573</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -1884,16 +1884,16 @@
         <v>1</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.2952392591396466</v>
+        <v>0.2952392476428616</v>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
           <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="AD7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AE7" s="2" t="b">
@@ -1903,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2924925951483215</v>
+        <v>0.3013748471079573</v>
       </c>
       <c r="AH7" s="2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AM7" s="2" t="n"/>
       <c r="AN7" s="3" t="n">
-        <v>0.4666253678703363</v>
+        <v>0.4652963675290791</v>
       </c>
       <c r="AO7" s="2" t="n">
         <v>1</v>
@@ -1942,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="AR7" s="3" t="n">
-        <v>-0.06086723162240304</v>
+        <v>-0.001328869264986654</v>
       </c>
       <c r="AS7" s="3" t="n">
-        <v>0.09777622901307459</v>
+        <v>0.05458120009895451</v>
       </c>
       <c r="AT7" s="2" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +11.7%, 3m +16.1%, 6m +16.7%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +11.7%, 3m +19.8%, 6m +20.6%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU7" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>69.745</v>
+        <v>69.98</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>68.70999999999999</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>0.01506330956192703</v>
+        <v>0.01848348129820998</v>
       </c>
       <c r="AY7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T17:40:08Z</t>
+          <t>2026-10-30T20:14:30Z</t>
         </is>
       </c>
       <c r="AZ7" s="2" t="n"/>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.02643972809826245</v>
+        <v>0.0267149558397286</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.0009561209725368336</v>
+        <v>-0.0006882391058053994</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>-0.0229805063373002</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.01433087307953185</v>
+        <v>-0.01406657749528184</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.001858506457046549</v>
+        <v>-0.00159086655437024</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.02254242162784004</v>
+        <v>0.02281660435241095</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.002080045095828709</v>
+        <v>0.002348741074784</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2055,17 +2055,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-30T17:39:52Z</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X8" t="b">
@@ -2087,14 +2087,14 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="AN8" s="4" t="n">
-        <v>-0.02969137366034236</v>
+        <v>-0.0229805063373002</v>
       </c>
       <c r="AO8" t="n">
         <v>7</v>
@@ -2140,14 +2140,14 @@
         <v>0</v>
       </c>
       <c r="AR8" s="4" t="n">
-        <v>-0.01805023679467355</v>
+        <v>0.006710936192320327</v>
       </c>
       <c r="AS8" s="4" t="n">
-        <v>0.09777622901307459</v>
+        <v>0.05458120009895451</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +2.3%, 3m -0.4%, 6m -1.3%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +2.3%, 3m -0.2%, 6m -1.4%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -2156,17 +2156,17 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>106.6614</v>
+        <v>106.69</v>
       </c>
       <c r="AW8" t="n">
         <v>106.44</v>
       </c>
       <c r="AX8" s="4" t="n">
-        <v>0.002080045095828709</v>
+        <v>0.002348741074784</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2026-10-30T17:39:52Z</t>
+          <t>2026-10-30T20:10:00Z</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.09508486131956229</v>
+        <v>0.09414163577148349</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.0712446991009148</v>
+        <v>0.07032200771495378</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.06884570149741576</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05892010215249899</v>
+        <v>0.05800802626778556</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.03035143769968029</v>
+        <v>0.02946396876109336</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.002244475138121427</v>
+        <v>0.001381215469613339</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.0005165289256198191</v>
+        <v>-0.001377410468319518</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -2252,17 +2252,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-30T17:39:35Z</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X9" t="b">
@@ -2284,14 +2284,14 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="AN9" s="4" t="n">
-        <v>0.06343494064375976</v>
+        <v>0.06884570149741576</v>
       </c>
       <c r="AO9" t="n">
         <v>4</v>
@@ -2337,14 +2337,14 @@
         <v>0</v>
       </c>
       <c r="AR9" s="4" t="n">
-        <v>0.008844657495538755</v>
+        <v>0.005410760853655994</v>
       </c>
       <c r="AS9" s="4" t="n">
-        <v>0.09777622901307459</v>
+        <v>0.05458120009895451</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +0.9%, 3m +3.1%, 6m +6.1%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +0.1%, 3m +2.9%, 6m +5.8%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2353,17 +2353,17 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>29.025</v>
+        <v>29</v>
       </c>
       <c r="AW9" t="n">
         <v>29.04</v>
       </c>
       <c r="AX9" s="4" t="n">
-        <v>-0.0005165289256198191</v>
+        <v>-0.001377410468319518</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2026-10-30T17:39:35Z</t>
+          <t>2026-10-30T20:10:00Z</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05960640875185041</v>
+        <v>0.05955355990259403</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03771214033825476</v>
+        <v>0.03766055175454563</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03436418336590208</v>
+        <v>0.03436410207161633</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01841906598617715</v>
+        <v>0.01836843802199595</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.00922194543339061</v>
+        <v>0.009171852519039403</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.003236729409421324</v>
+        <v>0.003186933572353334</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0002482375136532156</v>
+        <v>0.0001985900109224836</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-30T17:40:07Z</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>LIVE_PRICE_OVERLAY</t>
+          <t>COMPLETED_SESSION</t>
         </is>
       </c>
       <c r="X10" s="5" t="b">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="AC10" s="5" t="inlineStr">
         <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AD10" s="5" t="inlineStr">
+        <is>
           <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="AD10" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AE10" s="5" t="b">
@@ -2520,11 +2520,11 @@
       <c r="AQ10" s="5" t="n"/>
       <c r="AR10" s="6" t="n"/>
       <c r="AS10" s="6" t="n">
-        <v>0.09777622901307459</v>
+        <v>0.05458120009895451</v>
       </c>
       <c r="AT10" s="5" t="inlineStr">
         <is>
-          <t>CONTEXT ONLY; 1m +0.3%, 3m +0.9%, 6m +1.9%. No mechanical gate.</t>
+          <t>CONTEXT ONLY; 1m +0.3%, 3m +0.9%, 6m +1.8%. No mechanical gate.</t>
         </is>
       </c>
       <c r="AU10" s="5" t="inlineStr">
@@ -2533,17 +2533,17 @@
         </is>
       </c>
       <c r="AV10" s="5" t="n">
-        <v>100.735</v>
+        <v>100.7315</v>
       </c>
       <c r="AW10" s="5" t="n">
         <v>100.71</v>
       </c>
       <c r="AX10" s="6" t="n">
-        <v>0.0002482375136532156</v>
+        <v>0.0002134842617416144</v>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-30T17:40:07Z</t>
+          <t>2026-10-30T20:14:56Z</t>
         </is>
       </c>
       <c r="AZ10" s="5" t="n"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23: QQQ 36.4%, SPY 34.3%, XLE 29.2%</t>
+          <t>2026-10-30: QQQ 35.7%, SPY 34.1%, XLE 30.1%</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-16: QQQ 35.5%, SPY 34.4%, XLE 30.0%</t>
+          <t>2026-10-23: QQQ 36.4%, SPY 34.3%, XLE 29.2%</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>QQQ 35.9%, SPY 34.1%, XLE 30.0%</t>
+          <t>QQQ 35.7%, SPY 34.1%, XLE 30.1%</t>
         </is>
       </c>
     </row>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>-0.01151847537271422</v>
+        <v>-0.01082474901503949</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>-0.0007981414945803511</v>
+        <v>-9.689149788039142e-05</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.05323763329481612</v>
+        <v>0.05397680614621292</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-0.07168173793512389</v>
+        <v>-0.06825869574006438</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>-0.01501598898560297</v>
+        <v>-0.01138399986189276</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.02397922570640532</v>
+        <v>0.0277550041648198</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.04870673015055993</v>
+        <v>0.05314631321580254</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.0006477947287315544</v>
+        <v>0.003582851455925073</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.02934500051481403</v>
+        <v>-0.02523584075259078</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-0.06993938760581042</v>
+        <v>-0.07048803427735395</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-0.04229103333243645</v>
+        <v>-0.0428559898845875</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.1587740441419727</v>
+        <v>-0.1592702868755613</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.006176853055916753</v>
+        <v>0.006892067620286157</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.01468690180098164</v>
+        <v>-0.01398651769240711</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.009587940210993739</v>
+        <v>-0.008884028428457813</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1123604465709729</v>
+        <v>0.1167464114832535</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.1933928774174671</v>
+        <v>0.1980983479356375</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.2007738765914222</v>
+        <v>0.2055084499094038</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.02254242162784004</v>
+        <v>0.02281660435241095</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.001858506457046549</v>
+        <v>-0.00159086655437024</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.01433087307953185</v>
+        <v>-0.01406657749528184</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.002244475138121427</v>
+        <v>0.001381215469613339</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.03035143769968029</v>
+        <v>0.02946396876109336</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.05892010215249899</v>
+        <v>0.05800802626778556</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.003236729409421324</v>
+        <v>0.003186933572353334</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.00922194543339061</v>
+        <v>0.009171852519039403</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01841906598617715</v>
+        <v>0.01836843802199595</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.02933625610116319</v>
+        <v>0.02933614706677878</v>
       </c>
     </row>
     <row r="3">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.02285226703064946</v>
+        <v>0.0228523735523376</v>
       </c>
     </row>
     <row r="4">
@@ -3318,8 +3318,41 @@
         <v>0.09777622901307459</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>XLE, QQQ, SPY</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>QQQ 35.7%, SPY 34.1%, XLE 30.1%</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.05458120009895451</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>